--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,6 +146,11 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -337,7 +342,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -488,10 +493,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -683,7 +691,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -724,7 +732,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip r:embed="rId2"/>
+        <a:blip r:embed="rId4"/>
         <a:srcRect l="4540" t="12476" r="4665" b="12920"/>
         <a:stretch>
           <a:fillRect/>
@@ -745,6 +753,56 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -3218,7 +3276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3450,15 +3508,24 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
+      <c r="B10" s="59" t="n"/>
       <c r="C10" s="59" t="n"/>
       <c r="D10" s="59" t="n"/>
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
@@ -3466,15 +3533,24 @@
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>HD-VENT-001</t>
-        </is>
-      </c>
+      <c r="B11" s="61" t="n"/>
       <c r="C11" s="61" t="n"/>
       <c r="D11" s="61" t="n"/>
       <c r="E11" s="61" t="n"/>
       <c r="F11" s="61" t="n"/>
+      <c r="G11" s="61" t="n"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="I11" s="60" t="inlineStr">
+        <is>
+          <t>HD-VENT-001</t>
+        </is>
+      </c>
+      <c r="J11" s="61" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="61" t="n"/>
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
@@ -3482,15 +3558,24 @@
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="B12" s="61" t="n"/>
       <c r="C12" s="61" t="n"/>
       <c r="D12" s="61" t="n"/>
       <c r="E12" s="61" t="n"/>
       <c r="F12" s="61" t="n"/>
+      <c r="G12" s="61" t="n"/>
+      <c r="H12" s="61" t="n"/>
+      <c r="I12" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="61" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="61" t="n"/>
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
@@ -3498,15 +3583,24 @@
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+      <c r="B13" s="61" t="n"/>
       <c r="C13" s="61" t="n"/>
       <c r="D13" s="61" t="n"/>
       <c r="E13" s="61" t="n"/>
       <c r="F13" s="61" t="n"/>
+      <c r="G13" s="61" t="n"/>
+      <c r="H13" s="61" t="n"/>
+      <c r="I13" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J13" s="61" t="n"/>
+      <c r="K13" s="61" t="n"/>
+      <c r="L13" s="61" t="n"/>
+      <c r="M13" s="61" t="n"/>
+      <c r="N13" s="61" t="n"/>
+      <c r="O13" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="60" t="inlineStr">
@@ -3514,15 +3608,24 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
-        <is>
-          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
-        </is>
-      </c>
+      <c r="B14" s="61" t="n"/>
       <c r="C14" s="61" t="n"/>
       <c r="D14" s="61" t="n"/>
       <c r="E14" s="61" t="n"/>
       <c r="F14" s="61" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
+        </is>
+      </c>
+      <c r="J14" s="61" t="n"/>
+      <c r="K14" s="61" t="n"/>
+      <c r="L14" s="61" t="n"/>
+      <c r="M14" s="61" t="n"/>
+      <c r="N14" s="61" t="n"/>
+      <c r="O14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="60" t="inlineStr">
@@ -3530,15 +3633,24 @@
           <t>Etiqueta de equipo</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
-        <is>
-          <t>VENT-001 (ventilador de impulsión / presurización)</t>
-        </is>
-      </c>
+      <c r="B15" s="61" t="n"/>
       <c r="C15" s="61" t="n"/>
       <c r="D15" s="61" t="n"/>
       <c r="E15" s="61" t="n"/>
       <c r="F15" s="61" t="n"/>
+      <c r="G15" s="61" t="n"/>
+      <c r="H15" s="61" t="n"/>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>VENT-001 (ventilador de impulsión / presurización)</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="n"/>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="61" t="n"/>
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="n"/>
+      <c r="O15" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="62" t="inlineStr">
@@ -3556,899 +3668,1336 @@
     </row>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="63" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="63" t="inlineStr">
         <is>
           <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="23"/>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>2. Condiciones de sitio</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr">
-        <is>
-          <t>2. Condiciones de sitio</t>
-        </is>
-      </c>
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B27" s="59" t="n"/>
+      <c r="C27" s="59" t="n"/>
+      <c r="D27" s="59" t="n"/>
+      <c r="E27" s="59" t="n"/>
+      <c r="F27" s="59" t="n"/>
+      <c r="G27" s="59" t="n"/>
+      <c r="H27" s="59" t="n"/>
+      <c r="I27" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J27" s="59" t="n"/>
+      <c r="K27" s="59" t="n"/>
+      <c r="L27" s="59" t="n"/>
+      <c r="M27" s="59" t="n"/>
+      <c r="N27" s="59" t="n"/>
+      <c r="O27" s="59" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>Altitud</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="n"/>
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="61" t="n"/>
+      <c r="E28" s="61" t="n"/>
+      <c r="F28" s="61" t="n"/>
+      <c r="G28" s="61" t="n"/>
+      <c r="H28" s="61" t="n"/>
+      <c r="I28" s="60" t="inlineStr">
+        <is>
+          <t>2 558 msnm</t>
+        </is>
+      </c>
+      <c r="J28" s="61" t="n"/>
+      <c r="K28" s="61" t="n"/>
+      <c r="L28" s="61" t="n"/>
+      <c r="M28" s="61" t="n"/>
+      <c r="N28" s="61" t="n"/>
+      <c r="O28" s="61" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="60" t="inlineStr">
+        <is>
+          <t>Presión atmosférica</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="n"/>
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="61" t="n"/>
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="61" t="n"/>
+      <c r="G29" s="61" t="n"/>
+      <c r="H29" s="61" t="n"/>
+      <c r="I29" s="60" t="inlineStr">
+        <is>
+          <t>74.1 kPa</t>
+        </is>
+      </c>
+      <c r="J29" s="61" t="n"/>
+      <c r="K29" s="61" t="n"/>
+      <c r="L29" s="61" t="n"/>
+      <c r="M29" s="61" t="n"/>
+      <c r="N29" s="61" t="n"/>
+      <c r="O29" s="61" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="59" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B30" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C30" s="59" t="n"/>
-      <c r="D30" s="59" t="n"/>
-      <c r="E30" s="59" t="n"/>
-      <c r="F30" s="59" t="n"/>
+      <c r="A30" s="60" t="inlineStr">
+        <is>
+          <t>Temperatura de diseño verano / invierno / media</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="n"/>
+      <c r="C30" s="61" t="n"/>
+      <c r="D30" s="61" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="61" t="n"/>
+      <c r="G30" s="61" t="n"/>
+      <c r="H30" s="61" t="n"/>
+      <c r="I30" s="60" t="inlineStr">
+        <is>
+          <t>21 °C / 3 °C / 14 °C</t>
+        </is>
+      </c>
+      <c r="J30" s="61" t="n"/>
+      <c r="K30" s="61" t="n"/>
+      <c r="L30" s="61" t="n"/>
+      <c r="M30" s="61" t="n"/>
+      <c r="N30" s="61" t="n"/>
+      <c r="O30" s="61" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>Altitud</t>
-        </is>
-      </c>
-      <c r="B31" s="60" t="inlineStr">
-        <is>
-          <t>2 558 msnm</t>
-        </is>
-      </c>
+          <t>Humedad relativa media anual</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="n"/>
       <c r="C31" s="61" t="n"/>
       <c r="D31" s="61" t="n"/>
       <c r="E31" s="61" t="n"/>
       <c r="F31" s="61" t="n"/>
+      <c r="G31" s="61" t="n"/>
+      <c r="H31" s="61" t="n"/>
+      <c r="I31" s="60" t="inlineStr">
+        <is>
+          <t>84 %</t>
+        </is>
+      </c>
+      <c r="J31" s="61" t="n"/>
+      <c r="K31" s="61" t="n"/>
+      <c r="L31" s="61" t="n"/>
+      <c r="M31" s="61" t="n"/>
+      <c r="N31" s="61" t="n"/>
+      <c r="O31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="60" t="inlineStr">
         <is>
-          <t>Presión atmosférica</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="inlineStr">
-        <is>
-          <t>74.1 kPa</t>
-        </is>
-      </c>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="n"/>
       <c r="C32" s="61" t="n"/>
       <c r="D32" s="61" t="n"/>
       <c r="E32" s="61" t="n"/>
       <c r="F32" s="61" t="n"/>
+      <c r="G32" s="61" t="n"/>
+      <c r="H32" s="61" t="n"/>
+      <c r="I32" s="60" t="inlineStr">
+        <is>
+          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+        </is>
+      </c>
+      <c r="J32" s="61" t="n"/>
+      <c r="K32" s="61" t="n"/>
+      <c r="L32" s="61" t="n"/>
+      <c r="M32" s="61" t="n"/>
+      <c r="N32" s="61" t="n"/>
+      <c r="O32" s="61" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>Temperatura de diseño verano / invierno / media</t>
-        </is>
-      </c>
-      <c r="B33" s="60" t="inlineStr">
-        <is>
-          <t>21 °C / 3 °C / 14 °C</t>
-        </is>
-      </c>
+          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="n"/>
       <c r="C33" s="61" t="n"/>
       <c r="D33" s="61" t="n"/>
       <c r="E33" s="61" t="n"/>
       <c r="F33" s="61" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>Humedad relativa media anual</t>
-        </is>
-      </c>
-      <c r="B34" s="60" t="inlineStr">
-        <is>
-          <t>84 %</t>
-        </is>
-      </c>
-      <c r="C34" s="61" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="61" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="60" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B35" s="60" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
-        </is>
-      </c>
-      <c r="C35" s="61" t="n"/>
-      <c r="D35" s="61" t="n"/>
-      <c r="E35" s="61" t="n"/>
-      <c r="F35" s="61" t="n"/>
+      <c r="G33" s="61" t="n"/>
+      <c r="H33" s="61" t="n"/>
+      <c r="I33" s="60" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="J33" s="61" t="n"/>
+      <c r="K33" s="61" t="n"/>
+      <c r="L33" s="61" t="n"/>
+      <c r="M33" s="61" t="n"/>
+      <c r="N33" s="61" t="n"/>
+      <c r="O33" s="61" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
-        <is>
-          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B36" s="60" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="C36" s="61" t="n"/>
-      <c r="D36" s="61" t="n"/>
-      <c r="E36" s="61" t="n"/>
-      <c r="F36" s="61" t="n"/>
+      <c r="A36" s="62" t="inlineStr">
+        <is>
+          <t>3. Punto de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B38" s="59" t="n"/>
+      <c r="C38" s="59" t="n"/>
+      <c r="D38" s="59" t="n"/>
+      <c r="E38" s="59" t="n"/>
+      <c r="F38" s="59" t="inlineStr">
+        <is>
+          <t>En el sitio (ρ = 0.88 kg/m³)</t>
+        </is>
+      </c>
+      <c r="G38" s="59" t="n"/>
+      <c r="H38" s="59" t="n"/>
+      <c r="I38" s="59" t="n"/>
+      <c r="J38" s="59" t="n"/>
+      <c r="K38" s="59" t="inlineStr">
+        <is>
+          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="L38" s="59" t="n"/>
+      <c r="M38" s="59" t="n"/>
+      <c r="N38" s="59" t="n"/>
+      <c r="O38" s="59" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="62" t="inlineStr">
-        <is>
-          <t>3. Punto de trabajo</t>
-        </is>
-      </c>
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>Caudal</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="n"/>
+      <c r="C39" s="61" t="n"/>
+      <c r="D39" s="61" t="n"/>
+      <c r="E39" s="61" t="n"/>
+      <c r="F39" s="60" t="inlineStr">
+        <is>
+          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="n"/>
+      <c r="H39" s="61" t="n"/>
+      <c r="I39" s="61" t="n"/>
+      <c r="J39" s="61" t="n"/>
+      <c r="K39" s="60" t="inlineStr">
+        <is>
+          <t>Sin cambio (máquina de volumen constante)</t>
+        </is>
+      </c>
+      <c r="L39" s="61" t="n"/>
+      <c r="M39" s="61" t="n"/>
+      <c r="N39" s="61" t="n"/>
+      <c r="O39" s="61" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario de diseño (filtro cargado)</t>
+        </is>
+      </c>
+      <c r="B40" s="61" t="n"/>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="61" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="60" t="inlineStr">
+        <is>
+          <t>190 Pa</t>
+        </is>
+      </c>
+      <c r="G40" s="61" t="n"/>
+      <c r="H40" s="61" t="n"/>
+      <c r="I40" s="61" t="n"/>
+      <c r="J40" s="61" t="n"/>
+      <c r="K40" s="60" t="inlineStr">
+        <is>
+          <t>260 Pa</t>
+        </is>
+      </c>
+      <c r="L40" s="61" t="n"/>
+      <c r="M40" s="61" t="n"/>
+      <c r="N40" s="61" t="n"/>
+      <c r="O40" s="61" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario filtro limpio</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="n"/>
+      <c r="C41" s="61" t="n"/>
+      <c r="D41" s="61" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="60" t="inlineStr">
+        <is>
+          <t>95 Pa</t>
+        </is>
+      </c>
+      <c r="G41" s="61" t="n"/>
+      <c r="H41" s="61" t="n"/>
+      <c r="I41" s="61" t="n"/>
+      <c r="J41" s="61" t="n"/>
+      <c r="K41" s="60" t="inlineStr">
+        <is>
+          <t>130 Pa</t>
+        </is>
+      </c>
+      <c r="L41" s="61" t="n"/>
+      <c r="M41" s="61" t="n"/>
+      <c r="N41" s="61" t="n"/>
+      <c r="O41" s="61" t="n"/>
+    </row>
     <row r="42">
-      <c r="A42" s="59" t="inlineStr">
-        <is>
-          <t>Magnitud</t>
-        </is>
-      </c>
-      <c r="B42" s="59" t="inlineStr">
-        <is>
-          <t>En el sitio (ρ = 0.88 kg/m³)</t>
-        </is>
-      </c>
-      <c r="C42" s="59" t="inlineStr">
-        <is>
-          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="D42" s="59" t="n"/>
-      <c r="E42" s="59" t="n"/>
-      <c r="F42" s="59" t="n"/>
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Composición ΔP diseño</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="n"/>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="61" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="60" t="inlineStr">
+        <is>
+          <t>Filtro 154 Pa + presurización 25 Pa + rejillas 11 Pa</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="n"/>
+      <c r="H42" s="61" t="n"/>
+      <c r="I42" s="61" t="n"/>
+      <c r="J42" s="61" t="n"/>
+      <c r="K42" s="60" t="inlineStr">
+        <is>
+          <t>Filtro 210 Pa + 34 Pa + 15 Pa</t>
+        </is>
+      </c>
+      <c r="L42" s="61" t="n"/>
+      <c r="M42" s="61" t="n"/>
+      <c r="N42" s="61" t="n"/>
+      <c r="O42" s="61" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="60" t="inlineStr">
         <is>
-          <t>Caudal</t>
-        </is>
-      </c>
-      <c r="B43" s="60" t="inlineStr">
-        <is>
-          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
-        </is>
-      </c>
-      <c r="C43" s="60" t="inlineStr">
-        <is>
-          <t>Sin cambio (máquina de volumen constante)</t>
-        </is>
-      </c>
+          <t>Velocidad de inyección</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
       <c r="D43" s="61" t="n"/>
       <c r="E43" s="61" t="n"/>
-      <c r="F43" s="61" t="n"/>
+      <c r="F43" s="60" t="inlineStr">
+        <is>
+          <t>8 m/s (presión dinámica 28 Pa en el sitio)</t>
+        </is>
+      </c>
+      <c r="G43" s="61" t="n"/>
+      <c r="H43" s="61" t="n"/>
+      <c r="I43" s="61" t="n"/>
+      <c r="J43" s="61" t="n"/>
+      <c r="K43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="61" t="n"/>
+      <c r="M43" s="61" t="n"/>
+      <c r="N43" s="61" t="n"/>
+      <c r="O43" s="61" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="60" t="inlineStr">
         <is>
-          <t>ΔP total, escenario de diseño (filtro cargado)</t>
-        </is>
-      </c>
-      <c r="B44" s="60" t="inlineStr">
-        <is>
-          <t>190 Pa</t>
-        </is>
-      </c>
-      <c r="C44" s="60" t="inlineStr">
-        <is>
-          <t>260 Pa</t>
-        </is>
-      </c>
+          <t>Potencia teórica al freno (η = 0.60)</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="n"/>
+      <c r="C44" s="61" t="n"/>
       <c r="D44" s="61" t="n"/>
       <c r="E44" s="61" t="n"/>
-      <c r="F44" s="61" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="60" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario filtro limpio</t>
-        </is>
-      </c>
-      <c r="B45" s="60" t="inlineStr">
-        <is>
-          <t>95 Pa</t>
-        </is>
-      </c>
-      <c r="C45" s="60" t="inlineStr">
-        <is>
-          <t>130 Pa</t>
-        </is>
-      </c>
-      <c r="D45" s="61" t="n"/>
-      <c r="E45" s="61" t="n"/>
-      <c r="F45" s="61" t="n"/>
+      <c r="F44" s="60" t="inlineStr">
+        <is>
+          <t>0.338 kW = 0.45 HP</t>
+        </is>
+      </c>
+      <c r="G44" s="61" t="n"/>
+      <c r="H44" s="61" t="n"/>
+      <c r="I44" s="61" t="n"/>
+      <c r="J44" s="61" t="n"/>
+      <c r="K44" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="61" t="n"/>
+      <c r="M44" s="61" t="n"/>
+      <c r="N44" s="61" t="n"/>
+      <c r="O44" s="61" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
-        <is>
-          <t>Composición ΔP diseño</t>
-        </is>
-      </c>
-      <c r="B46" s="60" t="inlineStr">
-        <is>
-          <t>Filtro 154 Pa + presurización 25 Pa + rejillas 11 Pa</t>
-        </is>
-      </c>
-      <c r="C46" s="60" t="inlineStr">
-        <is>
-          <t>Filtro 210 Pa + 34 Pa + 15 Pa</t>
-        </is>
-      </c>
-      <c r="D46" s="61" t="n"/>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="61" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="60" t="inlineStr">
-        <is>
-          <t>Velocidad de inyección</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="inlineStr">
-        <is>
-          <t>8 m/s (presión dinámica 28 Pa en el sitio)</t>
-        </is>
-      </c>
-      <c r="C47" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="61" t="n"/>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="61" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="60" t="inlineStr">
-        <is>
-          <t>Potencia teórica al freno (η = 0.60)</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="inlineStr">
-        <is>
-          <t>0.338 kW = 0.45 HP</t>
-        </is>
-      </c>
-      <c r="C48" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="61" t="n"/>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="61" t="n"/>
-    </row>
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 260 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). Tamaño y RPM exactos: por confirmar con proveedor mediante su software de selección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="63" t="inlineStr">
         <is>
-          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 260 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). Tamaño y RPM exactos: por confirmar con proveedor mediante su software de selección.</t>
+          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; el margen sobre la potencia de eje (motor 1.0 HP vs. 0.45 HP teóricos) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio.</t>
         </is>
       </c>
     </row>
     <row r="51"/>
     <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
+    <row r="54">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>4. Tipo y materiales de construcción</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 3. Requisitos de construcción.</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" s="63" t="inlineStr">
-        <is>
-          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; el margen sobre la potencia de eje (motor 1.0 HP vs. 0.45 HP teóricos) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
+      <c r="A56" s="59" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B56" s="59" t="n"/>
+      <c r="C56" s="59" t="n"/>
+      <c r="D56" s="59" t="n"/>
+      <c r="E56" s="59" t="n"/>
+      <c r="F56" s="59" t="n"/>
+      <c r="G56" s="59" t="n"/>
+      <c r="H56" s="59" t="n"/>
+      <c r="I56" s="59" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J56" s="59" t="n"/>
+      <c r="K56" s="59" t="n"/>
+      <c r="L56" s="59" t="n"/>
+      <c r="M56" s="59" t="n"/>
+      <c r="N56" s="59" t="n"/>
+      <c r="O56" s="59" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="60" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="n"/>
+      <c r="C57" s="61" t="n"/>
+      <c r="D57" s="61" t="n"/>
+      <c r="E57" s="61" t="n"/>
+      <c r="F57" s="61" t="n"/>
+      <c r="G57" s="61" t="n"/>
+      <c r="H57" s="61" t="n"/>
+      <c r="I57" s="60" t="inlineStr">
+        <is>
+          <t>Centrífugo, álabes curvados hacia atrás, simple aspiración, transmisión directa o por bandas (dato típico según línea seleccionada)</t>
+        </is>
+      </c>
+      <c r="J57" s="61" t="n"/>
+      <c r="K57" s="61" t="n"/>
+      <c r="L57" s="61" t="n"/>
+      <c r="M57" s="61" t="n"/>
+      <c r="N57" s="61" t="n"/>
+      <c r="O57" s="61" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="60" t="inlineStr">
+        <is>
+          <t>Carcasa y rueda</t>
+        </is>
+      </c>
+      <c r="B58" s="61" t="n"/>
+      <c r="C58" s="61" t="n"/>
+      <c r="D58" s="61" t="n"/>
+      <c r="E58" s="61" t="n"/>
+      <c r="F58" s="61" t="n"/>
+      <c r="G58" s="61" t="n"/>
+      <c r="H58" s="61" t="n"/>
+      <c r="I58" s="60" t="inlineStr">
+        <is>
+          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167 (primera opción) o polipropileno (alternativa); velo superficial para oxidantes fuertes donde el fabricante lo ofrezca</t>
+        </is>
+      </c>
+      <c r="J58" s="61" t="n"/>
+      <c r="K58" s="61" t="n"/>
+      <c r="L58" s="61" t="n"/>
+      <c r="M58" s="61" t="n"/>
+      <c r="N58" s="61" t="n"/>
+      <c r="O58" s="61" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="60" t="inlineStr">
+        <is>
+          <t>Elementos metálicos en la corriente</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="n"/>
+      <c r="C59" s="61" t="n"/>
+      <c r="D59" s="61" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="61" t="n"/>
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="60" t="inlineStr">
+        <is>
+          <t>Ninguno (motor fuera de la corriente de aire)</t>
+        </is>
+      </c>
+      <c r="J59" s="61" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="61" t="n"/>
+      <c r="M59" s="61" t="n"/>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="60" t="inlineStr">
+        <is>
+          <t>Eje y buje</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="n"/>
+      <c r="C60" s="61" t="n"/>
+      <c r="D60" s="61" t="n"/>
+      <c r="E60" s="61" t="n"/>
+      <c r="F60" s="61" t="n"/>
+      <c r="G60" s="61" t="n"/>
+      <c r="H60" s="61" t="n"/>
+      <c r="I60" s="60" t="inlineStr">
+        <is>
+          <t>Encapsulados/protegidos contra la atmósfera clorada</t>
+        </is>
+      </c>
+      <c r="J60" s="61" t="n"/>
+      <c r="K60" s="61" t="n"/>
+      <c r="L60" s="61" t="n"/>
+      <c r="M60" s="61" t="n"/>
+      <c r="N60" s="61" t="n"/>
+      <c r="O60" s="61" t="n"/>
+    </row>
     <row r="61">
-      <c r="A61" s="62" t="inlineStr">
-        <is>
-          <t>4. Tipo y materiales de construcción</t>
-        </is>
-      </c>
+      <c r="A61" s="60" t="inlineStr">
+        <is>
+          <t>Construcción contra chispa</t>
+        </is>
+      </c>
+      <c r="B61" s="61" t="n"/>
+      <c r="C61" s="61" t="n"/>
+      <c r="D61" s="61" t="n"/>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="61" t="n"/>
+      <c r="G61" s="61" t="n"/>
+      <c r="H61" s="61" t="n"/>
+      <c r="I61" s="60" t="inlineStr">
+        <is>
+          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
+        </is>
+      </c>
+      <c r="J61" s="61" t="n"/>
+      <c r="K61" s="61" t="n"/>
+      <c r="L61" s="61" t="n"/>
+      <c r="M61" s="61" t="n"/>
+      <c r="N61" s="61" t="n"/>
+      <c r="O61" s="61" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 3. Requisitos de construcción.</t>
-        </is>
-      </c>
+      <c r="A62" s="60" t="inlineStr">
+        <is>
+          <t>Certificación de desempeño</t>
+        </is>
+      </c>
+      <c r="B62" s="61" t="n"/>
+      <c r="C62" s="61" t="n"/>
+      <c r="D62" s="61" t="n"/>
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="61" t="n"/>
+      <c r="G62" s="61" t="n"/>
+      <c r="H62" s="61" t="n"/>
+      <c r="I62" s="60" t="inlineStr">
+        <is>
+          <t>AMCA 210/211 (sello AMCA exigible)</t>
+        </is>
+      </c>
+      <c r="J62" s="61" t="n"/>
+      <c r="K62" s="61" t="n"/>
+      <c r="L62" s="61" t="n"/>
+      <c r="M62" s="61" t="n"/>
+      <c r="N62" s="61" t="n"/>
+      <c r="O62" s="61" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="59" t="inlineStr">
-        <is>
-          <t>Componente</t>
-        </is>
-      </c>
-      <c r="B63" s="59" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="C63" s="59" t="n"/>
-      <c r="D63" s="59" t="n"/>
-      <c r="E63" s="59" t="n"/>
-      <c r="F63" s="59" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="60" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>Centrífugo, álabes curvados hacia atrás, simple aspiración, transmisión directa o por bandas (dato típico según línea seleccionada)</t>
-        </is>
-      </c>
-      <c r="C64" s="61" t="n"/>
-      <c r="D64" s="61" t="n"/>
-      <c r="E64" s="61" t="n"/>
-      <c r="F64" s="61" t="n"/>
+      <c r="A63" s="60" t="inlineStr">
+        <is>
+          <t>Descartado</t>
+        </is>
+      </c>
+      <c r="B63" s="61" t="n"/>
+      <c r="C63" s="61" t="n"/>
+      <c r="D63" s="61" t="n"/>
+      <c r="E63" s="61" t="n"/>
+      <c r="F63" s="61" t="n"/>
+      <c r="G63" s="61" t="n"/>
+      <c r="H63" s="61" t="n"/>
+      <c r="I63" s="60" t="inlineStr">
+        <is>
+          <t>Axial PRFV (presión insuficiente con MERV 13-14); acero inoxidable en la corriente (picadura por cloruros); acero galvanizado</t>
+        </is>
+      </c>
+      <c r="J63" s="61" t="n"/>
+      <c r="K63" s="61" t="n"/>
+      <c r="L63" s="61" t="n"/>
+      <c r="M63" s="61" t="n"/>
+      <c r="N63" s="61" t="n"/>
+      <c r="O63" s="61" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="60" t="inlineStr">
-        <is>
-          <t>Carcasa y rueda</t>
-        </is>
-      </c>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167 (primera opción) o polipropileno (alternativa); velo superficial para oxidantes fuertes donde el fabricante lo ofrezca</t>
-        </is>
-      </c>
-      <c r="C65" s="61" t="n"/>
-      <c r="D65" s="61" t="n"/>
-      <c r="E65" s="61" t="n"/>
-      <c r="F65" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="60" t="inlineStr">
-        <is>
-          <t>Elementos metálicos en la corriente</t>
-        </is>
-      </c>
-      <c r="B66" s="60" t="inlineStr">
-        <is>
-          <t>Ninguno (motor fuera de la corriente de aire)</t>
-        </is>
-      </c>
-      <c r="C66" s="61" t="n"/>
-      <c r="D66" s="61" t="n"/>
-      <c r="E66" s="61" t="n"/>
-      <c r="F66" s="61" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="60" t="inlineStr">
-        <is>
-          <t>Eje y buje</t>
-        </is>
-      </c>
-      <c r="B67" s="60" t="inlineStr">
-        <is>
-          <t>Encapsulados/protegidos contra la atmósfera clorada</t>
-        </is>
-      </c>
-      <c r="C67" s="61" t="n"/>
-      <c r="D67" s="61" t="n"/>
-      <c r="E67" s="61" t="n"/>
-      <c r="F67" s="61" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="60" t="inlineStr">
-        <is>
-          <t>Construcción contra chispa</t>
-        </is>
-      </c>
-      <c r="B68" s="60" t="inlineStr">
-        <is>
-          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
-        </is>
-      </c>
-      <c r="C68" s="61" t="n"/>
-      <c r="D68" s="61" t="n"/>
-      <c r="E68" s="61" t="n"/>
-      <c r="F68" s="61" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="60" t="inlineStr">
-        <is>
-          <t>Certificación de desempeño</t>
-        </is>
-      </c>
-      <c r="B69" s="60" t="inlineStr">
-        <is>
-          <t>AMCA 210/211 (sello AMCA exigible)</t>
-        </is>
-      </c>
-      <c r="C69" s="61" t="n"/>
-      <c r="D69" s="61" t="n"/>
-      <c r="E69" s="61" t="n"/>
-      <c r="F69" s="61" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="60" t="inlineStr">
-        <is>
-          <t>Descartado</t>
-        </is>
-      </c>
-      <c r="B70" s="60" t="inlineStr">
-        <is>
-          <t>Axial PRFV (presión insuficiente con MERV 13-14); acero inoxidable en la corriente (picadura por cloruros); acero galvanizado</t>
-        </is>
-      </c>
-      <c r="C70" s="61" t="n"/>
-      <c r="D70" s="61" t="n"/>
-      <c r="E70" s="61" t="n"/>
-      <c r="F70" s="61" t="n"/>
+      <c r="A65" s="65" t="inlineStr">
+        <is>
+          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="71">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>5. Motor</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="63" t="inlineStr">
-        <is>
-          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
+      <c r="A72" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 4. Especificación del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="59" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B73" s="59" t="n"/>
+      <c r="C73" s="59" t="n"/>
+      <c r="D73" s="59" t="n"/>
+      <c r="E73" s="59" t="n"/>
+      <c r="F73" s="59" t="n"/>
+      <c r="G73" s="59" t="n"/>
+      <c r="H73" s="59" t="n"/>
+      <c r="I73" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J73" s="59" t="n"/>
+      <c r="K73" s="59" t="n"/>
+      <c r="L73" s="59" t="n"/>
+      <c r="M73" s="59" t="n"/>
+      <c r="N73" s="59" t="n"/>
+      <c r="O73" s="59" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="60" t="inlineStr">
+        <is>
+          <t>Potencia instalada</t>
+        </is>
+      </c>
+      <c r="B74" s="61" t="n"/>
+      <c r="C74" s="61" t="n"/>
+      <c r="D74" s="61" t="n"/>
+      <c r="E74" s="61" t="n"/>
+      <c r="F74" s="61" t="n"/>
+      <c r="G74" s="61" t="n"/>
+      <c r="H74" s="61" t="n"/>
+      <c r="I74" s="60" t="inlineStr">
+        <is>
+          <t>1.0 HP</t>
+        </is>
+      </c>
+      <c r="J74" s="61" t="n"/>
+      <c r="K74" s="61" t="n"/>
+      <c r="L74" s="61" t="n"/>
+      <c r="M74" s="61" t="n"/>
+      <c r="N74" s="61" t="n"/>
+      <c r="O74" s="61" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="60" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="B75" s="61" t="n"/>
+      <c r="C75" s="61" t="n"/>
+      <c r="D75" s="61" t="n"/>
+      <c r="E75" s="61" t="n"/>
+      <c r="F75" s="61" t="n"/>
+      <c r="G75" s="61" t="n"/>
+      <c r="H75" s="61" t="n"/>
+      <c r="I75" s="60" t="inlineStr">
+        <is>
+          <t>TEFC, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos (referencia IEEE 841 o equivalente)</t>
+        </is>
+      </c>
+      <c r="J75" s="61" t="n"/>
+      <c r="K75" s="61" t="n"/>
+      <c r="L75" s="61" t="n"/>
+      <c r="M75" s="61" t="n"/>
+      <c r="N75" s="61" t="n"/>
+      <c r="O75" s="61" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="60" t="inlineStr">
+        <is>
+          <t>Velocidad</t>
+        </is>
+      </c>
+      <c r="B76" s="61" t="n"/>
+      <c r="C76" s="61" t="n"/>
+      <c r="D76" s="61" t="n"/>
+      <c r="E76" s="61" t="n"/>
+      <c r="F76" s="61" t="n"/>
+      <c r="G76" s="61" t="n"/>
+      <c r="H76" s="61" t="n"/>
+      <c r="I76" s="60" t="inlineStr">
+        <is>
+          <t>1 800 RPM (4 polos, 60 Hz) — dato típico</t>
+        </is>
+      </c>
+      <c r="J76" s="61" t="n"/>
+      <c r="K76" s="61" t="n"/>
+      <c r="L76" s="61" t="n"/>
+      <c r="M76" s="61" t="n"/>
+      <c r="N76" s="61" t="n"/>
+      <c r="O76" s="61" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="60" t="inlineStr">
+        <is>
+          <t>Aislamiento / protección</t>
+        </is>
+      </c>
+      <c r="B77" s="61" t="n"/>
+      <c r="C77" s="61" t="n"/>
+      <c r="D77" s="61" t="n"/>
+      <c r="E77" s="61" t="n"/>
+      <c r="F77" s="61" t="n"/>
+      <c r="G77" s="61" t="n"/>
+      <c r="H77" s="61" t="n"/>
+      <c r="I77" s="60" t="inlineStr">
+        <is>
+          <t>Clase F / IP55 mínimo (IP56 preferible)</t>
+        </is>
+      </c>
+      <c r="J77" s="61" t="n"/>
+      <c r="K77" s="61" t="n"/>
+      <c r="L77" s="61" t="n"/>
+      <c r="M77" s="61" t="n"/>
+      <c r="N77" s="61" t="n"/>
+      <c r="O77" s="61" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="60" t="inlineStr">
+        <is>
+          <t>Tensión / fases / frecuencia</t>
+        </is>
+      </c>
+      <c r="B78" s="61" t="n"/>
+      <c r="C78" s="61" t="n"/>
+      <c r="D78" s="61" t="n"/>
+      <c r="E78" s="61" t="n"/>
+      <c r="F78" s="61" t="n"/>
+      <c r="G78" s="61" t="n"/>
+      <c r="H78" s="61" t="n"/>
+      <c r="I78" s="60" t="inlineStr">
+        <is>
+          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J78" s="61" t="n"/>
+      <c r="K78" s="61" t="n"/>
+      <c r="L78" s="61" t="n"/>
+      <c r="M78" s="61" t="n"/>
+      <c r="N78" s="61" t="n"/>
+      <c r="O78" s="61" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="60" t="inlineStr">
+        <is>
+          <t>Derateo por altitud</t>
+        </is>
+      </c>
+      <c r="B79" s="61" t="n"/>
+      <c r="C79" s="61" t="n"/>
+      <c r="D79" s="61" t="n"/>
+      <c r="E79" s="61" t="n"/>
+      <c r="F79" s="61" t="n"/>
+      <c r="G79" s="61" t="n"/>
+      <c r="H79" s="61" t="n"/>
+      <c r="I79" s="60" t="inlineStr">
+        <is>
+          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+        </is>
+      </c>
+      <c r="J79" s="61" t="n"/>
+      <c r="K79" s="61" t="n"/>
+      <c r="L79" s="61" t="n"/>
+      <c r="M79" s="61" t="n"/>
+      <c r="N79" s="61" t="n"/>
+      <c r="O79" s="61" t="n"/>
+    </row>
     <row r="80">
-      <c r="A80" s="62" t="inlineStr">
-        <is>
-          <t>5. Motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 4. Especificación del motor.</t>
-        </is>
-      </c>
+      <c r="A80" s="60" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B80" s="61" t="n"/>
+      <c r="C80" s="61" t="n"/>
+      <c r="D80" s="61" t="n"/>
+      <c r="E80" s="61" t="n"/>
+      <c r="F80" s="61" t="n"/>
+      <c r="G80" s="61" t="n"/>
+      <c r="H80" s="61" t="n"/>
+      <c r="I80" s="60" t="inlineStr">
+        <is>
+          <t>Calentador anticondensación si hay paradas largas (dato típico de buena práctica); caja de conexiones sellada, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="J80" s="61" t="n"/>
+      <c r="K80" s="61" t="n"/>
+      <c r="L80" s="61" t="n"/>
+      <c r="M80" s="61" t="n"/>
+      <c r="N80" s="61" t="n"/>
+      <c r="O80" s="61" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="59" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B82" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C82" s="59" t="n"/>
-      <c r="D82" s="59" t="n"/>
-      <c r="E82" s="59" t="n"/>
-      <c r="F82" s="59" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="60" t="inlineStr">
-        <is>
-          <t>Potencia instalada</t>
-        </is>
-      </c>
-      <c r="B83" s="60" t="inlineStr">
-        <is>
-          <t>1.0 HP</t>
-        </is>
-      </c>
-      <c r="C83" s="61" t="n"/>
-      <c r="D83" s="61" t="n"/>
-      <c r="E83" s="61" t="n"/>
-      <c r="F83" s="61" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="60" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="B84" s="60" t="inlineStr">
-        <is>
-          <t>TEFC, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos (referencia IEEE 841 o equivalente)</t>
-        </is>
-      </c>
-      <c r="C84" s="61" t="n"/>
-      <c r="D84" s="61" t="n"/>
-      <c r="E84" s="61" t="n"/>
-      <c r="F84" s="61" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="60" t="inlineStr">
-        <is>
-          <t>Velocidad</t>
-        </is>
-      </c>
-      <c r="B85" s="60" t="inlineStr">
-        <is>
-          <t>1 800 RPM (4 polos, 60 Hz) — dato típico</t>
-        </is>
-      </c>
-      <c r="C85" s="61" t="n"/>
-      <c r="D85" s="61" t="n"/>
-      <c r="E85" s="61" t="n"/>
-      <c r="F85" s="61" t="n"/>
-    </row>
+      <c r="A82" s="65" t="inlineStr">
+        <is>
+          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="86">
-      <c r="A86" s="60" t="inlineStr">
-        <is>
-          <t>Aislamiento / protección</t>
-        </is>
-      </c>
-      <c r="B86" s="60" t="inlineStr">
-        <is>
-          <t>Clase F / IP55 mínimo (IP56 preferible)</t>
-        </is>
-      </c>
-      <c r="C86" s="61" t="n"/>
-      <c r="D86" s="61" t="n"/>
-      <c r="E86" s="61" t="n"/>
-      <c r="F86" s="61" t="n"/>
+      <c r="A86" s="62" t="inlineStr">
+        <is>
+          <t>6. Accesorios</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="60" t="inlineStr">
-        <is>
-          <t>Tensión / fases / frecuencia</t>
-        </is>
-      </c>
-      <c r="B87" s="60" t="inlineStr">
-        <is>
-          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="C87" s="61" t="n"/>
-      <c r="D87" s="61" t="n"/>
-      <c r="E87" s="61" t="n"/>
-      <c r="F87" s="61" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="60" t="inlineStr">
-        <is>
-          <t>Derateo por altitud</t>
-        </is>
-      </c>
-      <c r="B88" s="60" t="inlineStr">
-        <is>
-          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
-        </is>
-      </c>
-      <c r="C88" s="61" t="n"/>
-      <c r="D88" s="61" t="n"/>
-      <c r="E88" s="61" t="n"/>
-      <c r="F88" s="61" t="n"/>
-    </row>
+      <c r="A87" s="63" t="inlineStr">
+        <is>
+          <t>6.1. Conexión flexible de descarga en hipalón (CSM) con bandas inox 316 (Hardcast Hypalon (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
     <row r="89">
-      <c r="A89" s="60" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B89" s="60" t="inlineStr">
-        <is>
-          <t>Calentador anticondensación si hay paradas largas (dato típico de buena práctica); caja de conexiones sellada, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="C89" s="61" t="n"/>
-      <c r="D89" s="61" t="n"/>
-      <c r="E89" s="61" t="n"/>
-      <c r="F89" s="61" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="63" t="inlineStr">
-        <is>
-          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
+      <c r="A89" s="63" t="inlineStr">
+        <is>
+          <t>6.2. Bancada y soportes con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructura galvanizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="63" t="inlineStr">
+        <is>
+          <t>6.3. Toma de aire ubicada a sotavento y alejada de las fuentes de cloro de la planta (recomendación de la investigación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="63" t="inlineStr">
+        <is>
+          <t>6.4. Guardamotor y tablero conforme a RETIE (ver listado_equipos.md, ítems 16-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="62" t="inlineStr">
+        <is>
+          <t>7. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 5. Candidatos (consulta 2026-07-23); tamaño/RPM final por confirmar con proveedor.</t>
+        </is>
+      </c>
+    </row>
     <row r="96">
-      <c r="A96" s="62" t="inlineStr">
-        <is>
-          <t>6. Accesorios</t>
-        </is>
-      </c>
+      <c r="A96" s="59" t="inlineStr">
+        <is>
+          <t>Fabricante / línea</t>
+        </is>
+      </c>
+      <c r="B96" s="59" t="n"/>
+      <c r="C96" s="59" t="n"/>
+      <c r="D96" s="59" t="n"/>
+      <c r="E96" s="59" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F96" s="59" t="n"/>
+      <c r="G96" s="59" t="n"/>
+      <c r="H96" s="59" t="n"/>
+      <c r="I96" s="59" t="inlineStr">
+        <is>
+          <t>Canal en Colombia</t>
+        </is>
+      </c>
+      <c r="J96" s="59" t="n"/>
+      <c r="K96" s="59" t="n"/>
+      <c r="L96" s="59" t="n"/>
+      <c r="M96" s="59" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N96" s="59" t="n"/>
+      <c r="O96" s="59" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="63" t="inlineStr">
-        <is>
-          <t>6.1. Conexión flexible de descarga en hipalón (CSM) con bandas inox 316 (Hardcast Hypalon (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf), consulta 2026-07-23). 6.2. Bancada y soportes con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructura galvanizada. 6.3. Toma de aire ubicada a sotavento y alejada de las fuentes de cloro de la planta (recomendación de la investigación). 6.4. Guardamotor y tablero conforme a RETIE (ver listado_equipos.md, ítems 16-17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
+      <c r="A97" s="60" t="inlineStr">
+        <is>
+          <t>Greenheck BCSW-FRP (primera opción)</t>
+        </is>
+      </c>
+      <c r="B97" s="61" t="n"/>
+      <c r="C97" s="61" t="n"/>
+      <c r="D97" s="61" t="n"/>
+      <c r="E97" s="60" t="inlineStr">
+        <is>
+          <t>PRFV poliéster ignífugo, opción velo Nexus</t>
+        </is>
+      </c>
+      <c r="F97" s="61" t="n"/>
+      <c r="G97" s="61" t="n"/>
+      <c r="H97" s="61" t="n"/>
+      <c r="I97" s="60" t="inlineStr">
+        <is>
+          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
+        </is>
+      </c>
+      <c r="J97" s="61" t="n"/>
+      <c r="K97" s="61" t="n"/>
+      <c r="L97" s="61" t="n"/>
+      <c r="M97" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
+        </is>
+      </c>
+      <c r="N97" s="61" t="n"/>
+      <c r="O97" s="61" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="60" t="inlineStr">
+        <is>
+          <t>New York Blower FRP Fume Exhauster</t>
+        </is>
+      </c>
+      <c r="B98" s="61" t="n"/>
+      <c r="C98" s="61" t="n"/>
+      <c r="D98" s="61" t="n"/>
+      <c r="E98" s="60" t="inlineStr">
+        <is>
+          <t>Rueda viniléster PRFV</t>
+        </is>
+      </c>
+      <c r="F98" s="61" t="n"/>
+      <c r="G98" s="61" t="n"/>
+      <c r="H98" s="61" t="n"/>
+      <c r="I98" s="60" t="inlineStr">
+        <is>
+          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J98" s="61" t="n"/>
+      <c r="K98" s="61" t="n"/>
+      <c r="L98" s="61" t="n"/>
+      <c r="M98" s="60" t="inlineStr">
+        <is>
+          <t>NYB (https://www.nyb.com/frp-fume-exhauster/)</t>
+        </is>
+      </c>
+      <c r="N98" s="61" t="n"/>
+      <c r="O98" s="61" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="60" t="inlineStr">
+        <is>
+          <t>Sodeca CPV</t>
+        </is>
+      </c>
+      <c r="B99" s="61" t="n"/>
+      <c r="C99" s="61" t="n"/>
+      <c r="D99" s="61" t="n"/>
+      <c r="E99" s="60" t="inlineStr">
+        <is>
+          <t>Polipropileno</t>
+        </is>
+      </c>
+      <c r="F99" s="61" t="n"/>
+      <c r="G99" s="61" t="n"/>
+      <c r="H99" s="61" t="n"/>
+      <c r="I99" s="60" t="inlineStr">
+        <is>
+          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
+        </is>
+      </c>
+      <c r="J99" s="61" t="n"/>
+      <c r="K99" s="61" t="n"/>
+      <c r="L99" s="61" t="n"/>
+      <c r="M99" s="60" t="inlineStr">
+        <is>
+          <t>CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
+        </is>
+      </c>
+      <c r="N99" s="61" t="n"/>
+      <c r="O99" s="61" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="60" t="inlineStr">
+        <is>
+          <t>Plastec 25/30</t>
+        </is>
+      </c>
+      <c r="B100" s="61" t="n"/>
+      <c r="C100" s="61" t="n"/>
+      <c r="D100" s="61" t="n"/>
+      <c r="E100" s="60" t="inlineStr">
+        <is>
+          <t>Polipropileno, sin metal en corriente</t>
+        </is>
+      </c>
+      <c r="F100" s="61" t="n"/>
+      <c r="G100" s="61" t="n"/>
+      <c r="H100" s="61" t="n"/>
+      <c r="I100" s="60" t="inlineStr">
+        <is>
+          <t>Importación directa (despacho 48 h declarado)</t>
+        </is>
+      </c>
+      <c r="J100" s="61" t="n"/>
+      <c r="K100" s="61" t="n"/>
+      <c r="L100" s="61" t="n"/>
+      <c r="M100" s="60" t="inlineStr">
+        <is>
+          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
+        </is>
+      </c>
+      <c r="N100" s="61" t="n"/>
+      <c r="O100" s="61" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="60" t="inlineStr">
+        <is>
+          <t>Soler &amp; Palau línea PP</t>
+        </is>
+      </c>
+      <c r="B101" s="61" t="n"/>
+      <c r="C101" s="61" t="n"/>
+      <c r="D101" s="61" t="n"/>
+      <c r="E101" s="60" t="inlineStr">
+        <is>
+          <t>Polipropileno</t>
+        </is>
+      </c>
+      <c r="F101" s="61" t="n"/>
+      <c r="G101" s="61" t="n"/>
+      <c r="H101" s="61" t="n"/>
+      <c r="I101" s="60" t="inlineStr">
+        <is>
+          <t>S&amp;P Colombia (filial); modelo por confirmar</t>
+        </is>
+      </c>
+      <c r="J101" s="61" t="n"/>
+      <c r="K101" s="61" t="n"/>
+      <c r="L101" s="61" t="n"/>
+      <c r="M101" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo Industrial (PDF) (https://www.solerpalau.mx/ASW/recursos/cata/Industrial.pdf)</t>
+        </is>
+      </c>
+      <c r="N101" s="61" t="n"/>
+      <c r="O101" s="61" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="62" t="inlineStr">
+        <is>
+          <t>8. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
     <row r="105">
-      <c r="A105" s="62" t="inlineStr">
-        <is>
-          <t>7. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 5. Candidatos (consulta 2026-07-23); tamaño/RPM final por confirmar con proveedor.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A105" s="63" t="inlineStr">
+        <is>
+          <t>8.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106"/>
     <row r="107"/>
     <row r="108">
-      <c r="A108" s="59" t="inlineStr">
-        <is>
-          <t>Fabricante / línea</t>
-        </is>
-      </c>
-      <c r="B108" s="59" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="C108" s="59" t="inlineStr">
-        <is>
-          <t>Canal en Colombia</t>
-        </is>
-      </c>
-      <c r="D108" s="59" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="E108" s="59" t="n"/>
-      <c r="F108" s="59" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="60" t="inlineStr">
-        <is>
-          <t>Greenheck BCSW-FRP (primera opción)</t>
-        </is>
-      </c>
-      <c r="B109" s="60" t="inlineStr">
-        <is>
-          <t>PRFV poliéster ignífugo, opción velo Nexus</t>
-        </is>
-      </c>
-      <c r="C109" s="60" t="inlineStr">
-        <is>
-          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
-        </is>
-      </c>
-      <c r="D109" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
-        </is>
-      </c>
-      <c r="E109" s="61" t="n"/>
-      <c r="F109" s="61" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="60" t="inlineStr">
-        <is>
-          <t>New York Blower FRP Fume Exhauster</t>
-        </is>
-      </c>
-      <c r="B110" s="60" t="inlineStr">
-        <is>
-          <t>Rueda viniléster PRFV</t>
-        </is>
-      </c>
-      <c r="C110" s="60" t="inlineStr">
-        <is>
-          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="D110" s="60" t="inlineStr">
-        <is>
-          <t>NYB (https://www.nyb.com/frp-fume-exhauster/)</t>
-        </is>
-      </c>
-      <c r="E110" s="61" t="n"/>
-      <c r="F110" s="61" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="60" t="inlineStr">
-        <is>
-          <t>Sodeca CPV</t>
-        </is>
-      </c>
-      <c r="B111" s="60" t="inlineStr">
-        <is>
-          <t>Polipropileno</t>
-        </is>
-      </c>
-      <c r="C111" s="60" t="inlineStr">
-        <is>
-          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
-        </is>
-      </c>
-      <c r="D111" s="60" t="inlineStr">
-        <is>
-          <t>CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
-        </is>
-      </c>
-      <c r="E111" s="61" t="n"/>
-      <c r="F111" s="61" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="60" t="inlineStr">
-        <is>
-          <t>Plastec 25/30</t>
-        </is>
-      </c>
-      <c r="B112" s="60" t="inlineStr">
-        <is>
-          <t>Polipropileno, sin metal en corriente</t>
-        </is>
-      </c>
-      <c r="C112" s="60" t="inlineStr">
-        <is>
-          <t>Importación directa (despacho 48 h declarado)</t>
-        </is>
-      </c>
-      <c r="D112" s="60" t="inlineStr">
-        <is>
-          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
-        </is>
-      </c>
-      <c r="E112" s="61" t="n"/>
-      <c r="F112" s="61" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="60" t="inlineStr">
-        <is>
-          <t>Soler &amp; Palau línea PP</t>
-        </is>
-      </c>
-      <c r="B113" s="60" t="inlineStr">
-        <is>
-          <t>Polipropileno</t>
-        </is>
-      </c>
-      <c r="C113" s="60" t="inlineStr">
-        <is>
-          <t>S&amp;P Colombia (filial); modelo por confirmar</t>
-        </is>
-      </c>
-      <c r="D113" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo Industrial (PDF) (https://www.solerpalau.mx/ASW/recursos/cata/Industrial.pdf)</t>
-        </is>
-      </c>
-      <c r="E113" s="61" t="n"/>
-      <c r="F113" s="61" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="62" t="inlineStr">
-        <is>
-          <t>8. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="63" t="inlineStr">
-        <is>
-          <t>8.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
+      <c r="A108" s="62" t="inlineStr">
+        <is>
+          <t>Referencia gráfica</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1"/>
+    <row r="111" ht="15" customHeight="1"/>
+    <row r="112" ht="15" customHeight="1"/>
+    <row r="113" ht="15" customHeight="1"/>
+    <row r="114" ht="15" customHeight="1"/>
+    <row r="115" ht="15" customHeight="1"/>
+    <row r="116" ht="15" customHeight="1"/>
+    <row r="117" ht="15" customHeight="1"/>
+    <row r="118" ht="15" customHeight="1"/>
+    <row r="119" ht="15" customHeight="1"/>
+    <row r="120" ht="15" customHeight="1"/>
+    <row r="121" ht="15" customHeight="1"/>
+    <row r="122" ht="15" customHeight="1"/>
+    <row r="123" ht="15" customHeight="1"/>
+    <row r="124" ht="15" customHeight="1"/>
+    <row r="125" ht="15" customHeight="1"/>
+    <row r="126" ht="15" customHeight="1"/>
+    <row r="127" ht="15" customHeight="1"/>
+    <row r="128" ht="15" customHeight="1"/>
+    <row r="129" ht="15" customHeight="1"/>
+    <row r="130" ht="15" customHeight="1"/>
+    <row r="131" ht="15" customHeight="1"/>
+    <row r="132" ht="15" customHeight="1"/>
+    <row r="133" ht="15" customHeight="1"/>
+    <row r="134" ht="15" customHeight="1"/>
+    <row r="135" ht="15" customHeight="1"/>
+    <row r="136" ht="15" customHeight="1"/>
+    <row r="137" ht="15" customHeight="1"/>
+    <row r="138" ht="15" customHeight="1"/>
+    <row r="139" ht="15" customHeight="1"/>
+    <row r="140" ht="15" customHeight="1"/>
+    <row r="141" ht="15" customHeight="1"/>
+    <row r="142" ht="15" customHeight="1"/>
+    <row r="143" ht="15" customHeight="1"/>
+    <row r="144" ht="15" customHeight="1"/>
+    <row r="145" ht="15" customHeight="1"/>
+    <row r="146" ht="15" customHeight="1"/>
+    <row r="147" ht="15" customHeight="1"/>
+    <row r="148" ht="15" customHeight="1"/>
+    <row r="149" ht="15" customHeight="1"/>
+    <row r="150" ht="15" customHeight="1"/>
+    <row r="151" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="A19:F22"/>
-    <mergeCell ref="A106:F107"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A105:F105"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A28:F29"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="D112:F112"/>
+  <mergeCells count="133">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A50:O52"/>
+    <mergeCell ref="E97:H97"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A40:F41"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A104:O104"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="I77:O77"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="I80:O80"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I61:O61"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="A90:O91"/>
+    <mergeCell ref="I57:O57"/>
+    <mergeCell ref="A87:O88"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I56:O56"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A46:O49"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="A82:O84"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A108:O108"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="I59:O59"/>
+    <mergeCell ref="A86:O86"/>
+    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="I74:O74"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="M97:O97"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="I96:L96"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="I62:O62"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="I98:L98"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A54:O54"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="M99:O99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="I79:O79"/>
+    <mergeCell ref="I73:O73"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="I63:O63"/>
+    <mergeCell ref="A65:O69"/>
+    <mergeCell ref="I99:L99"/>
+    <mergeCell ref="A105:O107"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="I76:O76"/>
+    <mergeCell ref="M96:O96"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I97:L97"/>
+    <mergeCell ref="I75:O75"/>
+    <mergeCell ref="A19:O21"/>
+    <mergeCell ref="M98:O98"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A94:O94"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="F44:J44"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="I78:O78"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="A71:O71"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="A23:F25"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A72:F78"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A56:F59"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="A50:F55"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="A97:F103"/>
-    <mergeCell ref="A117:F121"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="M100:O100"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I100:L100"/>
+    <mergeCell ref="F43:J43"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A91:F94"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="A22:O23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -490,6 +490,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -497,9 +500,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -757,7 +757,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -782,7 +782,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -1467,7 +1467,7 @@
       <c r="Y5" s="54" t="n"/>
       <c r="Z5" s="31" t="inlineStr">
         <is>
-          <t>HOJA DE DATOS Y ESPECIFICACIONES TÉCNICAS DEL VENTILADOR CENTRÍFUGO PRFV</t>
+          <t>HOJA DE DATOS Y ESPECIFICACIONES TÉCNICAS DEL VENTILADOR AXIAL TUBEAXIAL PRFV</t>
         </is>
       </c>
       <c r="AA5" s="44" t="n"/>
@@ -3276,7 +3276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3498,7 +3498,7 @@
     <row r="9">
       <c r="A9" s="58" t="inlineStr">
         <is>
-          <t>Hoja de datos: ventilador de impulsión</t>
+          <t>Hoja de datos: ventilador axial de impulsión</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       <c r="H12" s="61" t="n"/>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" s="61" t="n"/>
@@ -3592,7 +3592,7 @@
       <c r="H13" s="61" t="n"/>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="J13" s="61" t="n"/>
@@ -3642,7 +3642,7 @@
       <c r="H15" s="61" t="n"/>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>VENT-001 (ventilador de impulsión / presurización)</t>
+          <t>VENT-001 (ventilador axial de impulsión)</t>
         </is>
       </c>
       <c r="J15" s="61" t="n"/>
@@ -3652,148 +3652,82 @@
       <c r="N15" s="61" t="n"/>
       <c r="O15" s="61" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="62" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial en lugar de centrífugo, sin instrumentación de presión diferencial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="20">
+      <c r="A20" s="63" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="63" t="inlineStr">
-        <is>
-          <t>1.1. Impulsión de aire exterior filtrado (MERV 13-14) al laboratorio de análisis industrial para mantener presurización positiva de +25 Pa (mínimo +12.5 Pa) y excluir insectos, objetos extraños y polvo. Descarga directa al recinto, sin red de ductos de distribución. Operación continua.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="63" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>1.1. Impulsión de aire exterior filtrado (MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="25">
-      <c r="A25" s="62" t="inlineStr">
+    <row r="26"/>
+    <row r="28">
+      <c r="A28" s="63" t="inlineStr">
         <is>
           <t>2. Condiciones de sitio</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="64" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="59" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B27" s="59" t="n"/>
-      <c r="C27" s="59" t="n"/>
-      <c r="D27" s="59" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="59" t="n"/>
-      <c r="G27" s="59" t="n"/>
-      <c r="H27" s="59" t="n"/>
-      <c r="I27" s="59" t="inlineStr">
+      <c r="B30" s="59" t="n"/>
+      <c r="C30" s="59" t="n"/>
+      <c r="D30" s="59" t="n"/>
+      <c r="E30" s="59" t="n"/>
+      <c r="F30" s="59" t="n"/>
+      <c r="G30" s="59" t="n"/>
+      <c r="H30" s="59" t="n"/>
+      <c r="I30" s="59" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J27" s="59" t="n"/>
-      <c r="K27" s="59" t="n"/>
-      <c r="L27" s="59" t="n"/>
-      <c r="M27" s="59" t="n"/>
-      <c r="N27" s="59" t="n"/>
-      <c r="O27" s="59" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="60" t="inlineStr">
-        <is>
-          <t>Altitud</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n"/>
-      <c r="C28" s="61" t="n"/>
-      <c r="D28" s="61" t="n"/>
-      <c r="E28" s="61" t="n"/>
-      <c r="F28" s="61" t="n"/>
-      <c r="G28" s="61" t="n"/>
-      <c r="H28" s="61" t="n"/>
-      <c r="I28" s="60" t="inlineStr">
-        <is>
-          <t>2 558 msnm</t>
-        </is>
-      </c>
-      <c r="J28" s="61" t="n"/>
-      <c r="K28" s="61" t="n"/>
-      <c r="L28" s="61" t="n"/>
-      <c r="M28" s="61" t="n"/>
-      <c r="N28" s="61" t="n"/>
-      <c r="O28" s="61" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="60" t="inlineStr">
-        <is>
-          <t>Presión atmosférica</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="n"/>
-      <c r="C29" s="61" t="n"/>
-      <c r="D29" s="61" t="n"/>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="61" t="n"/>
-      <c r="H29" s="61" t="n"/>
-      <c r="I29" s="60" t="inlineStr">
-        <is>
-          <t>74.1 kPa</t>
-        </is>
-      </c>
-      <c r="J29" s="61" t="n"/>
-      <c r="K29" s="61" t="n"/>
-      <c r="L29" s="61" t="n"/>
-      <c r="M29" s="61" t="n"/>
-      <c r="N29" s="61" t="n"/>
-      <c r="O29" s="61" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="60" t="inlineStr">
-        <is>
-          <t>Temperatura de diseño verano / invierno / media</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="n"/>
-      <c r="C30" s="61" t="n"/>
-      <c r="D30" s="61" t="n"/>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="61" t="n"/>
-      <c r="H30" s="61" t="n"/>
-      <c r="I30" s="60" t="inlineStr">
-        <is>
-          <t>21 °C / 3 °C / 14 °C</t>
-        </is>
-      </c>
-      <c r="J30" s="61" t="n"/>
-      <c r="K30" s="61" t="n"/>
-      <c r="L30" s="61" t="n"/>
-      <c r="M30" s="61" t="n"/>
-      <c r="N30" s="61" t="n"/>
-      <c r="O30" s="61" t="n"/>
+      <c r="J30" s="59" t="n"/>
+      <c r="K30" s="59" t="n"/>
+      <c r="L30" s="59" t="n"/>
+      <c r="M30" s="59" t="n"/>
+      <c r="N30" s="59" t="n"/>
+      <c r="O30" s="59" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>Humedad relativa media anual</t>
+          <t>Altitud</t>
         </is>
       </c>
       <c r="B31" s="61" t="n"/>
@@ -3805,7 +3739,7 @@
       <c r="H31" s="61" t="n"/>
       <c r="I31" s="60" t="inlineStr">
         <is>
-          <t>84 %</t>
+          <t>2 558 msnm</t>
         </is>
       </c>
       <c r="J31" s="61" t="n"/>
@@ -3818,7 +3752,7 @@
     <row r="32">
       <c r="A32" s="60" t="inlineStr">
         <is>
-          <t>Densidad del aire de diseño</t>
+          <t>Presión atmosférica</t>
         </is>
       </c>
       <c r="B32" s="61" t="n"/>
@@ -3830,7 +3764,7 @@
       <c r="H32" s="61" t="n"/>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+          <t>74.1 kPa</t>
         </is>
       </c>
       <c r="J32" s="61" t="n"/>
@@ -3843,7 +3777,7 @@
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+          <t>Temperatura de diseño verano / invierno / media</t>
         </is>
       </c>
       <c r="B33" s="61" t="n"/>
@@ -3855,7 +3789,7 @@
       <c r="H33" s="61" t="n"/>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>21 °C / 3 °C / 14 °C</t>
         </is>
       </c>
       <c r="J33" s="61" t="n"/>
@@ -3865,140 +3799,128 @@
       <c r="N33" s="61" t="n"/>
       <c r="O33" s="61" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>Humedad relativa media anual</t>
+        </is>
+      </c>
+      <c r="B34" s="61" t="n"/>
+      <c r="C34" s="61" t="n"/>
+      <c r="D34" s="61" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="61" t="n"/>
+      <c r="G34" s="61" t="n"/>
+      <c r="H34" s="61" t="n"/>
+      <c r="I34" s="60" t="inlineStr">
+        <is>
+          <t>84 %</t>
+        </is>
+      </c>
+      <c r="J34" s="61" t="n"/>
+      <c r="K34" s="61" t="n"/>
+      <c r="L34" s="61" t="n"/>
+      <c r="M34" s="61" t="n"/>
+      <c r="N34" s="61" t="n"/>
+      <c r="O34" s="61" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B35" s="61" t="n"/>
+      <c r="C35" s="61" t="n"/>
+      <c r="D35" s="61" t="n"/>
+      <c r="E35" s="61" t="n"/>
+      <c r="F35" s="61" t="n"/>
+      <c r="G35" s="61" t="n"/>
+      <c r="H35" s="61" t="n"/>
+      <c r="I35" s="60" t="inlineStr">
+        <is>
+          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+        </is>
+      </c>
+      <c r="J35" s="61" t="n"/>
+      <c r="K35" s="61" t="n"/>
+      <c r="L35" s="61" t="n"/>
+      <c r="M35" s="61" t="n"/>
+      <c r="N35" s="61" t="n"/>
+      <c r="O35" s="61" t="n"/>
+    </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B36" s="61" t="n"/>
+      <c r="C36" s="61" t="n"/>
+      <c r="D36" s="61" t="n"/>
+      <c r="E36" s="61" t="n"/>
+      <c r="F36" s="61" t="n"/>
+      <c r="G36" s="61" t="n"/>
+      <c r="H36" s="61" t="n"/>
+      <c r="I36" s="60" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="J36" s="61" t="n"/>
+      <c r="K36" s="61" t="n"/>
+      <c r="L36" s="61" t="n"/>
+      <c r="M36" s="61" t="n"/>
+      <c r="N36" s="61" t="n"/>
+      <c r="O36" s="61" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="63" t="inlineStr">
         <is>
           <t>3. Punto de trabajo</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="64" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="65" t="inlineStr">
         <is>
           <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="59" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="59" t="inlineStr">
         <is>
           <t>Magnitud</t>
         </is>
       </c>
-      <c r="B38" s="59" t="n"/>
-      <c r="C38" s="59" t="n"/>
-      <c r="D38" s="59" t="n"/>
-      <c r="E38" s="59" t="n"/>
-      <c r="F38" s="59" t="inlineStr">
+      <c r="B41" s="59" t="n"/>
+      <c r="C41" s="59" t="n"/>
+      <c r="D41" s="59" t="n"/>
+      <c r="E41" s="59" t="n"/>
+      <c r="F41" s="59" t="inlineStr">
         <is>
           <t>En el sitio (ρ = 0.88 kg/m³)</t>
         </is>
       </c>
-      <c r="G38" s="59" t="n"/>
-      <c r="H38" s="59" t="n"/>
-      <c r="I38" s="59" t="n"/>
-      <c r="J38" s="59" t="n"/>
-      <c r="K38" s="59" t="inlineStr">
+      <c r="G41" s="59" t="n"/>
+      <c r="H41" s="59" t="n"/>
+      <c r="I41" s="59" t="n"/>
+      <c r="J41" s="59" t="n"/>
+      <c r="K41" s="59" t="inlineStr">
         <is>
           <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
         </is>
       </c>
-      <c r="L38" s="59" t="n"/>
-      <c r="M38" s="59" t="n"/>
-      <c r="N38" s="59" t="n"/>
-      <c r="O38" s="59" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="60" t="inlineStr">
-        <is>
-          <t>Caudal</t>
-        </is>
-      </c>
-      <c r="B39" s="61" t="n"/>
-      <c r="C39" s="61" t="n"/>
-      <c r="D39" s="61" t="n"/>
-      <c r="E39" s="61" t="n"/>
-      <c r="F39" s="60" t="inlineStr">
-        <is>
-          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
-        </is>
-      </c>
-      <c r="G39" s="61" t="n"/>
-      <c r="H39" s="61" t="n"/>
-      <c r="I39" s="61" t="n"/>
-      <c r="J39" s="61" t="n"/>
-      <c r="K39" s="60" t="inlineStr">
-        <is>
-          <t>Sin cambio (máquina de volumen constante)</t>
-        </is>
-      </c>
-      <c r="L39" s="61" t="n"/>
-      <c r="M39" s="61" t="n"/>
-      <c r="N39" s="61" t="n"/>
-      <c r="O39" s="61" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario de diseño (filtro cargado)</t>
-        </is>
-      </c>
-      <c r="B40" s="61" t="n"/>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="61" t="n"/>
-      <c r="E40" s="61" t="n"/>
-      <c r="F40" s="60" t="inlineStr">
-        <is>
-          <t>190 Pa</t>
-        </is>
-      </c>
-      <c r="G40" s="61" t="n"/>
-      <c r="H40" s="61" t="n"/>
-      <c r="I40" s="61" t="n"/>
-      <c r="J40" s="61" t="n"/>
-      <c r="K40" s="60" t="inlineStr">
-        <is>
-          <t>260 Pa</t>
-        </is>
-      </c>
-      <c r="L40" s="61" t="n"/>
-      <c r="M40" s="61" t="n"/>
-      <c r="N40" s="61" t="n"/>
-      <c r="O40" s="61" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="60" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario filtro limpio</t>
-        </is>
-      </c>
-      <c r="B41" s="61" t="n"/>
-      <c r="C41" s="61" t="n"/>
-      <c r="D41" s="61" t="n"/>
-      <c r="E41" s="61" t="n"/>
-      <c r="F41" s="60" t="inlineStr">
-        <is>
-          <t>95 Pa</t>
-        </is>
-      </c>
-      <c r="G41" s="61" t="n"/>
-      <c r="H41" s="61" t="n"/>
-      <c r="I41" s="61" t="n"/>
-      <c r="J41" s="61" t="n"/>
-      <c r="K41" s="60" t="inlineStr">
-        <is>
-          <t>130 Pa</t>
-        </is>
-      </c>
-      <c r="L41" s="61" t="n"/>
-      <c r="M41" s="61" t="n"/>
-      <c r="N41" s="61" t="n"/>
-      <c r="O41" s="61" t="n"/>
+      <c r="L41" s="59" t="n"/>
+      <c r="M41" s="59" t="n"/>
+      <c r="N41" s="59" t="n"/>
+      <c r="O41" s="59" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="60" t="inlineStr">
         <is>
-          <t>Composición ΔP diseño</t>
+          <t>Caudal</t>
         </is>
       </c>
       <c r="B42" s="61" t="n"/>
@@ -4007,7 +3929,7 @@
       <c r="E42" s="61" t="n"/>
       <c r="F42" s="60" t="inlineStr">
         <is>
-          <t>Filtro 154 Pa + presurización 25 Pa + rejillas 11 Pa</t>
+          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
         </is>
       </c>
       <c r="G42" s="61" t="n"/>
@@ -4016,7 +3938,7 @@
       <c r="J42" s="61" t="n"/>
       <c r="K42" s="60" t="inlineStr">
         <is>
-          <t>Filtro 210 Pa + 34 Pa + 15 Pa</t>
+          <t>Sin cambio (máquina de volumen constante)</t>
         </is>
       </c>
       <c r="L42" s="61" t="n"/>
@@ -4027,7 +3949,7 @@
     <row r="43">
       <c r="A43" s="60" t="inlineStr">
         <is>
-          <t>Velocidad de inyección</t>
+          <t>ΔP total, escenario de diseño (filtro cargado)</t>
         </is>
       </c>
       <c r="B43" s="61" t="n"/>
@@ -4036,7 +3958,7 @@
       <c r="E43" s="61" t="n"/>
       <c r="F43" s="60" t="inlineStr">
         <is>
-          <t>8 m/s (presión dinámica 28 Pa en el sitio)</t>
+          <t>165 Pa</t>
         </is>
       </c>
       <c r="G43" s="61" t="n"/>
@@ -4045,7 +3967,7 @@
       <c r="J43" s="61" t="n"/>
       <c r="K43" s="60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225 Pa</t>
         </is>
       </c>
       <c r="L43" s="61" t="n"/>
@@ -4056,7 +3978,7 @@
     <row r="44">
       <c r="A44" s="60" t="inlineStr">
         <is>
-          <t>Potencia teórica al freno (η = 0.60)</t>
+          <t>ΔP total, escenario filtro limpio</t>
         </is>
       </c>
       <c r="B44" s="61" t="n"/>
@@ -4065,7 +3987,7 @@
       <c r="E44" s="61" t="n"/>
       <c r="F44" s="60" t="inlineStr">
         <is>
-          <t>0.338 kW = 0.45 HP</t>
+          <t>70 Pa</t>
         </is>
       </c>
       <c r="G44" s="61" t="n"/>
@@ -4074,7 +3996,7 @@
       <c r="J44" s="61" t="n"/>
       <c r="K44" s="60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95 Pa</t>
         </is>
       </c>
       <c r="L44" s="61" t="n"/>
@@ -4082,168 +4004,128 @@
       <c r="N44" s="61" t="n"/>
       <c r="O44" s="61" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>Composición ΔP diseño</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="n"/>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="60" t="inlineStr">
+        <is>
+          <t>Filtro 154 Pa + rejillas 11 Pa</t>
+        </is>
+      </c>
+      <c r="G45" s="61" t="n"/>
+      <c r="H45" s="61" t="n"/>
+      <c r="I45" s="61" t="n"/>
+      <c r="J45" s="61" t="n"/>
+      <c r="K45" s="60" t="inlineStr">
+        <is>
+          <t>Filtro 210 Pa + 15 Pa</t>
+        </is>
+      </c>
+      <c r="L45" s="61" t="n"/>
+      <c r="M45" s="61" t="n"/>
+      <c r="N45" s="61" t="n"/>
+      <c r="O45" s="61" t="n"/>
+    </row>
     <row r="46">
-      <c r="A46" s="63" t="inlineStr">
-        <is>
-          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 260 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). Tamaño y RPM exactos: por confirmar con proveedor mediante su software de selección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" s="60" t="inlineStr">
+        <is>
+          <t>Potencia teórica de aire (η = 0.55)</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="n"/>
+      <c r="C46" s="61" t="n"/>
+      <c r="D46" s="61" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="60" t="inlineStr">
+        <is>
+          <t>0.320 kW = 0.43 HP</t>
+        </is>
+      </c>
+      <c r="G46" s="61" t="n"/>
+      <c r="H46" s="61" t="n"/>
+      <c r="I46" s="61" t="n"/>
+      <c r="J46" s="61" t="n"/>
+      <c r="K46" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="61" t="n"/>
+      <c r="M46" s="61" t="n"/>
+      <c r="N46" s="61" t="n"/>
+      <c r="O46" s="61" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr">
+        <is>
+          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). Tamaño y RPM exactos: por confirmar con proveedor mediante su software de selección.</t>
+        </is>
+      </c>
+    </row>
     <row r="49"/>
-    <row r="50">
-      <c r="A50" s="63" t="inlineStr">
-        <is>
-          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; el margen sobre la potencia de eje (motor 1.0 HP vs. 0.45 HP teóricos) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio.</t>
-        </is>
-      </c>
-    </row>
+    <row r="50"/>
     <row r="51"/>
-    <row r="52"/>
-    <row r="54">
-      <c r="A54" s="62" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="64" t="inlineStr">
+        <is>
+          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; la eficiencia mínima exigible es 0.55 (dato provisional, a verificar contra la curva de la selección final). El margen sobre la potencia de eje (motor provisional 0.75 HP vs. 0.43 HP teóricos, con margen de servicio 1.5) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio; la potencia final del motor se confirma con la curva de catálogo de la selección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
         <is>
           <t>4. Tipo y materiales de construcción</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="64" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="65" t="inlineStr">
         <is>
           <t>Tabla 3. Requisitos de construcción.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="59" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="59" t="inlineStr">
         <is>
           <t>Componente</t>
         </is>
       </c>
-      <c r="B56" s="59" t="n"/>
-      <c r="C56" s="59" t="n"/>
-      <c r="D56" s="59" t="n"/>
-      <c r="E56" s="59" t="n"/>
-      <c r="F56" s="59" t="n"/>
-      <c r="G56" s="59" t="n"/>
-      <c r="H56" s="59" t="n"/>
-      <c r="I56" s="59" t="inlineStr">
+      <c r="B60" s="59" t="n"/>
+      <c r="C60" s="59" t="n"/>
+      <c r="D60" s="59" t="n"/>
+      <c r="E60" s="59" t="n"/>
+      <c r="F60" s="59" t="n"/>
+      <c r="G60" s="59" t="n"/>
+      <c r="H60" s="59" t="n"/>
+      <c r="I60" s="59" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J56" s="59" t="n"/>
-      <c r="K56" s="59" t="n"/>
-      <c r="L56" s="59" t="n"/>
-      <c r="M56" s="59" t="n"/>
-      <c r="N56" s="59" t="n"/>
-      <c r="O56" s="59" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="60" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B57" s="61" t="n"/>
-      <c r="C57" s="61" t="n"/>
-      <c r="D57" s="61" t="n"/>
-      <c r="E57" s="61" t="n"/>
-      <c r="F57" s="61" t="n"/>
-      <c r="G57" s="61" t="n"/>
-      <c r="H57" s="61" t="n"/>
-      <c r="I57" s="60" t="inlineStr">
-        <is>
-          <t>Centrífugo, álabes curvados hacia atrás, simple aspiración, transmisión directa o por bandas (dato típico según línea seleccionada)</t>
-        </is>
-      </c>
-      <c r="J57" s="61" t="n"/>
-      <c r="K57" s="61" t="n"/>
-      <c r="L57" s="61" t="n"/>
-      <c r="M57" s="61" t="n"/>
-      <c r="N57" s="61" t="n"/>
-      <c r="O57" s="61" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="60" t="inlineStr">
-        <is>
-          <t>Carcasa y rueda</t>
-        </is>
-      </c>
-      <c r="B58" s="61" t="n"/>
-      <c r="C58" s="61" t="n"/>
-      <c r="D58" s="61" t="n"/>
-      <c r="E58" s="61" t="n"/>
-      <c r="F58" s="61" t="n"/>
-      <c r="G58" s="61" t="n"/>
-      <c r="H58" s="61" t="n"/>
-      <c r="I58" s="60" t="inlineStr">
-        <is>
-          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167 (primera opción) o polipropileno (alternativa); velo superficial para oxidantes fuertes donde el fabricante lo ofrezca</t>
-        </is>
-      </c>
-      <c r="J58" s="61" t="n"/>
-      <c r="K58" s="61" t="n"/>
-      <c r="L58" s="61" t="n"/>
-      <c r="M58" s="61" t="n"/>
-      <c r="N58" s="61" t="n"/>
-      <c r="O58" s="61" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="60" t="inlineStr">
-        <is>
-          <t>Elementos metálicos en la corriente</t>
-        </is>
-      </c>
-      <c r="B59" s="61" t="n"/>
-      <c r="C59" s="61" t="n"/>
-      <c r="D59" s="61" t="n"/>
-      <c r="E59" s="61" t="n"/>
-      <c r="F59" s="61" t="n"/>
-      <c r="G59" s="61" t="n"/>
-      <c r="H59" s="61" t="n"/>
-      <c r="I59" s="60" t="inlineStr">
-        <is>
-          <t>Ninguno (motor fuera de la corriente de aire)</t>
-        </is>
-      </c>
-      <c r="J59" s="61" t="n"/>
-      <c r="K59" s="61" t="n"/>
-      <c r="L59" s="61" t="n"/>
-      <c r="M59" s="61" t="n"/>
-      <c r="N59" s="61" t="n"/>
-      <c r="O59" s="61" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="60" t="inlineStr">
-        <is>
-          <t>Eje y buje</t>
-        </is>
-      </c>
-      <c r="B60" s="61" t="n"/>
-      <c r="C60" s="61" t="n"/>
-      <c r="D60" s="61" t="n"/>
-      <c r="E60" s="61" t="n"/>
-      <c r="F60" s="61" t="n"/>
-      <c r="G60" s="61" t="n"/>
-      <c r="H60" s="61" t="n"/>
-      <c r="I60" s="60" t="inlineStr">
-        <is>
-          <t>Encapsulados/protegidos contra la atmósfera clorada</t>
-        </is>
-      </c>
-      <c r="J60" s="61" t="n"/>
-      <c r="K60" s="61" t="n"/>
-      <c r="L60" s="61" t="n"/>
-      <c r="M60" s="61" t="n"/>
-      <c r="N60" s="61" t="n"/>
-      <c r="O60" s="61" t="n"/>
+      <c r="J60" s="59" t="n"/>
+      <c r="K60" s="59" t="n"/>
+      <c r="L60" s="59" t="n"/>
+      <c r="M60" s="59" t="n"/>
+      <c r="N60" s="59" t="n"/>
+      <c r="O60" s="59" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="60" t="inlineStr">
         <is>
-          <t>Construcción contra chispa</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="B61" s="61" t="n"/>
@@ -4255,7 +4137,7 @@
       <c r="H61" s="61" t="n"/>
       <c r="I61" s="60" t="inlineStr">
         <is>
-          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
+          <t>Axial tubeaxial, transmisión por bandas (motor fuera de la corriente de aire, ajuste de RPM por poleas); montaje directo en muro/pasamuros</t>
         </is>
       </c>
       <c r="J61" s="61" t="n"/>
@@ -4268,7 +4150,7 @@
     <row r="62">
       <c r="A62" s="60" t="inlineStr">
         <is>
-          <t>Certificación de desempeño</t>
+          <t>Carcasa y rodete</t>
         </is>
       </c>
       <c r="B62" s="61" t="n"/>
@@ -4280,7 +4162,7 @@
       <c r="H62" s="61" t="n"/>
       <c r="I62" s="60" t="inlineStr">
         <is>
-          <t>AMCA 210/211 (sello AMCA exigible)</t>
+          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167; velo superficial para oxidantes fuertes donde el fabricante lo ofrezca</t>
         </is>
       </c>
       <c r="J62" s="61" t="n"/>
@@ -4293,7 +4175,7 @@
     <row r="63">
       <c r="A63" s="60" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Elementos metálicos en la corriente</t>
         </is>
       </c>
       <c r="B63" s="61" t="n"/>
@@ -4305,7 +4187,7 @@
       <c r="H63" s="61" t="n"/>
       <c r="I63" s="60" t="inlineStr">
         <is>
-          <t>Axial PRFV (presión insuficiente con MERV 13-14); acero inoxidable en la corriente (picadura por cloruros); acero galvanizado</t>
+          <t>Ninguno (transmisión por bandas con motor fuera de la corriente de aire)</t>
         </is>
       </c>
       <c r="J63" s="61" t="n"/>
@@ -4315,160 +4197,160 @@
       <c r="N63" s="61" t="n"/>
       <c r="O63" s="61" t="n"/>
     </row>
+    <row r="64">
+      <c r="A64" s="60" t="inlineStr">
+        <is>
+          <t>Eje, buje y componentes de transmisión</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="n"/>
+      <c r="C64" s="61" t="n"/>
+      <c r="D64" s="61" t="n"/>
+      <c r="E64" s="61" t="n"/>
+      <c r="F64" s="61" t="n"/>
+      <c r="G64" s="61" t="n"/>
+      <c r="H64" s="61" t="n"/>
+      <c r="I64" s="60" t="inlineStr">
+        <is>
+          <t>Encapsulados/protegidos contra la atmósfera clorada; bandas en compartimento ventilado y sellado</t>
+        </is>
+      </c>
+      <c r="J64" s="61" t="n"/>
+      <c r="K64" s="61" t="n"/>
+      <c r="L64" s="61" t="n"/>
+      <c r="M64" s="61" t="n"/>
+      <c r="N64" s="61" t="n"/>
+      <c r="O64" s="61" t="n"/>
+    </row>
     <row r="65">
-      <c r="A65" s="65" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr">
+        <is>
+          <t>Construcción contra chispa</t>
+        </is>
+      </c>
+      <c r="B65" s="61" t="n"/>
+      <c r="C65" s="61" t="n"/>
+      <c r="D65" s="61" t="n"/>
+      <c r="E65" s="61" t="n"/>
+      <c r="F65" s="61" t="n"/>
+      <c r="G65" s="61" t="n"/>
+      <c r="H65" s="61" t="n"/>
+      <c r="I65" s="60" t="inlineStr">
+        <is>
+          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
+        </is>
+      </c>
+      <c r="J65" s="61" t="n"/>
+      <c r="K65" s="61" t="n"/>
+      <c r="L65" s="61" t="n"/>
+      <c r="M65" s="61" t="n"/>
+      <c r="N65" s="61" t="n"/>
+      <c r="O65" s="61" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="60" t="inlineStr">
+        <is>
+          <t>Certificación de desempeño</t>
+        </is>
+      </c>
+      <c r="B66" s="61" t="n"/>
+      <c r="C66" s="61" t="n"/>
+      <c r="D66" s="61" t="n"/>
+      <c r="E66" s="61" t="n"/>
+      <c r="F66" s="61" t="n"/>
+      <c r="G66" s="61" t="n"/>
+      <c r="H66" s="61" t="n"/>
+      <c r="I66" s="60" t="inlineStr">
+        <is>
+          <t>AMCA 210/211 (sello AMCA exigible)</t>
+        </is>
+      </c>
+      <c r="J66" s="61" t="n"/>
+      <c r="K66" s="61" t="n"/>
+      <c r="L66" s="61" t="n"/>
+      <c r="M66" s="61" t="n"/>
+      <c r="N66" s="61" t="n"/>
+      <c r="O66" s="61" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="60" t="inlineStr">
+        <is>
+          <t>Descartado</t>
+        </is>
+      </c>
+      <c r="B67" s="61" t="n"/>
+      <c r="C67" s="61" t="n"/>
+      <c r="D67" s="61" t="n"/>
+      <c r="E67" s="61" t="n"/>
+      <c r="F67" s="61" t="n"/>
+      <c r="G67" s="61" t="n"/>
+      <c r="H67" s="61" t="n"/>
+      <c r="I67" s="60" t="inlineStr">
+        <is>
+          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado; acero con epóxico solo como segunda línea con inspección programada (alternativa Greenheck VAB)</t>
+        </is>
+      </c>
+      <c r="J67" s="61" t="n"/>
+      <c r="K67" s="61" t="n"/>
+      <c r="L67" s="61" t="n"/>
+      <c r="M67" s="61" t="n"/>
+      <c r="N67" s="61" t="n"/>
+      <c r="O67" s="61" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="62" t="inlineStr">
         <is>
           <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="71">
-      <c r="A71" s="62" t="inlineStr">
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
         <is>
           <t>5. Motor</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="64" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="65" t="inlineStr">
         <is>
           <t>Tabla 4. Especificación del motor.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="59" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="59" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B73" s="59" t="n"/>
-      <c r="C73" s="59" t="n"/>
-      <c r="D73" s="59" t="n"/>
-      <c r="E73" s="59" t="n"/>
-      <c r="F73" s="59" t="n"/>
-      <c r="G73" s="59" t="n"/>
-      <c r="H73" s="59" t="n"/>
-      <c r="I73" s="59" t="inlineStr">
+      <c r="B77" s="59" t="n"/>
+      <c r="C77" s="59" t="n"/>
+      <c r="D77" s="59" t="n"/>
+      <c r="E77" s="59" t="n"/>
+      <c r="F77" s="59" t="n"/>
+      <c r="G77" s="59" t="n"/>
+      <c r="H77" s="59" t="n"/>
+      <c r="I77" s="59" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J73" s="59" t="n"/>
-      <c r="K73" s="59" t="n"/>
-      <c r="L73" s="59" t="n"/>
-      <c r="M73" s="59" t="n"/>
-      <c r="N73" s="59" t="n"/>
-      <c r="O73" s="59" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="60" t="inlineStr">
-        <is>
-          <t>Potencia instalada</t>
-        </is>
-      </c>
-      <c r="B74" s="61" t="n"/>
-      <c r="C74" s="61" t="n"/>
-      <c r="D74" s="61" t="n"/>
-      <c r="E74" s="61" t="n"/>
-      <c r="F74" s="61" t="n"/>
-      <c r="G74" s="61" t="n"/>
-      <c r="H74" s="61" t="n"/>
-      <c r="I74" s="60" t="inlineStr">
-        <is>
-          <t>1.0 HP</t>
-        </is>
-      </c>
-      <c r="J74" s="61" t="n"/>
-      <c r="K74" s="61" t="n"/>
-      <c r="L74" s="61" t="n"/>
-      <c r="M74" s="61" t="n"/>
-      <c r="N74" s="61" t="n"/>
-      <c r="O74" s="61" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="60" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="B75" s="61" t="n"/>
-      <c r="C75" s="61" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="61" t="n"/>
-      <c r="F75" s="61" t="n"/>
-      <c r="G75" s="61" t="n"/>
-      <c r="H75" s="61" t="n"/>
-      <c r="I75" s="60" t="inlineStr">
-        <is>
-          <t>TEFC, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos (referencia IEEE 841 o equivalente)</t>
-        </is>
-      </c>
-      <c r="J75" s="61" t="n"/>
-      <c r="K75" s="61" t="n"/>
-      <c r="L75" s="61" t="n"/>
-      <c r="M75" s="61" t="n"/>
-      <c r="N75" s="61" t="n"/>
-      <c r="O75" s="61" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="60" t="inlineStr">
-        <is>
-          <t>Velocidad</t>
-        </is>
-      </c>
-      <c r="B76" s="61" t="n"/>
-      <c r="C76" s="61" t="n"/>
-      <c r="D76" s="61" t="n"/>
-      <c r="E76" s="61" t="n"/>
-      <c r="F76" s="61" t="n"/>
-      <c r="G76" s="61" t="n"/>
-      <c r="H76" s="61" t="n"/>
-      <c r="I76" s="60" t="inlineStr">
-        <is>
-          <t>1 800 RPM (4 polos, 60 Hz) — dato típico</t>
-        </is>
-      </c>
-      <c r="J76" s="61" t="n"/>
-      <c r="K76" s="61" t="n"/>
-      <c r="L76" s="61" t="n"/>
-      <c r="M76" s="61" t="n"/>
-      <c r="N76" s="61" t="n"/>
-      <c r="O76" s="61" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="60" t="inlineStr">
-        <is>
-          <t>Aislamiento / protección</t>
-        </is>
-      </c>
-      <c r="B77" s="61" t="n"/>
-      <c r="C77" s="61" t="n"/>
-      <c r="D77" s="61" t="n"/>
-      <c r="E77" s="61" t="n"/>
-      <c r="F77" s="61" t="n"/>
-      <c r="G77" s="61" t="n"/>
-      <c r="H77" s="61" t="n"/>
-      <c r="I77" s="60" t="inlineStr">
-        <is>
-          <t>Clase F / IP55 mínimo (IP56 preferible)</t>
-        </is>
-      </c>
-      <c r="J77" s="61" t="n"/>
-      <c r="K77" s="61" t="n"/>
-      <c r="L77" s="61" t="n"/>
-      <c r="M77" s="61" t="n"/>
-      <c r="N77" s="61" t="n"/>
-      <c r="O77" s="61" t="n"/>
+      <c r="J77" s="59" t="n"/>
+      <c r="K77" s="59" t="n"/>
+      <c r="L77" s="59" t="n"/>
+      <c r="M77" s="59" t="n"/>
+      <c r="N77" s="59" t="n"/>
+      <c r="O77" s="59" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="60" t="inlineStr">
         <is>
-          <t>Tensión / fases / frecuencia</t>
+          <t>Potencia instalada</t>
         </is>
       </c>
       <c r="B78" s="61" t="n"/>
@@ -4480,7 +4362,7 @@
       <c r="H78" s="61" t="n"/>
       <c r="I78" s="60" t="inlineStr">
         <is>
-          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
         </is>
       </c>
       <c r="J78" s="61" t="n"/>
@@ -4493,7 +4375,7 @@
     <row r="79">
       <c r="A79" s="60" t="inlineStr">
         <is>
-          <t>Derateo por altitud</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="B79" s="61" t="n"/>
@@ -4505,7 +4387,7 @@
       <c r="H79" s="61" t="n"/>
       <c r="I79" s="60" t="inlineStr">
         <is>
-          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+          <t>TEFC, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos (referencia IEEE 841 o equivalente)</t>
         </is>
       </c>
       <c r="J79" s="61" t="n"/>
@@ -4518,7 +4400,7 @@
     <row r="80">
       <c r="A80" s="60" t="inlineStr">
         <is>
-          <t>Accesorios</t>
+          <t>Velocidad</t>
         </is>
       </c>
       <c r="B80" s="61" t="n"/>
@@ -4530,7 +4412,7 @@
       <c r="H80" s="61" t="n"/>
       <c r="I80" s="60" t="inlineStr">
         <is>
-          <t>Calentador anticondensación si hay paradas largas (dato típico de buena práctica); caja de conexiones sellada, prensaestopas niquelados</t>
+          <t>1 800 RPM (4 polos, 60 Hz) — dato típico</t>
         </is>
       </c>
       <c r="J80" s="61" t="n"/>
@@ -4540,295 +4422,403 @@
       <c r="N80" s="61" t="n"/>
       <c r="O80" s="61" t="n"/>
     </row>
+    <row r="81">
+      <c r="A81" s="60" t="inlineStr">
+        <is>
+          <t>Aislamiento / protección</t>
+        </is>
+      </c>
+      <c r="B81" s="61" t="n"/>
+      <c r="C81" s="61" t="n"/>
+      <c r="D81" s="61" t="n"/>
+      <c r="E81" s="61" t="n"/>
+      <c r="F81" s="61" t="n"/>
+      <c r="G81" s="61" t="n"/>
+      <c r="H81" s="61" t="n"/>
+      <c r="I81" s="60" t="inlineStr">
+        <is>
+          <t>Clase F / IP55 mínimo (IP56 preferible)</t>
+        </is>
+      </c>
+      <c r="J81" s="61" t="n"/>
+      <c r="K81" s="61" t="n"/>
+      <c r="L81" s="61" t="n"/>
+      <c r="M81" s="61" t="n"/>
+      <c r="N81" s="61" t="n"/>
+      <c r="O81" s="61" t="n"/>
+    </row>
     <row r="82">
-      <c r="A82" s="65" t="inlineStr">
-        <is>
-          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84"/>
+      <c r="A82" s="60" t="inlineStr">
+        <is>
+          <t>Tensión / fases / frecuencia</t>
+        </is>
+      </c>
+      <c r="B82" s="61" t="n"/>
+      <c r="C82" s="61" t="n"/>
+      <c r="D82" s="61" t="n"/>
+      <c r="E82" s="61" t="n"/>
+      <c r="F82" s="61" t="n"/>
+      <c r="G82" s="61" t="n"/>
+      <c r="H82" s="61" t="n"/>
+      <c r="I82" s="60" t="inlineStr">
+        <is>
+          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J82" s="61" t="n"/>
+      <c r="K82" s="61" t="n"/>
+      <c r="L82" s="61" t="n"/>
+      <c r="M82" s="61" t="n"/>
+      <c r="N82" s="61" t="n"/>
+      <c r="O82" s="61" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="60" t="inlineStr">
+        <is>
+          <t>Derateo por altitud</t>
+        </is>
+      </c>
+      <c r="B83" s="61" t="n"/>
+      <c r="C83" s="61" t="n"/>
+      <c r="D83" s="61" t="n"/>
+      <c r="E83" s="61" t="n"/>
+      <c r="F83" s="61" t="n"/>
+      <c r="G83" s="61" t="n"/>
+      <c r="H83" s="61" t="n"/>
+      <c r="I83" s="60" t="inlineStr">
+        <is>
+          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+        </is>
+      </c>
+      <c r="J83" s="61" t="n"/>
+      <c r="K83" s="61" t="n"/>
+      <c r="L83" s="61" t="n"/>
+      <c r="M83" s="61" t="n"/>
+      <c r="N83" s="61" t="n"/>
+      <c r="O83" s="61" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="60" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B84" s="61" t="n"/>
+      <c r="C84" s="61" t="n"/>
+      <c r="D84" s="61" t="n"/>
+      <c r="E84" s="61" t="n"/>
+      <c r="F84" s="61" t="n"/>
+      <c r="G84" s="61" t="n"/>
+      <c r="H84" s="61" t="n"/>
+      <c r="I84" s="60" t="inlineStr">
+        <is>
+          <t>Calentador anticondensación si hay paradas largas (dato típico de buena práctica); caja de conexiones sellada, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="J84" s="61" t="n"/>
+      <c r="K84" s="61" t="n"/>
+      <c r="L84" s="61" t="n"/>
+      <c r="M84" s="61" t="n"/>
+      <c r="N84" s="61" t="n"/>
+      <c r="O84" s="61" t="n"/>
+    </row>
     <row r="86">
       <c r="A86" s="62" t="inlineStr">
         <is>
-          <t>6. Accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="63" t="inlineStr">
-        <is>
-          <t>6.1. Conexión flexible de descarga en hipalón (CSM) con bandas inox 316 (Hardcast Hypalon (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
     <row r="88"/>
-    <row r="89">
-      <c r="A89" s="63" t="inlineStr">
-        <is>
-          <t>6.2. Bancada y soportes con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructura galvanizada.</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
       <c r="A90" s="63" t="inlineStr">
         <is>
-          <t>6.3. Toma de aire ubicada a sotavento y alejada de las fuentes de cloro de la planta (recomendación de la investigación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="63" t="inlineStr">
-        <is>
-          <t>6.4. Guardamotor y tablero conforme a RETIE (ver listado_equipos.md, ítems 16-17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="62" t="inlineStr">
-        <is>
-          <t>7. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
+          <t>6. Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="64" t="inlineStr">
+        <is>
+          <t>6.1. Conexión flexible de descarga en hipalón (CSM) con bandas inox 316 (Hardcast Hypalon (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="64" t="inlineStr">
+        <is>
+          <t>6.2. Persiana de gravedad de cierre automático en inox o PRFV (opcional), para sellar la abertura cuando el equipo está detenido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" s="64" t="inlineStr">
         <is>
-          <t>Tabla 5. Candidatos (consulta 2026-07-23); tamaño/RPM final por confirmar con proveedor.</t>
+          <t>6.3. Guarda de seguridad en el lado de aspiración/descarga accesible, según configuración final de montaje.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="59" t="inlineStr">
+      <c r="A96" s="64" t="inlineStr">
+        <is>
+          <t>6.4. Bancada y soportes con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructura galvanizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="64" t="inlineStr">
+        <is>
+          <t>6.5. Toma de aire ubicada a sotavento y alejada de las fuentes de cloro de la planta (recomendación de la investigación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="64" t="inlineStr">
+        <is>
+          <t>6.6. Guardamotor y tablero conforme a RETIE (ver listado_equipos.md, ítems 11-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="63" t="inlineStr">
+        <is>
+          <t>7. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65" t="inlineStr">
+        <is>
+          <t>Tabla 5. Candidatos (consulta 2026-07-23, ampliada 2026-07-27); modelo de referencia, tamaño/RPM final por confirmar con proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="59" t="inlineStr">
         <is>
           <t>Fabricante / línea</t>
         </is>
       </c>
-      <c r="B96" s="59" t="n"/>
-      <c r="C96" s="59" t="n"/>
-      <c r="D96" s="59" t="n"/>
-      <c r="E96" s="59" t="inlineStr">
+      <c r="B104" s="59" t="n"/>
+      <c r="C104" s="59" t="n"/>
+      <c r="D104" s="59" t="n"/>
+      <c r="E104" s="59" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="F96" s="59" t="n"/>
-      <c r="G96" s="59" t="n"/>
-      <c r="H96" s="59" t="n"/>
-      <c r="I96" s="59" t="inlineStr">
+      <c r="F104" s="59" t="n"/>
+      <c r="G104" s="59" t="n"/>
+      <c r="H104" s="59" t="n"/>
+      <c r="I104" s="59" t="inlineStr">
         <is>
           <t>Canal en Colombia</t>
         </is>
       </c>
-      <c r="J96" s="59" t="n"/>
-      <c r="K96" s="59" t="n"/>
-      <c r="L96" s="59" t="n"/>
-      <c r="M96" s="59" t="inlineStr">
+      <c r="J104" s="59" t="n"/>
+      <c r="K104" s="59" t="n"/>
+      <c r="L104" s="59" t="n"/>
+      <c r="M104" s="59" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N96" s="59" t="n"/>
-      <c r="O96" s="59" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="60" t="inlineStr">
-        <is>
-          <t>Greenheck BCSW-FRP (primera opción)</t>
-        </is>
-      </c>
-      <c r="B97" s="61" t="n"/>
-      <c r="C97" s="61" t="n"/>
-      <c r="D97" s="61" t="n"/>
-      <c r="E97" s="60" t="inlineStr">
-        <is>
-          <t>PRFV poliéster ignífugo, opción velo Nexus</t>
-        </is>
-      </c>
-      <c r="F97" s="61" t="n"/>
-      <c r="G97" s="61" t="n"/>
-      <c r="H97" s="61" t="n"/>
-      <c r="I97" s="60" t="inlineStr">
+      <c r="N104" s="59" t="n"/>
+      <c r="O104" s="59" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="60" t="inlineStr">
+        <is>
+          <t>Aerovent FBD (Twin City Fan / Aerovent) — primera opción</t>
+        </is>
+      </c>
+      <c r="B105" s="61" t="n"/>
+      <c r="C105" s="61" t="n"/>
+      <c r="D105" s="61" t="n"/>
+      <c r="E105" s="60" t="inlineStr">
+        <is>
+          <t>PRFV, tubeaxial de bandas (Catálogo 185: 355-1 525 mm, hasta 370 Pa estática)</t>
+        </is>
+      </c>
+      <c r="F105" s="61" t="n"/>
+      <c r="G105" s="61" t="n"/>
+      <c r="H105" s="61" t="n"/>
+      <c r="I105" s="60" t="inlineStr">
+        <is>
+          <t>Por confirmar representante/canal local</t>
+        </is>
+      </c>
+      <c r="J105" s="61" t="n"/>
+      <c r="K105" s="61" t="n"/>
+      <c r="L105" s="61" t="n"/>
+      <c r="M105" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf)</t>
+        </is>
+      </c>
+      <c r="N105" s="61" t="n"/>
+      <c r="O105" s="61" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="60" t="inlineStr">
+        <is>
+          <t>Greenheck VAB (vaneaxial de bandas)</t>
+        </is>
+      </c>
+      <c r="B106" s="61" t="n"/>
+      <c r="C106" s="61" t="n"/>
+      <c r="D106" s="61" t="n"/>
+      <c r="E106" s="60" t="inlineStr">
+        <is>
+          <t>Acero con recubrimiento epóxico</t>
+        </is>
+      </c>
+      <c r="F106" s="61" t="n"/>
+      <c r="G106" s="61" t="n"/>
+      <c r="H106" s="61" t="n"/>
+      <c r="I106" s="60" t="inlineStr">
         <is>
           <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
         </is>
       </c>
-      <c r="J97" s="61" t="n"/>
-      <c r="K97" s="61" t="n"/>
-      <c r="L97" s="61" t="n"/>
-      <c r="M97" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
-        </is>
-      </c>
-      <c r="N97" s="61" t="n"/>
-      <c r="O97" s="61" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="60" t="inlineStr">
-        <is>
-          <t>New York Blower FRP Fume Exhauster</t>
-        </is>
-      </c>
-      <c r="B98" s="61" t="n"/>
-      <c r="C98" s="61" t="n"/>
-      <c r="D98" s="61" t="n"/>
-      <c r="E98" s="60" t="inlineStr">
-        <is>
-          <t>Rueda viniléster PRFV</t>
-        </is>
-      </c>
-      <c r="F98" s="61" t="n"/>
-      <c r="G98" s="61" t="n"/>
-      <c r="H98" s="61" t="n"/>
-      <c r="I98" s="60" t="inlineStr">
+      <c r="J106" s="61" t="n"/>
+      <c r="K106" s="61" t="n"/>
+      <c r="L106" s="61" t="n"/>
+      <c r="M106" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
+        </is>
+      </c>
+      <c r="N106" s="61" t="n"/>
+      <c r="O106" s="61" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="60" t="inlineStr">
+        <is>
+          <t>Sodeca HCT/HGT versión anticorrosiva</t>
+        </is>
+      </c>
+      <c r="B107" s="61" t="n"/>
+      <c r="C107" s="61" t="n"/>
+      <c r="D107" s="61" t="n"/>
+      <c r="E107" s="60" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F107" s="61" t="n"/>
+      <c r="G107" s="61" t="n"/>
+      <c r="H107" s="61" t="n"/>
+      <c r="I107" s="60" t="inlineStr">
+        <is>
+          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
+        </is>
+      </c>
+      <c r="J107" s="61" t="n"/>
+      <c r="K107" s="61" t="n"/>
+      <c r="L107" s="61" t="n"/>
+      <c r="M107" s="60" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
+        </is>
+      </c>
+      <c r="N107" s="61" t="n"/>
+      <c r="O107" s="61" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="60" t="inlineStr">
+        <is>
+          <t>New York Blower FRP tubeaxial</t>
+        </is>
+      </c>
+      <c r="B108" s="61" t="n"/>
+      <c r="C108" s="61" t="n"/>
+      <c r="D108" s="61" t="n"/>
+      <c r="E108" s="60" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F108" s="61" t="n"/>
+      <c r="G108" s="61" t="n"/>
+      <c r="H108" s="61" t="n"/>
+      <c r="I108" s="60" t="inlineStr">
         <is>
           <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
         </is>
       </c>
-      <c r="J98" s="61" t="n"/>
-      <c r="K98" s="61" t="n"/>
-      <c r="L98" s="61" t="n"/>
-      <c r="M98" s="60" t="inlineStr">
-        <is>
-          <t>NYB (https://www.nyb.com/frp-fume-exhauster/)</t>
-        </is>
-      </c>
-      <c r="N98" s="61" t="n"/>
-      <c r="O98" s="61" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="60" t="inlineStr">
-        <is>
-          <t>Sodeca CPV</t>
-        </is>
-      </c>
-      <c r="B99" s="61" t="n"/>
-      <c r="C99" s="61" t="n"/>
-      <c r="D99" s="61" t="n"/>
-      <c r="E99" s="60" t="inlineStr">
+      <c r="J108" s="61" t="n"/>
+      <c r="K108" s="61" t="n"/>
+      <c r="L108" s="61" t="n"/>
+      <c r="M108" s="60" t="inlineStr">
+        <is>
+          <t>NYB (https://www.nyb.com/)</t>
+        </is>
+      </c>
+      <c r="N108" s="61" t="n"/>
+      <c r="O108" s="61" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="60" t="inlineStr">
+        <is>
+          <t>Plastec</t>
+        </is>
+      </c>
+      <c r="B109" s="61" t="n"/>
+      <c r="C109" s="61" t="n"/>
+      <c r="D109" s="61" t="n"/>
+      <c r="E109" s="60" t="inlineStr">
         <is>
           <t>Polipropileno</t>
         </is>
       </c>
-      <c r="F99" s="61" t="n"/>
-      <c r="G99" s="61" t="n"/>
-      <c r="H99" s="61" t="n"/>
-      <c r="I99" s="60" t="inlineStr">
-        <is>
-          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
-        </is>
-      </c>
-      <c r="J99" s="61" t="n"/>
-      <c r="K99" s="61" t="n"/>
-      <c r="L99" s="61" t="n"/>
-      <c r="M99" s="60" t="inlineStr">
-        <is>
-          <t>CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
-        </is>
-      </c>
-      <c r="N99" s="61" t="n"/>
-      <c r="O99" s="61" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="60" t="inlineStr">
-        <is>
-          <t>Plastec 25/30</t>
-        </is>
-      </c>
-      <c r="B100" s="61" t="n"/>
-      <c r="C100" s="61" t="n"/>
-      <c r="D100" s="61" t="n"/>
-      <c r="E100" s="60" t="inlineStr">
-        <is>
-          <t>Polipropileno, sin metal en corriente</t>
-        </is>
-      </c>
-      <c r="F100" s="61" t="n"/>
-      <c r="G100" s="61" t="n"/>
-      <c r="H100" s="61" t="n"/>
-      <c r="I100" s="60" t="inlineStr">
+      <c r="F109" s="61" t="n"/>
+      <c r="G109" s="61" t="n"/>
+      <c r="H109" s="61" t="n"/>
+      <c r="I109" s="60" t="inlineStr">
         <is>
           <t>Importación directa (despacho 48 h declarado)</t>
         </is>
       </c>
-      <c r="J100" s="61" t="n"/>
-      <c r="K100" s="61" t="n"/>
-      <c r="L100" s="61" t="n"/>
-      <c r="M100" s="60" t="inlineStr">
+      <c r="J109" s="61" t="n"/>
+      <c r="K109" s="61" t="n"/>
+      <c r="L109" s="61" t="n"/>
+      <c r="M109" s="60" t="inlineStr">
         <is>
           <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
         </is>
       </c>
-      <c r="N100" s="61" t="n"/>
-      <c r="O100" s="61" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="60" t="inlineStr">
-        <is>
-          <t>Soler &amp; Palau línea PP</t>
-        </is>
-      </c>
-      <c r="B101" s="61" t="n"/>
-      <c r="C101" s="61" t="n"/>
-      <c r="D101" s="61" t="n"/>
-      <c r="E101" s="60" t="inlineStr">
-        <is>
-          <t>Polipropileno</t>
-        </is>
-      </c>
-      <c r="F101" s="61" t="n"/>
-      <c r="G101" s="61" t="n"/>
-      <c r="H101" s="61" t="n"/>
-      <c r="I101" s="60" t="inlineStr">
-        <is>
-          <t>S&amp;P Colombia (filial); modelo por confirmar</t>
-        </is>
-      </c>
-      <c r="J101" s="61" t="n"/>
-      <c r="K101" s="61" t="n"/>
-      <c r="L101" s="61" t="n"/>
-      <c r="M101" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo Industrial (PDF) (https://www.solerpalau.mx/ASW/recursos/cata/Industrial.pdf)</t>
-        </is>
-      </c>
-      <c r="N101" s="61" t="n"/>
-      <c r="O101" s="61" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="62" t="inlineStr">
+      <c r="N109" s="61" t="n"/>
+      <c r="O109" s="61" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="63" t="inlineStr">
         <is>
           <t>8. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="63" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="64" t="inlineStr">
         <is>
           <t>8.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
         </is>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" s="62" t="inlineStr">
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="63" t="inlineStr">
         <is>
           <t>Referencia gráfica</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1"/>
-    <row r="111" ht="15" customHeight="1"/>
-    <row r="112" ht="15" customHeight="1"/>
-    <row r="113" ht="15" customHeight="1"/>
-    <row r="114" ht="15" customHeight="1"/>
-    <row r="115" ht="15" customHeight="1"/>
-    <row r="116" ht="15" customHeight="1"/>
-    <row r="117" ht="15" customHeight="1"/>
     <row r="118" ht="15" customHeight="1"/>
     <row r="119" ht="15" customHeight="1"/>
     <row r="120" ht="15" customHeight="1"/>
@@ -4863,141 +4853,149 @@
     <row r="149" ht="15" customHeight="1"/>
     <row r="150" ht="15" customHeight="1"/>
     <row r="151" ht="15" customHeight="1"/>
+    <row r="152" ht="15" customHeight="1"/>
+    <row r="153" ht="15" customHeight="1"/>
+    <row r="154" ht="15" customHeight="1"/>
+    <row r="155" ht="15" customHeight="1"/>
+    <row r="156" ht="15" customHeight="1"/>
+    <row r="157" ht="15" customHeight="1"/>
+    <row r="158" ht="15" customHeight="1"/>
+    <row r="159" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A25:O25"/>
     <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A50:O52"/>
-    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="I83:O83"/>
+    <mergeCell ref="A69:O73"/>
+    <mergeCell ref="A75:O75"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="I109:L109"/>
+    <mergeCell ref="M104:O104"/>
+    <mergeCell ref="A102:O103"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A104:O104"/>
-    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E109:H109"/>
+    <mergeCell ref="I84:O84"/>
     <mergeCell ref="I30:O30"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="K41:O41"/>
+    <mergeCell ref="F45:J45"/>
+    <mergeCell ref="A66:H66"/>
     <mergeCell ref="I77:O77"/>
-    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="I104:L104"/>
+    <mergeCell ref="M106:O106"/>
+    <mergeCell ref="A107:D107"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C2:L3"/>
     <mergeCell ref="I80:O80"/>
-    <mergeCell ref="E98:H98"/>
     <mergeCell ref="I61:O61"/>
     <mergeCell ref="K43:O43"/>
-    <mergeCell ref="A90:O91"/>
-    <mergeCell ref="I57:O57"/>
-    <mergeCell ref="A87:O88"/>
+    <mergeCell ref="I106:L106"/>
+    <mergeCell ref="F46:J46"/>
+    <mergeCell ref="A58:O58"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="I32:O32"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A21:O24"/>
     <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I56:O56"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="E105:H105"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A17:O18"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A46:O49"/>
     <mergeCell ref="I33:O33"/>
-    <mergeCell ref="A82:O84"/>
-    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="M109:O109"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A108:O108"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="I82:O82"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I35:O35"/>
     <mergeCell ref="I10:O10"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="I59:O59"/>
-    <mergeCell ref="A86:O86"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="A101:O101"/>
     <mergeCell ref="I60:O60"/>
-    <mergeCell ref="I74:O74"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="K44:O44"/>
+    <mergeCell ref="I108:L108"/>
     <mergeCell ref="F41:J41"/>
-    <mergeCell ref="M97:O97"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="K46:O46"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A112:O112"/>
     <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="I96:L96"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="M107:O107"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="E104:H104"/>
     <mergeCell ref="I62:O62"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="I98:L98"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="I107:L107"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A54:O54"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="M99:O99"/>
-    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A90:O90"/>
+    <mergeCell ref="A97:O98"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="I64:O64"/>
     <mergeCell ref="I79:O79"/>
-    <mergeCell ref="I73:O73"/>
+    <mergeCell ref="M108:O108"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A93:O94"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="A61:H61"/>
-    <mergeCell ref="F40:J40"/>
     <mergeCell ref="I63:O63"/>
-    <mergeCell ref="A65:O69"/>
-    <mergeCell ref="I99:L99"/>
-    <mergeCell ref="A105:O107"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="A113:O115"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="A116:O116"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="I36:O36"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="E107:H107"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="I76:O76"/>
-    <mergeCell ref="M96:O96"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="I97:L97"/>
-    <mergeCell ref="I75:O75"/>
-    <mergeCell ref="A19:O21"/>
-    <mergeCell ref="M98:O98"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A25:O26"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="A52:O56"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A94:O94"/>
+    <mergeCell ref="A104:D104"/>
     <mergeCell ref="I12:O12"/>
+    <mergeCell ref="E108:H108"/>
     <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="I67:O67"/>
     <mergeCell ref="F44:J44"/>
+    <mergeCell ref="A106:D106"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="I78:O78"/>
+    <mergeCell ref="M105:O105"/>
     <mergeCell ref="I13:O13"/>
     <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A86:O88"/>
     <mergeCell ref="I31:O31"/>
-    <mergeCell ref="A71:O71"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="I105:L105"/>
     <mergeCell ref="F42:J42"/>
     <mergeCell ref="I15:O15"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="I81:O81"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="M100:O100"/>
+    <mergeCell ref="A48:O51"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="K42:O42"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I100:L100"/>
     <mergeCell ref="F43:J43"/>
+    <mergeCell ref="A91:O92"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="I58:O58"/>
-    <mergeCell ref="A22:O23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -865,7 +865,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>148</row>
+      <row>165</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -890,7 +890,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>169</row>
+      <row>186</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -3776,7 +3776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.6" customWidth="1" min="1" max="1"/>
@@ -3910,6 +3910,22 @@
     <col width="13" customWidth="1" min="145" max="145"/>
     <col width="13" customWidth="1" min="146" max="146"/>
     <col width="13" customWidth="1" min="147" max="147"/>
+    <col width="13" customWidth="1" min="148" max="148"/>
+    <col width="13" customWidth="1" min="149" max="149"/>
+    <col width="13" customWidth="1" min="150" max="150"/>
+    <col width="13" customWidth="1" min="151" max="151"/>
+    <col width="13" customWidth="1" min="152" max="152"/>
+    <col width="13" customWidth="1" min="153" max="153"/>
+    <col width="13" customWidth="1" min="154" max="154"/>
+    <col width="13" customWidth="1" min="155" max="155"/>
+    <col width="13" customWidth="1" min="157" max="157"/>
+    <col width="13" customWidth="1" min="158" max="158"/>
+    <col width="13" customWidth="1" min="159" max="159"/>
+    <col width="13" customWidth="1" min="160" max="160"/>
+    <col width="13" customWidth="1" min="161" max="161"/>
+    <col width="13" customWidth="1" min="162" max="162"/>
+    <col width="13" customWidth="1" min="163" max="163"/>
+    <col width="13" customWidth="1" min="164" max="164"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -5462,49 +5478,79 @@
     </row>
     <row r="138" ht="15" customHeight="1"/>
     <row r="139" ht="15" customHeight="1"/>
-    <row r="140" ht="60" customHeight="1">
+    <row r="140" ht="30" customHeight="1">
       <c r="A140" s="86" t="inlineStr">
         <is>
-          <t>8. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="165" customHeight="1">
+          <t>8. Montaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="180" customHeight="1">
       <c r="A141" s="87" t="inlineStr">
         <is>
-          <t>8.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
+          <t>8.1. El ventilador se instalará en muro/pasamuros, con el eje horizontal y a una cota aproximada de 3,0 m sobre el piso terminado del laboratorio. El sentido de flujo es: aspiración de aire exterior filtrado, descarga directa al interior del recinto.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1"/>
     <row r="143" ht="15" customHeight="1"/>
     <row r="144" ht="15" customHeight="1"/>
-    <row r="145" ht="15" customHeight="1"/>
+    <row r="145" ht="165" customHeight="1">
+      <c r="A145" s="87" t="inlineStr">
+        <is>
+          <t>8.2. La transmisión por bandas ubica el motor fuera de la corriente de aire corrosivo. La altura de 3,0 m exige garantizar el acceso para mantenimiento periódico de bandas, lubricación e inspección del motor (plataforma fija o escalera industrial).</t>
+        </is>
+      </c>
+    </row>
     <row r="146" ht="15" customHeight="1"/>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" s="86" t="inlineStr">
-        <is>
-          <t>Referencia gráfica</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="15" customHeight="1"/>
+    <row r="147" ht="15" customHeight="1"/>
+    <row r="148" ht="15" customHeight="1"/>
+    <row r="149" ht="165" customHeight="1">
+      <c r="A149" s="87" t="inlineStr">
+        <is>
+          <t>8.3. La carcasa tubular se apoyará en una bancada/soporte anclado a la estructura del muro con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructuras galvanizadas. El pasamuros se sellará con silicona RTV neutra.</t>
+        </is>
+      </c>
+    </row>
     <row r="150" ht="15" customHeight="1"/>
     <row r="151" ht="15" customHeight="1"/>
     <row r="152" ht="15" customHeight="1"/>
-    <row r="153" ht="15" customHeight="1"/>
+    <row r="153" ht="150" customHeight="1">
+      <c r="A153" s="87" t="inlineStr">
+        <is>
+          <t>8.4. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
+        </is>
+      </c>
+    </row>
     <row r="154" ht="15" customHeight="1"/>
     <row r="155" ht="15" customHeight="1"/>
     <row r="156" ht="15" customHeight="1"/>
-    <row r="157" ht="15" customHeight="1"/>
-    <row r="158" ht="15" customHeight="1"/>
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" s="86" t="inlineStr">
+        <is>
+          <t>9. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="165" customHeight="1">
+      <c r="A158" s="87" t="inlineStr">
+        <is>
+          <t>9.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
+        </is>
+      </c>
+    </row>
     <row r="159" ht="15" customHeight="1"/>
     <row r="160" ht="15" customHeight="1"/>
     <row r="161" ht="15" customHeight="1"/>
     <row r="162" ht="15" customHeight="1"/>
     <row r="163" ht="15" customHeight="1"/>
-    <row r="164" ht="15" customHeight="1"/>
-    <row r="165" ht="15" customHeight="1"/>
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" s="86" t="inlineStr">
+        <is>
+          <t>Referencia gráfica</t>
+        </is>
+      </c>
+    </row>
     <row r="166" ht="15" customHeight="1"/>
     <row r="167" ht="15" customHeight="1"/>
     <row r="168" ht="15" customHeight="1"/>
@@ -5530,8 +5576,25 @@
     <row r="188" ht="15" customHeight="1"/>
     <row r="189" ht="15" customHeight="1"/>
     <row r="190" ht="15" customHeight="1"/>
+    <row r="191" ht="15" customHeight="1"/>
+    <row r="192" ht="15" customHeight="1"/>
+    <row r="193" ht="15" customHeight="1"/>
+    <row r="194" ht="15" customHeight="1"/>
+    <row r="195" ht="15" customHeight="1"/>
+    <row r="196" ht="15" customHeight="1"/>
+    <row r="197" ht="15" customHeight="1"/>
+    <row r="198" ht="15" customHeight="1"/>
+    <row r="199" ht="15" customHeight="1"/>
+    <row r="200" ht="15" customHeight="1"/>
+    <row r="201" ht="15" customHeight="1"/>
+    <row r="202" ht="15" customHeight="1"/>
+    <row r="203" ht="15" customHeight="1"/>
+    <row r="204" ht="15" customHeight="1"/>
+    <row r="205" ht="15" customHeight="1"/>
+    <row r="206" ht="15" customHeight="1"/>
+    <row r="207" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="138">
+  <mergeCells count="143">
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="A83:H83"/>
     <mergeCell ref="I83:O83"/>
@@ -5539,6 +5602,7 @@
     <mergeCell ref="A125:O126"/>
     <mergeCell ref="F54:J54"/>
     <mergeCell ref="I44:O44"/>
+    <mergeCell ref="A141:O144"/>
     <mergeCell ref="A134:D134"/>
     <mergeCell ref="K54:O54"/>
     <mergeCell ref="K55:O55"/>
@@ -5557,6 +5621,7 @@
     <mergeCell ref="A97:H97"/>
     <mergeCell ref="I97:O97"/>
     <mergeCell ref="E137:H137"/>
+    <mergeCell ref="A158:O163"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A81:H81"/>
@@ -5565,10 +5630,12 @@
     <mergeCell ref="I43:O43"/>
     <mergeCell ref="M132:O132"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A145:O148"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="I98:O98"/>
+    <mergeCell ref="A153:O155"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="I132:L132"/>
     <mergeCell ref="A135:D135"/>
@@ -5603,6 +5670,7 @@
     <mergeCell ref="A85:O92"/>
     <mergeCell ref="I79:O79"/>
     <mergeCell ref="A98:H98"/>
+    <mergeCell ref="A164:O164"/>
     <mergeCell ref="A74:O74"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="M133:O133"/>
@@ -5625,6 +5693,7 @@
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A133:D133"/>
     <mergeCell ref="C1:L1"/>
+    <mergeCell ref="A149:O152"/>
     <mergeCell ref="F52:J52"/>
     <mergeCell ref="A100:H100"/>
     <mergeCell ref="A10:H10"/>
@@ -5640,7 +5709,6 @@
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A112:O115"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A141:O146"/>
     <mergeCell ref="I38:O38"/>
     <mergeCell ref="A103:H103"/>
     <mergeCell ref="I78:O78"/>
@@ -5661,10 +5729,10 @@
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A147:O147"/>
     <mergeCell ref="K52:O52"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A157:O157"/>
     <mergeCell ref="K53:O53"/>
     <mergeCell ref="C4:L6"/>
     <mergeCell ref="A43:H43"/>

--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -865,7 +865,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>165</row>
+      <row>201</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -890,7 +890,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>186</row>
+      <row>222</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -3776,7 +3776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O164"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.6" customWidth="1" min="1" max="1"/>
@@ -3797,6 +3797,7 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
@@ -3805,11 +3806,11 @@
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
@@ -3820,8 +3821,9 @@
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
     <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
@@ -3829,10 +3831,9 @@
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
     <col width="13" customWidth="1" min="61" max="61"/>
     <col width="13" customWidth="1" min="62" max="62"/>
     <col width="13" customWidth="1" min="63" max="63"/>
@@ -3844,8 +3845,9 @@
     <col width="13" customWidth="1" min="69" max="69"/>
     <col width="13" customWidth="1" min="70" max="70"/>
     <col width="13" customWidth="1" min="71" max="71"/>
-    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="13" customWidth="1" min="73" max="73"/>
     <col width="13" customWidth="1" min="74" max="74"/>
+    <col width="13" customWidth="1" min="75" max="75"/>
     <col width="13" customWidth="1" min="76" max="76"/>
     <col width="13" customWidth="1" min="77" max="77"/>
     <col width="13" customWidth="1" min="78" max="78"/>
@@ -3854,28 +3856,30 @@
     <col width="13" customWidth="1" min="81" max="81"/>
     <col width="13" customWidth="1" min="82" max="82"/>
     <col width="13" customWidth="1" min="83" max="83"/>
+    <col width="13" customWidth="1" min="84" max="84"/>
     <col width="13" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
     <col width="13" customWidth="1" min="87" max="87"/>
     <col width="13" customWidth="1" min="88" max="88"/>
     <col width="13" customWidth="1" min="89" max="89"/>
     <col width="13" customWidth="1" min="90" max="90"/>
-    <col width="13" customWidth="1" min="91" max="91"/>
     <col width="13" customWidth="1" min="92" max="92"/>
     <col width="13" customWidth="1" min="94" max="94"/>
+    <col width="13" customWidth="1" min="95" max="95"/>
     <col width="13" customWidth="1" min="96" max="96"/>
     <col width="13" customWidth="1" min="97" max="97"/>
     <col width="13" customWidth="1" min="98" max="98"/>
     <col width="13" customWidth="1" min="99" max="99"/>
     <col width="13" customWidth="1" min="100" max="100"/>
     <col width="13" customWidth="1" min="101" max="101"/>
-    <col width="13" customWidth="1" min="102" max="102"/>
     <col width="13" customWidth="1" min="103" max="103"/>
+    <col width="13" customWidth="1" min="104" max="104"/>
     <col width="13" customWidth="1" min="105" max="105"/>
     <col width="13" customWidth="1" min="106" max="106"/>
     <col width="13" customWidth="1" min="107" max="107"/>
     <col width="13" customWidth="1" min="108" max="108"/>
     <col width="13" customWidth="1" min="109" max="109"/>
+    <col width="13" customWidth="1" min="110" max="110"/>
     <col width="13" customWidth="1" min="111" max="111"/>
     <col width="13" customWidth="1" min="112" max="112"/>
     <col width="13" customWidth="1" min="113" max="113"/>
@@ -3888,21 +3892,20 @@
     <col width="13" customWidth="1" min="120" max="120"/>
     <col width="13" customWidth="1" min="121" max="121"/>
     <col width="13" customWidth="1" min="122" max="122"/>
-    <col width="13" customWidth="1" min="123" max="123"/>
     <col width="13" customWidth="1" min="124" max="124"/>
-    <col width="13" customWidth="1" min="125" max="125"/>
     <col width="13" customWidth="1" min="126" max="126"/>
+    <col width="13" customWidth="1" min="127" max="127"/>
     <col width="13" customWidth="1" min="128" max="128"/>
     <col width="13" customWidth="1" min="129" max="129"/>
     <col width="13" customWidth="1" min="130" max="130"/>
     <col width="13" customWidth="1" min="131" max="131"/>
     <col width="13" customWidth="1" min="132" max="132"/>
     <col width="13" customWidth="1" min="133" max="133"/>
-    <col width="13" customWidth="1" min="134" max="134"/>
     <col width="13" customWidth="1" min="135" max="135"/>
     <col width="13" customWidth="1" min="136" max="136"/>
     <col width="13" customWidth="1" min="137" max="137"/>
-    <col width="13" customWidth="1" min="140" max="140"/>
+    <col width="13" customWidth="1" min="138" max="138"/>
+    <col width="13" customWidth="1" min="139" max="139"/>
     <col width="13" customWidth="1" min="141" max="141"/>
     <col width="13" customWidth="1" min="142" max="142"/>
     <col width="13" customWidth="1" min="143" max="143"/>
@@ -3912,12 +3915,11 @@
     <col width="13" customWidth="1" min="147" max="147"/>
     <col width="13" customWidth="1" min="148" max="148"/>
     <col width="13" customWidth="1" min="149" max="149"/>
-    <col width="13" customWidth="1" min="150" max="150"/>
     <col width="13" customWidth="1" min="151" max="151"/>
     <col width="13" customWidth="1" min="152" max="152"/>
     <col width="13" customWidth="1" min="153" max="153"/>
-    <col width="13" customWidth="1" min="154" max="154"/>
     <col width="13" customWidth="1" min="155" max="155"/>
+    <col width="13" customWidth="1" min="156" max="156"/>
     <col width="13" customWidth="1" min="157" max="157"/>
     <col width="13" customWidth="1" min="158" max="158"/>
     <col width="13" customWidth="1" min="159" max="159"/>
@@ -3926,6 +3928,39 @@
     <col width="13" customWidth="1" min="162" max="162"/>
     <col width="13" customWidth="1" min="163" max="163"/>
     <col width="13" customWidth="1" min="164" max="164"/>
+    <col width="13" customWidth="1" min="167" max="167"/>
+    <col width="13" customWidth="1" min="168" max="168"/>
+    <col width="13" customWidth="1" min="169" max="169"/>
+    <col width="13" customWidth="1" min="170" max="170"/>
+    <col width="13" customWidth="1" min="171" max="171"/>
+    <col width="13" customWidth="1" min="172" max="172"/>
+    <col width="13" customWidth="1" min="173" max="173"/>
+    <col width="13" customWidth="1" min="174" max="174"/>
+    <col width="13" customWidth="1" min="175" max="175"/>
+    <col width="13" customWidth="1" min="176" max="176"/>
+    <col width="13" customWidth="1" min="177" max="177"/>
+    <col width="13" customWidth="1" min="178" max="178"/>
+    <col width="13" customWidth="1" min="179" max="179"/>
+    <col width="13" customWidth="1" min="180" max="180"/>
+    <col width="13" customWidth="1" min="181" max="181"/>
+    <col width="13" customWidth="1" min="182" max="182"/>
+    <col width="13" customWidth="1" min="183" max="183"/>
+    <col width="13" customWidth="1" min="184" max="184"/>
+    <col width="13" customWidth="1" min="185" max="185"/>
+    <col width="13" customWidth="1" min="186" max="186"/>
+    <col width="13" customWidth="1" min="187" max="187"/>
+    <col width="13" customWidth="1" min="188" max="188"/>
+    <col width="13" customWidth="1" min="189" max="189"/>
+    <col width="13" customWidth="1" min="191" max="191"/>
+    <col width="13" customWidth="1" min="192" max="192"/>
+    <col width="13" customWidth="1" min="193" max="193"/>
+    <col width="13" customWidth="1" min="194" max="194"/>
+    <col width="13" customWidth="1" min="195" max="195"/>
+    <col width="13" customWidth="1" min="196" max="196"/>
+    <col width="13" customWidth="1" min="197" max="197"/>
+    <col width="13" customWidth="1" min="198" max="198"/>
+    <col width="13" customWidth="1" min="199" max="199"/>
+    <col width="13" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4135,10 +4170,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="255" customHeight="1">
+    <row r="9" ht="300" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
-          <t>Hoja de datos: ventilador axial de impulsión</t>
+          <t>Hoja de datos: ventilador axial mural de inyección</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4242,7 @@
       <c r="H12" s="84" t="n"/>
       <c r="I12" s="83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" s="84" t="n"/>
@@ -4267,7 +4302,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="150" customHeight="1">
+    <row r="15" ht="165" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4282,7 +4317,7 @@
       <c r="H15" s="84" t="n"/>
       <c r="I15" s="83" t="inlineStr">
         <is>
-          <t>VENT-001 (ventilador axial de impulsión)</t>
+          <t>VENT-001 (ventilador axial mural de inyección)</t>
         </is>
       </c>
       <c r="J15" s="84" t="n"/>
@@ -4296,729 +4331,635 @@
     <row r="17" ht="165" customHeight="1">
       <c r="A17" s="85" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial en lugar de centrífugo, sin instrumentación de presión diferencial.</t>
+          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png y Montaje/Descripcion_Tecnica_Sistema_Ventilacion_Inyeccion_2260CFM_v2.md): ventilador axial mural (placa mural) Ø560 mm, transmisión directa, con cubierta intemperie que aloja el banco de filtración, estructura de unión pernada al muro y malla de protección interior. Se conservan caudal, ΔP de diseño, filtración MERV 8 + MERV 13-14, rejillas y ausencia de presurización.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1"/>
     <row r="19" ht="15" customHeight="1"/>
     <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="86" t="inlineStr">
-        <is>
-          <t>1. Servicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="165" customHeight="1">
-      <c r="A22" s="87" t="inlineStr">
-        <is>
-          <t>1.1. Impulsión de aire exterior filtrado (MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
-        </is>
-      </c>
-    </row>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1"/>
-    <row r="26" ht="15" customHeight="1"/>
+    <row r="26" ht="165" customHeight="1">
+      <c r="A26" s="85" t="inlineStr">
+        <is>
+          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial en lugar de centrífugo, sin instrumentación de presión diferencial.</t>
+        </is>
+      </c>
+    </row>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
     <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="87" t="inlineStr">
-        <is>
-          <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1"/>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="86" t="inlineStr">
+        <is>
+          <t>1. Servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="165" customHeight="1">
+      <c r="A31" s="87" t="inlineStr">
+        <is>
+          <t>1.1. Impulsión de aire exterior filtrado (MERV 8 + MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="15" customHeight="1"/>
     <row r="33" ht="15" customHeight="1"/>
     <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="75" customHeight="1">
-      <c r="A35" s="86" t="inlineStr">
-        <is>
-          <t>2. Condiciones de sitio</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
     <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="82" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B38" s="82" t="n"/>
-      <c r="C38" s="82" t="n"/>
-      <c r="D38" s="82" t="n"/>
-      <c r="E38" s="82" t="n"/>
-      <c r="F38" s="82" t="n"/>
-      <c r="G38" s="82" t="n"/>
-      <c r="H38" s="82" t="n"/>
-      <c r="I38" s="82" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="J38" s="82" t="n"/>
-      <c r="K38" s="82" t="n"/>
-      <c r="L38" s="82" t="n"/>
-      <c r="M38" s="82" t="n"/>
-      <c r="N38" s="82" t="n"/>
-      <c r="O38" s="82" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="83" t="inlineStr">
-        <is>
-          <t>Altitud</t>
-        </is>
-      </c>
-      <c r="B39" s="84" t="n"/>
-      <c r="C39" s="84" t="n"/>
-      <c r="D39" s="84" t="n"/>
-      <c r="E39" s="84" t="n"/>
-      <c r="F39" s="84" t="n"/>
-      <c r="G39" s="84" t="n"/>
-      <c r="H39" s="84" t="n"/>
-      <c r="I39" s="83" t="inlineStr">
-        <is>
-          <t>2 558 msnm</t>
-        </is>
-      </c>
-      <c r="J39" s="84" t="n"/>
-      <c r="K39" s="84" t="n"/>
-      <c r="L39" s="84" t="n"/>
-      <c r="M39" s="84" t="n"/>
-      <c r="N39" s="84" t="n"/>
-      <c r="O39" s="84" t="n"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="83" t="inlineStr">
-        <is>
-          <t>Presión atmosférica</t>
-        </is>
-      </c>
-      <c r="B40" s="84" t="n"/>
-      <c r="C40" s="84" t="n"/>
-      <c r="D40" s="84" t="n"/>
-      <c r="E40" s="84" t="n"/>
-      <c r="F40" s="84" t="n"/>
-      <c r="G40" s="84" t="n"/>
-      <c r="H40" s="84" t="n"/>
-      <c r="I40" s="83" t="inlineStr">
-        <is>
-          <t>74.1 kPa</t>
-        </is>
-      </c>
-      <c r="J40" s="84" t="n"/>
-      <c r="K40" s="84" t="n"/>
-      <c r="L40" s="84" t="n"/>
-      <c r="M40" s="84" t="n"/>
-      <c r="N40" s="84" t="n"/>
-      <c r="O40" s="84" t="n"/>
-    </row>
-    <row r="41" ht="135" customHeight="1">
-      <c r="A41" s="83" t="inlineStr">
-        <is>
-          <t>Temperatura de diseño verano / invierno / media</t>
-        </is>
-      </c>
-      <c r="B41" s="84" t="n"/>
-      <c r="C41" s="84" t="n"/>
-      <c r="D41" s="84" t="n"/>
-      <c r="E41" s="84" t="n"/>
-      <c r="F41" s="84" t="n"/>
-      <c r="G41" s="84" t="n"/>
-      <c r="H41" s="84" t="n"/>
-      <c r="I41" s="83" t="inlineStr">
-        <is>
-          <t>21 °C / 3 °C / 14 °C</t>
-        </is>
-      </c>
-      <c r="J41" s="84" t="n"/>
-      <c r="K41" s="84" t="n"/>
-      <c r="L41" s="84" t="n"/>
-      <c r="M41" s="84" t="n"/>
-      <c r="N41" s="84" t="n"/>
-      <c r="O41" s="84" t="n"/>
-    </row>
-    <row r="42" ht="75" customHeight="1">
-      <c r="A42" s="83" t="inlineStr">
-        <is>
-          <t>Humedad relativa media anual</t>
-        </is>
-      </c>
-      <c r="B42" s="84" t="n"/>
-      <c r="C42" s="84" t="n"/>
-      <c r="D42" s="84" t="n"/>
-      <c r="E42" s="84" t="n"/>
-      <c r="F42" s="84" t="n"/>
-      <c r="G42" s="84" t="n"/>
-      <c r="H42" s="84" t="n"/>
-      <c r="I42" s="83" t="inlineStr">
-        <is>
-          <t>84 %</t>
-        </is>
-      </c>
-      <c r="J42" s="84" t="n"/>
-      <c r="K42" s="84" t="n"/>
-      <c r="L42" s="84" t="n"/>
-      <c r="M42" s="84" t="n"/>
-      <c r="N42" s="84" t="n"/>
-      <c r="O42" s="84" t="n"/>
-    </row>
-    <row r="43" ht="135" customHeight="1">
-      <c r="A43" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B43" s="84" t="n"/>
-      <c r="C43" s="84" t="n"/>
-      <c r="D43" s="84" t="n"/>
-      <c r="E43" s="84" t="n"/>
-      <c r="F43" s="84" t="n"/>
-      <c r="G43" s="84" t="n"/>
-      <c r="H43" s="84" t="n"/>
-      <c r="I43" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
-        </is>
-      </c>
-      <c r="J43" s="84" t="n"/>
-      <c r="K43" s="84" t="n"/>
-      <c r="L43" s="84" t="n"/>
-      <c r="M43" s="84" t="n"/>
-      <c r="N43" s="84" t="n"/>
-      <c r="O43" s="84" t="n"/>
-    </row>
-    <row r="44" ht="120" customHeight="1">
-      <c r="A44" s="83" t="inlineStr">
-        <is>
-          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B44" s="84" t="n"/>
-      <c r="C44" s="84" t="n"/>
-      <c r="D44" s="84" t="n"/>
-      <c r="E44" s="84" t="n"/>
-      <c r="F44" s="84" t="n"/>
-      <c r="G44" s="84" t="n"/>
-      <c r="H44" s="84" t="n"/>
-      <c r="I44" s="83" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="J44" s="84" t="n"/>
-      <c r="K44" s="84" t="n"/>
-      <c r="L44" s="84" t="n"/>
-      <c r="M44" s="84" t="n"/>
-      <c r="N44" s="84" t="n"/>
-      <c r="O44" s="84" t="n"/>
-    </row>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="87" t="inlineStr">
+        <is>
+          <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="87" t="inlineStr">
+        <is>
+          <t>1.3. Configuración de montaje uniforme con la planta (secuencia de flujo): exterior → cubierta intemperie (aloja prefiltro MERV 8 y filtro final MERV 13-14) → ventilador axial mural → paso por muro con estructura de unión → malla de protección interior → descarga al recinto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1"/>
     <row r="45" ht="15" customHeight="1"/>
     <row r="46" ht="15" customHeight="1"/>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="86" t="inlineStr">
-        <is>
-          <t>3. Punto de trabajo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="120" customHeight="1">
-      <c r="A48" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="105" customHeight="1">
-      <c r="A50" s="82" t="inlineStr">
-        <is>
-          <t>Magnitud</t>
-        </is>
-      </c>
-      <c r="B50" s="82" t="n"/>
-      <c r="C50" s="82" t="n"/>
-      <c r="D50" s="82" t="n"/>
-      <c r="E50" s="82" t="n"/>
-      <c r="F50" s="82" t="inlineStr">
-        <is>
-          <t>En el sitio (ρ = 0.88 kg/m³)</t>
-        </is>
-      </c>
-      <c r="G50" s="82" t="n"/>
-      <c r="H50" s="82" t="n"/>
-      <c r="I50" s="82" t="n"/>
-      <c r="J50" s="82" t="n"/>
-      <c r="K50" s="82" t="inlineStr">
-        <is>
-          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="L50" s="82" t="n"/>
-      <c r="M50" s="82" t="n"/>
-      <c r="N50" s="82" t="n"/>
-      <c r="O50" s="82" t="n"/>
-    </row>
-    <row r="51" ht="135" customHeight="1">
-      <c r="A51" s="83" t="inlineStr">
-        <is>
-          <t>Caudal</t>
-        </is>
-      </c>
-      <c r="B51" s="84" t="n"/>
-      <c r="C51" s="84" t="n"/>
-      <c r="D51" s="84" t="n"/>
-      <c r="E51" s="84" t="n"/>
-      <c r="F51" s="83" t="inlineStr">
-        <is>
-          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
-        </is>
-      </c>
-      <c r="G51" s="84" t="n"/>
-      <c r="H51" s="84" t="n"/>
-      <c r="I51" s="84" t="n"/>
-      <c r="J51" s="84" t="n"/>
-      <c r="K51" s="83" t="inlineStr">
-        <is>
-          <t>Sin cambio (máquina de volumen constante)</t>
-        </is>
-      </c>
-      <c r="L51" s="84" t="n"/>
-      <c r="M51" s="84" t="n"/>
-      <c r="N51" s="84" t="n"/>
-      <c r="O51" s="84" t="n"/>
-    </row>
-    <row r="52" ht="135" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario de diseño (filtro cargado)</t>
-        </is>
-      </c>
-      <c r="B52" s="84" t="n"/>
-      <c r="C52" s="84" t="n"/>
-      <c r="D52" s="84" t="n"/>
-      <c r="E52" s="84" t="n"/>
-      <c r="F52" s="83" t="inlineStr">
-        <is>
-          <t>165 Pa</t>
-        </is>
-      </c>
-      <c r="G52" s="84" t="n"/>
-      <c r="H52" s="84" t="n"/>
-      <c r="I52" s="84" t="n"/>
-      <c r="J52" s="84" t="n"/>
-      <c r="K52" s="83" t="inlineStr">
-        <is>
-          <t>225 Pa</t>
-        </is>
-      </c>
-      <c r="L52" s="84" t="n"/>
-      <c r="M52" s="84" t="n"/>
-      <c r="N52" s="84" t="n"/>
-      <c r="O52" s="84" t="n"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
+    <row r="47" ht="15" customHeight="1"/>
+    <row r="48" ht="15" customHeight="1"/>
+    <row r="49" ht="75" customHeight="1">
+      <c r="A49" s="86" t="inlineStr">
+        <is>
+          <t>2. Condiciones de sitio</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="150" customHeight="1">
+      <c r="A50" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="n"/>
+      <c r="C52" s="82" t="n"/>
+      <c r="D52" s="82" t="n"/>
+      <c r="E52" s="82" t="n"/>
+      <c r="F52" s="82" t="n"/>
+      <c r="G52" s="82" t="n"/>
+      <c r="H52" s="82" t="n"/>
+      <c r="I52" s="82" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J52" s="82" t="n"/>
+      <c r="K52" s="82" t="n"/>
+      <c r="L52" s="82" t="n"/>
+      <c r="M52" s="82" t="n"/>
+      <c r="N52" s="82" t="n"/>
+      <c r="O52" s="82" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="83" t="inlineStr">
         <is>
-          <t>ΔP total, escenario filtro limpio</t>
+          <t>Altitud</t>
         </is>
       </c>
       <c r="B53" s="84" t="n"/>
       <c r="C53" s="84" t="n"/>
       <c r="D53" s="84" t="n"/>
       <c r="E53" s="84" t="n"/>
-      <c r="F53" s="83" t="inlineStr">
-        <is>
-          <t>70 Pa</t>
-        </is>
-      </c>
+      <c r="F53" s="84" t="n"/>
       <c r="G53" s="84" t="n"/>
       <c r="H53" s="84" t="n"/>
-      <c r="I53" s="84" t="n"/>
+      <c r="I53" s="83" t="inlineStr">
+        <is>
+          <t>2 558 msnm</t>
+        </is>
+      </c>
       <c r="J53" s="84" t="n"/>
-      <c r="K53" s="83" t="inlineStr">
-        <is>
-          <t>95 Pa</t>
-        </is>
-      </c>
+      <c r="K53" s="84" t="n"/>
       <c r="L53" s="84" t="n"/>
       <c r="M53" s="84" t="n"/>
       <c r="N53" s="84" t="n"/>
       <c r="O53" s="84" t="n"/>
     </row>
-    <row r="54" ht="90" customHeight="1">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="83" t="inlineStr">
         <is>
-          <t>Composición ΔP diseño</t>
+          <t>Presión atmosférica</t>
         </is>
       </c>
       <c r="B54" s="84" t="n"/>
       <c r="C54" s="84" t="n"/>
       <c r="D54" s="84" t="n"/>
       <c r="E54" s="84" t="n"/>
-      <c r="F54" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 154 Pa + rejillas 11 Pa</t>
-        </is>
-      </c>
+      <c r="F54" s="84" t="n"/>
       <c r="G54" s="84" t="n"/>
       <c r="H54" s="84" t="n"/>
-      <c r="I54" s="84" t="n"/>
+      <c r="I54" s="83" t="inlineStr">
+        <is>
+          <t>74.1 kPa</t>
+        </is>
+      </c>
       <c r="J54" s="84" t="n"/>
-      <c r="K54" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 210 Pa + 15 Pa</t>
-        </is>
-      </c>
+      <c r="K54" s="84" t="n"/>
       <c r="L54" s="84" t="n"/>
       <c r="M54" s="84" t="n"/>
       <c r="N54" s="84" t="n"/>
       <c r="O54" s="84" t="n"/>
     </row>
-    <row r="55" ht="105" customHeight="1">
+    <row r="55" ht="135" customHeight="1">
       <c r="A55" s="83" t="inlineStr">
         <is>
-          <t>Potencia teórica de aire (η = 0.55)</t>
+          <t>Temperatura de diseño verano / invierno / media</t>
         </is>
       </c>
       <c r="B55" s="84" t="n"/>
       <c r="C55" s="84" t="n"/>
       <c r="D55" s="84" t="n"/>
       <c r="E55" s="84" t="n"/>
-      <c r="F55" s="83" t="inlineStr">
-        <is>
-          <t>0.320 kW = 0.43 HP</t>
-        </is>
-      </c>
+      <c r="F55" s="84" t="n"/>
       <c r="G55" s="84" t="n"/>
       <c r="H55" s="84" t="n"/>
-      <c r="I55" s="84" t="n"/>
+      <c r="I55" s="83" t="inlineStr">
+        <is>
+          <t>21 °C / 3 °C / 14 °C</t>
+        </is>
+      </c>
       <c r="J55" s="84" t="n"/>
-      <c r="K55" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K55" s="84" t="n"/>
       <c r="L55" s="84" t="n"/>
       <c r="M55" s="84" t="n"/>
       <c r="N55" s="84" t="n"/>
       <c r="O55" s="84" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1"/>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="87" t="inlineStr">
-        <is>
-          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). Tamaño y RPM exactos: por confirmar con proveedor mediante su software de selección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1"/>
+    <row r="56" ht="75" customHeight="1">
+      <c r="A56" s="83" t="inlineStr">
+        <is>
+          <t>Humedad relativa media anual</t>
+        </is>
+      </c>
+      <c r="B56" s="84" t="n"/>
+      <c r="C56" s="84" t="n"/>
+      <c r="D56" s="84" t="n"/>
+      <c r="E56" s="84" t="n"/>
+      <c r="F56" s="84" t="n"/>
+      <c r="G56" s="84" t="n"/>
+      <c r="H56" s="84" t="n"/>
+      <c r="I56" s="83" t="inlineStr">
+        <is>
+          <t>84 %</t>
+        </is>
+      </c>
+      <c r="J56" s="84" t="n"/>
+      <c r="K56" s="84" t="n"/>
+      <c r="L56" s="84" t="n"/>
+      <c r="M56" s="84" t="n"/>
+      <c r="N56" s="84" t="n"/>
+      <c r="O56" s="84" t="n"/>
+    </row>
+    <row r="57" ht="135" customHeight="1">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B57" s="84" t="n"/>
+      <c r="C57" s="84" t="n"/>
+      <c r="D57" s="84" t="n"/>
+      <c r="E57" s="84" t="n"/>
+      <c r="F57" s="84" t="n"/>
+      <c r="G57" s="84" t="n"/>
+      <c r="H57" s="84" t="n"/>
+      <c r="I57" s="83" t="inlineStr">
+        <is>
+          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+        </is>
+      </c>
+      <c r="J57" s="84" t="n"/>
+      <c r="K57" s="84" t="n"/>
+      <c r="L57" s="84" t="n"/>
+      <c r="M57" s="84" t="n"/>
+      <c r="N57" s="84" t="n"/>
+      <c r="O57" s="84" t="n"/>
+    </row>
+    <row r="58" ht="120" customHeight="1">
+      <c r="A58" s="83" t="inlineStr">
+        <is>
+          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B58" s="84" t="n"/>
+      <c r="C58" s="84" t="n"/>
+      <c r="D58" s="84" t="n"/>
+      <c r="E58" s="84" t="n"/>
+      <c r="F58" s="84" t="n"/>
+      <c r="G58" s="84" t="n"/>
+      <c r="H58" s="84" t="n"/>
+      <c r="I58" s="83" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="J58" s="84" t="n"/>
+      <c r="K58" s="84" t="n"/>
+      <c r="L58" s="84" t="n"/>
+      <c r="M58" s="84" t="n"/>
+      <c r="N58" s="84" t="n"/>
+      <c r="O58" s="84" t="n"/>
+    </row>
     <row r="59" ht="15" customHeight="1"/>
     <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="15" customHeight="1"/>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="86" t="inlineStr">
+        <is>
+          <t>3. Punto de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="120" customHeight="1">
+      <c r="A62" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
+        </is>
+      </c>
+    </row>
     <row r="63" ht="15" customHeight="1"/>
-    <row r="64" ht="165" customHeight="1">
-      <c r="A64" s="87" t="inlineStr">
+    <row r="64" ht="105" customHeight="1">
+      <c r="A64" s="82" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B64" s="82" t="n"/>
+      <c r="C64" s="82" t="n"/>
+      <c r="D64" s="82" t="n"/>
+      <c r="E64" s="82" t="n"/>
+      <c r="F64" s="82" t="inlineStr">
+        <is>
+          <t>En el sitio (ρ = 0.88 kg/m³)</t>
+        </is>
+      </c>
+      <c r="G64" s="82" t="n"/>
+      <c r="H64" s="82" t="n"/>
+      <c r="I64" s="82" t="n"/>
+      <c r="J64" s="82" t="n"/>
+      <c r="K64" s="82" t="inlineStr">
+        <is>
+          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="L64" s="82" t="n"/>
+      <c r="M64" s="82" t="n"/>
+      <c r="N64" s="82" t="n"/>
+      <c r="O64" s="82" t="n"/>
+    </row>
+    <row r="65" ht="135" customHeight="1">
+      <c r="A65" s="83" t="inlineStr">
+        <is>
+          <t>Caudal</t>
+        </is>
+      </c>
+      <c r="B65" s="84" t="n"/>
+      <c r="C65" s="84" t="n"/>
+      <c r="D65" s="84" t="n"/>
+      <c r="E65" s="84" t="n"/>
+      <c r="F65" s="83" t="inlineStr">
+        <is>
+          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
+        </is>
+      </c>
+      <c r="G65" s="84" t="n"/>
+      <c r="H65" s="84" t="n"/>
+      <c r="I65" s="84" t="n"/>
+      <c r="J65" s="84" t="n"/>
+      <c r="K65" s="83" t="inlineStr">
+        <is>
+          <t>Sin cambio (máquina de volumen constante)</t>
+        </is>
+      </c>
+      <c r="L65" s="84" t="n"/>
+      <c r="M65" s="84" t="n"/>
+      <c r="N65" s="84" t="n"/>
+      <c r="O65" s="84" t="n"/>
+    </row>
+    <row r="66" ht="135" customHeight="1">
+      <c r="A66" s="83" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario de diseño (filtro cargado)</t>
+        </is>
+      </c>
+      <c r="B66" s="84" t="n"/>
+      <c r="C66" s="84" t="n"/>
+      <c r="D66" s="84" t="n"/>
+      <c r="E66" s="84" t="n"/>
+      <c r="F66" s="83" t="inlineStr">
+        <is>
+          <t>165 Pa</t>
+        </is>
+      </c>
+      <c r="G66" s="84" t="n"/>
+      <c r="H66" s="84" t="n"/>
+      <c r="I66" s="84" t="n"/>
+      <c r="J66" s="84" t="n"/>
+      <c r="K66" s="83" t="inlineStr">
+        <is>
+          <t>225 Pa</t>
+        </is>
+      </c>
+      <c r="L66" s="84" t="n"/>
+      <c r="M66" s="84" t="n"/>
+      <c r="N66" s="84" t="n"/>
+      <c r="O66" s="84" t="n"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="83" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario filtro limpio</t>
+        </is>
+      </c>
+      <c r="B67" s="84" t="n"/>
+      <c r="C67" s="84" t="n"/>
+      <c r="D67" s="84" t="n"/>
+      <c r="E67" s="84" t="n"/>
+      <c r="F67" s="83" t="inlineStr">
+        <is>
+          <t>70 Pa</t>
+        </is>
+      </c>
+      <c r="G67" s="84" t="n"/>
+      <c r="H67" s="84" t="n"/>
+      <c r="I67" s="84" t="n"/>
+      <c r="J67" s="84" t="n"/>
+      <c r="K67" s="83" t="inlineStr">
+        <is>
+          <t>95 Pa</t>
+        </is>
+      </c>
+      <c r="L67" s="84" t="n"/>
+      <c r="M67" s="84" t="n"/>
+      <c r="N67" s="84" t="n"/>
+      <c r="O67" s="84" t="n"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="83" t="inlineStr">
+        <is>
+          <t>Composición ΔP diseño</t>
+        </is>
+      </c>
+      <c r="B68" s="84" t="n"/>
+      <c r="C68" s="84" t="n"/>
+      <c r="D68" s="84" t="n"/>
+      <c r="E68" s="84" t="n"/>
+      <c r="F68" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 154 Pa + rejillas 11 Pa</t>
+        </is>
+      </c>
+      <c r="G68" s="84" t="n"/>
+      <c r="H68" s="84" t="n"/>
+      <c r="I68" s="84" t="n"/>
+      <c r="J68" s="84" t="n"/>
+      <c r="K68" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 210 Pa + 15 Pa</t>
+        </is>
+      </c>
+      <c r="L68" s="84" t="n"/>
+      <c r="M68" s="84" t="n"/>
+      <c r="N68" s="84" t="n"/>
+      <c r="O68" s="84" t="n"/>
+    </row>
+    <row r="69" ht="120" customHeight="1">
+      <c r="A69" s="83" t="inlineStr">
+        <is>
+          <t>Diámetro del impulsor (uniformidad planta)</t>
+        </is>
+      </c>
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="84" t="n"/>
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="83" t="inlineStr">
+        <is>
+          <t>560 mm (22 in)</t>
+        </is>
+      </c>
+      <c r="G69" s="84" t="n"/>
+      <c r="H69" s="84" t="n"/>
+      <c r="I69" s="84" t="n"/>
+      <c r="J69" s="84" t="n"/>
+      <c r="K69" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="84" t="n"/>
+      <c r="M69" s="84" t="n"/>
+      <c r="N69" s="84" t="n"/>
+      <c r="O69" s="84" t="n"/>
+    </row>
+    <row r="70" ht="75" customHeight="1">
+      <c r="A70" s="83" t="inlineStr">
+        <is>
+          <t>Velocidad en boca (Ø560 mm)</t>
+        </is>
+      </c>
+      <c r="B70" s="84" t="n"/>
+      <c r="C70" s="84" t="n"/>
+      <c r="D70" s="84" t="n"/>
+      <c r="E70" s="84" t="n"/>
+      <c r="F70" s="83" t="inlineStr">
+        <is>
+          <t>4.33 m/s</t>
+        </is>
+      </c>
+      <c r="G70" s="84" t="n"/>
+      <c r="H70" s="84" t="n"/>
+      <c r="I70" s="84" t="n"/>
+      <c r="J70" s="84" t="n"/>
+      <c r="K70" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="84" t="n"/>
+      <c r="M70" s="84" t="n"/>
+      <c r="N70" s="84" t="n"/>
+      <c r="O70" s="84" t="n"/>
+    </row>
+    <row r="71" ht="105" customHeight="1">
+      <c r="A71" s="83" t="inlineStr">
+        <is>
+          <t>Potencia teórica de aire (η = 0.55)</t>
+        </is>
+      </c>
+      <c r="B71" s="84" t="n"/>
+      <c r="C71" s="84" t="n"/>
+      <c r="D71" s="84" t="n"/>
+      <c r="E71" s="84" t="n"/>
+      <c r="F71" s="83" t="inlineStr">
+        <is>
+          <t>0.320 kW = 0.43 HP</t>
+        </is>
+      </c>
+      <c r="G71" s="84" t="n"/>
+      <c r="H71" s="84" t="n"/>
+      <c r="I71" s="84" t="n"/>
+      <c r="J71" s="84" t="n"/>
+      <c r="K71" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="84" t="n"/>
+      <c r="M71" s="84" t="n"/>
+      <c r="N71" s="84" t="n"/>
+      <c r="O71" s="84" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1"/>
+    <row r="73" ht="150" customHeight="1">
+      <c r="A73" s="87" t="inlineStr">
+        <is>
+          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). El tamaño comercial queda fijado en Ø560 mm por uniformidad con el montaje típico instalado en la planta; las RPM exactas se confirman con el software de selección del fabricante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1"/>
+    <row r="76" ht="15" customHeight="1"/>
+    <row r="77" ht="15" customHeight="1"/>
+    <row r="78" ht="15" customHeight="1"/>
+    <row r="79" ht="15" customHeight="1"/>
+    <row r="80" ht="15" customHeight="1"/>
+    <row r="81" ht="15" customHeight="1"/>
+    <row r="82" ht="165" customHeight="1">
+      <c r="A82" s="87" t="inlineStr">
         <is>
           <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; la eficiencia mínima exigible es 0.55 (dato provisional, a verificar contra la curva de la selección final). El margen sobre la potencia de eje (motor provisional 0.75 HP vs. 0.43 HP teóricos, con margen de servicio 1.5) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio; la potencia final del motor se confirma con la curva de catálogo de la selección.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1"/>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="15" customHeight="1"/>
-    <row r="72" ht="15" customHeight="1"/>
-    <row r="73" ht="15" customHeight="1"/>
-    <row r="74" ht="105" customHeight="1">
-      <c r="A74" s="86" t="inlineStr">
-        <is>
-          <t>4. Tipo y materiales de construcción</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 3. Requisitos de construcción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="82" t="inlineStr">
-        <is>
-          <t>Componente</t>
-        </is>
-      </c>
-      <c r="B76" s="82" t="n"/>
-      <c r="C76" s="82" t="n"/>
-      <c r="D76" s="82" t="n"/>
-      <c r="E76" s="82" t="n"/>
-      <c r="F76" s="82" t="n"/>
-      <c r="G76" s="82" t="n"/>
-      <c r="H76" s="82" t="n"/>
-      <c r="I76" s="82" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="J76" s="82" t="n"/>
-      <c r="K76" s="82" t="n"/>
-      <c r="L76" s="82" t="n"/>
-      <c r="M76" s="82" t="n"/>
-      <c r="N76" s="82" t="n"/>
-      <c r="O76" s="82" t="n"/>
-    </row>
-    <row r="77" ht="375" customHeight="1">
-      <c r="A77" s="83" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B77" s="84" t="n"/>
-      <c r="C77" s="84" t="n"/>
-      <c r="D77" s="84" t="n"/>
-      <c r="E77" s="84" t="n"/>
-      <c r="F77" s="84" t="n"/>
-      <c r="G77" s="84" t="n"/>
-      <c r="H77" s="84" t="n"/>
-      <c r="I77" s="83" t="inlineStr">
-        <is>
-          <t>Axial tubeaxial, transmisión por bandas (motor fuera de la corriente de aire, ajuste de RPM por poleas); montaje directo en muro/pasamuros</t>
-        </is>
-      </c>
-      <c r="J77" s="84" t="n"/>
-      <c r="K77" s="84" t="n"/>
-      <c r="L77" s="84" t="n"/>
-      <c r="M77" s="84" t="n"/>
-      <c r="N77" s="84" t="n"/>
-      <c r="O77" s="84" t="n"/>
-    </row>
-    <row r="78" ht="345" customHeight="1">
-      <c r="A78" s="83" t="inlineStr">
-        <is>
-          <t>Carcasa y rodete</t>
-        </is>
-      </c>
-      <c r="B78" s="84" t="n"/>
-      <c r="C78" s="84" t="n"/>
-      <c r="D78" s="84" t="n"/>
-      <c r="E78" s="84" t="n"/>
-      <c r="F78" s="84" t="n"/>
-      <c r="G78" s="84" t="n"/>
-      <c r="H78" s="84" t="n"/>
-      <c r="I78" s="83" t="inlineStr">
-        <is>
-          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167; velo superficial para oxidantes fuertes donde el fabricante lo ofrezca</t>
-        </is>
-      </c>
-      <c r="J78" s="84" t="n"/>
-      <c r="K78" s="84" t="n"/>
-      <c r="L78" s="84" t="n"/>
-      <c r="M78" s="84" t="n"/>
-      <c r="N78" s="84" t="n"/>
-      <c r="O78" s="84" t="n"/>
-    </row>
-    <row r="79" ht="195" customHeight="1">
-      <c r="A79" s="83" t="inlineStr">
-        <is>
-          <t>Elementos metálicos en la corriente</t>
-        </is>
-      </c>
-      <c r="B79" s="84" t="n"/>
-      <c r="C79" s="84" t="n"/>
-      <c r="D79" s="84" t="n"/>
-      <c r="E79" s="84" t="n"/>
-      <c r="F79" s="84" t="n"/>
-      <c r="G79" s="84" t="n"/>
-      <c r="H79" s="84" t="n"/>
-      <c r="I79" s="83" t="inlineStr">
-        <is>
-          <t>Ninguno (transmisión por bandas con motor fuera de la corriente de aire)</t>
-        </is>
-      </c>
-      <c r="J79" s="84" t="n"/>
-      <c r="K79" s="84" t="n"/>
-      <c r="L79" s="84" t="n"/>
-      <c r="M79" s="84" t="n"/>
-      <c r="N79" s="84" t="n"/>
-      <c r="O79" s="84" t="n"/>
-    </row>
-    <row r="80" ht="255" customHeight="1">
-      <c r="A80" s="83" t="inlineStr">
-        <is>
-          <t>Eje, buje y componentes de transmisión</t>
-        </is>
-      </c>
-      <c r="B80" s="84" t="n"/>
-      <c r="C80" s="84" t="n"/>
-      <c r="D80" s="84" t="n"/>
-      <c r="E80" s="84" t="n"/>
-      <c r="F80" s="84" t="n"/>
-      <c r="G80" s="84" t="n"/>
-      <c r="H80" s="84" t="n"/>
-      <c r="I80" s="83" t="inlineStr">
-        <is>
-          <t>Encapsulados/protegidos contra la atmósfera clorada; bandas en compartimento ventilado y sellado</t>
-        </is>
-      </c>
-      <c r="J80" s="84" t="n"/>
-      <c r="K80" s="84" t="n"/>
-      <c r="L80" s="84" t="n"/>
-      <c r="M80" s="84" t="n"/>
-      <c r="N80" s="84" t="n"/>
-      <c r="O80" s="84" t="n"/>
-    </row>
-    <row r="81" ht="165" customHeight="1">
-      <c r="A81" s="83" t="inlineStr">
-        <is>
-          <t>Construcción contra chispa</t>
-        </is>
-      </c>
-      <c r="B81" s="84" t="n"/>
-      <c r="C81" s="84" t="n"/>
-      <c r="D81" s="84" t="n"/>
-      <c r="E81" s="84" t="n"/>
-      <c r="F81" s="84" t="n"/>
-      <c r="G81" s="84" t="n"/>
-      <c r="H81" s="84" t="n"/>
-      <c r="I81" s="83" t="inlineStr">
-        <is>
-          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
-        </is>
-      </c>
-      <c r="J81" s="84" t="n"/>
-      <c r="K81" s="84" t="n"/>
-      <c r="L81" s="84" t="n"/>
-      <c r="M81" s="84" t="n"/>
-      <c r="N81" s="84" t="n"/>
-      <c r="O81" s="84" t="n"/>
-    </row>
-    <row r="82" ht="105" customHeight="1">
-      <c r="A82" s="83" t="inlineStr">
-        <is>
-          <t>Certificación de desempeño</t>
-        </is>
-      </c>
-      <c r="B82" s="84" t="n"/>
-      <c r="C82" s="84" t="n"/>
-      <c r="D82" s="84" t="n"/>
-      <c r="E82" s="84" t="n"/>
-      <c r="F82" s="84" t="n"/>
-      <c r="G82" s="84" t="n"/>
-      <c r="H82" s="84" t="n"/>
-      <c r="I82" s="83" t="inlineStr">
-        <is>
-          <t>AMCA 210/211 (sello AMCA exigible)</t>
-        </is>
-      </c>
-      <c r="J82" s="84" t="n"/>
-      <c r="K82" s="84" t="n"/>
-      <c r="L82" s="84" t="n"/>
-      <c r="M82" s="84" t="n"/>
-      <c r="N82" s="84" t="n"/>
-      <c r="O82" s="84" t="n"/>
-    </row>
-    <row r="83" ht="465" customHeight="1">
-      <c r="A83" s="83" t="inlineStr">
-        <is>
-          <t>Descartado</t>
-        </is>
-      </c>
-      <c r="B83" s="84" t="n"/>
-      <c r="C83" s="84" t="n"/>
-      <c r="D83" s="84" t="n"/>
-      <c r="E83" s="84" t="n"/>
-      <c r="F83" s="84" t="n"/>
-      <c r="G83" s="84" t="n"/>
-      <c r="H83" s="84" t="n"/>
-      <c r="I83" s="83" t="inlineStr">
-        <is>
-          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado; acero con epóxico solo como segunda línea con inspección programada (alternativa Greenheck VAB)</t>
-        </is>
-      </c>
-      <c r="J83" s="84" t="n"/>
-      <c r="K83" s="84" t="n"/>
-      <c r="L83" s="84" t="n"/>
-      <c r="M83" s="84" t="n"/>
-      <c r="N83" s="84" t="n"/>
-      <c r="O83" s="84" t="n"/>
-    </row>
+    <row r="83" ht="15" customHeight="1"/>
     <row r="84" ht="15" customHeight="1"/>
-    <row r="85" ht="165" customHeight="1">
-      <c r="A85" s="85" t="inlineStr">
-        <is>
-          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+    <row r="85" ht="15" customHeight="1"/>
     <row r="86" ht="15" customHeight="1"/>
     <row r="87" ht="15" customHeight="1"/>
     <row r="88" ht="15" customHeight="1"/>
     <row r="89" ht="15" customHeight="1"/>
     <row r="90" ht="15" customHeight="1"/>
     <row r="91" ht="15" customHeight="1"/>
-    <row r="92" ht="15" customHeight="1"/>
-    <row r="93" ht="15" customHeight="1"/>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="86" t="inlineStr">
-        <is>
-          <t>5. Motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1">
-      <c r="A95" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 4. Especificación del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="82" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B96" s="82" t="n"/>
-      <c r="C96" s="82" t="n"/>
-      <c r="D96" s="82" t="n"/>
-      <c r="E96" s="82" t="n"/>
-      <c r="F96" s="82" t="n"/>
-      <c r="G96" s="82" t="n"/>
-      <c r="H96" s="82" t="n"/>
-      <c r="I96" s="82" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="J96" s="82" t="n"/>
-      <c r="K96" s="82" t="n"/>
-      <c r="L96" s="82" t="n"/>
-      <c r="M96" s="82" t="n"/>
-      <c r="N96" s="82" t="n"/>
-      <c r="O96" s="82" t="n"/>
-    </row>
-    <row r="97" ht="180" customHeight="1">
+    <row r="92" ht="105" customHeight="1">
+      <c r="A92" s="86" t="inlineStr">
+        <is>
+          <t>4. Tipo y materiales de construcción</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 3. Requisitos de construcción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="82" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B94" s="82" t="n"/>
+      <c r="C94" s="82" t="n"/>
+      <c r="D94" s="82" t="n"/>
+      <c r="E94" s="82" t="n"/>
+      <c r="F94" s="82" t="n"/>
+      <c r="G94" s="82" t="n"/>
+      <c r="H94" s="82" t="n"/>
+      <c r="I94" s="82" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J94" s="82" t="n"/>
+      <c r="K94" s="82" t="n"/>
+      <c r="L94" s="82" t="n"/>
+      <c r="M94" s="82" t="n"/>
+      <c r="N94" s="82" t="n"/>
+      <c r="O94" s="82" t="n"/>
+    </row>
+    <row r="95" ht="390" customHeight="1">
+      <c r="A95" s="83" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B95" s="84" t="n"/>
+      <c r="C95" s="84" t="n"/>
+      <c r="D95" s="84" t="n"/>
+      <c r="E95" s="84" t="n"/>
+      <c r="F95" s="84" t="n"/>
+      <c r="G95" s="84" t="n"/>
+      <c r="H95" s="84" t="n"/>
+      <c r="I95" s="83" t="inlineStr">
+        <is>
+          <t>Axial mural (placa mural / wall fan), Ø560 mm, transmisión directa (motor en el cubo del impulsor); montaje en muro mediante estructura de unión</t>
+        </is>
+      </c>
+      <c r="J95" s="84" t="n"/>
+      <c r="K95" s="84" t="n"/>
+      <c r="L95" s="84" t="n"/>
+      <c r="M95" s="84" t="n"/>
+      <c r="N95" s="84" t="n"/>
+      <c r="O95" s="84" t="n"/>
+    </row>
+    <row r="96" ht="435" customHeight="1">
+      <c r="A96" s="83" t="inlineStr">
+        <is>
+          <t>Carcasa, placa mural y rodete</t>
+        </is>
+      </c>
+      <c r="B96" s="84" t="n"/>
+      <c r="C96" s="84" t="n"/>
+      <c r="D96" s="84" t="n"/>
+      <c r="E96" s="84" t="n"/>
+      <c r="F96" s="84" t="n"/>
+      <c r="G96" s="84" t="n"/>
+      <c r="H96" s="84" t="n"/>
+      <c r="I96" s="83" t="inlineStr">
+        <is>
+          <t>PRFV con resina viniléster, laminado según ASTM C582/D4167; alternativa: acero con recubrimiento epóxico anticorrosivo (segunda línea, con inspección programada)</t>
+        </is>
+      </c>
+      <c r="J96" s="84" t="n"/>
+      <c r="K96" s="84" t="n"/>
+      <c r="L96" s="84" t="n"/>
+      <c r="M96" s="84" t="n"/>
+      <c r="N96" s="84" t="n"/>
+      <c r="O96" s="84" t="n"/>
+    </row>
+    <row r="97" ht="195" customHeight="1">
       <c r="A97" s="83" t="inlineStr">
         <is>
-          <t>Potencia instalada</t>
+          <t>Elementos metálicos en la corriente</t>
         </is>
       </c>
       <c r="B97" s="84" t="n"/>
@@ -5030,7 +4971,7 @@
       <c r="H97" s="84" t="n"/>
       <c r="I97" s="83" t="inlineStr">
         <is>
-          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
+          <t>Mínimos; eje del motor en acero inoxidable con protección anticorrosiva</t>
         </is>
       </c>
       <c r="J97" s="84" t="n"/>
@@ -5040,10 +4981,10 @@
       <c r="N97" s="84" t="n"/>
       <c r="O97" s="84" t="n"/>
     </row>
-    <row r="98" ht="375" customHeight="1">
+    <row r="98" ht="540" customHeight="1">
       <c r="A98" s="83" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Motor en la corriente de aire</t>
         </is>
       </c>
       <c r="B98" s="84" t="n"/>
@@ -5055,7 +4996,7 @@
       <c r="H98" s="84" t="n"/>
       <c r="I98" s="83" t="inlineStr">
         <is>
-          <t>TEFC, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos (referencia IEEE 841 o equivalente)</t>
+          <t>Encapsulado severe duty (ver Tabla 4) — la transmisión directa ubica el motor dentro de la corriente; se exige ejecución anticorrosiva reforzada, criterio ya operado por la planta en sus montajes típicos</t>
         </is>
       </c>
       <c r="J98" s="84" t="n"/>
@@ -5065,10 +5006,10 @@
       <c r="N98" s="84" t="n"/>
       <c r="O98" s="84" t="n"/>
     </row>
-    <row r="99" ht="120" customHeight="1">
+    <row r="99" ht="165" customHeight="1">
       <c r="A99" s="83" t="inlineStr">
         <is>
-          <t>Velocidad</t>
+          <t>Construcción contra chispa</t>
         </is>
       </c>
       <c r="B99" s="84" t="n"/>
@@ -5080,7 +5021,7 @@
       <c r="H99" s="84" t="n"/>
       <c r="I99" s="83" t="inlineStr">
         <is>
-          <t>1 800 RPM (4 polos, 60 Hz) — dato típico</t>
+          <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
         </is>
       </c>
       <c r="J99" s="84" t="n"/>
@@ -5093,7 +5034,7 @@
     <row r="100" ht="105" customHeight="1">
       <c r="A100" s="83" t="inlineStr">
         <is>
-          <t>Aislamiento / protección</t>
+          <t>Certificación de desempeño</t>
         </is>
       </c>
       <c r="B100" s="84" t="n"/>
@@ -5105,7 +5046,7 @@
       <c r="H100" s="84" t="n"/>
       <c r="I100" s="83" t="inlineStr">
         <is>
-          <t>Clase F / IP55 mínimo (IP56 preferible)</t>
+          <t>AMCA 210/211 (sello AMCA exigible)</t>
         </is>
       </c>
       <c r="J100" s="84" t="n"/>
@@ -5115,10 +5056,10 @@
       <c r="N100" s="84" t="n"/>
       <c r="O100" s="84" t="n"/>
     </row>
-    <row r="101" ht="150" customHeight="1">
+    <row r="101" ht="285" customHeight="1">
       <c r="A101" s="83" t="inlineStr">
         <is>
-          <t>Tensión / fases / frecuencia</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="B101" s="84" t="n"/>
@@ -5130,7 +5071,7 @@
       <c r="H101" s="84" t="n"/>
       <c r="I101" s="83" t="inlineStr">
         <is>
-          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado desnudo en la corriente de aire</t>
         </is>
       </c>
       <c r="J101" s="84" t="n"/>
@@ -5140,444 +5081,757 @@
       <c r="N101" s="84" t="n"/>
       <c r="O101" s="84" t="n"/>
     </row>
-    <row r="102" ht="165" customHeight="1">
-      <c r="A102" s="83" t="inlineStr">
-        <is>
-          <t>Derateo por altitud</t>
-        </is>
-      </c>
-      <c r="B102" s="84" t="n"/>
-      <c r="C102" s="84" t="n"/>
-      <c r="D102" s="84" t="n"/>
-      <c r="E102" s="84" t="n"/>
-      <c r="F102" s="84" t="n"/>
-      <c r="G102" s="84" t="n"/>
-      <c r="H102" s="84" t="n"/>
-      <c r="I102" s="83" t="inlineStr">
-        <is>
-          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
-        </is>
-      </c>
-      <c r="J102" s="84" t="n"/>
-      <c r="K102" s="84" t="n"/>
-      <c r="L102" s="84" t="n"/>
-      <c r="M102" s="84" t="n"/>
-      <c r="N102" s="84" t="n"/>
-      <c r="O102" s="84" t="n"/>
-    </row>
-    <row r="103" ht="360" customHeight="1">
-      <c r="A103" s="83" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B103" s="84" t="n"/>
-      <c r="C103" s="84" t="n"/>
-      <c r="D103" s="84" t="n"/>
-      <c r="E103" s="84" t="n"/>
-      <c r="F103" s="84" t="n"/>
-      <c r="G103" s="84" t="n"/>
-      <c r="H103" s="84" t="n"/>
-      <c r="I103" s="83" t="inlineStr">
-        <is>
-          <t>Calentador anticondensación si hay paradas largas (dato típico de buena práctica); caja de conexiones sellada, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="J103" s="84" t="n"/>
-      <c r="K103" s="84" t="n"/>
-      <c r="L103" s="84" t="n"/>
-      <c r="M103" s="84" t="n"/>
-      <c r="N103" s="84" t="n"/>
-      <c r="O103" s="84" t="n"/>
+    <row r="102" ht="15" customHeight="1"/>
+    <row r="103" ht="165" customHeight="1">
+      <c r="A103" s="85" t="inlineStr">
+        <is>
+          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23). El montaje típico de la planta usa acero galvanizado y pintura electrostática; para este servicio se eleva la especificación a PRFV o epóxico anticorrosivo por la atmósfera clorada.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1"/>
-    <row r="105" ht="165" customHeight="1">
-      <c r="A105" s="85" t="inlineStr">
-        <is>
-          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+    <row r="105" ht="15" customHeight="1"/>
     <row r="106" ht="15" customHeight="1"/>
     <row r="107" ht="15" customHeight="1"/>
     <row r="108" ht="15" customHeight="1"/>
     <row r="109" ht="15" customHeight="1"/>
     <row r="110" ht="15" customHeight="1"/>
-    <row r="111" ht="45" customHeight="1">
-      <c r="A111" s="86" t="inlineStr">
-        <is>
-          <t>6. Accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="165" customHeight="1">
-      <c r="A112" s="87" t="inlineStr">
-        <is>
-          <t>6.1. Conexión flexible de descarga en hipalón (CSM) con bandas inox 316 (Hardcast Hypalon (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+    <row r="111" ht="15" customHeight="1"/>
+    <row r="112" ht="15" customHeight="1"/>
     <row r="113" ht="15" customHeight="1"/>
-    <row r="114" ht="15" customHeight="1"/>
+    <row r="114" ht="165" customHeight="1">
+      <c r="A114" s="85" t="inlineStr">
+        <is>
+          <t>Nota de ingeniería (REV2). La adopción del montaje mural de transmisión directa deja el motor dentro de la corriente de aire corrosivo, a diferencia de la configuración de transmisión por bandas evaluada en REV1. El riesgo se mitiga con la ejecución encapsulada severe duty de la Tabla 4 y con el programa de inspección semestral de la Tabla de mantenimiento de la descripción técnica de planta; la alternativa de transmisión por bandas queda documentada como opción si la vida del motor en servicio resultara inferior a la esperada.</t>
+        </is>
+      </c>
+    </row>
     <row r="115" ht="15" customHeight="1"/>
-    <row r="116" ht="120" customHeight="1">
-      <c r="A116" s="87" t="inlineStr">
-        <is>
-          <t>6.2. Persiana de gravedad de cierre automático en inox o PRFV (opcional), para sellar la abertura cuando el equipo está detenido.</t>
-        </is>
-      </c>
-    </row>
+    <row r="116" ht="15" customHeight="1"/>
     <row r="117" ht="15" customHeight="1"/>
     <row r="118" ht="15" customHeight="1"/>
-    <row r="119" ht="150" customHeight="1">
-      <c r="A119" s="87" t="inlineStr">
-        <is>
-          <t>6.3. Guarda de seguridad en el lado de aspiración/descarga accesible, según configuración final de montaje.</t>
-        </is>
-      </c>
-    </row>
+    <row r="119" ht="15" customHeight="1"/>
     <row r="120" ht="15" customHeight="1"/>
-    <row r="121" ht="150" customHeight="1">
-      <c r="A121" s="87" t="inlineStr">
-        <is>
-          <t>6.4. Bancada y soportes con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructura galvanizada.</t>
-        </is>
-      </c>
-    </row>
+    <row r="121" ht="15" customHeight="1"/>
     <row r="122" ht="15" customHeight="1"/>
-    <row r="123" ht="165" customHeight="1">
-      <c r="A123" s="87" t="inlineStr">
-        <is>
-          <t>6.5. Toma de aire ubicada a sotavento y alejada de las fuentes de cloro de la planta (recomendación de la investigación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15" customHeight="1"/>
-    <row r="125" ht="120" customHeight="1">
-      <c r="A125" s="87" t="inlineStr">
-        <is>
-          <t>6.6. Guardamotor y tablero conforme a RETIE (ver listado_equipos.md, ítems 11-12).</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1"/>
-    <row r="127" ht="15" customHeight="1"/>
-    <row r="128" ht="75" customHeight="1">
-      <c r="A128" s="86" t="inlineStr">
-        <is>
-          <t>7. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="120" customHeight="1">
-      <c r="A129" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 5. Candidatos (consulta 2026-07-23, ampliada 2026-07-27); modelo de referencia, tamaño/RPM final por confirmar con proveedor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1"/>
-    <row r="131" ht="15" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="82" t="inlineStr">
-        <is>
-          <t>Fabricante / línea</t>
-        </is>
-      </c>
-      <c r="B132" s="82" t="n"/>
-      <c r="C132" s="82" t="n"/>
-      <c r="D132" s="82" t="n"/>
-      <c r="E132" s="82" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="F132" s="82" t="n"/>
-      <c r="G132" s="82" t="n"/>
-      <c r="H132" s="82" t="n"/>
-      <c r="I132" s="82" t="inlineStr">
-        <is>
-          <t>Canal en Colombia</t>
-        </is>
-      </c>
-      <c r="J132" s="82" t="n"/>
-      <c r="K132" s="82" t="n"/>
-      <c r="L132" s="82" t="n"/>
-      <c r="M132" s="82" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N132" s="82" t="n"/>
-      <c r="O132" s="82" t="n"/>
-    </row>
-    <row r="133" ht="405" customHeight="1">
+    <row r="123" ht="15" customHeight="1"/>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="86" t="inlineStr">
+        <is>
+          <t>5. Motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="45" customHeight="1">
+      <c r="A125" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 4. Especificación del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="82" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B126" s="82" t="n"/>
+      <c r="C126" s="82" t="n"/>
+      <c r="D126" s="82" t="n"/>
+      <c r="E126" s="82" t="n"/>
+      <c r="F126" s="82" t="n"/>
+      <c r="G126" s="82" t="n"/>
+      <c r="H126" s="82" t="n"/>
+      <c r="I126" s="82" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J126" s="82" t="n"/>
+      <c r="K126" s="82" t="n"/>
+      <c r="L126" s="82" t="n"/>
+      <c r="M126" s="82" t="n"/>
+      <c r="N126" s="82" t="n"/>
+      <c r="O126" s="82" t="n"/>
+    </row>
+    <row r="127" ht="180" customHeight="1">
+      <c r="A127" s="83" t="inlineStr">
+        <is>
+          <t>Potencia instalada</t>
+        </is>
+      </c>
+      <c r="B127" s="84" t="n"/>
+      <c r="C127" s="84" t="n"/>
+      <c r="D127" s="84" t="n"/>
+      <c r="E127" s="84" t="n"/>
+      <c r="F127" s="84" t="n"/>
+      <c r="G127" s="84" t="n"/>
+      <c r="H127" s="84" t="n"/>
+      <c r="I127" s="83" t="inlineStr">
+        <is>
+          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
+        </is>
+      </c>
+      <c r="J127" s="84" t="n"/>
+      <c r="K127" s="84" t="n"/>
+      <c r="L127" s="84" t="n"/>
+      <c r="M127" s="84" t="n"/>
+      <c r="N127" s="84" t="n"/>
+      <c r="O127" s="84" t="n"/>
+    </row>
+    <row r="128" ht="435" customHeight="1">
+      <c r="A128" s="83" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="B128" s="84" t="n"/>
+      <c r="C128" s="84" t="n"/>
+      <c r="D128" s="84" t="n"/>
+      <c r="E128" s="84" t="n"/>
+      <c r="F128" s="84" t="n"/>
+      <c r="G128" s="84" t="n"/>
+      <c r="H128" s="84" t="n"/>
+      <c r="I128" s="83" t="inlineStr">
+        <is>
+          <t>TEFC encapsulado, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos, eje inox (referencia IEEE 841 o equivalente)</t>
+        </is>
+      </c>
+      <c r="J128" s="84" t="n"/>
+      <c r="K128" s="84" t="n"/>
+      <c r="L128" s="84" t="n"/>
+      <c r="M128" s="84" t="n"/>
+      <c r="N128" s="84" t="n"/>
+      <c r="O128" s="84" t="n"/>
+    </row>
+    <row r="129" ht="210" customHeight="1">
+      <c r="A129" s="83" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B129" s="84" t="n"/>
+      <c r="C129" s="84" t="n"/>
+      <c r="D129" s="84" t="n"/>
+      <c r="E129" s="84" t="n"/>
+      <c r="F129" s="84" t="n"/>
+      <c r="G129" s="84" t="n"/>
+      <c r="H129" s="84" t="n"/>
+      <c r="I129" s="83" t="inlineStr">
+        <is>
+          <t>En el cubo del impulsor, dentro de la corriente de aire (transmisión directa)</t>
+        </is>
+      </c>
+      <c r="J129" s="84" t="n"/>
+      <c r="K129" s="84" t="n"/>
+      <c r="L129" s="84" t="n"/>
+      <c r="M129" s="84" t="n"/>
+      <c r="N129" s="84" t="n"/>
+      <c r="O129" s="84" t="n"/>
+    </row>
+    <row r="130" ht="150" customHeight="1">
+      <c r="A130" s="83" t="inlineStr">
+        <is>
+          <t>Aislamiento / protección</t>
+        </is>
+      </c>
+      <c r="B130" s="84" t="n"/>
+      <c r="C130" s="84" t="n"/>
+      <c r="D130" s="84" t="n"/>
+      <c r="E130" s="84" t="n"/>
+      <c r="F130" s="84" t="n"/>
+      <c r="G130" s="84" t="n"/>
+      <c r="H130" s="84" t="n"/>
+      <c r="I130" s="83" t="inlineStr">
+        <is>
+          <t>Clase F (H preferible) / IP56 mínimo (IP66 preferible)</t>
+        </is>
+      </c>
+      <c r="J130" s="84" t="n"/>
+      <c r="K130" s="84" t="n"/>
+      <c r="L130" s="84" t="n"/>
+      <c r="M130" s="84" t="n"/>
+      <c r="N130" s="84" t="n"/>
+      <c r="O130" s="84" t="n"/>
+    </row>
+    <row r="131" ht="150" customHeight="1">
+      <c r="A131" s="83" t="inlineStr">
+        <is>
+          <t>Tensión / fases / frecuencia</t>
+        </is>
+      </c>
+      <c r="B131" s="84" t="n"/>
+      <c r="C131" s="84" t="n"/>
+      <c r="D131" s="84" t="n"/>
+      <c r="E131" s="84" t="n"/>
+      <c r="F131" s="84" t="n"/>
+      <c r="G131" s="84" t="n"/>
+      <c r="H131" s="84" t="n"/>
+      <c r="I131" s="83" t="inlineStr">
+        <is>
+          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J131" s="84" t="n"/>
+      <c r="K131" s="84" t="n"/>
+      <c r="L131" s="84" t="n"/>
+      <c r="M131" s="84" t="n"/>
+      <c r="N131" s="84" t="n"/>
+      <c r="O131" s="84" t="n"/>
+    </row>
+    <row r="132" ht="165" customHeight="1">
+      <c r="A132" s="83" t="inlineStr">
+        <is>
+          <t>Derateo por altitud</t>
+        </is>
+      </c>
+      <c r="B132" s="84" t="n"/>
+      <c r="C132" s="84" t="n"/>
+      <c r="D132" s="84" t="n"/>
+      <c r="E132" s="84" t="n"/>
+      <c r="F132" s="84" t="n"/>
+      <c r="G132" s="84" t="n"/>
+      <c r="H132" s="84" t="n"/>
+      <c r="I132" s="83" t="inlineStr">
+        <is>
+          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+        </is>
+      </c>
+      <c r="J132" s="84" t="n"/>
+      <c r="K132" s="84" t="n"/>
+      <c r="L132" s="84" t="n"/>
+      <c r="M132" s="84" t="n"/>
+      <c r="N132" s="84" t="n"/>
+      <c r="O132" s="84" t="n"/>
+    </row>
+    <row r="133" ht="270" customHeight="1">
       <c r="A133" s="83" t="inlineStr">
         <is>
-          <t>Aerovent FBD (Twin City Fan / Aerovent) — primera opción</t>
+          <t>Accesorios</t>
         </is>
       </c>
       <c r="B133" s="84" t="n"/>
       <c r="C133" s="84" t="n"/>
       <c r="D133" s="84" t="n"/>
-      <c r="E133" s="83" t="inlineStr">
-        <is>
-          <t>PRFV, tubeaxial de bandas (Catálogo 185: 355-1 525 mm, hasta 370 Pa estática)</t>
-        </is>
-      </c>
+      <c r="E133" s="84" t="n"/>
       <c r="F133" s="84" t="n"/>
       <c r="G133" s="84" t="n"/>
       <c r="H133" s="84" t="n"/>
       <c r="I133" s="83" t="inlineStr">
         <is>
-          <t>Por confirmar representante/canal local</t>
+          <t>Calentador anticondensación (paradas largas); caja de conexiones sellada, prensaestopas niquelados</t>
         </is>
       </c>
       <c r="J133" s="84" t="n"/>
       <c r="K133" s="84" t="n"/>
       <c r="L133" s="84" t="n"/>
-      <c r="M133" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf)</t>
-        </is>
-      </c>
+      <c r="M133" s="84" t="n"/>
       <c r="N133" s="84" t="n"/>
       <c r="O133" s="84" t="n"/>
     </row>
-    <row r="134" ht="480" customHeight="1">
-      <c r="A134" s="83" t="inlineStr">
-        <is>
-          <t>Greenheck VAB (vaneaxial de bandas)</t>
-        </is>
-      </c>
-      <c r="B134" s="84" t="n"/>
-      <c r="C134" s="84" t="n"/>
-      <c r="D134" s="84" t="n"/>
-      <c r="E134" s="83" t="inlineStr">
-        <is>
-          <t>Acero con recubrimiento epóxico</t>
-        </is>
-      </c>
-      <c r="F134" s="84" t="n"/>
-      <c r="G134" s="84" t="n"/>
-      <c r="H134" s="84" t="n"/>
-      <c r="I134" s="83" t="inlineStr">
-        <is>
-          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
-        </is>
-      </c>
-      <c r="J134" s="84" t="n"/>
-      <c r="K134" s="84" t="n"/>
-      <c r="L134" s="84" t="n"/>
-      <c r="M134" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
-        </is>
-      </c>
-      <c r="N134" s="84" t="n"/>
-      <c r="O134" s="84" t="n"/>
-    </row>
-    <row r="135" ht="360" customHeight="1">
-      <c r="A135" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca HCT/HGT versión anticorrosiva</t>
-        </is>
-      </c>
-      <c r="B135" s="84" t="n"/>
-      <c r="C135" s="84" t="n"/>
-      <c r="D135" s="84" t="n"/>
-      <c r="E135" s="83" t="inlineStr">
-        <is>
-          <t>PRFV</t>
-        </is>
-      </c>
-      <c r="F135" s="84" t="n"/>
-      <c r="G135" s="84" t="n"/>
-      <c r="H135" s="84" t="n"/>
-      <c r="I135" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
-        </is>
-      </c>
-      <c r="J135" s="84" t="n"/>
-      <c r="K135" s="84" t="n"/>
-      <c r="L135" s="84" t="n"/>
-      <c r="M135" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
-        </is>
-      </c>
-      <c r="N135" s="84" t="n"/>
-      <c r="O135" s="84" t="n"/>
-    </row>
-    <row r="136" ht="165" customHeight="1">
-      <c r="A136" s="83" t="inlineStr">
-        <is>
-          <t>New York Blower FRP tubeaxial</t>
-        </is>
-      </c>
-      <c r="B136" s="84" t="n"/>
-      <c r="C136" s="84" t="n"/>
-      <c r="D136" s="84" t="n"/>
-      <c r="E136" s="83" t="inlineStr">
-        <is>
-          <t>PRFV</t>
-        </is>
-      </c>
-      <c r="F136" s="84" t="n"/>
-      <c r="G136" s="84" t="n"/>
-      <c r="H136" s="84" t="n"/>
-      <c r="I136" s="83" t="inlineStr">
-        <is>
-          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="J136" s="84" t="n"/>
-      <c r="K136" s="84" t="n"/>
-      <c r="L136" s="84" t="n"/>
-      <c r="M136" s="83" t="inlineStr">
-        <is>
-          <t>NYB (https://www.nyb.com/)</t>
-        </is>
-      </c>
-      <c r="N136" s="84" t="n"/>
-      <c r="O136" s="84" t="n"/>
-    </row>
-    <row r="137" ht="195" customHeight="1">
-      <c r="A137" s="83" t="inlineStr">
-        <is>
-          <t>Plastec</t>
-        </is>
-      </c>
-      <c r="B137" s="84" t="n"/>
-      <c r="C137" s="84" t="n"/>
-      <c r="D137" s="84" t="n"/>
-      <c r="E137" s="83" t="inlineStr">
-        <is>
-          <t>Polipropileno</t>
-        </is>
-      </c>
-      <c r="F137" s="84" t="n"/>
-      <c r="G137" s="84" t="n"/>
-      <c r="H137" s="84" t="n"/>
-      <c r="I137" s="83" t="inlineStr">
-        <is>
-          <t>Importación directa (despacho 48 h declarado)</t>
-        </is>
-      </c>
-      <c r="J137" s="84" t="n"/>
-      <c r="K137" s="84" t="n"/>
-      <c r="L137" s="84" t="n"/>
-      <c r="M137" s="83" t="inlineStr">
-        <is>
-          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
-        </is>
-      </c>
-      <c r="N137" s="84" t="n"/>
-      <c r="O137" s="84" t="n"/>
-    </row>
+    <row r="134" ht="15" customHeight="1"/>
+    <row r="135" ht="165" customHeight="1">
+      <c r="A135" s="85" t="inlineStr">
+        <is>
+          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="15" customHeight="1"/>
+    <row r="137" ht="15" customHeight="1"/>
     <row r="138" ht="15" customHeight="1"/>
     <row r="139" ht="15" customHeight="1"/>
-    <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="86" t="inlineStr">
+    <row r="140" ht="15" customHeight="1"/>
+    <row r="141" ht="45" customHeight="1">
+      <c r="A141" s="86" t="inlineStr">
+        <is>
+          <t>6. Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="105" customHeight="1">
+      <c r="A142" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 5. Accesorios del conjunto de montaje (uniformidad con la planta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1"/>
+    <row r="144" ht="75" customHeight="1">
+      <c r="A144" s="82" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="B144" s="82" t="n"/>
+      <c r="C144" s="82" t="n"/>
+      <c r="D144" s="82" t="n"/>
+      <c r="E144" s="82" t="n"/>
+      <c r="F144" s="82" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="G144" s="82" t="n"/>
+      <c r="H144" s="82" t="n"/>
+      <c r="I144" s="82" t="n"/>
+      <c r="J144" s="82" t="n"/>
+      <c r="K144" s="82" t="inlineStr">
+        <is>
+          <t>Material / especificación</t>
+        </is>
+      </c>
+      <c r="L144" s="82" t="n"/>
+      <c r="M144" s="82" t="n"/>
+      <c r="N144" s="82" t="n"/>
+      <c r="O144" s="82" t="n"/>
+    </row>
+    <row r="145" ht="315" customHeight="1">
+      <c r="A145" s="83" t="inlineStr">
+        <is>
+          <t>Cubierta intemperie</t>
+        </is>
+      </c>
+      <c r="B145" s="84" t="n"/>
+      <c r="C145" s="84" t="n"/>
+      <c r="D145" s="84" t="n"/>
+      <c r="E145" s="84" t="n"/>
+      <c r="F145" s="83" t="inlineStr">
+        <is>
+          <t>Protección contra lluvia, radiación solar e ingreso directo de agua; aloja el banco de filtración (ver HD-FILT-001)</t>
+        </is>
+      </c>
+      <c r="G145" s="84" t="n"/>
+      <c r="H145" s="84" t="n"/>
+      <c r="I145" s="84" t="n"/>
+      <c r="J145" s="84" t="n"/>
+      <c r="K145" s="83" t="inlineStr">
+        <is>
+          <t>PRFV o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L</t>
+        </is>
+      </c>
+      <c r="L145" s="84" t="n"/>
+      <c r="M145" s="84" t="n"/>
+      <c r="N145" s="84" t="n"/>
+      <c r="O145" s="84" t="n"/>
+    </row>
+    <row r="146" ht="330" customHeight="1">
+      <c r="A146" s="83" t="inlineStr">
+        <is>
+          <t>Estructura de unión</t>
+        </is>
+      </c>
+      <c r="B146" s="84" t="n"/>
+      <c r="C146" s="84" t="n"/>
+      <c r="D146" s="84" t="n"/>
+      <c r="E146" s="84" t="n"/>
+      <c r="F146" s="83" t="inlineStr">
+        <is>
+          <t>Marco de soporte pernado al muro para fijación segura del ventilador; transmite cargas estáticas, dinámicas y vibraciones</t>
+        </is>
+      </c>
+      <c r="G146" s="84" t="n"/>
+      <c r="H146" s="84" t="n"/>
+      <c r="I146" s="84" t="n"/>
+      <c r="J146" s="84" t="n"/>
+      <c r="K146" s="83" t="inlineStr">
+        <is>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (A4) con aislamiento dieléctrico</t>
+        </is>
+      </c>
+      <c r="L146" s="84" t="n"/>
+      <c r="M146" s="84" t="n"/>
+      <c r="N146" s="84" t="n"/>
+      <c r="O146" s="84" t="n"/>
+    </row>
+    <row r="147" ht="240" customHeight="1">
+      <c r="A147" s="83" t="inlineStr">
+        <is>
+          <t>Malla de protección interior</t>
+        </is>
+      </c>
+      <c r="B147" s="84" t="n"/>
+      <c r="C147" s="84" t="n"/>
+      <c r="D147" s="84" t="n"/>
+      <c r="E147" s="84" t="n"/>
+      <c r="F147" s="83" t="inlineStr">
+        <is>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor</t>
+        </is>
+      </c>
+      <c r="G147" s="84" t="n"/>
+      <c r="H147" s="84" t="n"/>
+      <c r="I147" s="84" t="n"/>
+      <c r="J147" s="84" t="n"/>
+      <c r="K147" s="83" t="inlineStr">
+        <is>
+          <t>Malla inox 316 o galvanizada con pintura epóxica, marco desmontable</t>
+        </is>
+      </c>
+      <c r="L147" s="84" t="n"/>
+      <c r="M147" s="84" t="n"/>
+      <c r="N147" s="84" t="n"/>
+      <c r="O147" s="84" t="n"/>
+    </row>
+    <row r="148" ht="165" customHeight="1">
+      <c r="A148" s="83" t="inlineStr">
+        <is>
+          <t>Sellado del pasamuros</t>
+        </is>
+      </c>
+      <c r="B148" s="84" t="n"/>
+      <c r="C148" s="84" t="n"/>
+      <c r="D148" s="84" t="n"/>
+      <c r="E148" s="84" t="n"/>
+      <c r="F148" s="83" t="inlineStr">
+        <is>
+          <t>Evita recirculaciones y filtraciones no controladas en el vano</t>
+        </is>
+      </c>
+      <c r="G148" s="84" t="n"/>
+      <c r="H148" s="84" t="n"/>
+      <c r="I148" s="84" t="n"/>
+      <c r="J148" s="84" t="n"/>
+      <c r="K148" s="83" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi)</t>
+        </is>
+      </c>
+      <c r="L148" s="84" t="n"/>
+      <c r="M148" s="84" t="n"/>
+      <c r="N148" s="84" t="n"/>
+      <c r="O148" s="84" t="n"/>
+    </row>
+    <row r="149" ht="210" customHeight="1">
+      <c r="A149" s="83" t="inlineStr">
+        <is>
+          <t>Guardamotor y tablero</t>
+        </is>
+      </c>
+      <c r="B149" s="84" t="n"/>
+      <c r="C149" s="84" t="n"/>
+      <c r="D149" s="84" t="n"/>
+      <c r="E149" s="84" t="n"/>
+      <c r="F149" s="83" t="inlineStr">
+        <is>
+          <t>Protección eléctrica conforme a RETIE (ver listado_equipos.md, ítems 11-12)</t>
+        </is>
+      </c>
+      <c r="G149" s="84" t="n"/>
+      <c r="H149" s="84" t="n"/>
+      <c r="I149" s="84" t="n"/>
+      <c r="J149" s="84" t="n"/>
+      <c r="K149" s="83" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="L149" s="84" t="n"/>
+      <c r="M149" s="84" t="n"/>
+      <c r="N149" s="84" t="n"/>
+      <c r="O149" s="84" t="n"/>
+    </row>
+    <row r="150" ht="15" customHeight="1"/>
+    <row r="151" ht="150" customHeight="1">
+      <c r="A151" s="87" t="inlineStr">
+        <is>
+          <t>6.1. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1"/>
+    <row r="153" ht="15" customHeight="1"/>
+    <row r="154" ht="15" customHeight="1"/>
+    <row r="155" ht="75" customHeight="1">
+      <c r="A155" s="86" t="inlineStr">
+        <is>
+          <t>7. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="135" customHeight="1">
+      <c r="A156" s="88" t="inlineStr">
+        <is>
+          <t>Tabla 6. Candidatos (consulta 2026-07-23, ajustada 2026-07-27 a tipo mural); RPM final por confirmar con proveedor en el punto 3 840 m³/h @ 225 Pa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1"/>
+    <row r="158" ht="15" customHeight="1"/>
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" s="82" t="inlineStr">
+        <is>
+          <t>Fabricante / línea</t>
+        </is>
+      </c>
+      <c r="B159" s="82" t="n"/>
+      <c r="C159" s="82" t="n"/>
+      <c r="D159" s="82" t="n"/>
+      <c r="E159" s="82" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F159" s="82" t="n"/>
+      <c r="G159" s="82" t="n"/>
+      <c r="H159" s="82" t="n"/>
+      <c r="I159" s="82" t="inlineStr">
+        <is>
+          <t>Canal en Colombia</t>
+        </is>
+      </c>
+      <c r="J159" s="82" t="n"/>
+      <c r="K159" s="82" t="n"/>
+      <c r="L159" s="82" t="n"/>
+      <c r="M159" s="82" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N159" s="82" t="n"/>
+      <c r="O159" s="82" t="n"/>
+    </row>
+    <row r="160" ht="360" customHeight="1">
+      <c r="A160" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca HQD/HGT mural anticorrosivo — primera opción por uniformidad y canal local</t>
+        </is>
+      </c>
+      <c r="B160" s="84" t="n"/>
+      <c r="C160" s="84" t="n"/>
+      <c r="D160" s="84" t="n"/>
+      <c r="E160" s="83" t="inlineStr">
+        <is>
+          <t>PRFV / epóxico, mural transmisión directa</t>
+        </is>
+      </c>
+      <c r="F160" s="84" t="n"/>
+      <c r="G160" s="84" t="n"/>
+      <c r="H160" s="84" t="n"/>
+      <c r="I160" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
+        </is>
+      </c>
+      <c r="J160" s="84" t="n"/>
+      <c r="K160" s="84" t="n"/>
+      <c r="L160" s="84" t="n"/>
+      <c r="M160" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
+        </is>
+      </c>
+      <c r="N160" s="84" t="n"/>
+      <c r="O160" s="84" t="n"/>
+    </row>
+    <row r="161" ht="300" customHeight="1">
+      <c r="A161" s="83" t="inlineStr">
+        <is>
+          <t>Greenheck mural (línea industrial)</t>
+        </is>
+      </c>
+      <c r="B161" s="84" t="n"/>
+      <c r="C161" s="84" t="n"/>
+      <c r="D161" s="84" t="n"/>
+      <c r="E161" s="83" t="inlineStr">
+        <is>
+          <t>Acero con recubrimiento epóxico</t>
+        </is>
+      </c>
+      <c r="F161" s="84" t="n"/>
+      <c r="G161" s="84" t="n"/>
+      <c r="H161" s="84" t="n"/>
+      <c r="I161" s="83" t="inlineStr">
+        <is>
+          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
+        </is>
+      </c>
+      <c r="J161" s="84" t="n"/>
+      <c r="K161" s="84" t="n"/>
+      <c r="L161" s="84" t="n"/>
+      <c r="M161" s="83" t="inlineStr">
+        <is>
+          <t>Greenheck (https://www.greenheck.com); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
+        </is>
+      </c>
+      <c r="N161" s="84" t="n"/>
+      <c r="O161" s="84" t="n"/>
+    </row>
+    <row r="162" ht="120" customHeight="1">
+      <c r="A162" s="83" t="inlineStr">
+        <is>
+          <t>Aerovent / Twin City Fan (línea mural FRP)</t>
+        </is>
+      </c>
+      <c r="B162" s="84" t="n"/>
+      <c r="C162" s="84" t="n"/>
+      <c r="D162" s="84" t="n"/>
+      <c r="E162" s="83" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F162" s="84" t="n"/>
+      <c r="G162" s="84" t="n"/>
+      <c r="H162" s="84" t="n"/>
+      <c r="I162" s="83" t="inlineStr">
+        <is>
+          <t>Por confirmar representante/canal local</t>
+        </is>
+      </c>
+      <c r="J162" s="84" t="n"/>
+      <c r="K162" s="84" t="n"/>
+      <c r="L162" s="84" t="n"/>
+      <c r="M162" s="83" t="inlineStr">
+        <is>
+          <t>Aerovent (https://www.aerovent.com)</t>
+        </is>
+      </c>
+      <c r="N162" s="84" t="n"/>
+      <c r="O162" s="84" t="n"/>
+    </row>
+    <row r="163" ht="165" customHeight="1">
+      <c r="A163" s="83" t="inlineStr">
+        <is>
+          <t>New York Blower FRP mural</t>
+        </is>
+      </c>
+      <c r="B163" s="84" t="n"/>
+      <c r="C163" s="84" t="n"/>
+      <c r="D163" s="84" t="n"/>
+      <c r="E163" s="83" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F163" s="84" t="n"/>
+      <c r="G163" s="84" t="n"/>
+      <c r="H163" s="84" t="n"/>
+      <c r="I163" s="83" t="inlineStr">
+        <is>
+          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J163" s="84" t="n"/>
+      <c r="K163" s="84" t="n"/>
+      <c r="L163" s="84" t="n"/>
+      <c r="M163" s="83" t="inlineStr">
+        <is>
+          <t>NYB (https://www.nyb.com/)</t>
+        </is>
+      </c>
+      <c r="N163" s="84" t="n"/>
+      <c r="O163" s="84" t="n"/>
+    </row>
+    <row r="164" ht="195" customHeight="1">
+      <c r="A164" s="83" t="inlineStr">
+        <is>
+          <t>Plastec</t>
+        </is>
+      </c>
+      <c r="B164" s="84" t="n"/>
+      <c r="C164" s="84" t="n"/>
+      <c r="D164" s="84" t="n"/>
+      <c r="E164" s="83" t="inlineStr">
+        <is>
+          <t>Polipropileno</t>
+        </is>
+      </c>
+      <c r="F164" s="84" t="n"/>
+      <c r="G164" s="84" t="n"/>
+      <c r="H164" s="84" t="n"/>
+      <c r="I164" s="83" t="inlineStr">
+        <is>
+          <t>Importación directa (despacho 48 h declarado)</t>
+        </is>
+      </c>
+      <c r="J164" s="84" t="n"/>
+      <c r="K164" s="84" t="n"/>
+      <c r="L164" s="84" t="n"/>
+      <c r="M164" s="83" t="inlineStr">
+        <is>
+          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
+        </is>
+      </c>
+      <c r="N164" s="84" t="n"/>
+      <c r="O164" s="84" t="n"/>
+    </row>
+    <row r="165" ht="15" customHeight="1"/>
+    <row r="166" ht="15" customHeight="1"/>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="86" t="inlineStr">
         <is>
           <t>8. Montaje</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="180" customHeight="1">
-      <c r="A141" s="87" t="inlineStr">
-        <is>
-          <t>8.1. El ventilador se instalará en muro/pasamuros, con el eje horizontal y a una cota aproximada de 3,0 m sobre el piso terminado del laboratorio. El sentido de flujo es: aspiración de aire exterior filtrado, descarga directa al interior del recinto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1"/>
-    <row r="143" ht="15" customHeight="1"/>
-    <row r="144" ht="15" customHeight="1"/>
-    <row r="145" ht="165" customHeight="1">
-      <c r="A145" s="87" t="inlineStr">
-        <is>
-          <t>8.2. La transmisión por bandas ubica el motor fuera de la corriente de aire corrosivo. La altura de 3,0 m exige garantizar el acceso para mantenimiento periódico de bandas, lubricación e inspección del motor (plataforma fija o escalera industrial).</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1"/>
-    <row r="147" ht="15" customHeight="1"/>
-    <row r="148" ht="15" customHeight="1"/>
-    <row r="149" ht="165" customHeight="1">
-      <c r="A149" s="87" t="inlineStr">
-        <is>
-          <t>8.3. La carcasa tubular se apoyará en una bancada/soporte anclado a la estructura del muro con ferretería inox 316 (A4) y aislamiento dieléctrico frente a estructuras galvanizadas. El pasamuros se sellará con silicona RTV neutra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15" customHeight="1"/>
-    <row r="151" ht="15" customHeight="1"/>
-    <row r="152" ht="15" customHeight="1"/>
-    <row r="153" ht="150" customHeight="1">
-      <c r="A153" s="87" t="inlineStr">
-        <is>
-          <t>8.4. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1"/>
-    <row r="155" ht="15" customHeight="1"/>
-    <row r="156" ht="15" customHeight="1"/>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" s="86" t="inlineStr">
-        <is>
-          <t>9. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="165" customHeight="1">
-      <c r="A158" s="87" t="inlineStr">
-        <is>
-          <t>9.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="15" customHeight="1"/>
-    <row r="160" ht="15" customHeight="1"/>
-    <row r="161" ht="15" customHeight="1"/>
-    <row r="162" ht="15" customHeight="1"/>
-    <row r="163" ht="15" customHeight="1"/>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" s="86" t="inlineStr">
-        <is>
-          <t>Referencia gráfica</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="15" customHeight="1"/>
-    <row r="167" ht="15" customHeight="1"/>
-    <row r="168" ht="15" customHeight="1"/>
+    <row r="168" ht="165" customHeight="1">
+      <c r="A168" s="87" t="inlineStr">
+        <is>
+          <t>8.1. El ventilador se instalará en muro/pasamuros, con el eje horizontal y a una cota aproximada de 3,0 m sobre el piso terminado del laboratorio. El sentido de flujo es: aspiración del aire exterior a través de la cubierta intemperie y su banco de filtración, descarga directa al interior del recinto.</t>
+        </is>
+      </c>
+    </row>
     <row r="169" ht="15" customHeight="1"/>
     <row r="170" ht="15" customHeight="1"/>
     <row r="171" ht="15" customHeight="1"/>
     <row r="172" ht="15" customHeight="1"/>
-    <row r="173" ht="15" customHeight="1"/>
+    <row r="173" ht="165" customHeight="1">
+      <c r="A173" s="87" t="inlineStr">
+        <is>
+          <t>8.2. El conjunto se soporta mediante una estructura de unión (marco de perfiles ASTM A36 galvanizados) pernada al muro con anclajes inox 316 (A4) y aislamiento dieléctrico frente a estructuras galvanizadas. El vano del muro se sella con silicona RTV neutra para evitar recirculaciones.</t>
+        </is>
+      </c>
+    </row>
     <row r="174" ht="15" customHeight="1"/>
     <row r="175" ht="15" customHeight="1"/>
     <row r="176" ht="15" customHeight="1"/>
     <row r="177" ht="15" customHeight="1"/>
-    <row r="178" ht="15" customHeight="1"/>
+    <row r="178" ht="165" customHeight="1">
+      <c r="A178" s="87" t="inlineStr">
+        <is>
+          <t>8.3. La cubierta intemperie se embrida directamente a la placa mural del ventilador por el lado exterior; aloja el banco de filtración (HD-FILT-001) y protege el conjunto contra lluvia y radiación solar. La altura de 3,0 m exige garantizar el acceso para cambio de filtros e inspección del ventilador (plataforma fija o escalera industrial).</t>
+        </is>
+      </c>
+    </row>
     <row r="179" ht="15" customHeight="1"/>
     <row r="180" ht="15" customHeight="1"/>
     <row r="181" ht="15" customHeight="1"/>
     <row r="182" ht="15" customHeight="1"/>
     <row r="183" ht="15" customHeight="1"/>
-    <row r="184" ht="15" customHeight="1"/>
+    <row r="184" ht="135" customHeight="1">
+      <c r="A184" s="87" t="inlineStr">
+        <is>
+          <t>8.4. La malla de protección interior (jaula) se instala en la descarga del lado interior del muro, desmontable para inspección del impulsor.</t>
+        </is>
+      </c>
+    </row>
     <row r="185" ht="15" customHeight="1"/>
     <row r="186" ht="15" customHeight="1"/>
-    <row r="187" ht="15" customHeight="1"/>
+    <row r="187" ht="150" customHeight="1">
+      <c r="A187" s="87" t="inlineStr">
+        <is>
+          <t>8.5. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
+        </is>
+      </c>
+    </row>
     <row r="188" ht="15" customHeight="1"/>
     <row r="189" ht="15" customHeight="1"/>
     <row r="190" ht="15" customHeight="1"/>
-    <row r="191" ht="15" customHeight="1"/>
-    <row r="192" ht="15" customHeight="1"/>
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="86" t="inlineStr">
+        <is>
+          <t>9. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="150" customHeight="1">
+      <c r="A192" s="87" t="inlineStr">
+        <is>
+          <t>9.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), AMCA 300 (nivel sonoro), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación), SMACNA HVAC Duct Construction Standards (referencia de construcción del montaje).</t>
+        </is>
+      </c>
+    </row>
     <row r="193" ht="15" customHeight="1"/>
     <row r="194" ht="15" customHeight="1"/>
     <row r="195" ht="15" customHeight="1"/>
@@ -5585,159 +5839,224 @@
     <row r="197" ht="15" customHeight="1"/>
     <row r="198" ht="15" customHeight="1"/>
     <row r="199" ht="15" customHeight="1"/>
-    <row r="200" ht="15" customHeight="1"/>
-    <row r="201" ht="15" customHeight="1"/>
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" s="86" t="inlineStr">
+        <is>
+          <t>Referencia gráfica</t>
+        </is>
+      </c>
+    </row>
     <row r="202" ht="15" customHeight="1"/>
     <row r="203" ht="15" customHeight="1"/>
     <row r="204" ht="15" customHeight="1"/>
     <row r="205" ht="15" customHeight="1"/>
     <row r="206" ht="15" customHeight="1"/>
     <row r="207" ht="15" customHeight="1"/>
+    <row r="208" ht="15" customHeight="1"/>
+    <row r="209" ht="15" customHeight="1"/>
+    <row r="210" ht="15" customHeight="1"/>
+    <row r="211" ht="15" customHeight="1"/>
+    <row r="212" ht="15" customHeight="1"/>
+    <row r="213" ht="15" customHeight="1"/>
+    <row r="214" ht="15" customHeight="1"/>
+    <row r="215" ht="15" customHeight="1"/>
+    <row r="216" ht="15" customHeight="1"/>
+    <row r="217" ht="15" customHeight="1"/>
+    <row r="218" ht="15" customHeight="1"/>
+    <row r="219" ht="15" customHeight="1"/>
+    <row r="220" ht="15" customHeight="1"/>
+    <row r="221" ht="15" customHeight="1"/>
+    <row r="222" ht="15" customHeight="1"/>
+    <row r="223" ht="15" customHeight="1"/>
+    <row r="224" ht="15" customHeight="1"/>
+    <row r="225" ht="15" customHeight="1"/>
+    <row r="226" ht="15" customHeight="1"/>
+    <row r="227" ht="15" customHeight="1"/>
+    <row r="228" ht="15" customHeight="1"/>
+    <row r="229" ht="15" customHeight="1"/>
+    <row r="230" ht="15" customHeight="1"/>
+    <row r="231" ht="15" customHeight="1"/>
+    <row r="232" ht="15" customHeight="1"/>
+    <row r="233" ht="15" customHeight="1"/>
+    <row r="234" ht="15" customHeight="1"/>
+    <row r="235" ht="15" customHeight="1"/>
+    <row r="236" ht="15" customHeight="1"/>
+    <row r="237" ht="15" customHeight="1"/>
+    <row r="238" ht="15" customHeight="1"/>
+    <row r="239" ht="15" customHeight="1"/>
+    <row r="240" ht="15" customHeight="1"/>
+    <row r="241" ht="15" customHeight="1"/>
+    <row r="242" ht="15" customHeight="1"/>
+    <row r="243" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="143">
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="I83:O83"/>
-    <mergeCell ref="A64:O72"/>
-    <mergeCell ref="A125:O126"/>
-    <mergeCell ref="F54:J54"/>
-    <mergeCell ref="I44:O44"/>
-    <mergeCell ref="A141:O144"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="K54:O54"/>
-    <mergeCell ref="K55:O55"/>
+  <mergeCells count="167">
+    <mergeCell ref="A192:O199"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="I52:O52"/>
+    <mergeCell ref="A159:D159"/>
+    <mergeCell ref="A73:O81"/>
+    <mergeCell ref="A82:O90"/>
+    <mergeCell ref="F146:J146"/>
+    <mergeCell ref="A62:O63"/>
+    <mergeCell ref="A114:O122"/>
+    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A161:D161"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="I94:O94"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="M164:O164"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="A48:O49"/>
-    <mergeCell ref="I77:O77"/>
-    <mergeCell ref="A119:O120"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A39:O42"/>
+    <mergeCell ref="K144:O144"/>
+    <mergeCell ref="A151:O153"/>
+    <mergeCell ref="A133:H133"/>
+    <mergeCell ref="I133:O133"/>
+    <mergeCell ref="I164:L164"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="I80:O80"/>
-    <mergeCell ref="I136:L136"/>
-    <mergeCell ref="A30:O33"/>
-    <mergeCell ref="I103:O103"/>
-    <mergeCell ref="I41:O41"/>
+    <mergeCell ref="F66:J66"/>
+    <mergeCell ref="A200:O200"/>
+    <mergeCell ref="A184:O186"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="K71:O71"/>
+    <mergeCell ref="I57:O57"/>
+    <mergeCell ref="A135:O139"/>
+    <mergeCell ref="K145:O145"/>
+    <mergeCell ref="I54:O54"/>
+    <mergeCell ref="A164:D164"/>
     <mergeCell ref="A97:H97"/>
     <mergeCell ref="I97:O97"/>
-    <mergeCell ref="E137:H137"/>
-    <mergeCell ref="A158:O163"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="K147:O147"/>
+    <mergeCell ref="I96:O96"/>
+    <mergeCell ref="I56:O56"/>
     <mergeCell ref="A96:H96"/>
-    <mergeCell ref="I96:O96"/>
-    <mergeCell ref="I43:O43"/>
-    <mergeCell ref="M132:O132"/>
+    <mergeCell ref="I127:O127"/>
+    <mergeCell ref="A163:D163"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A145:O148"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="K66:O66"/>
+    <mergeCell ref="K146:O146"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A124:O124"/>
     <mergeCell ref="I98:O98"/>
-    <mergeCell ref="A153:O155"/>
+    <mergeCell ref="F64:J64"/>
+    <mergeCell ref="E163:H163"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A187:O189"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I132:L132"/>
-    <mergeCell ref="A135:D135"/>
-    <mergeCell ref="A121:O122"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="I82:O82"/>
-    <mergeCell ref="E136:H136"/>
+    <mergeCell ref="K68:O68"/>
+    <mergeCell ref="F65:J65"/>
+    <mergeCell ref="F147:J147"/>
     <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="I99:O99"/>
-    <mergeCell ref="F51:J51"/>
+    <mergeCell ref="M160:O160"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A47:O47"/>
-    <mergeCell ref="M136:O136"/>
-    <mergeCell ref="I133:L133"/>
-    <mergeCell ref="A116:O118"/>
-    <mergeCell ref="F50:J50"/>
-    <mergeCell ref="A17:O19"/>
+    <mergeCell ref="A141:O141"/>
+    <mergeCell ref="A31:O38"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="I160:L160"/>
     <mergeCell ref="A101:H101"/>
-    <mergeCell ref="M134:O134"/>
-    <mergeCell ref="A36:O37"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="I134:L134"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="I102:O102"/>
-    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A50:O51"/>
+    <mergeCell ref="A162:D162"/>
+    <mergeCell ref="I126:O126"/>
+    <mergeCell ref="M162:O162"/>
+    <mergeCell ref="K70:O70"/>
+    <mergeCell ref="A167:O167"/>
+    <mergeCell ref="A126:H126"/>
+    <mergeCell ref="F149:J149"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A17:O25"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="I162:L162"/>
+    <mergeCell ref="A191:O191"/>
     <mergeCell ref="N6:O6"/>
+    <mergeCell ref="K65:O65"/>
+    <mergeCell ref="A61:O61"/>
+    <mergeCell ref="A67:E67"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A85:O92"/>
-    <mergeCell ref="I79:O79"/>
+    <mergeCell ref="A127:H127"/>
+    <mergeCell ref="F69:J69"/>
     <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A164:O164"/>
-    <mergeCell ref="A74:O74"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="M133:O133"/>
-    <mergeCell ref="F55:J55"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="M135:O135"/>
-    <mergeCell ref="A105:O109"/>
-    <mergeCell ref="A140:O140"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="A168:O172"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="I128:O128"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A103:O113"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="F145:J145"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="E160:H160"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="K149:O149"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="M159:O159"/>
+    <mergeCell ref="A156:O158"/>
     <mergeCell ref="I101:O101"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="I76:O76"/>
-    <mergeCell ref="A111:O111"/>
-    <mergeCell ref="A57:O63"/>
+    <mergeCell ref="A129:H129"/>
     <mergeCell ref="I100:O100"/>
+    <mergeCell ref="F71:J71"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A133:D133"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A149:O152"/>
-    <mergeCell ref="F52:J52"/>
+    <mergeCell ref="E161:H161"/>
+    <mergeCell ref="A92:O92"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="I159:L159"/>
+    <mergeCell ref="A43:O47"/>
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="F67:J67"/>
     <mergeCell ref="A100:H100"/>
+    <mergeCell ref="M161:O161"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="I53:O53"/>
+    <mergeCell ref="A178:O183"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A94:O94"/>
+    <mergeCell ref="I130:O130"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="F53:J53"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="I161:L161"/>
+    <mergeCell ref="A173:O177"/>
+    <mergeCell ref="I55:O55"/>
+    <mergeCell ref="F148:J148"/>
+    <mergeCell ref="I132:O132"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I39:O39"/>
-    <mergeCell ref="M137:O137"/>
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A112:O115"/>
+    <mergeCell ref="E162:H162"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="F68:J68"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="I38:O38"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="I78:O78"/>
-    <mergeCell ref="E134:H134"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="A142:O143"/>
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="E164:H164"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="I137:L137"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="I40:O40"/>
-    <mergeCell ref="A129:O131"/>
-    <mergeCell ref="A22:O29"/>
+    <mergeCell ref="M163:O163"/>
     <mergeCell ref="I15:O15"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="I81:O81"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A123:O124"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="I95:O95"/>
+    <mergeCell ref="A26:O28"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="F70:J70"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="K52:O52"/>
+    <mergeCell ref="F144:J144"/>
+    <mergeCell ref="I163:L163"/>
+    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A155:O155"/>
+    <mergeCell ref="I129:O129"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A157:O157"/>
-    <mergeCell ref="K53:O53"/>
+    <mergeCell ref="K148:O148"/>
+    <mergeCell ref="I131:O131"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="E133:H133"/>
-    <mergeCell ref="I42:O42"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="K69:O69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,35 +135,23 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00375623"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
       <color rgb="00404040"/>
-      <sz val="10"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -243,8 +231,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +389,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -519,12 +507,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,77 +525,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -865,7 +850,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>201</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -890,7 +875,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>222</row>
+      <row>130</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -3774,37 +3759,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -3813,9 +3794,7 @@
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
@@ -3829,16 +3808,15 @@
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
-    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
     <col width="13" customWidth="1" min="61" max="61"/>
     <col width="13" customWidth="1" min="62" max="62"/>
     <col width="13" customWidth="1" min="63" max="63"/>
     <col width="13" customWidth="1" min="64" max="64"/>
-    <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
     <col width="13" customWidth="1" min="68" max="68"/>
@@ -3846,7 +3824,6 @@
     <col width="13" customWidth="1" min="70" max="70"/>
     <col width="13" customWidth="1" min="71" max="71"/>
     <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="74" max="74"/>
     <col width="13" customWidth="1" min="75" max="75"/>
     <col width="13" customWidth="1" min="76" max="76"/>
     <col width="13" customWidth="1" min="77" max="77"/>
@@ -3855,27 +3832,22 @@
     <col width="13" customWidth="1" min="80" max="80"/>
     <col width="13" customWidth="1" min="81" max="81"/>
     <col width="13" customWidth="1" min="82" max="82"/>
-    <col width="13" customWidth="1" min="83" max="83"/>
     <col width="13" customWidth="1" min="84" max="84"/>
     <col width="13" customWidth="1" min="85" max="85"/>
-    <col width="13" customWidth="1" min="86" max="86"/>
     <col width="13" customWidth="1" min="87" max="87"/>
-    <col width="13" customWidth="1" min="88" max="88"/>
     <col width="13" customWidth="1" min="89" max="89"/>
     <col width="13" customWidth="1" min="90" max="90"/>
+    <col width="13" customWidth="1" min="91" max="91"/>
     <col width="13" customWidth="1" min="92" max="92"/>
+    <col width="13" customWidth="1" min="93" max="93"/>
     <col width="13" customWidth="1" min="94" max="94"/>
-    <col width="13" customWidth="1" min="95" max="95"/>
-    <col width="13" customWidth="1" min="96" max="96"/>
-    <col width="13" customWidth="1" min="97" max="97"/>
     <col width="13" customWidth="1" min="98" max="98"/>
-    <col width="13" customWidth="1" min="99" max="99"/>
     <col width="13" customWidth="1" min="100" max="100"/>
     <col width="13" customWidth="1" min="101" max="101"/>
+    <col width="13" customWidth="1" min="102" max="102"/>
     <col width="13" customWidth="1" min="103" max="103"/>
     <col width="13" customWidth="1" min="104" max="104"/>
     <col width="13" customWidth="1" min="105" max="105"/>
-    <col width="13" customWidth="1" min="106" max="106"/>
     <col width="13" customWidth="1" min="107" max="107"/>
     <col width="13" customWidth="1" min="108" max="108"/>
     <col width="13" customWidth="1" min="109" max="109"/>
@@ -3883,84 +3855,10 @@
     <col width="13" customWidth="1" min="111" max="111"/>
     <col width="13" customWidth="1" min="112" max="112"/>
     <col width="13" customWidth="1" min="113" max="113"/>
-    <col width="13" customWidth="1" min="114" max="114"/>
-    <col width="13" customWidth="1" min="115" max="115"/>
-    <col width="13" customWidth="1" min="116" max="116"/>
     <col width="13" customWidth="1" min="117" max="117"/>
     <col width="13" customWidth="1" min="118" max="118"/>
     <col width="13" customWidth="1" min="119" max="119"/>
     <col width="13" customWidth="1" min="120" max="120"/>
-    <col width="13" customWidth="1" min="121" max="121"/>
-    <col width="13" customWidth="1" min="122" max="122"/>
-    <col width="13" customWidth="1" min="124" max="124"/>
-    <col width="13" customWidth="1" min="126" max="126"/>
-    <col width="13" customWidth="1" min="127" max="127"/>
-    <col width="13" customWidth="1" min="128" max="128"/>
-    <col width="13" customWidth="1" min="129" max="129"/>
-    <col width="13" customWidth="1" min="130" max="130"/>
-    <col width="13" customWidth="1" min="131" max="131"/>
-    <col width="13" customWidth="1" min="132" max="132"/>
-    <col width="13" customWidth="1" min="133" max="133"/>
-    <col width="13" customWidth="1" min="135" max="135"/>
-    <col width="13" customWidth="1" min="136" max="136"/>
-    <col width="13" customWidth="1" min="137" max="137"/>
-    <col width="13" customWidth="1" min="138" max="138"/>
-    <col width="13" customWidth="1" min="139" max="139"/>
-    <col width="13" customWidth="1" min="141" max="141"/>
-    <col width="13" customWidth="1" min="142" max="142"/>
-    <col width="13" customWidth="1" min="143" max="143"/>
-    <col width="13" customWidth="1" min="144" max="144"/>
-    <col width="13" customWidth="1" min="145" max="145"/>
-    <col width="13" customWidth="1" min="146" max="146"/>
-    <col width="13" customWidth="1" min="147" max="147"/>
-    <col width="13" customWidth="1" min="148" max="148"/>
-    <col width="13" customWidth="1" min="149" max="149"/>
-    <col width="13" customWidth="1" min="151" max="151"/>
-    <col width="13" customWidth="1" min="152" max="152"/>
-    <col width="13" customWidth="1" min="153" max="153"/>
-    <col width="13" customWidth="1" min="155" max="155"/>
-    <col width="13" customWidth="1" min="156" max="156"/>
-    <col width="13" customWidth="1" min="157" max="157"/>
-    <col width="13" customWidth="1" min="158" max="158"/>
-    <col width="13" customWidth="1" min="159" max="159"/>
-    <col width="13" customWidth="1" min="160" max="160"/>
-    <col width="13" customWidth="1" min="161" max="161"/>
-    <col width="13" customWidth="1" min="162" max="162"/>
-    <col width="13" customWidth="1" min="163" max="163"/>
-    <col width="13" customWidth="1" min="164" max="164"/>
-    <col width="13" customWidth="1" min="167" max="167"/>
-    <col width="13" customWidth="1" min="168" max="168"/>
-    <col width="13" customWidth="1" min="169" max="169"/>
-    <col width="13" customWidth="1" min="170" max="170"/>
-    <col width="13" customWidth="1" min="171" max="171"/>
-    <col width="13" customWidth="1" min="172" max="172"/>
-    <col width="13" customWidth="1" min="173" max="173"/>
-    <col width="13" customWidth="1" min="174" max="174"/>
-    <col width="13" customWidth="1" min="175" max="175"/>
-    <col width="13" customWidth="1" min="176" max="176"/>
-    <col width="13" customWidth="1" min="177" max="177"/>
-    <col width="13" customWidth="1" min="178" max="178"/>
-    <col width="13" customWidth="1" min="179" max="179"/>
-    <col width="13" customWidth="1" min="180" max="180"/>
-    <col width="13" customWidth="1" min="181" max="181"/>
-    <col width="13" customWidth="1" min="182" max="182"/>
-    <col width="13" customWidth="1" min="183" max="183"/>
-    <col width="13" customWidth="1" min="184" max="184"/>
-    <col width="13" customWidth="1" min="185" max="185"/>
-    <col width="13" customWidth="1" min="186" max="186"/>
-    <col width="13" customWidth="1" min="187" max="187"/>
-    <col width="13" customWidth="1" min="188" max="188"/>
-    <col width="13" customWidth="1" min="189" max="189"/>
-    <col width="13" customWidth="1" min="191" max="191"/>
-    <col width="13" customWidth="1" min="192" max="192"/>
-    <col width="13" customWidth="1" min="193" max="193"/>
-    <col width="13" customWidth="1" min="194" max="194"/>
-    <col width="13" customWidth="1" min="195" max="195"/>
-    <col width="13" customWidth="1" min="196" max="196"/>
-    <col width="13" customWidth="1" min="197" max="197"/>
-    <col width="13" customWidth="1" min="198" max="198"/>
-    <col width="13" customWidth="1" min="199" max="199"/>
-    <col width="13" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4170,14 +4068,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="300" customHeight="1">
+    <row r="9" ht="190" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: ventilador axial mural de inyección</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4202,7 +4100,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4227,7 +4125,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4252,7 +4150,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="38" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4277,7 +4175,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="240" customHeight="1">
+    <row r="14" ht="152" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4302,7 +4200,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="165" customHeight="1">
+    <row r="15" ht="114" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4327,244 +4225,552 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="165" customHeight="1">
+    <row r="16" ht="38" customHeight="1"/>
+    <row r="17" ht="684" customHeight="1">
       <c r="A17" s="85" t="inlineStr">
         <is>
           <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png y Montaje/Descripcion_Tecnica_Sistema_Ventilacion_Inyeccion_2260CFM_v2.md): ventilador axial mural (placa mural) Ø560 mm, transmisión directa, con cubierta intemperie que aloja el banco de filtración, estructura de unión pernada al muro y malla de protección interior. Se conservan caudal, ΔP de diseño, filtración MERV 8 + MERV 13-14, rejillas y ausencia de presurización.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1"/>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
-    <row r="26" ht="165" customHeight="1">
-      <c r="A26" s="85" t="inlineStr">
+    <row r="18" ht="38" customHeight="1"/>
+    <row r="19" ht="152" customHeight="1">
+      <c r="A19" s="85" t="inlineStr">
         <is>
           <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial en lugar de centrífugo, sin instrumentación de presión diferencial.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="86" t="inlineStr">
+    <row r="20" ht="38" customHeight="1"/>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="165" customHeight="1">
-      <c r="A31" s="87" t="inlineStr">
+    <row r="22" ht="646" customHeight="1">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>1.1. Impulsión de aire exterior filtrado (MERV 8 + MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="150" customHeight="1">
+    <row r="23" ht="38" customHeight="1"/>
+    <row r="24" ht="152" customHeight="1">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="380" customHeight="1">
+      <c r="A25" s="86" t="inlineStr">
+        <is>
+          <t>1.3. Configuración de montaje uniforme con la planta (secuencia de flujo): exterior → cubierta intemperie (aloja prefiltro MERV 8 y filtro final MERV 13-14) → ventilador axial mural → paso por muro con estructura de unión → malla de protección interior → descarga al recinto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1"/>
+    <row r="27" ht="38" customHeight="1"/>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>2. Condiciones de sitio</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="87" t="inlineStr">
+        <is>
+          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="82" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="n"/>
+      <c r="C30" s="82" t="n"/>
+      <c r="D30" s="82" t="n"/>
+      <c r="E30" s="82" t="n"/>
+      <c r="F30" s="82" t="n"/>
+      <c r="G30" s="82" t="n"/>
+      <c r="H30" s="82" t="n"/>
+      <c r="I30" s="82" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J30" s="82" t="n"/>
+      <c r="K30" s="82" t="n"/>
+      <c r="L30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
+      <c r="N30" s="82" t="n"/>
+      <c r="O30" s="82" t="n"/>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="83" t="inlineStr">
+        <is>
+          <t>Altitud</t>
+        </is>
+      </c>
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="84" t="n"/>
+      <c r="F31" s="84" t="n"/>
+      <c r="G31" s="84" t="n"/>
+      <c r="H31" s="84" t="n"/>
+      <c r="I31" s="83" t="inlineStr">
+        <is>
+          <t>2 558 msnm</t>
+        </is>
+      </c>
+      <c r="J31" s="84" t="n"/>
+      <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
+      <c r="O31" s="84" t="n"/>
+    </row>
+    <row r="32" ht="76" customHeight="1">
+      <c r="A32" s="83" t="inlineStr">
+        <is>
+          <t>Presión atmosférica</t>
+        </is>
+      </c>
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="84" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="84" t="n"/>
+      <c r="F32" s="84" t="n"/>
+      <c r="G32" s="84" t="n"/>
+      <c r="H32" s="84" t="n"/>
+      <c r="I32" s="83" t="inlineStr">
+        <is>
+          <t>74.1 kPa</t>
+        </is>
+      </c>
+      <c r="J32" s="84" t="n"/>
+      <c r="K32" s="84" t="n"/>
+      <c r="L32" s="84" t="n"/>
+      <c r="M32" s="84" t="n"/>
+      <c r="N32" s="84" t="n"/>
+      <c r="O32" s="84" t="n"/>
+    </row>
+    <row r="33" ht="152" customHeight="1">
+      <c r="A33" s="83" t="inlineStr">
+        <is>
+          <t>Temperatura de diseño verano / invierno / media</t>
+        </is>
+      </c>
+      <c r="B33" s="84" t="n"/>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="84" t="n"/>
+      <c r="F33" s="84" t="n"/>
+      <c r="G33" s="84" t="n"/>
+      <c r="H33" s="84" t="n"/>
+      <c r="I33" s="83" t="inlineStr">
+        <is>
+          <t>21 °C / 3 °C / 14 °C</t>
+        </is>
+      </c>
+      <c r="J33" s="84" t="n"/>
+      <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
+      <c r="O33" s="84" t="n"/>
+    </row>
+    <row r="34" ht="76" customHeight="1">
+      <c r="A34" s="83" t="inlineStr">
+        <is>
+          <t>Humedad relativa media anual</t>
+        </is>
+      </c>
+      <c r="B34" s="84" t="n"/>
+      <c r="C34" s="84" t="n"/>
+      <c r="D34" s="84" t="n"/>
+      <c r="E34" s="84" t="n"/>
+      <c r="F34" s="84" t="n"/>
+      <c r="G34" s="84" t="n"/>
+      <c r="H34" s="84" t="n"/>
+      <c r="I34" s="83" t="inlineStr">
+        <is>
+          <t>84 %</t>
+        </is>
+      </c>
+      <c r="J34" s="84" t="n"/>
+      <c r="K34" s="84" t="n"/>
+      <c r="L34" s="84" t="n"/>
+      <c r="M34" s="84" t="n"/>
+      <c r="N34" s="84" t="n"/>
+      <c r="O34" s="84" t="n"/>
+    </row>
+    <row r="35" ht="152" customHeight="1">
+      <c r="A35" s="83" t="inlineStr">
+        <is>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B35" s="84" t="n"/>
+      <c r="C35" s="84" t="n"/>
+      <c r="D35" s="84" t="n"/>
+      <c r="E35" s="84" t="n"/>
+      <c r="F35" s="84" t="n"/>
+      <c r="G35" s="84" t="n"/>
+      <c r="H35" s="84" t="n"/>
+      <c r="I35" s="83" t="inlineStr">
+        <is>
+          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+        </is>
+      </c>
+      <c r="J35" s="84" t="n"/>
+      <c r="K35" s="84" t="n"/>
+      <c r="L35" s="84" t="n"/>
+      <c r="M35" s="84" t="n"/>
+      <c r="N35" s="84" t="n"/>
+      <c r="O35" s="84" t="n"/>
+    </row>
+    <row r="36" ht="152" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
+        <is>
+          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="83" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+    </row>
+    <row r="37" ht="38" customHeight="1"/>
+    <row r="38" ht="76" customHeight="1">
+      <c r="A38" s="81" t="inlineStr">
+        <is>
+          <t>3. Punto de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="76" customHeight="1">
       <c r="A39" s="87" t="inlineStr">
         <is>
-          <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
-        <is>
-          <t>1.3. Configuración de montaje uniforme con la planta (secuencia de flujo): exterior → cubierta intemperie (aloja prefiltro MERV 8 y filtro final MERV 13-14) → ventilador axial mural → paso por muro con estructura de unión → malla de protección interior → descarga al recinto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1"/>
-    <row r="45" ht="15" customHeight="1"/>
-    <row r="46" ht="15" customHeight="1"/>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1"/>
-    <row r="49" ht="75" customHeight="1">
+          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="114" customHeight="1">
+      <c r="A40" s="82" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B40" s="82" t="n"/>
+      <c r="C40" s="82" t="n"/>
+      <c r="D40" s="82" t="n"/>
+      <c r="E40" s="82" t="n"/>
+      <c r="F40" s="82" t="inlineStr">
+        <is>
+          <t>En el sitio (ρ = 0.88 kg/m³)</t>
+        </is>
+      </c>
+      <c r="G40" s="82" t="n"/>
+      <c r="H40" s="82" t="n"/>
+      <c r="I40" s="82" t="n"/>
+      <c r="J40" s="82" t="n"/>
+      <c r="K40" s="82" t="inlineStr">
+        <is>
+          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="L40" s="82" t="n"/>
+      <c r="M40" s="82" t="n"/>
+      <c r="N40" s="82" t="n"/>
+      <c r="O40" s="82" t="n"/>
+    </row>
+    <row r="41" ht="152" customHeight="1">
+      <c r="A41" s="83" t="inlineStr">
+        <is>
+          <t>Caudal</t>
+        </is>
+      </c>
+      <c r="B41" s="84" t="n"/>
+      <c r="C41" s="84" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="83" t="inlineStr">
+        <is>
+          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
+        </is>
+      </c>
+      <c r="G41" s="84" t="n"/>
+      <c r="H41" s="84" t="n"/>
+      <c r="I41" s="84" t="n"/>
+      <c r="J41" s="84" t="n"/>
+      <c r="K41" s="83" t="inlineStr">
+        <is>
+          <t>Sin cambio (máquina de volumen constante)</t>
+        </is>
+      </c>
+      <c r="L41" s="84" t="n"/>
+      <c r="M41" s="84" t="n"/>
+      <c r="N41" s="84" t="n"/>
+      <c r="O41" s="84" t="n"/>
+    </row>
+    <row r="42" ht="152" customHeight="1">
+      <c r="A42" s="83" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario de diseño (filtro cargado)</t>
+        </is>
+      </c>
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="84" t="n"/>
+      <c r="D42" s="84" t="n"/>
+      <c r="E42" s="84" t="n"/>
+      <c r="F42" s="83" t="inlineStr">
+        <is>
+          <t>165 Pa</t>
+        </is>
+      </c>
+      <c r="G42" s="84" t="n"/>
+      <c r="H42" s="84" t="n"/>
+      <c r="I42" s="84" t="n"/>
+      <c r="J42" s="84" t="n"/>
+      <c r="K42" s="83" t="inlineStr">
+        <is>
+          <t>225 Pa</t>
+        </is>
+      </c>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+    </row>
+    <row r="43" ht="114" customHeight="1">
+      <c r="A43" s="83" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario filtro limpio</t>
+        </is>
+      </c>
+      <c r="B43" s="84" t="n"/>
+      <c r="C43" s="84" t="n"/>
+      <c r="D43" s="84" t="n"/>
+      <c r="E43" s="84" t="n"/>
+      <c r="F43" s="83" t="inlineStr">
+        <is>
+          <t>70 Pa</t>
+        </is>
+      </c>
+      <c r="G43" s="84" t="n"/>
+      <c r="H43" s="84" t="n"/>
+      <c r="I43" s="84" t="n"/>
+      <c r="J43" s="84" t="n"/>
+      <c r="K43" s="83" t="inlineStr">
+        <is>
+          <t>95 Pa</t>
+        </is>
+      </c>
+      <c r="L43" s="84" t="n"/>
+      <c r="M43" s="84" t="n"/>
+      <c r="N43" s="84" t="n"/>
+      <c r="O43" s="84" t="n"/>
+    </row>
+    <row r="44" ht="114" customHeight="1">
+      <c r="A44" s="83" t="inlineStr">
+        <is>
+          <t>Composición ΔP diseño</t>
+        </is>
+      </c>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="84" t="n"/>
+      <c r="D44" s="84" t="n"/>
+      <c r="E44" s="84" t="n"/>
+      <c r="F44" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 154 Pa + rejillas 11 Pa</t>
+        </is>
+      </c>
+      <c r="G44" s="84" t="n"/>
+      <c r="H44" s="84" t="n"/>
+      <c r="I44" s="84" t="n"/>
+      <c r="J44" s="84" t="n"/>
+      <c r="K44" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 210 Pa + 15 Pa</t>
+        </is>
+      </c>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+    </row>
+    <row r="45" ht="114" customHeight="1">
+      <c r="A45" s="83" t="inlineStr">
+        <is>
+          <t>Diámetro del impulsor (uniformidad planta)</t>
+        </is>
+      </c>
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="84" t="n"/>
+      <c r="D45" s="84" t="n"/>
+      <c r="E45" s="84" t="n"/>
+      <c r="F45" s="83" t="inlineStr">
+        <is>
+          <t>560 mm (22 in)</t>
+        </is>
+      </c>
+      <c r="G45" s="84" t="n"/>
+      <c r="H45" s="84" t="n"/>
+      <c r="I45" s="84" t="n"/>
+      <c r="J45" s="84" t="n"/>
+      <c r="K45" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="84" t="n"/>
+      <c r="M45" s="84" t="n"/>
+      <c r="N45" s="84" t="n"/>
+      <c r="O45" s="84" t="n"/>
+    </row>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="83" t="inlineStr">
+        <is>
+          <t>Velocidad en boca (Ø560 mm)</t>
+        </is>
+      </c>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="84" t="n"/>
+      <c r="D46" s="84" t="n"/>
+      <c r="E46" s="84" t="n"/>
+      <c r="F46" s="83" t="inlineStr">
+        <is>
+          <t>4.33 m/s</t>
+        </is>
+      </c>
+      <c r="G46" s="84" t="n"/>
+      <c r="H46" s="84" t="n"/>
+      <c r="I46" s="84" t="n"/>
+      <c r="J46" s="84" t="n"/>
+      <c r="K46" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+    </row>
+    <row r="47" ht="114" customHeight="1">
+      <c r="A47" s="83" t="inlineStr">
+        <is>
+          <t>Potencia teórica de aire (η = 0.55)</t>
+        </is>
+      </c>
+      <c r="B47" s="84" t="n"/>
+      <c r="C47" s="84" t="n"/>
+      <c r="D47" s="84" t="n"/>
+      <c r="E47" s="84" t="n"/>
+      <c r="F47" s="83" t="inlineStr">
+        <is>
+          <t>0.320 kW = 0.43 HP</t>
+        </is>
+      </c>
+      <c r="G47" s="84" t="n"/>
+      <c r="H47" s="84" t="n"/>
+      <c r="I47" s="84" t="n"/>
+      <c r="J47" s="84" t="n"/>
+      <c r="K47" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="84" t="n"/>
+      <c r="M47" s="84" t="n"/>
+      <c r="N47" s="84" t="n"/>
+      <c r="O47" s="84" t="n"/>
+    </row>
+    <row r="48" ht="38" customHeight="1"/>
+    <row r="49" ht="684" customHeight="1">
       <c r="A49" s="86" t="inlineStr">
         <is>
-          <t>2. Condiciones de sitio</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="150" customHeight="1">
-      <c r="A50" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1"/>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="82" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B52" s="82" t="n"/>
-      <c r="C52" s="82" t="n"/>
-      <c r="D52" s="82" t="n"/>
-      <c r="E52" s="82" t="n"/>
-      <c r="F52" s="82" t="n"/>
-      <c r="G52" s="82" t="n"/>
-      <c r="H52" s="82" t="n"/>
-      <c r="I52" s="82" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="J52" s="82" t="n"/>
-      <c r="K52" s="82" t="n"/>
-      <c r="L52" s="82" t="n"/>
-      <c r="M52" s="82" t="n"/>
-      <c r="N52" s="82" t="n"/>
-      <c r="O52" s="82" t="n"/>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="83" t="inlineStr">
-        <is>
-          <t>Altitud</t>
-        </is>
-      </c>
-      <c r="B53" s="84" t="n"/>
-      <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
-      <c r="E53" s="84" t="n"/>
-      <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
-      <c r="H53" s="84" t="n"/>
-      <c r="I53" s="83" t="inlineStr">
-        <is>
-          <t>2 558 msnm</t>
-        </is>
-      </c>
-      <c r="J53" s="84" t="n"/>
-      <c r="K53" s="84" t="n"/>
-      <c r="L53" s="84" t="n"/>
-      <c r="M53" s="84" t="n"/>
-      <c r="N53" s="84" t="n"/>
-      <c r="O53" s="84" t="n"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="83" t="inlineStr">
-        <is>
-          <t>Presión atmosférica</t>
-        </is>
-      </c>
-      <c r="B54" s="84" t="n"/>
-      <c r="C54" s="84" t="n"/>
-      <c r="D54" s="84" t="n"/>
-      <c r="E54" s="84" t="n"/>
-      <c r="F54" s="84" t="n"/>
-      <c r="G54" s="84" t="n"/>
-      <c r="H54" s="84" t="n"/>
-      <c r="I54" s="83" t="inlineStr">
-        <is>
-          <t>74.1 kPa</t>
-        </is>
-      </c>
-      <c r="J54" s="84" t="n"/>
-      <c r="K54" s="84" t="n"/>
-      <c r="L54" s="84" t="n"/>
-      <c r="M54" s="84" t="n"/>
-      <c r="N54" s="84" t="n"/>
-      <c r="O54" s="84" t="n"/>
-    </row>
-    <row r="55" ht="135" customHeight="1">
-      <c r="A55" s="83" t="inlineStr">
-        <is>
-          <t>Temperatura de diseño verano / invierno / media</t>
-        </is>
-      </c>
-      <c r="B55" s="84" t="n"/>
-      <c r="C55" s="84" t="n"/>
-      <c r="D55" s="84" t="n"/>
-      <c r="E55" s="84" t="n"/>
-      <c r="F55" s="84" t="n"/>
-      <c r="G55" s="84" t="n"/>
-      <c r="H55" s="84" t="n"/>
-      <c r="I55" s="83" t="inlineStr">
-        <is>
-          <t>21 °C / 3 °C / 14 °C</t>
-        </is>
-      </c>
-      <c r="J55" s="84" t="n"/>
-      <c r="K55" s="84" t="n"/>
-      <c r="L55" s="84" t="n"/>
-      <c r="M55" s="84" t="n"/>
-      <c r="N55" s="84" t="n"/>
-      <c r="O55" s="84" t="n"/>
-    </row>
-    <row r="56" ht="75" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>Humedad relativa media anual</t>
-        </is>
-      </c>
-      <c r="B56" s="84" t="n"/>
-      <c r="C56" s="84" t="n"/>
-      <c r="D56" s="84" t="n"/>
-      <c r="E56" s="84" t="n"/>
-      <c r="F56" s="84" t="n"/>
-      <c r="G56" s="84" t="n"/>
-      <c r="H56" s="84" t="n"/>
-      <c r="I56" s="83" t="inlineStr">
-        <is>
-          <t>84 %</t>
-        </is>
-      </c>
-      <c r="J56" s="84" t="n"/>
-      <c r="K56" s="84" t="n"/>
-      <c r="L56" s="84" t="n"/>
-      <c r="M56" s="84" t="n"/>
-      <c r="N56" s="84" t="n"/>
-      <c r="O56" s="84" t="n"/>
-    </row>
-    <row r="57" ht="135" customHeight="1">
-      <c r="A57" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B57" s="84" t="n"/>
-      <c r="C57" s="84" t="n"/>
-      <c r="D57" s="84" t="n"/>
-      <c r="E57" s="84" t="n"/>
-      <c r="F57" s="84" t="n"/>
-      <c r="G57" s="84" t="n"/>
-      <c r="H57" s="84" t="n"/>
-      <c r="I57" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
-        </is>
-      </c>
-      <c r="J57" s="84" t="n"/>
-      <c r="K57" s="84" t="n"/>
-      <c r="L57" s="84" t="n"/>
-      <c r="M57" s="84" t="n"/>
-      <c r="N57" s="84" t="n"/>
-      <c r="O57" s="84" t="n"/>
-    </row>
-    <row r="58" ht="120" customHeight="1">
+          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). El tamaño comercial queda fijado en Ø560 mm por uniformidad con el montaje típico instalado en la planta; las RPM exactas se confirman con el software de selección del fabricante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1"/>
+    <row r="51" ht="494" customHeight="1">
+      <c r="A51" s="86" t="inlineStr">
+        <is>
+          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; la eficiencia mínima exigible es 0.55 (dato provisional, a verificar contra la curva de la selección final). El margen sobre la potencia de eje (motor provisional 0.75 HP vs. 0.43 HP teóricos, con margen de servicio 1.5) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio; la potencia final del motor se confirma con la curva de catálogo de la selección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1"/>
+    <row r="53" ht="38" customHeight="1"/>
+    <row r="54" ht="38" customHeight="1"/>
+    <row r="55" ht="114" customHeight="1">
+      <c r="A55" s="81" t="inlineStr">
+        <is>
+          <t>4. Tipo y materiales de construcción</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="38" customHeight="1">
+      <c r="A56" s="87" t="inlineStr">
+        <is>
+          <t>Tabla 3. Requisitos de construcción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="38" customHeight="1">
+      <c r="A57" s="82" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B57" s="82" t="n"/>
+      <c r="C57" s="82" t="n"/>
+      <c r="D57" s="82" t="n"/>
+      <c r="E57" s="82" t="n"/>
+      <c r="F57" s="82" t="n"/>
+      <c r="G57" s="82" t="n"/>
+      <c r="H57" s="82" t="n"/>
+      <c r="I57" s="82" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J57" s="82" t="n"/>
+      <c r="K57" s="82" t="n"/>
+      <c r="L57" s="82" t="n"/>
+      <c r="M57" s="82" t="n"/>
+      <c r="N57" s="82" t="n"/>
+      <c r="O57" s="82" t="n"/>
+    </row>
+    <row r="58" ht="380" customHeight="1">
       <c r="A58" s="83" t="inlineStr">
         <is>
-          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="B58" s="84" t="n"/>
@@ -4576,7 +4782,7 @@
       <c r="H58" s="84" t="n"/>
       <c r="I58" s="83" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>Axial mural (placa mural / wall fan), Ø560 mm, transmisión directa (motor en el cubo del impulsor); montaje en muro mediante estructura de unión</t>
         </is>
       </c>
       <c r="J58" s="84" t="n"/>
@@ -4586,1479 +4792,1041 @@
       <c r="N58" s="84" t="n"/>
       <c r="O58" s="84" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="86" t="inlineStr">
-        <is>
-          <t>3. Punto de trabajo</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="120" customHeight="1">
-      <c r="A62" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1"/>
-    <row r="64" ht="105" customHeight="1">
-      <c r="A64" s="82" t="inlineStr">
-        <is>
-          <t>Magnitud</t>
-        </is>
-      </c>
-      <c r="B64" s="82" t="n"/>
-      <c r="C64" s="82" t="n"/>
-      <c r="D64" s="82" t="n"/>
-      <c r="E64" s="82" t="n"/>
-      <c r="F64" s="82" t="inlineStr">
-        <is>
-          <t>En el sitio (ρ = 0.88 kg/m³)</t>
-        </is>
-      </c>
-      <c r="G64" s="82" t="n"/>
-      <c r="H64" s="82" t="n"/>
-      <c r="I64" s="82" t="n"/>
-      <c r="J64" s="82" t="n"/>
-      <c r="K64" s="82" t="inlineStr">
-        <is>
-          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="L64" s="82" t="n"/>
-      <c r="M64" s="82" t="n"/>
-      <c r="N64" s="82" t="n"/>
-      <c r="O64" s="82" t="n"/>
-    </row>
-    <row r="65" ht="135" customHeight="1">
-      <c r="A65" s="83" t="inlineStr">
-        <is>
-          <t>Caudal</t>
-        </is>
-      </c>
-      <c r="B65" s="84" t="n"/>
-      <c r="C65" s="84" t="n"/>
-      <c r="D65" s="84" t="n"/>
-      <c r="E65" s="84" t="n"/>
-      <c r="F65" s="83" t="inlineStr">
-        <is>
-          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
-        </is>
-      </c>
-      <c r="G65" s="84" t="n"/>
-      <c r="H65" s="84" t="n"/>
-      <c r="I65" s="84" t="n"/>
-      <c r="J65" s="84" t="n"/>
-      <c r="K65" s="83" t="inlineStr">
-        <is>
-          <t>Sin cambio (máquina de volumen constante)</t>
-        </is>
-      </c>
-      <c r="L65" s="84" t="n"/>
-      <c r="M65" s="84" t="n"/>
-      <c r="N65" s="84" t="n"/>
-      <c r="O65" s="84" t="n"/>
-    </row>
-    <row r="66" ht="135" customHeight="1">
-      <c r="A66" s="83" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario de diseño (filtro cargado)</t>
-        </is>
-      </c>
-      <c r="B66" s="84" t="n"/>
-      <c r="C66" s="84" t="n"/>
-      <c r="D66" s="84" t="n"/>
-      <c r="E66" s="84" t="n"/>
-      <c r="F66" s="83" t="inlineStr">
-        <is>
-          <t>165 Pa</t>
-        </is>
-      </c>
-      <c r="G66" s="84" t="n"/>
-      <c r="H66" s="84" t="n"/>
-      <c r="I66" s="84" t="n"/>
-      <c r="J66" s="84" t="n"/>
-      <c r="K66" s="83" t="inlineStr">
-        <is>
-          <t>225 Pa</t>
-        </is>
-      </c>
-      <c r="L66" s="84" t="n"/>
-      <c r="M66" s="84" t="n"/>
-      <c r="N66" s="84" t="n"/>
-      <c r="O66" s="84" t="n"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="83" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario filtro limpio</t>
-        </is>
-      </c>
-      <c r="B67" s="84" t="n"/>
-      <c r="C67" s="84" t="n"/>
-      <c r="D67" s="84" t="n"/>
-      <c r="E67" s="84" t="n"/>
-      <c r="F67" s="83" t="inlineStr">
-        <is>
-          <t>70 Pa</t>
-        </is>
-      </c>
-      <c r="G67" s="84" t="n"/>
-      <c r="H67" s="84" t="n"/>
-      <c r="I67" s="84" t="n"/>
-      <c r="J67" s="84" t="n"/>
-      <c r="K67" s="83" t="inlineStr">
-        <is>
-          <t>95 Pa</t>
-        </is>
-      </c>
-      <c r="L67" s="84" t="n"/>
-      <c r="M67" s="84" t="n"/>
-      <c r="N67" s="84" t="n"/>
-      <c r="O67" s="84" t="n"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="83" t="inlineStr">
-        <is>
-          <t>Composición ΔP diseño</t>
-        </is>
-      </c>
-      <c r="B68" s="84" t="n"/>
-      <c r="C68" s="84" t="n"/>
-      <c r="D68" s="84" t="n"/>
-      <c r="E68" s="84" t="n"/>
-      <c r="F68" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 154 Pa + rejillas 11 Pa</t>
-        </is>
-      </c>
-      <c r="G68" s="84" t="n"/>
-      <c r="H68" s="84" t="n"/>
-      <c r="I68" s="84" t="n"/>
-      <c r="J68" s="84" t="n"/>
-      <c r="K68" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 210 Pa + 15 Pa</t>
-        </is>
-      </c>
-      <c r="L68" s="84" t="n"/>
-      <c r="M68" s="84" t="n"/>
-      <c r="N68" s="84" t="n"/>
-      <c r="O68" s="84" t="n"/>
-    </row>
-    <row r="69" ht="120" customHeight="1">
-      <c r="A69" s="83" t="inlineStr">
-        <is>
-          <t>Diámetro del impulsor (uniformidad planta)</t>
-        </is>
-      </c>
-      <c r="B69" s="84" t="n"/>
-      <c r="C69" s="84" t="n"/>
-      <c r="D69" s="84" t="n"/>
-      <c r="E69" s="84" t="n"/>
-      <c r="F69" s="83" t="inlineStr">
-        <is>
-          <t>560 mm (22 in)</t>
-        </is>
-      </c>
-      <c r="G69" s="84" t="n"/>
-      <c r="H69" s="84" t="n"/>
-      <c r="I69" s="84" t="n"/>
-      <c r="J69" s="84" t="n"/>
-      <c r="K69" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="84" t="n"/>
-      <c r="M69" s="84" t="n"/>
-      <c r="N69" s="84" t="n"/>
-      <c r="O69" s="84" t="n"/>
-    </row>
-    <row r="70" ht="75" customHeight="1">
-      <c r="A70" s="83" t="inlineStr">
-        <is>
-          <t>Velocidad en boca (Ø560 mm)</t>
-        </is>
-      </c>
-      <c r="B70" s="84" t="n"/>
-      <c r="C70" s="84" t="n"/>
-      <c r="D70" s="84" t="n"/>
-      <c r="E70" s="84" t="n"/>
-      <c r="F70" s="83" t="inlineStr">
-        <is>
-          <t>4.33 m/s</t>
-        </is>
-      </c>
-      <c r="G70" s="84" t="n"/>
-      <c r="H70" s="84" t="n"/>
-      <c r="I70" s="84" t="n"/>
-      <c r="J70" s="84" t="n"/>
-      <c r="K70" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="84" t="n"/>
-      <c r="M70" s="84" t="n"/>
-      <c r="N70" s="84" t="n"/>
-      <c r="O70" s="84" t="n"/>
-    </row>
-    <row r="71" ht="105" customHeight="1">
-      <c r="A71" s="83" t="inlineStr">
-        <is>
-          <t>Potencia teórica de aire (η = 0.55)</t>
-        </is>
-      </c>
-      <c r="B71" s="84" t="n"/>
-      <c r="C71" s="84" t="n"/>
-      <c r="D71" s="84" t="n"/>
-      <c r="E71" s="84" t="n"/>
-      <c r="F71" s="83" t="inlineStr">
-        <is>
-          <t>0.320 kW = 0.43 HP</t>
-        </is>
-      </c>
-      <c r="G71" s="84" t="n"/>
-      <c r="H71" s="84" t="n"/>
-      <c r="I71" s="84" t="n"/>
-      <c r="J71" s="84" t="n"/>
-      <c r="K71" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="84" t="n"/>
-      <c r="M71" s="84" t="n"/>
-      <c r="N71" s="84" t="n"/>
-      <c r="O71" s="84" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1"/>
-    <row r="73" ht="150" customHeight="1">
-      <c r="A73" s="87" t="inlineStr">
-        <is>
-          <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). El tamaño comercial queda fijado en Ø560 mm por uniformidad con el montaje típico instalado en la planta; las RPM exactas se confirman con el software de selección del fabricante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
-    <row r="76" ht="15" customHeight="1"/>
-    <row r="77" ht="15" customHeight="1"/>
-    <row r="78" ht="15" customHeight="1"/>
-    <row r="79" ht="15" customHeight="1"/>
-    <row r="80" ht="15" customHeight="1"/>
-    <row r="81" ht="15" customHeight="1"/>
-    <row r="82" ht="165" customHeight="1">
-      <c r="A82" s="87" t="inlineStr">
-        <is>
-          <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; la eficiencia mínima exigible es 0.55 (dato provisional, a verificar contra la curva de la selección final). El margen sobre la potencia de eje (motor provisional 0.75 HP vs. 0.43 HP teóricos, con margen de servicio 1.5) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio; la potencia final del motor se confirma con la curva de catálogo de la selección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1"/>
-    <row r="84" ht="15" customHeight="1"/>
-    <row r="85" ht="15" customHeight="1"/>
-    <row r="86" ht="15" customHeight="1"/>
-    <row r="87" ht="15" customHeight="1"/>
-    <row r="88" ht="15" customHeight="1"/>
-    <row r="89" ht="15" customHeight="1"/>
-    <row r="90" ht="15" customHeight="1"/>
-    <row r="91" ht="15" customHeight="1"/>
-    <row r="92" ht="105" customHeight="1">
-      <c r="A92" s="86" t="inlineStr">
-        <is>
-          <t>4. Tipo y materiales de construcción</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="45" customHeight="1">
-      <c r="A93" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 3. Requisitos de construcción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="45" customHeight="1">
-      <c r="A94" s="82" t="inlineStr">
-        <is>
-          <t>Componente</t>
-        </is>
-      </c>
-      <c r="B94" s="82" t="n"/>
-      <c r="C94" s="82" t="n"/>
-      <c r="D94" s="82" t="n"/>
-      <c r="E94" s="82" t="n"/>
-      <c r="F94" s="82" t="n"/>
-      <c r="G94" s="82" t="n"/>
-      <c r="H94" s="82" t="n"/>
-      <c r="I94" s="82" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="J94" s="82" t="n"/>
-      <c r="K94" s="82" t="n"/>
-      <c r="L94" s="82" t="n"/>
-      <c r="M94" s="82" t="n"/>
-      <c r="N94" s="82" t="n"/>
-      <c r="O94" s="82" t="n"/>
-    </row>
-    <row r="95" ht="390" customHeight="1">
-      <c r="A95" s="83" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B95" s="84" t="n"/>
-      <c r="C95" s="84" t="n"/>
-      <c r="D95" s="84" t="n"/>
-      <c r="E95" s="84" t="n"/>
-      <c r="F95" s="84" t="n"/>
-      <c r="G95" s="84" t="n"/>
-      <c r="H95" s="84" t="n"/>
-      <c r="I95" s="83" t="inlineStr">
-        <is>
-          <t>Axial mural (placa mural / wall fan), Ø560 mm, transmisión directa (motor en el cubo del impulsor); montaje en muro mediante estructura de unión</t>
-        </is>
-      </c>
-      <c r="J95" s="84" t="n"/>
-      <c r="K95" s="84" t="n"/>
-      <c r="L95" s="84" t="n"/>
-      <c r="M95" s="84" t="n"/>
-      <c r="N95" s="84" t="n"/>
-      <c r="O95" s="84" t="n"/>
-    </row>
-    <row r="96" ht="435" customHeight="1">
-      <c r="A96" s="83" t="inlineStr">
+    <row r="59" ht="456" customHeight="1">
+      <c r="A59" s="83" t="inlineStr">
         <is>
           <t>Carcasa, placa mural y rodete</t>
         </is>
       </c>
-      <c r="B96" s="84" t="n"/>
-      <c r="C96" s="84" t="n"/>
-      <c r="D96" s="84" t="n"/>
-      <c r="E96" s="84" t="n"/>
-      <c r="F96" s="84" t="n"/>
-      <c r="G96" s="84" t="n"/>
-      <c r="H96" s="84" t="n"/>
-      <c r="I96" s="83" t="inlineStr">
+      <c r="B59" s="84" t="n"/>
+      <c r="C59" s="84" t="n"/>
+      <c r="D59" s="84" t="n"/>
+      <c r="E59" s="84" t="n"/>
+      <c r="F59" s="84" t="n"/>
+      <c r="G59" s="84" t="n"/>
+      <c r="H59" s="84" t="n"/>
+      <c r="I59" s="83" t="inlineStr">
         <is>
           <t>PRFV con resina viniléster, laminado según ASTM C582/D4167; alternativa: acero con recubrimiento epóxico anticorrosivo (segunda línea, con inspección programada)</t>
         </is>
       </c>
-      <c r="J96" s="84" t="n"/>
-      <c r="K96" s="84" t="n"/>
-      <c r="L96" s="84" t="n"/>
-      <c r="M96" s="84" t="n"/>
-      <c r="N96" s="84" t="n"/>
-      <c r="O96" s="84" t="n"/>
-    </row>
-    <row r="97" ht="195" customHeight="1">
-      <c r="A97" s="83" t="inlineStr">
+      <c r="J59" s="84" t="n"/>
+      <c r="K59" s="84" t="n"/>
+      <c r="L59" s="84" t="n"/>
+      <c r="M59" s="84" t="n"/>
+      <c r="N59" s="84" t="n"/>
+      <c r="O59" s="84" t="n"/>
+    </row>
+    <row r="60" ht="190" customHeight="1">
+      <c r="A60" s="83" t="inlineStr">
         <is>
           <t>Elementos metálicos en la corriente</t>
         </is>
       </c>
-      <c r="B97" s="84" t="n"/>
-      <c r="C97" s="84" t="n"/>
-      <c r="D97" s="84" t="n"/>
-      <c r="E97" s="84" t="n"/>
-      <c r="F97" s="84" t="n"/>
-      <c r="G97" s="84" t="n"/>
-      <c r="H97" s="84" t="n"/>
-      <c r="I97" s="83" t="inlineStr">
+      <c r="B60" s="84" t="n"/>
+      <c r="C60" s="84" t="n"/>
+      <c r="D60" s="84" t="n"/>
+      <c r="E60" s="84" t="n"/>
+      <c r="F60" s="84" t="n"/>
+      <c r="G60" s="84" t="n"/>
+      <c r="H60" s="84" t="n"/>
+      <c r="I60" s="83" t="inlineStr">
         <is>
           <t>Mínimos; eje del motor en acero inoxidable con protección anticorrosiva</t>
         </is>
       </c>
-      <c r="J97" s="84" t="n"/>
-      <c r="K97" s="84" t="n"/>
-      <c r="L97" s="84" t="n"/>
-      <c r="M97" s="84" t="n"/>
-      <c r="N97" s="84" t="n"/>
-      <c r="O97" s="84" t="n"/>
-    </row>
-    <row r="98" ht="540" customHeight="1">
-      <c r="A98" s="83" t="inlineStr">
+      <c r="J60" s="84" t="n"/>
+      <c r="K60" s="84" t="n"/>
+      <c r="L60" s="84" t="n"/>
+      <c r="M60" s="84" t="n"/>
+      <c r="N60" s="84" t="n"/>
+      <c r="O60" s="84" t="n"/>
+    </row>
+    <row r="61" ht="570" customHeight="1">
+      <c r="A61" s="83" t="inlineStr">
         <is>
           <t>Motor en la corriente de aire</t>
         </is>
       </c>
-      <c r="B98" s="84" t="n"/>
-      <c r="C98" s="84" t="n"/>
-      <c r="D98" s="84" t="n"/>
-      <c r="E98" s="84" t="n"/>
-      <c r="F98" s="84" t="n"/>
-      <c r="G98" s="84" t="n"/>
-      <c r="H98" s="84" t="n"/>
-      <c r="I98" s="83" t="inlineStr">
+      <c r="B61" s="84" t="n"/>
+      <c r="C61" s="84" t="n"/>
+      <c r="D61" s="84" t="n"/>
+      <c r="E61" s="84" t="n"/>
+      <c r="F61" s="84" t="n"/>
+      <c r="G61" s="84" t="n"/>
+      <c r="H61" s="84" t="n"/>
+      <c r="I61" s="83" t="inlineStr">
         <is>
           <t>Encapsulado severe duty (ver Tabla 4) — la transmisión directa ubica el motor dentro de la corriente; se exige ejecución anticorrosiva reforzada, criterio ya operado por la planta en sus montajes típicos</t>
         </is>
       </c>
-      <c r="J98" s="84" t="n"/>
-      <c r="K98" s="84" t="n"/>
-      <c r="L98" s="84" t="n"/>
-      <c r="M98" s="84" t="n"/>
-      <c r="N98" s="84" t="n"/>
-      <c r="O98" s="84" t="n"/>
-    </row>
-    <row r="99" ht="165" customHeight="1">
-      <c r="A99" s="83" t="inlineStr">
+      <c r="J61" s="84" t="n"/>
+      <c r="K61" s="84" t="n"/>
+      <c r="L61" s="84" t="n"/>
+      <c r="M61" s="84" t="n"/>
+      <c r="N61" s="84" t="n"/>
+      <c r="O61" s="84" t="n"/>
+    </row>
+    <row r="62" ht="152" customHeight="1">
+      <c r="A62" s="83" t="inlineStr">
         <is>
           <t>Construcción contra chispa</t>
         </is>
       </c>
-      <c r="B99" s="84" t="n"/>
-      <c r="C99" s="84" t="n"/>
-      <c r="D99" s="84" t="n"/>
-      <c r="E99" s="84" t="n"/>
-      <c r="F99" s="84" t="n"/>
-      <c r="G99" s="84" t="n"/>
-      <c r="H99" s="84" t="n"/>
-      <c r="I99" s="83" t="inlineStr">
+      <c r="B62" s="84" t="n"/>
+      <c r="C62" s="84" t="n"/>
+      <c r="D62" s="84" t="n"/>
+      <c r="E62" s="84" t="n"/>
+      <c r="F62" s="84" t="n"/>
+      <c r="G62" s="84" t="n"/>
+      <c r="H62" s="84" t="n"/>
+      <c r="I62" s="83" t="inlineStr">
         <is>
           <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
         </is>
       </c>
-      <c r="J99" s="84" t="n"/>
-      <c r="K99" s="84" t="n"/>
-      <c r="L99" s="84" t="n"/>
-      <c r="M99" s="84" t="n"/>
-      <c r="N99" s="84" t="n"/>
-      <c r="O99" s="84" t="n"/>
-    </row>
-    <row r="100" ht="105" customHeight="1">
-      <c r="A100" s="83" t="inlineStr">
+      <c r="J62" s="84" t="n"/>
+      <c r="K62" s="84" t="n"/>
+      <c r="L62" s="84" t="n"/>
+      <c r="M62" s="84" t="n"/>
+      <c r="N62" s="84" t="n"/>
+      <c r="O62" s="84" t="n"/>
+    </row>
+    <row r="63" ht="114" customHeight="1">
+      <c r="A63" s="83" t="inlineStr">
         <is>
           <t>Certificación de desempeño</t>
         </is>
       </c>
-      <c r="B100" s="84" t="n"/>
-      <c r="C100" s="84" t="n"/>
-      <c r="D100" s="84" t="n"/>
-      <c r="E100" s="84" t="n"/>
-      <c r="F100" s="84" t="n"/>
-      <c r="G100" s="84" t="n"/>
-      <c r="H100" s="84" t="n"/>
-      <c r="I100" s="83" t="inlineStr">
+      <c r="B63" s="84" t="n"/>
+      <c r="C63" s="84" t="n"/>
+      <c r="D63" s="84" t="n"/>
+      <c r="E63" s="84" t="n"/>
+      <c r="F63" s="84" t="n"/>
+      <c r="G63" s="84" t="n"/>
+      <c r="H63" s="84" t="n"/>
+      <c r="I63" s="83" t="inlineStr">
         <is>
           <t>AMCA 210/211 (sello AMCA exigible)</t>
         </is>
       </c>
-      <c r="J100" s="84" t="n"/>
-      <c r="K100" s="84" t="n"/>
-      <c r="L100" s="84" t="n"/>
-      <c r="M100" s="84" t="n"/>
-      <c r="N100" s="84" t="n"/>
-      <c r="O100" s="84" t="n"/>
-    </row>
-    <row r="101" ht="285" customHeight="1">
+      <c r="J63" s="84" t="n"/>
+      <c r="K63" s="84" t="n"/>
+      <c r="L63" s="84" t="n"/>
+      <c r="M63" s="84" t="n"/>
+      <c r="N63" s="84" t="n"/>
+      <c r="O63" s="84" t="n"/>
+    </row>
+    <row r="64" ht="304" customHeight="1">
+      <c r="A64" s="83" t="inlineStr">
+        <is>
+          <t>Descartado</t>
+        </is>
+      </c>
+      <c r="B64" s="84" t="n"/>
+      <c r="C64" s="84" t="n"/>
+      <c r="D64" s="84" t="n"/>
+      <c r="E64" s="84" t="n"/>
+      <c r="F64" s="84" t="n"/>
+      <c r="G64" s="84" t="n"/>
+      <c r="H64" s="84" t="n"/>
+      <c r="I64" s="83" t="inlineStr">
+        <is>
+          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado desnudo en la corriente de aire</t>
+        </is>
+      </c>
+      <c r="J64" s="84" t="n"/>
+      <c r="K64" s="84" t="n"/>
+      <c r="L64" s="84" t="n"/>
+      <c r="M64" s="84" t="n"/>
+      <c r="N64" s="84" t="n"/>
+      <c r="O64" s="84" t="n"/>
+    </row>
+    <row r="65" ht="38" customHeight="1"/>
+    <row r="66" ht="608" customHeight="1">
+      <c r="A66" s="85" t="inlineStr">
+        <is>
+          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23). El montaje típico de la planta usa acero galvanizado y pintura electrostática; para este servicio se eleva la especificación a PRFV o epóxico anticorrosivo por la atmósfera clorada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="38" customHeight="1"/>
+    <row r="68" ht="38" customHeight="1"/>
+    <row r="69" ht="494" customHeight="1">
+      <c r="A69" s="85" t="inlineStr">
+        <is>
+          <t>Nota de ingeniería (REV2). La adopción del montaje mural de transmisión directa deja el motor dentro de la corriente de aire corrosivo, a diferencia de la configuración de transmisión por bandas evaluada en REV1. El riesgo se mitiga con la ejecución encapsulada severe duty de la Tabla 4 y con el programa de inspección semestral de la Tabla de mantenimiento de la descripción técnica de planta; la alternativa de transmisión por bandas queda documentada como opción si la vida del motor en servicio resultara inferior a la esperada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1"/>
+    <row r="71" ht="38" customHeight="1"/>
+    <row r="72" ht="38" customHeight="1"/>
+    <row r="73" ht="38" customHeight="1">
+      <c r="A73" s="81" t="inlineStr">
+        <is>
+          <t>5. Motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="38" customHeight="1">
+      <c r="A74" s="87" t="inlineStr">
+        <is>
+          <t>Tabla 4. Especificación del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="38" customHeight="1">
+      <c r="A75" s="82" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="n"/>
+      <c r="C75" s="82" t="n"/>
+      <c r="D75" s="82" t="n"/>
+      <c r="E75" s="82" t="n"/>
+      <c r="F75" s="82" t="n"/>
+      <c r="G75" s="82" t="n"/>
+      <c r="H75" s="82" t="n"/>
+      <c r="I75" s="82" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J75" s="82" t="n"/>
+      <c r="K75" s="82" t="n"/>
+      <c r="L75" s="82" t="n"/>
+      <c r="M75" s="82" t="n"/>
+      <c r="N75" s="82" t="n"/>
+      <c r="O75" s="82" t="n"/>
+    </row>
+    <row r="76" ht="190" customHeight="1">
+      <c r="A76" s="83" t="inlineStr">
+        <is>
+          <t>Potencia instalada</t>
+        </is>
+      </c>
+      <c r="B76" s="84" t="n"/>
+      <c r="C76" s="84" t="n"/>
+      <c r="D76" s="84" t="n"/>
+      <c r="E76" s="84" t="n"/>
+      <c r="F76" s="84" t="n"/>
+      <c r="G76" s="84" t="n"/>
+      <c r="H76" s="84" t="n"/>
+      <c r="I76" s="83" t="inlineStr">
+        <is>
+          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
+        </is>
+      </c>
+      <c r="J76" s="84" t="n"/>
+      <c r="K76" s="84" t="n"/>
+      <c r="L76" s="84" t="n"/>
+      <c r="M76" s="84" t="n"/>
+      <c r="N76" s="84" t="n"/>
+      <c r="O76" s="84" t="n"/>
+    </row>
+    <row r="77" ht="456" customHeight="1">
+      <c r="A77" s="83" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="B77" s="84" t="n"/>
+      <c r="C77" s="84" t="n"/>
+      <c r="D77" s="84" t="n"/>
+      <c r="E77" s="84" t="n"/>
+      <c r="F77" s="84" t="n"/>
+      <c r="G77" s="84" t="n"/>
+      <c r="H77" s="84" t="n"/>
+      <c r="I77" s="83" t="inlineStr">
+        <is>
+          <t>TEFC encapsulado, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos, eje inox (referencia IEEE 841 o equivalente)</t>
+        </is>
+      </c>
+      <c r="J77" s="84" t="n"/>
+      <c r="K77" s="84" t="n"/>
+      <c r="L77" s="84" t="n"/>
+      <c r="M77" s="84" t="n"/>
+      <c r="N77" s="84" t="n"/>
+      <c r="O77" s="84" t="n"/>
+    </row>
+    <row r="78" ht="228" customHeight="1">
+      <c r="A78" s="83" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B78" s="84" t="n"/>
+      <c r="C78" s="84" t="n"/>
+      <c r="D78" s="84" t="n"/>
+      <c r="E78" s="84" t="n"/>
+      <c r="F78" s="84" t="n"/>
+      <c r="G78" s="84" t="n"/>
+      <c r="H78" s="84" t="n"/>
+      <c r="I78" s="83" t="inlineStr">
+        <is>
+          <t>En el cubo del impulsor, dentro de la corriente de aire (transmisión directa)</t>
+        </is>
+      </c>
+      <c r="J78" s="84" t="n"/>
+      <c r="K78" s="84" t="n"/>
+      <c r="L78" s="84" t="n"/>
+      <c r="M78" s="84" t="n"/>
+      <c r="N78" s="84" t="n"/>
+      <c r="O78" s="84" t="n"/>
+    </row>
+    <row r="79" ht="152" customHeight="1">
+      <c r="A79" s="83" t="inlineStr">
+        <is>
+          <t>Aislamiento / protección</t>
+        </is>
+      </c>
+      <c r="B79" s="84" t="n"/>
+      <c r="C79" s="84" t="n"/>
+      <c r="D79" s="84" t="n"/>
+      <c r="E79" s="84" t="n"/>
+      <c r="F79" s="84" t="n"/>
+      <c r="G79" s="84" t="n"/>
+      <c r="H79" s="84" t="n"/>
+      <c r="I79" s="83" t="inlineStr">
+        <is>
+          <t>Clase F (H preferible) / IP56 mínimo (IP66 preferible)</t>
+        </is>
+      </c>
+      <c r="J79" s="84" t="n"/>
+      <c r="K79" s="84" t="n"/>
+      <c r="L79" s="84" t="n"/>
+      <c r="M79" s="84" t="n"/>
+      <c r="N79" s="84" t="n"/>
+      <c r="O79" s="84" t="n"/>
+    </row>
+    <row r="80" ht="152" customHeight="1">
+      <c r="A80" s="83" t="inlineStr">
+        <is>
+          <t>Tensión / fases / frecuencia</t>
+        </is>
+      </c>
+      <c r="B80" s="84" t="n"/>
+      <c r="C80" s="84" t="n"/>
+      <c r="D80" s="84" t="n"/>
+      <c r="E80" s="84" t="n"/>
+      <c r="F80" s="84" t="n"/>
+      <c r="G80" s="84" t="n"/>
+      <c r="H80" s="84" t="n"/>
+      <c r="I80" s="83" t="inlineStr">
+        <is>
+          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J80" s="84" t="n"/>
+      <c r="K80" s="84" t="n"/>
+      <c r="L80" s="84" t="n"/>
+      <c r="M80" s="84" t="n"/>
+      <c r="N80" s="84" t="n"/>
+      <c r="O80" s="84" t="n"/>
+    </row>
+    <row r="81" ht="190" customHeight="1">
+      <c r="A81" s="83" t="inlineStr">
+        <is>
+          <t>Derateo por altitud</t>
+        </is>
+      </c>
+      <c r="B81" s="84" t="n"/>
+      <c r="C81" s="84" t="n"/>
+      <c r="D81" s="84" t="n"/>
+      <c r="E81" s="84" t="n"/>
+      <c r="F81" s="84" t="n"/>
+      <c r="G81" s="84" t="n"/>
+      <c r="H81" s="84" t="n"/>
+      <c r="I81" s="83" t="inlineStr">
+        <is>
+          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+        </is>
+      </c>
+      <c r="J81" s="84" t="n"/>
+      <c r="K81" s="84" t="n"/>
+      <c r="L81" s="84" t="n"/>
+      <c r="M81" s="84" t="n"/>
+      <c r="N81" s="84" t="n"/>
+      <c r="O81" s="84" t="n"/>
+    </row>
+    <row r="82" ht="266" customHeight="1">
+      <c r="A82" s="83" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B82" s="84" t="n"/>
+      <c r="C82" s="84" t="n"/>
+      <c r="D82" s="84" t="n"/>
+      <c r="E82" s="84" t="n"/>
+      <c r="F82" s="84" t="n"/>
+      <c r="G82" s="84" t="n"/>
+      <c r="H82" s="84" t="n"/>
+      <c r="I82" s="83" t="inlineStr">
+        <is>
+          <t>Calentador anticondensación (paradas largas); caja de conexiones sellada, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="J82" s="84" t="n"/>
+      <c r="K82" s="84" t="n"/>
+      <c r="L82" s="84" t="n"/>
+      <c r="M82" s="84" t="n"/>
+      <c r="N82" s="84" t="n"/>
+      <c r="O82" s="84" t="n"/>
+    </row>
+    <row r="83" ht="38" customHeight="1"/>
+    <row r="84" ht="380" customHeight="1">
+      <c r="A84" s="85" t="inlineStr">
+        <is>
+          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="38" customHeight="1"/>
+    <row r="86" ht="38" customHeight="1"/>
+    <row r="87" ht="38" customHeight="1">
+      <c r="A87" s="81" t="inlineStr">
+        <is>
+          <t>6. Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="76" customHeight="1">
+      <c r="A88" s="87" t="inlineStr">
+        <is>
+          <t>Tabla 5. Accesorios del conjunto de montaje (uniformidad con la planta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="76" customHeight="1">
+      <c r="A89" s="82" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="B89" s="82" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="n"/>
+      <c r="F89" s="82" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="n"/>
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="inlineStr">
+        <is>
+          <t>Material / especificación</t>
+        </is>
+      </c>
+      <c r="L89" s="82" t="n"/>
+      <c r="M89" s="82" t="n"/>
+      <c r="N89" s="82" t="n"/>
+      <c r="O89" s="82" t="n"/>
+    </row>
+    <row r="90" ht="304" customHeight="1">
+      <c r="A90" s="83" t="inlineStr">
+        <is>
+          <t>Cubierta intemperie</t>
+        </is>
+      </c>
+      <c r="B90" s="84" t="n"/>
+      <c r="C90" s="84" t="n"/>
+      <c r="D90" s="84" t="n"/>
+      <c r="E90" s="84" t="n"/>
+      <c r="F90" s="83" t="inlineStr">
+        <is>
+          <t>Protección contra lluvia, radiación solar e ingreso directo de agua; aloja el banco de filtración (ver HD-FILT-001)</t>
+        </is>
+      </c>
+      <c r="G90" s="84" t="n"/>
+      <c r="H90" s="84" t="n"/>
+      <c r="I90" s="84" t="n"/>
+      <c r="J90" s="84" t="n"/>
+      <c r="K90" s="83" t="inlineStr">
+        <is>
+          <t>PRFV o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L</t>
+        </is>
+      </c>
+      <c r="L90" s="84" t="n"/>
+      <c r="M90" s="84" t="n"/>
+      <c r="N90" s="84" t="n"/>
+      <c r="O90" s="84" t="n"/>
+    </row>
+    <row r="91" ht="342" customHeight="1">
+      <c r="A91" s="83" t="inlineStr">
+        <is>
+          <t>Estructura de unión</t>
+        </is>
+      </c>
+      <c r="B91" s="84" t="n"/>
+      <c r="C91" s="84" t="n"/>
+      <c r="D91" s="84" t="n"/>
+      <c r="E91" s="84" t="n"/>
+      <c r="F91" s="83" t="inlineStr">
+        <is>
+          <t>Marco de soporte pernado al muro para fijación segura del ventilador; transmite cargas estáticas, dinámicas y vibraciones</t>
+        </is>
+      </c>
+      <c r="G91" s="84" t="n"/>
+      <c r="H91" s="84" t="n"/>
+      <c r="I91" s="84" t="n"/>
+      <c r="J91" s="84" t="n"/>
+      <c r="K91" s="83" t="inlineStr">
+        <is>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (A4) con aislamiento dieléctrico</t>
+        </is>
+      </c>
+      <c r="L91" s="84" t="n"/>
+      <c r="M91" s="84" t="n"/>
+      <c r="N91" s="84" t="n"/>
+      <c r="O91" s="84" t="n"/>
+    </row>
+    <row r="92" ht="228" customHeight="1">
+      <c r="A92" s="83" t="inlineStr">
+        <is>
+          <t>Malla de protección interior</t>
+        </is>
+      </c>
+      <c r="B92" s="84" t="n"/>
+      <c r="C92" s="84" t="n"/>
+      <c r="D92" s="84" t="n"/>
+      <c r="E92" s="84" t="n"/>
+      <c r="F92" s="83" t="inlineStr">
+        <is>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor</t>
+        </is>
+      </c>
+      <c r="G92" s="84" t="n"/>
+      <c r="H92" s="84" t="n"/>
+      <c r="I92" s="84" t="n"/>
+      <c r="J92" s="84" t="n"/>
+      <c r="K92" s="83" t="inlineStr">
+        <is>
+          <t>Malla inox 316 o galvanizada con pintura epóxica, marco desmontable</t>
+        </is>
+      </c>
+      <c r="L92" s="84" t="n"/>
+      <c r="M92" s="84" t="n"/>
+      <c r="N92" s="84" t="n"/>
+      <c r="O92" s="84" t="n"/>
+    </row>
+    <row r="93" ht="190" customHeight="1">
+      <c r="A93" s="83" t="inlineStr">
+        <is>
+          <t>Sellado del pasamuros</t>
+        </is>
+      </c>
+      <c r="B93" s="84" t="n"/>
+      <c r="C93" s="84" t="n"/>
+      <c r="D93" s="84" t="n"/>
+      <c r="E93" s="84" t="n"/>
+      <c r="F93" s="83" t="inlineStr">
+        <is>
+          <t>Evita recirculaciones y filtraciones no controladas en el vano</t>
+        </is>
+      </c>
+      <c r="G93" s="84" t="n"/>
+      <c r="H93" s="84" t="n"/>
+      <c r="I93" s="84" t="n"/>
+      <c r="J93" s="84" t="n"/>
+      <c r="K93" s="83" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi)</t>
+        </is>
+      </c>
+      <c r="L93" s="84" t="n"/>
+      <c r="M93" s="84" t="n"/>
+      <c r="N93" s="84" t="n"/>
+      <c r="O93" s="84" t="n"/>
+    </row>
+    <row r="94" ht="228" customHeight="1">
+      <c r="A94" s="83" t="inlineStr">
+        <is>
+          <t>Guardamotor y tablero</t>
+        </is>
+      </c>
+      <c r="B94" s="84" t="n"/>
+      <c r="C94" s="84" t="n"/>
+      <c r="D94" s="84" t="n"/>
+      <c r="E94" s="84" t="n"/>
+      <c r="F94" s="83" t="inlineStr">
+        <is>
+          <t>Protección eléctrica conforme a RETIE (ver listado_equipos.md, ítems 11-12)</t>
+        </is>
+      </c>
+      <c r="G94" s="84" t="n"/>
+      <c r="H94" s="84" t="n"/>
+      <c r="I94" s="84" t="n"/>
+      <c r="J94" s="84" t="n"/>
+      <c r="K94" s="83" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="L94" s="84" t="n"/>
+      <c r="M94" s="84" t="n"/>
+      <c r="N94" s="84" t="n"/>
+      <c r="O94" s="84" t="n"/>
+    </row>
+    <row r="95" ht="38" customHeight="1"/>
+    <row r="96" ht="152" customHeight="1">
+      <c r="A96" s="86" t="inlineStr">
+        <is>
+          <t>6.1. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="38" customHeight="1"/>
+    <row r="98" ht="76" customHeight="1">
+      <c r="A98" s="81" t="inlineStr">
+        <is>
+          <t>7. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="114" customHeight="1">
+      <c r="A99" s="87" t="inlineStr">
+        <is>
+          <t>Tabla 6. Candidatos (consulta 2026-07-23, ajustada 2026-07-27 a tipo mural); RPM final por confirmar con proveedor en el punto 3 840 m³/h @ 225 Pa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="76" customHeight="1">
+      <c r="A100" s="82" t="inlineStr">
+        <is>
+          <t>Fabricante / línea</t>
+        </is>
+      </c>
+      <c r="B100" s="82" t="n"/>
+      <c r="C100" s="82" t="n"/>
+      <c r="D100" s="82" t="n"/>
+      <c r="E100" s="82" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F100" s="82" t="n"/>
+      <c r="G100" s="82" t="n"/>
+      <c r="H100" s="82" t="n"/>
+      <c r="I100" s="82" t="inlineStr">
+        <is>
+          <t>Canal en Colombia</t>
+        </is>
+      </c>
+      <c r="J100" s="82" t="n"/>
+      <c r="K100" s="82" t="n"/>
+      <c r="L100" s="82" t="n"/>
+      <c r="M100" s="82" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N100" s="82" t="n"/>
+      <c r="O100" s="82" t="n"/>
+    </row>
+    <row r="101" ht="380" customHeight="1">
       <c r="A101" s="83" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Sodeca HQD/HGT mural anticorrosivo — primera opción por uniformidad y canal local</t>
         </is>
       </c>
       <c r="B101" s="84" t="n"/>
       <c r="C101" s="84" t="n"/>
       <c r="D101" s="84" t="n"/>
-      <c r="E101" s="84" t="n"/>
+      <c r="E101" s="83" t="inlineStr">
+        <is>
+          <t>PRFV / epóxico, mural transmisión directa</t>
+        </is>
+      </c>
       <c r="F101" s="84" t="n"/>
       <c r="G101" s="84" t="n"/>
       <c r="H101" s="84" t="n"/>
       <c r="I101" s="83" t="inlineStr">
         <is>
-          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado desnudo en la corriente de aire</t>
+          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
         </is>
       </c>
       <c r="J101" s="84" t="n"/>
       <c r="K101" s="84" t="n"/>
       <c r="L101" s="84" t="n"/>
-      <c r="M101" s="84" t="n"/>
+      <c r="M101" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
+        </is>
+      </c>
       <c r="N101" s="84" t="n"/>
       <c r="O101" s="84" t="n"/>
     </row>
-    <row r="102" ht="15" customHeight="1"/>
-    <row r="103" ht="165" customHeight="1">
-      <c r="A103" s="85" t="inlineStr">
-        <is>
-          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23). El montaje típico de la planta usa acero galvanizado y pintura electrostática; para este servicio se eleva la especificación a PRFV o epóxico anticorrosivo por la atmósfera clorada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1"/>
-    <row r="105" ht="15" customHeight="1"/>
-    <row r="106" ht="15" customHeight="1"/>
-    <row r="107" ht="15" customHeight="1"/>
-    <row r="108" ht="15" customHeight="1"/>
-    <row r="109" ht="15" customHeight="1"/>
-    <row r="110" ht="15" customHeight="1"/>
-    <row r="111" ht="15" customHeight="1"/>
-    <row r="112" ht="15" customHeight="1"/>
-    <row r="113" ht="15" customHeight="1"/>
-    <row r="114" ht="165" customHeight="1">
-      <c r="A114" s="85" t="inlineStr">
-        <is>
-          <t>Nota de ingeniería (REV2). La adopción del montaje mural de transmisión directa deja el motor dentro de la corriente de aire corrosivo, a diferencia de la configuración de transmisión por bandas evaluada en REV1. El riesgo se mitiga con la ejecución encapsulada severe duty de la Tabla 4 y con el programa de inspección semestral de la Tabla de mantenimiento de la descripción técnica de planta; la alternativa de transmisión por bandas queda documentada como opción si la vida del motor en servicio resultara inferior a la esperada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1"/>
-    <row r="116" ht="15" customHeight="1"/>
-    <row r="117" ht="15" customHeight="1"/>
-    <row r="118" ht="15" customHeight="1"/>
-    <row r="119" ht="15" customHeight="1"/>
-    <row r="120" ht="15" customHeight="1"/>
-    <row r="121" ht="15" customHeight="1"/>
-    <row r="122" ht="15" customHeight="1"/>
-    <row r="123" ht="15" customHeight="1"/>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="86" t="inlineStr">
-        <is>
-          <t>5. Motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="45" customHeight="1">
-      <c r="A125" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 4. Especificación del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="82" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B126" s="82" t="n"/>
-      <c r="C126" s="82" t="n"/>
-      <c r="D126" s="82" t="n"/>
-      <c r="E126" s="82" t="n"/>
-      <c r="F126" s="82" t="n"/>
-      <c r="G126" s="82" t="n"/>
-      <c r="H126" s="82" t="n"/>
-      <c r="I126" s="82" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="J126" s="82" t="n"/>
-      <c r="K126" s="82" t="n"/>
-      <c r="L126" s="82" t="n"/>
-      <c r="M126" s="82" t="n"/>
-      <c r="N126" s="82" t="n"/>
-      <c r="O126" s="82" t="n"/>
-    </row>
-    <row r="127" ht="180" customHeight="1">
-      <c r="A127" s="83" t="inlineStr">
-        <is>
-          <t>Potencia instalada</t>
-        </is>
-      </c>
-      <c r="B127" s="84" t="n"/>
-      <c r="C127" s="84" t="n"/>
-      <c r="D127" s="84" t="n"/>
-      <c r="E127" s="84" t="n"/>
-      <c r="F127" s="84" t="n"/>
-      <c r="G127" s="84" t="n"/>
-      <c r="H127" s="84" t="n"/>
-      <c r="I127" s="83" t="inlineStr">
-        <is>
-          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
-        </is>
-      </c>
-      <c r="J127" s="84" t="n"/>
-      <c r="K127" s="84" t="n"/>
-      <c r="L127" s="84" t="n"/>
-      <c r="M127" s="84" t="n"/>
-      <c r="N127" s="84" t="n"/>
-      <c r="O127" s="84" t="n"/>
-    </row>
-    <row r="128" ht="435" customHeight="1">
-      <c r="A128" s="83" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="B128" s="84" t="n"/>
-      <c r="C128" s="84" t="n"/>
-      <c r="D128" s="84" t="n"/>
-      <c r="E128" s="84" t="n"/>
-      <c r="F128" s="84" t="n"/>
-      <c r="G128" s="84" t="n"/>
-      <c r="H128" s="84" t="n"/>
-      <c r="I128" s="83" t="inlineStr">
-        <is>
-          <t>TEFC encapsulado, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos, eje inox (referencia IEEE 841 o equivalente)</t>
-        </is>
-      </c>
-      <c r="J128" s="84" t="n"/>
-      <c r="K128" s="84" t="n"/>
-      <c r="L128" s="84" t="n"/>
-      <c r="M128" s="84" t="n"/>
-      <c r="N128" s="84" t="n"/>
-      <c r="O128" s="84" t="n"/>
-    </row>
-    <row r="129" ht="210" customHeight="1">
-      <c r="A129" s="83" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="B129" s="84" t="n"/>
-      <c r="C129" s="84" t="n"/>
-      <c r="D129" s="84" t="n"/>
-      <c r="E129" s="84" t="n"/>
-      <c r="F129" s="84" t="n"/>
-      <c r="G129" s="84" t="n"/>
-      <c r="H129" s="84" t="n"/>
-      <c r="I129" s="83" t="inlineStr">
-        <is>
-          <t>En el cubo del impulsor, dentro de la corriente de aire (transmisión directa)</t>
-        </is>
-      </c>
-      <c r="J129" s="84" t="n"/>
-      <c r="K129" s="84" t="n"/>
-      <c r="L129" s="84" t="n"/>
-      <c r="M129" s="84" t="n"/>
-      <c r="N129" s="84" t="n"/>
-      <c r="O129" s="84" t="n"/>
-    </row>
-    <row r="130" ht="150" customHeight="1">
-      <c r="A130" s="83" t="inlineStr">
-        <is>
-          <t>Aislamiento / protección</t>
-        </is>
-      </c>
-      <c r="B130" s="84" t="n"/>
-      <c r="C130" s="84" t="n"/>
-      <c r="D130" s="84" t="n"/>
-      <c r="E130" s="84" t="n"/>
-      <c r="F130" s="84" t="n"/>
-      <c r="G130" s="84" t="n"/>
-      <c r="H130" s="84" t="n"/>
-      <c r="I130" s="83" t="inlineStr">
-        <is>
-          <t>Clase F (H preferible) / IP56 mínimo (IP66 preferible)</t>
-        </is>
-      </c>
-      <c r="J130" s="84" t="n"/>
-      <c r="K130" s="84" t="n"/>
-      <c r="L130" s="84" t="n"/>
-      <c r="M130" s="84" t="n"/>
-      <c r="N130" s="84" t="n"/>
-      <c r="O130" s="84" t="n"/>
-    </row>
-    <row r="131" ht="150" customHeight="1">
-      <c r="A131" s="83" t="inlineStr">
-        <is>
-          <t>Tensión / fases / frecuencia</t>
-        </is>
-      </c>
-      <c r="B131" s="84" t="n"/>
-      <c r="C131" s="84" t="n"/>
-      <c r="D131" s="84" t="n"/>
-      <c r="E131" s="84" t="n"/>
-      <c r="F131" s="84" t="n"/>
-      <c r="G131" s="84" t="n"/>
-      <c r="H131" s="84" t="n"/>
-      <c r="I131" s="83" t="inlineStr">
-        <is>
-          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="J131" s="84" t="n"/>
-      <c r="K131" s="84" t="n"/>
-      <c r="L131" s="84" t="n"/>
-      <c r="M131" s="84" t="n"/>
-      <c r="N131" s="84" t="n"/>
-      <c r="O131" s="84" t="n"/>
-    </row>
-    <row r="132" ht="165" customHeight="1">
-      <c r="A132" s="83" t="inlineStr">
-        <is>
-          <t>Derateo por altitud</t>
-        </is>
-      </c>
-      <c r="B132" s="84" t="n"/>
-      <c r="C132" s="84" t="n"/>
-      <c r="D132" s="84" t="n"/>
-      <c r="E132" s="84" t="n"/>
-      <c r="F132" s="84" t="n"/>
-      <c r="G132" s="84" t="n"/>
-      <c r="H132" s="84" t="n"/>
-      <c r="I132" s="83" t="inlineStr">
-        <is>
-          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
-        </is>
-      </c>
-      <c r="J132" s="84" t="n"/>
-      <c r="K132" s="84" t="n"/>
-      <c r="L132" s="84" t="n"/>
-      <c r="M132" s="84" t="n"/>
-      <c r="N132" s="84" t="n"/>
-      <c r="O132" s="84" t="n"/>
-    </row>
-    <row r="133" ht="270" customHeight="1">
-      <c r="A133" s="83" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B133" s="84" t="n"/>
-      <c r="C133" s="84" t="n"/>
-      <c r="D133" s="84" t="n"/>
-      <c r="E133" s="84" t="n"/>
-      <c r="F133" s="84" t="n"/>
-      <c r="G133" s="84" t="n"/>
-      <c r="H133" s="84" t="n"/>
-      <c r="I133" s="83" t="inlineStr">
-        <is>
-          <t>Calentador anticondensación (paradas largas); caja de conexiones sellada, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="J133" s="84" t="n"/>
-      <c r="K133" s="84" t="n"/>
-      <c r="L133" s="84" t="n"/>
-      <c r="M133" s="84" t="n"/>
-      <c r="N133" s="84" t="n"/>
-      <c r="O133" s="84" t="n"/>
-    </row>
-    <row r="134" ht="15" customHeight="1"/>
-    <row r="135" ht="165" customHeight="1">
-      <c r="A135" s="85" t="inlineStr">
-        <is>
-          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15" customHeight="1"/>
-    <row r="137" ht="15" customHeight="1"/>
-    <row r="138" ht="15" customHeight="1"/>
-    <row r="139" ht="15" customHeight="1"/>
-    <row r="140" ht="15" customHeight="1"/>
-    <row r="141" ht="45" customHeight="1">
-      <c r="A141" s="86" t="inlineStr">
-        <is>
-          <t>6. Accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="105" customHeight="1">
-      <c r="A142" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 5. Accesorios del conjunto de montaje (uniformidad con la planta).</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15" customHeight="1"/>
-    <row r="144" ht="75" customHeight="1">
-      <c r="A144" s="82" t="inlineStr">
-        <is>
-          <t>Ítem</t>
-        </is>
-      </c>
-      <c r="B144" s="82" t="n"/>
-      <c r="C144" s="82" t="n"/>
-      <c r="D144" s="82" t="n"/>
-      <c r="E144" s="82" t="n"/>
-      <c r="F144" s="82" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="G144" s="82" t="n"/>
-      <c r="H144" s="82" t="n"/>
-      <c r="I144" s="82" t="n"/>
-      <c r="J144" s="82" t="n"/>
-      <c r="K144" s="82" t="inlineStr">
-        <is>
-          <t>Material / especificación</t>
-        </is>
-      </c>
-      <c r="L144" s="82" t="n"/>
-      <c r="M144" s="82" t="n"/>
-      <c r="N144" s="82" t="n"/>
-      <c r="O144" s="82" t="n"/>
-    </row>
-    <row r="145" ht="315" customHeight="1">
-      <c r="A145" s="83" t="inlineStr">
-        <is>
-          <t>Cubierta intemperie</t>
-        </is>
-      </c>
-      <c r="B145" s="84" t="n"/>
-      <c r="C145" s="84" t="n"/>
-      <c r="D145" s="84" t="n"/>
-      <c r="E145" s="84" t="n"/>
-      <c r="F145" s="83" t="inlineStr">
-        <is>
-          <t>Protección contra lluvia, radiación solar e ingreso directo de agua; aloja el banco de filtración (ver HD-FILT-001)</t>
-        </is>
-      </c>
-      <c r="G145" s="84" t="n"/>
-      <c r="H145" s="84" t="n"/>
-      <c r="I145" s="84" t="n"/>
-      <c r="J145" s="84" t="n"/>
-      <c r="K145" s="83" t="inlineStr">
-        <is>
-          <t>PRFV o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L</t>
-        </is>
-      </c>
-      <c r="L145" s="84" t="n"/>
-      <c r="M145" s="84" t="n"/>
-      <c r="N145" s="84" t="n"/>
-      <c r="O145" s="84" t="n"/>
-    </row>
-    <row r="146" ht="330" customHeight="1">
-      <c r="A146" s="83" t="inlineStr">
-        <is>
-          <t>Estructura de unión</t>
-        </is>
-      </c>
-      <c r="B146" s="84" t="n"/>
-      <c r="C146" s="84" t="n"/>
-      <c r="D146" s="84" t="n"/>
-      <c r="E146" s="84" t="n"/>
-      <c r="F146" s="83" t="inlineStr">
-        <is>
-          <t>Marco de soporte pernado al muro para fijación segura del ventilador; transmite cargas estáticas, dinámicas y vibraciones</t>
-        </is>
-      </c>
-      <c r="G146" s="84" t="n"/>
-      <c r="H146" s="84" t="n"/>
-      <c r="I146" s="84" t="n"/>
-      <c r="J146" s="84" t="n"/>
-      <c r="K146" s="83" t="inlineStr">
-        <is>
-          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (A4) con aislamiento dieléctrico</t>
-        </is>
-      </c>
-      <c r="L146" s="84" t="n"/>
-      <c r="M146" s="84" t="n"/>
-      <c r="N146" s="84" t="n"/>
-      <c r="O146" s="84" t="n"/>
-    </row>
-    <row r="147" ht="240" customHeight="1">
-      <c r="A147" s="83" t="inlineStr">
-        <is>
-          <t>Malla de protección interior</t>
-        </is>
-      </c>
-      <c r="B147" s="84" t="n"/>
-      <c r="C147" s="84" t="n"/>
-      <c r="D147" s="84" t="n"/>
-      <c r="E147" s="84" t="n"/>
-      <c r="F147" s="83" t="inlineStr">
-        <is>
-          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor</t>
-        </is>
-      </c>
-      <c r="G147" s="84" t="n"/>
-      <c r="H147" s="84" t="n"/>
-      <c r="I147" s="84" t="n"/>
-      <c r="J147" s="84" t="n"/>
-      <c r="K147" s="83" t="inlineStr">
-        <is>
-          <t>Malla inox 316 o galvanizada con pintura epóxica, marco desmontable</t>
-        </is>
-      </c>
-      <c r="L147" s="84" t="n"/>
-      <c r="M147" s="84" t="n"/>
-      <c r="N147" s="84" t="n"/>
-      <c r="O147" s="84" t="n"/>
-    </row>
-    <row r="148" ht="165" customHeight="1">
-      <c r="A148" s="83" t="inlineStr">
-        <is>
-          <t>Sellado del pasamuros</t>
-        </is>
-      </c>
-      <c r="B148" s="84" t="n"/>
-      <c r="C148" s="84" t="n"/>
-      <c r="D148" s="84" t="n"/>
-      <c r="E148" s="84" t="n"/>
-      <c r="F148" s="83" t="inlineStr">
-        <is>
-          <t>Evita recirculaciones y filtraciones no controladas en el vano</t>
-        </is>
-      </c>
-      <c r="G148" s="84" t="n"/>
-      <c r="H148" s="84" t="n"/>
-      <c r="I148" s="84" t="n"/>
-      <c r="J148" s="84" t="n"/>
-      <c r="K148" s="83" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi)</t>
-        </is>
-      </c>
-      <c r="L148" s="84" t="n"/>
-      <c r="M148" s="84" t="n"/>
-      <c r="N148" s="84" t="n"/>
-      <c r="O148" s="84" t="n"/>
-    </row>
-    <row r="149" ht="210" customHeight="1">
-      <c r="A149" s="83" t="inlineStr">
-        <is>
-          <t>Guardamotor y tablero</t>
-        </is>
-      </c>
-      <c r="B149" s="84" t="n"/>
-      <c r="C149" s="84" t="n"/>
-      <c r="D149" s="84" t="n"/>
-      <c r="E149" s="84" t="n"/>
-      <c r="F149" s="83" t="inlineStr">
-        <is>
-          <t>Protección eléctrica conforme a RETIE (ver listado_equipos.md, ítems 11-12)</t>
-        </is>
-      </c>
-      <c r="G149" s="84" t="n"/>
-      <c r="H149" s="84" t="n"/>
-      <c r="I149" s="84" t="n"/>
-      <c r="J149" s="84" t="n"/>
-      <c r="K149" s="83" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="L149" s="84" t="n"/>
-      <c r="M149" s="84" t="n"/>
-      <c r="N149" s="84" t="n"/>
-      <c r="O149" s="84" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1"/>
-    <row r="151" ht="150" customHeight="1">
-      <c r="A151" s="87" t="inlineStr">
-        <is>
-          <t>6.1. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="15" customHeight="1"/>
-    <row r="153" ht="15" customHeight="1"/>
-    <row r="154" ht="15" customHeight="1"/>
-    <row r="155" ht="75" customHeight="1">
-      <c r="A155" s="86" t="inlineStr">
-        <is>
-          <t>7. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="135" customHeight="1">
-      <c r="A156" s="88" t="inlineStr">
-        <is>
-          <t>Tabla 6. Candidatos (consulta 2026-07-23, ajustada 2026-07-27 a tipo mural); RPM final por confirmar con proveedor en el punto 3 840 m³/h @ 225 Pa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1"/>
-    <row r="158" ht="15" customHeight="1"/>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" s="82" t="inlineStr">
-        <is>
-          <t>Fabricante / línea</t>
-        </is>
-      </c>
-      <c r="B159" s="82" t="n"/>
-      <c r="C159" s="82" t="n"/>
-      <c r="D159" s="82" t="n"/>
-      <c r="E159" s="82" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="F159" s="82" t="n"/>
-      <c r="G159" s="82" t="n"/>
-      <c r="H159" s="82" t="n"/>
-      <c r="I159" s="82" t="inlineStr">
-        <is>
-          <t>Canal en Colombia</t>
-        </is>
-      </c>
-      <c r="J159" s="82" t="n"/>
-      <c r="K159" s="82" t="n"/>
-      <c r="L159" s="82" t="n"/>
-      <c r="M159" s="82" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N159" s="82" t="n"/>
-      <c r="O159" s="82" t="n"/>
-    </row>
-    <row r="160" ht="360" customHeight="1">
-      <c r="A160" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca HQD/HGT mural anticorrosivo — primera opción por uniformidad y canal local</t>
-        </is>
-      </c>
-      <c r="B160" s="84" t="n"/>
-      <c r="C160" s="84" t="n"/>
-      <c r="D160" s="84" t="n"/>
-      <c r="E160" s="83" t="inlineStr">
-        <is>
-          <t>PRFV / epóxico, mural transmisión directa</t>
-        </is>
-      </c>
-      <c r="F160" s="84" t="n"/>
-      <c r="G160" s="84" t="n"/>
-      <c r="H160" s="84" t="n"/>
-      <c r="I160" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
-        </is>
-      </c>
-      <c r="J160" s="84" t="n"/>
-      <c r="K160" s="84" t="n"/>
-      <c r="L160" s="84" t="n"/>
-      <c r="M160" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
-        </is>
-      </c>
-      <c r="N160" s="84" t="n"/>
-      <c r="O160" s="84" t="n"/>
-    </row>
-    <row r="161" ht="300" customHeight="1">
-      <c r="A161" s="83" t="inlineStr">
+    <row r="102" ht="304" customHeight="1">
+      <c r="A102" s="83" t="inlineStr">
         <is>
           <t>Greenheck mural (línea industrial)</t>
         </is>
       </c>
-      <c r="B161" s="84" t="n"/>
-      <c r="C161" s="84" t="n"/>
-      <c r="D161" s="84" t="n"/>
-      <c r="E161" s="83" t="inlineStr">
+      <c r="B102" s="84" t="n"/>
+      <c r="C102" s="84" t="n"/>
+      <c r="D102" s="84" t="n"/>
+      <c r="E102" s="83" t="inlineStr">
         <is>
           <t>Acero con recubrimiento epóxico</t>
         </is>
       </c>
-      <c r="F161" s="84" t="n"/>
-      <c r="G161" s="84" t="n"/>
-      <c r="H161" s="84" t="n"/>
-      <c r="I161" s="83" t="inlineStr">
+      <c r="F102" s="84" t="n"/>
+      <c r="G102" s="84" t="n"/>
+      <c r="H102" s="84" t="n"/>
+      <c r="I102" s="83" t="inlineStr">
         <is>
           <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
         </is>
       </c>
-      <c r="J161" s="84" t="n"/>
-      <c r="K161" s="84" t="n"/>
-      <c r="L161" s="84" t="n"/>
-      <c r="M161" s="83" t="inlineStr">
+      <c r="J102" s="84" t="n"/>
+      <c r="K102" s="84" t="n"/>
+      <c r="L102" s="84" t="n"/>
+      <c r="M102" s="83" t="inlineStr">
         <is>
           <t>Greenheck (https://www.greenheck.com); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
         </is>
       </c>
-      <c r="N161" s="84" t="n"/>
-      <c r="O161" s="84" t="n"/>
-    </row>
-    <row r="162" ht="120" customHeight="1">
-      <c r="A162" s="83" t="inlineStr">
+      <c r="N102" s="84" t="n"/>
+      <c r="O102" s="84" t="n"/>
+    </row>
+    <row r="103" ht="114" customHeight="1">
+      <c r="A103" s="83" t="inlineStr">
         <is>
           <t>Aerovent / Twin City Fan (línea mural FRP)</t>
         </is>
       </c>
-      <c r="B162" s="84" t="n"/>
-      <c r="C162" s="84" t="n"/>
-      <c r="D162" s="84" t="n"/>
-      <c r="E162" s="83" t="inlineStr">
+      <c r="B103" s="84" t="n"/>
+      <c r="C103" s="84" t="n"/>
+      <c r="D103" s="84" t="n"/>
+      <c r="E103" s="83" t="inlineStr">
         <is>
           <t>PRFV</t>
         </is>
       </c>
-      <c r="F162" s="84" t="n"/>
-      <c r="G162" s="84" t="n"/>
-      <c r="H162" s="84" t="n"/>
-      <c r="I162" s="83" t="inlineStr">
+      <c r="F103" s="84" t="n"/>
+      <c r="G103" s="84" t="n"/>
+      <c r="H103" s="84" t="n"/>
+      <c r="I103" s="83" t="inlineStr">
         <is>
           <t>Por confirmar representante/canal local</t>
         </is>
       </c>
-      <c r="J162" s="84" t="n"/>
-      <c r="K162" s="84" t="n"/>
-      <c r="L162" s="84" t="n"/>
-      <c r="M162" s="83" t="inlineStr">
+      <c r="J103" s="84" t="n"/>
+      <c r="K103" s="84" t="n"/>
+      <c r="L103" s="84" t="n"/>
+      <c r="M103" s="83" t="inlineStr">
         <is>
           <t>Aerovent (https://www.aerovent.com)</t>
         </is>
       </c>
-      <c r="N162" s="84" t="n"/>
-      <c r="O162" s="84" t="n"/>
-    </row>
-    <row r="163" ht="165" customHeight="1">
-      <c r="A163" s="83" t="inlineStr">
+      <c r="N103" s="84" t="n"/>
+      <c r="O103" s="84" t="n"/>
+    </row>
+    <row r="104" ht="190" customHeight="1">
+      <c r="A104" s="83" t="inlineStr">
         <is>
           <t>New York Blower FRP mural</t>
         </is>
       </c>
-      <c r="B163" s="84" t="n"/>
-      <c r="C163" s="84" t="n"/>
-      <c r="D163" s="84" t="n"/>
-      <c r="E163" s="83" t="inlineStr">
+      <c r="B104" s="84" t="n"/>
+      <c r="C104" s="84" t="n"/>
+      <c r="D104" s="84" t="n"/>
+      <c r="E104" s="83" t="inlineStr">
         <is>
           <t>PRFV</t>
         </is>
       </c>
-      <c r="F163" s="84" t="n"/>
-      <c r="G163" s="84" t="n"/>
-      <c r="H163" s="84" t="n"/>
-      <c r="I163" s="83" t="inlineStr">
+      <c r="F104" s="84" t="n"/>
+      <c r="G104" s="84" t="n"/>
+      <c r="H104" s="84" t="n"/>
+      <c r="I104" s="83" t="inlineStr">
         <is>
           <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
         </is>
       </c>
-      <c r="J163" s="84" t="n"/>
-      <c r="K163" s="84" t="n"/>
-      <c r="L163" s="84" t="n"/>
-      <c r="M163" s="83" t="inlineStr">
+      <c r="J104" s="84" t="n"/>
+      <c r="K104" s="84" t="n"/>
+      <c r="L104" s="84" t="n"/>
+      <c r="M104" s="83" t="inlineStr">
         <is>
           <t>NYB (https://www.nyb.com/)</t>
         </is>
       </c>
-      <c r="N163" s="84" t="n"/>
-      <c r="O163" s="84" t="n"/>
-    </row>
-    <row r="164" ht="195" customHeight="1">
-      <c r="A164" s="83" t="inlineStr">
+      <c r="N104" s="84" t="n"/>
+      <c r="O104" s="84" t="n"/>
+    </row>
+    <row r="105" ht="190" customHeight="1">
+      <c r="A105" s="83" t="inlineStr">
         <is>
           <t>Plastec</t>
         </is>
       </c>
-      <c r="B164" s="84" t="n"/>
-      <c r="C164" s="84" t="n"/>
-      <c r="D164" s="84" t="n"/>
-      <c r="E164" s="83" t="inlineStr">
+      <c r="B105" s="84" t="n"/>
+      <c r="C105" s="84" t="n"/>
+      <c r="D105" s="84" t="n"/>
+      <c r="E105" s="83" t="inlineStr">
         <is>
           <t>Polipropileno</t>
         </is>
       </c>
-      <c r="F164" s="84" t="n"/>
-      <c r="G164" s="84" t="n"/>
-      <c r="H164" s="84" t="n"/>
-      <c r="I164" s="83" t="inlineStr">
+      <c r="F105" s="84" t="n"/>
+      <c r="G105" s="84" t="n"/>
+      <c r="H105" s="84" t="n"/>
+      <c r="I105" s="83" t="inlineStr">
         <is>
           <t>Importación directa (despacho 48 h declarado)</t>
         </is>
       </c>
-      <c r="J164" s="84" t="n"/>
-      <c r="K164" s="84" t="n"/>
-      <c r="L164" s="84" t="n"/>
-      <c r="M164" s="83" t="inlineStr">
+      <c r="J105" s="84" t="n"/>
+      <c r="K105" s="84" t="n"/>
+      <c r="L105" s="84" t="n"/>
+      <c r="M105" s="83" t="inlineStr">
         <is>
           <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
         </is>
       </c>
-      <c r="N164" s="84" t="n"/>
-      <c r="O164" s="84" t="n"/>
-    </row>
-    <row r="165" ht="15" customHeight="1"/>
-    <row r="166" ht="15" customHeight="1"/>
-    <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="86" t="inlineStr">
+      <c r="N105" s="84" t="n"/>
+      <c r="O105" s="84" t="n"/>
+    </row>
+    <row r="106" ht="38" customHeight="1"/>
+    <row r="107" ht="38" customHeight="1">
+      <c r="A107" s="81" t="inlineStr">
         <is>
           <t>8. Montaje</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="165" customHeight="1">
-      <c r="A168" s="87" t="inlineStr">
+    <row r="108" ht="418" customHeight="1">
+      <c r="A108" s="86" t="inlineStr">
         <is>
           <t>8.1. El ventilador se instalará en muro/pasamuros, con el eje horizontal y a una cota aproximada de 3,0 m sobre el piso terminado del laboratorio. El sentido de flujo es: aspiración del aire exterior a través de la cubierta intemperie y su banco de filtración, descarga directa al interior del recinto.</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1"/>
-    <row r="170" ht="15" customHeight="1"/>
-    <row r="171" ht="15" customHeight="1"/>
-    <row r="172" ht="15" customHeight="1"/>
-    <row r="173" ht="165" customHeight="1">
-      <c r="A173" s="87" t="inlineStr">
+    <row r="109" ht="38" customHeight="1"/>
+    <row r="110" ht="380" customHeight="1">
+      <c r="A110" s="86" t="inlineStr">
         <is>
           <t>8.2. El conjunto se soporta mediante una estructura de unión (marco de perfiles ASTM A36 galvanizados) pernada al muro con anclajes inox 316 (A4) y aislamiento dieléctrico frente a estructuras galvanizadas. El vano del muro se sella con silicona RTV neutra para evitar recirculaciones.</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="15" customHeight="1"/>
-    <row r="175" ht="15" customHeight="1"/>
-    <row r="176" ht="15" customHeight="1"/>
-    <row r="177" ht="15" customHeight="1"/>
-    <row r="178" ht="165" customHeight="1">
-      <c r="A178" s="87" t="inlineStr">
+    <row r="111" ht="38" customHeight="1"/>
+    <row r="112" ht="456" customHeight="1">
+      <c r="A112" s="86" t="inlineStr">
         <is>
           <t>8.3. La cubierta intemperie se embrida directamente a la placa mural del ventilador por el lado exterior; aloja el banco de filtración (HD-FILT-001) y protege el conjunto contra lluvia y radiación solar. La altura de 3,0 m exige garantizar el acceso para cambio de filtros e inspección del ventilador (plataforma fija o escalera industrial).</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="15" customHeight="1"/>
-    <row r="180" ht="15" customHeight="1"/>
-    <row r="181" ht="15" customHeight="1"/>
-    <row r="182" ht="15" customHeight="1"/>
-    <row r="183" ht="15" customHeight="1"/>
-    <row r="184" ht="135" customHeight="1">
-      <c r="A184" s="87" t="inlineStr">
+    <row r="113" ht="38" customHeight="1"/>
+    <row r="114" ht="114" customHeight="1">
+      <c r="A114" s="86" t="inlineStr">
         <is>
           <t>8.4. La malla de protección interior (jaula) se instala en la descarga del lado interior del muro, desmontable para inspección del impulsor.</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="15" customHeight="1"/>
-    <row r="186" ht="15" customHeight="1"/>
-    <row r="187" ht="150" customHeight="1">
-      <c r="A187" s="87" t="inlineStr">
+    <row r="115" ht="152" customHeight="1">
+      <c r="A115" s="86" t="inlineStr">
         <is>
           <t>8.5. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="15" customHeight="1"/>
-    <row r="189" ht="15" customHeight="1"/>
-    <row r="190" ht="15" customHeight="1"/>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" s="86" t="inlineStr">
+    <row r="116" ht="38" customHeight="1"/>
+    <row r="117" ht="76" customHeight="1">
+      <c r="A117" s="81" t="inlineStr">
         <is>
           <t>9. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="150" customHeight="1">
-      <c r="A192" s="87" t="inlineStr">
+    <row r="118" ht="608" customHeight="1">
+      <c r="A118" s="86" t="inlineStr">
         <is>
           <t>9.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), AMCA 300 (nivel sonoro), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación), SMACNA HVAC Duct Construction Standards (referencia de construcción del montaje).</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="15" customHeight="1"/>
-    <row r="194" ht="15" customHeight="1"/>
-    <row r="195" ht="15" customHeight="1"/>
-    <row r="196" ht="15" customHeight="1"/>
-    <row r="197" ht="15" customHeight="1"/>
-    <row r="198" ht="15" customHeight="1"/>
-    <row r="199" ht="15" customHeight="1"/>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" s="86" t="inlineStr">
+    <row r="119" ht="38" customHeight="1"/>
+    <row r="120" ht="76" customHeight="1">
+      <c r="A120" s="81" t="inlineStr">
         <is>
           <t>Referencia gráfica</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="15" customHeight="1"/>
-    <row r="203" ht="15" customHeight="1"/>
-    <row r="204" ht="15" customHeight="1"/>
-    <row r="205" ht="15" customHeight="1"/>
-    <row r="206" ht="15" customHeight="1"/>
-    <row r="207" ht="15" customHeight="1"/>
-    <row r="208" ht="15" customHeight="1"/>
-    <row r="209" ht="15" customHeight="1"/>
-    <row r="210" ht="15" customHeight="1"/>
-    <row r="211" ht="15" customHeight="1"/>
-    <row r="212" ht="15" customHeight="1"/>
-    <row r="213" ht="15" customHeight="1"/>
-    <row r="214" ht="15" customHeight="1"/>
-    <row r="215" ht="15" customHeight="1"/>
-    <row r="216" ht="15" customHeight="1"/>
-    <row r="217" ht="15" customHeight="1"/>
-    <row r="218" ht="15" customHeight="1"/>
-    <row r="219" ht="15" customHeight="1"/>
-    <row r="220" ht="15" customHeight="1"/>
-    <row r="221" ht="15" customHeight="1"/>
-    <row r="222" ht="15" customHeight="1"/>
-    <row r="223" ht="15" customHeight="1"/>
-    <row r="224" ht="15" customHeight="1"/>
-    <row r="225" ht="15" customHeight="1"/>
-    <row r="226" ht="15" customHeight="1"/>
-    <row r="227" ht="15" customHeight="1"/>
-    <row r="228" ht="15" customHeight="1"/>
-    <row r="229" ht="15" customHeight="1"/>
-    <row r="230" ht="15" customHeight="1"/>
-    <row r="231" ht="15" customHeight="1"/>
-    <row r="232" ht="15" customHeight="1"/>
-    <row r="233" ht="15" customHeight="1"/>
-    <row r="234" ht="15" customHeight="1"/>
-    <row r="235" ht="15" customHeight="1"/>
-    <row r="236" ht="15" customHeight="1"/>
-    <row r="237" ht="15" customHeight="1"/>
-    <row r="238" ht="15" customHeight="1"/>
-    <row r="239" ht="15" customHeight="1"/>
-    <row r="240" ht="15" customHeight="1"/>
-    <row r="241" ht="15" customHeight="1"/>
-    <row r="242" ht="15" customHeight="1"/>
-    <row r="243" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="167">
-    <mergeCell ref="A192:O199"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="I52:O52"/>
-    <mergeCell ref="A159:D159"/>
-    <mergeCell ref="A73:O81"/>
-    <mergeCell ref="A82:O90"/>
-    <mergeCell ref="F146:J146"/>
-    <mergeCell ref="A62:O63"/>
-    <mergeCell ref="A114:O122"/>
-    <mergeCell ref="A132:H132"/>
-    <mergeCell ref="A161:D161"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="I94:O94"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="M164:O164"/>
+  <mergeCells count="158">
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="K92:O92"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A120:O120"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="M104:O104"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A39:O42"/>
-    <mergeCell ref="K144:O144"/>
-    <mergeCell ref="A151:O153"/>
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="I133:O133"/>
-    <mergeCell ref="I164:L164"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="F45:J45"/>
+    <mergeCell ref="I77:O77"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="I104:L104"/>
+    <mergeCell ref="A110:O111"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="F66:J66"/>
-    <mergeCell ref="A200:O200"/>
-    <mergeCell ref="A184:O186"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="K71:O71"/>
+    <mergeCell ref="I80:O80"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="I61:O61"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="F47:J47"/>
     <mergeCell ref="I57:O57"/>
-    <mergeCell ref="A135:O139"/>
-    <mergeCell ref="K145:O145"/>
-    <mergeCell ref="I54:O54"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="I97:O97"/>
-    <mergeCell ref="K147:O147"/>
-    <mergeCell ref="I96:O96"/>
-    <mergeCell ref="I56:O56"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="I127:O127"/>
-    <mergeCell ref="A163:D163"/>
+    <mergeCell ref="F46:J46"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="F92:J92"/>
+    <mergeCell ref="A73:O73"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A107:O107"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E105:H105"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="K66:O66"/>
-    <mergeCell ref="K146:O146"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A17:O18"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="K93:O93"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A124:O124"/>
-    <mergeCell ref="I98:O98"/>
-    <mergeCell ref="F64:J64"/>
-    <mergeCell ref="E163:H163"/>
-    <mergeCell ref="A148:E148"/>
-    <mergeCell ref="A187:O189"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="A69:O71"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="K68:O68"/>
-    <mergeCell ref="F65:J65"/>
-    <mergeCell ref="F147:J147"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="I82:O82"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I10:O10"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="I99:O99"/>
-    <mergeCell ref="M160:O160"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="F89:J89"/>
+    <mergeCell ref="I59:O59"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="K94:O94"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A141:O141"/>
-    <mergeCell ref="A31:O38"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="A84:O85"/>
+    <mergeCell ref="K40:O40"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="I160:L160"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A50:O51"/>
-    <mergeCell ref="A162:D162"/>
-    <mergeCell ref="I126:O126"/>
-    <mergeCell ref="M162:O162"/>
-    <mergeCell ref="K70:O70"/>
-    <mergeCell ref="A167:O167"/>
-    <mergeCell ref="A126:H126"/>
-    <mergeCell ref="F149:J149"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A17:O25"/>
-    <mergeCell ref="A147:E147"/>
-    <mergeCell ref="I162:L162"/>
-    <mergeCell ref="A191:O191"/>
+    <mergeCell ref="F91:J91"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="F93:J93"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A98:O98"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="K65:O65"/>
-    <mergeCell ref="A61:O61"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="E104:H104"/>
+    <mergeCell ref="I62:O62"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A127:H127"/>
-    <mergeCell ref="F69:J69"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A168:O172"/>
-    <mergeCell ref="A146:E146"/>
-    <mergeCell ref="I128:O128"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A103:O113"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="F145:J145"/>
-    <mergeCell ref="A149:E149"/>
-    <mergeCell ref="E160:H160"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="K149:O149"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="M159:O159"/>
-    <mergeCell ref="A156:O158"/>
-    <mergeCell ref="I101:O101"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="I100:O100"/>
-    <mergeCell ref="F71:J71"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A51:O53"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A112:O113"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="I64:O64"/>
+    <mergeCell ref="I79:O79"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="I63:O63"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="K91:O91"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="A49:O50"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="M103:O103"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F90:J90"/>
+    <mergeCell ref="A117:O117"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="I76:O76"/>
+    <mergeCell ref="A118:O119"/>
+    <mergeCell ref="E103:H103"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
-    <mergeCell ref="E161:H161"/>
-    <mergeCell ref="A92:O92"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="A43:O47"/>
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="F67:J67"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="M161:O161"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="I53:O53"/>
-    <mergeCell ref="A178:O183"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="A25:O26"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="A108:O109"/>
+    <mergeCell ref="I75:O75"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="I130:O130"/>
+    <mergeCell ref="A104:D104"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="I161:L161"/>
-    <mergeCell ref="A173:O177"/>
-    <mergeCell ref="I55:O55"/>
-    <mergeCell ref="F148:J148"/>
-    <mergeCell ref="I132:O132"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A87:O87"/>
+    <mergeCell ref="F44:J44"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="E162:H162"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="F68:J68"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A142:O143"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="E164:H164"/>
+    <mergeCell ref="A66:O68"/>
+    <mergeCell ref="K89:O89"/>
+    <mergeCell ref="I78:O78"/>
+    <mergeCell ref="M105:O105"/>
+    <mergeCell ref="A21:O21"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="M163:O163"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="F42:J42"/>
     <mergeCell ref="I15:O15"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="I95:O95"/>
-    <mergeCell ref="A26:O28"/>
-    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="I105:L105"/>
+    <mergeCell ref="K90:O90"/>
+    <mergeCell ref="I81:O81"/>
+    <mergeCell ref="F94:J94"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="F70:J70"/>
+    <mergeCell ref="M100:O100"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="F144:J144"/>
-    <mergeCell ref="I163:L163"/>
-    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="I101:L101"/>
     <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A155:O155"/>
-    <mergeCell ref="I129:O129"/>
+    <mergeCell ref="M102:O102"/>
+    <mergeCell ref="K42:O42"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="K148:O148"/>
-    <mergeCell ref="I131:O131"/>
+    <mergeCell ref="I100:L100"/>
+    <mergeCell ref="F43:J43"/>
+    <mergeCell ref="I102:L102"/>
     <mergeCell ref="C4:L6"/>
     <mergeCell ref="I58:O58"/>
-    <mergeCell ref="A49:O49"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A160:D160"/>
-    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="A22:O23"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/build/dts/P2437-HV-DTS-001 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-001 REV0.xlsx
@@ -586,13 +586,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,7 +850,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -875,7 +875,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5715000" cy="3810000"/>
@@ -3761,104 +3761,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
     <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="13" customWidth="1" min="62" max="62"/>
     <col width="13" customWidth="1" min="63" max="63"/>
     <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
     <col width="13" customWidth="1" min="68" max="68"/>
     <col width="13" customWidth="1" min="69" max="69"/>
     <col width="13" customWidth="1" min="70" max="70"/>
-    <col width="13" customWidth="1" min="71" max="71"/>
-    <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="75" max="75"/>
+    <col width="13" customWidth="1" min="74" max="74"/>
     <col width="13" customWidth="1" min="76" max="76"/>
     <col width="13" customWidth="1" min="77" max="77"/>
     <col width="13" customWidth="1" min="78" max="78"/>
     <col width="13" customWidth="1" min="79" max="79"/>
     <col width="13" customWidth="1" min="80" max="80"/>
     <col width="13" customWidth="1" min="81" max="81"/>
-    <col width="13" customWidth="1" min="82" max="82"/>
-    <col width="13" customWidth="1" min="84" max="84"/>
     <col width="13" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="87" max="87"/>
+    <col width="13" customWidth="1" min="88" max="88"/>
     <col width="13" customWidth="1" min="89" max="89"/>
     <col width="13" customWidth="1" min="90" max="90"/>
     <col width="13" customWidth="1" min="91" max="91"/>
     <col width="13" customWidth="1" min="92" max="92"/>
-    <col width="13" customWidth="1" min="93" max="93"/>
     <col width="13" customWidth="1" min="94" max="94"/>
-    <col width="13" customWidth="1" min="98" max="98"/>
-    <col width="13" customWidth="1" min="100" max="100"/>
     <col width="13" customWidth="1" min="101" max="101"/>
-    <col width="13" customWidth="1" min="102" max="102"/>
     <col width="13" customWidth="1" min="103" max="103"/>
-    <col width="13" customWidth="1" min="104" max="104"/>
-    <col width="13" customWidth="1" min="105" max="105"/>
-    <col width="13" customWidth="1" min="107" max="107"/>
-    <col width="13" customWidth="1" min="108" max="108"/>
-    <col width="13" customWidth="1" min="109" max="109"/>
-    <col width="13" customWidth="1" min="110" max="110"/>
-    <col width="13" customWidth="1" min="111" max="111"/>
-    <col width="13" customWidth="1" min="112" max="112"/>
-    <col width="13" customWidth="1" min="113" max="113"/>
-    <col width="13" customWidth="1" min="117" max="117"/>
-    <col width="13" customWidth="1" min="118" max="118"/>
-    <col width="13" customWidth="1" min="119" max="119"/>
-    <col width="13" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4068,14 +4043,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="190" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: ventilador axial mural de inyección</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4100,7 +4075,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4125,7 +4100,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4140,7 +4115,7 @@
       <c r="H12" s="84" t="n"/>
       <c r="I12" s="83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" s="84" t="n"/>
@@ -4150,7 +4125,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4175,7 +4150,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="152" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4200,7 +4175,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="114" customHeight="1">
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4225,291 +4200,447 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="38" customHeight="1"/>
-    <row r="17" ht="684" customHeight="1">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png y Montaje/Descripcion_Tecnica_Sistema_Ventilacion_Inyeccion_2260CFM_v2.md): ventilador axial mural (placa mural) Ø560 mm, transmisión directa, con cubierta intemperie que aloja el banco de filtración, estructura de unión pernada al muro y malla de protección interior. Se conservan caudal, ΔP de diseño, filtración MERV 8 + MERV 13-14, rejillas y ausencia de presurización.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1"/>
-    <row r="19" ht="152" customHeight="1">
+    <row r="16" ht="50" customHeight="1"/>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>1. Servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="650" customHeight="1">
+      <c r="A18" s="85" t="inlineStr">
+        <is>
+          <t>1.1. Impulsión de aire exterior filtrado (MERV 8 + MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="300" customHeight="1">
       <c r="A19" s="85" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial en lugar de centrífugo, sin instrumentación de presión diferencial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1"/>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
-        <is>
-          <t>1. Servicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="646" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
-        <is>
-          <t>1.1. Impulsión de aire exterior filtrado (MERV 8 + MERV 13-14) al laboratorio de análisis industrial para ventilación general a 12 renovaciones/h (3 840 m³/h sobre 320 m³), con exclusión de polvo, insectos y objetos extraños del aire de impulsión. Descarga directa al recinto a través del muro, sin red de ductos de distribución; el aire sale del recinto por rejillas de descarga libre a la atmósfera. El sistema no mantiene consigna de presión interior. Operación continua.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1"/>
-    <row r="24" ht="152" customHeight="1">
-      <c r="A24" s="86" t="inlineStr">
-        <is>
           <t>1.2. Ambiente de instalación: exterior o semi-cubierto dentro de planta de hipoclorito de calcio; atmósfera con Cl₂/ClO⁻, polvo de Ca(ClO)₂ y humedad relativa media 84 %. Servicio clasificado como altamente corrosivo.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="380" customHeight="1">
-      <c r="A25" s="86" t="inlineStr">
+    <row r="20" ht="400" customHeight="1">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>1.3. Configuración de montaje uniforme con la planta (secuencia de flujo): exterior → cubierta intemperie (aloja prefiltro MERV 8 y filtro final MERV 13-14) → ventilador axial mural → paso por muro con estructura de unión → malla de protección interior → descarga al recinto.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="38" customHeight="1"/>
-    <row r="27" ht="38" customHeight="1"/>
-    <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="81" t="inlineStr">
+    <row r="21" ht="50" customHeight="1"/>
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>2. Condiciones de sitio</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="87" t="inlineStr">
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones ambientales de diseño (fuentes en informe_investigacion.md §3.1; consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="82" t="inlineStr">
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B30" s="82" t="n"/>
-      <c r="C30" s="82" t="n"/>
-      <c r="D30" s="82" t="n"/>
-      <c r="E30" s="82" t="n"/>
-      <c r="F30" s="82" t="n"/>
-      <c r="G30" s="82" t="n"/>
-      <c r="H30" s="82" t="n"/>
-      <c r="I30" s="82" t="inlineStr">
+      <c r="B24" s="82" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J30" s="82" t="n"/>
-      <c r="K30" s="82" t="n"/>
-      <c r="L30" s="82" t="n"/>
-      <c r="M30" s="82" t="n"/>
-      <c r="N30" s="82" t="n"/>
-      <c r="O30" s="82" t="n"/>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="83" t="inlineStr">
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="82" t="n"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="83" t="inlineStr">
         <is>
           <t>Altitud</t>
         </is>
       </c>
-      <c r="B31" s="84" t="n"/>
-      <c r="C31" s="84" t="n"/>
-      <c r="D31" s="84" t="n"/>
-      <c r="E31" s="84" t="n"/>
-      <c r="F31" s="84" t="n"/>
-      <c r="G31" s="84" t="n"/>
-      <c r="H31" s="84" t="n"/>
-      <c r="I31" s="83" t="inlineStr">
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="83" t="inlineStr">
         <is>
           <t>2 558 msnm</t>
         </is>
       </c>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="84" t="n"/>
-      <c r="L31" s="84" t="n"/>
-      <c r="M31" s="84" t="n"/>
-      <c r="N31" s="84" t="n"/>
-      <c r="O31" s="84" t="n"/>
-    </row>
-    <row r="32" ht="76" customHeight="1">
-      <c r="A32" s="83" t="inlineStr">
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+    </row>
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Presión atmosférica</t>
         </is>
       </c>
-      <c r="B32" s="84" t="n"/>
-      <c r="C32" s="84" t="n"/>
-      <c r="D32" s="84" t="n"/>
-      <c r="E32" s="84" t="n"/>
-      <c r="F32" s="84" t="n"/>
-      <c r="G32" s="84" t="n"/>
-      <c r="H32" s="84" t="n"/>
-      <c r="I32" s="83" t="inlineStr">
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
+      <c r="H26" s="84" t="n"/>
+      <c r="I26" s="83" t="inlineStr">
         <is>
           <t>74.1 kPa</t>
         </is>
       </c>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="84" t="n"/>
-      <c r="L32" s="84" t="n"/>
-      <c r="M32" s="84" t="n"/>
-      <c r="N32" s="84" t="n"/>
-      <c r="O32" s="84" t="n"/>
-    </row>
-    <row r="33" ht="152" customHeight="1">
-      <c r="A33" s="83" t="inlineStr">
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="84" t="n"/>
+      <c r="L26" s="84" t="n"/>
+      <c r="M26" s="84" t="n"/>
+      <c r="N26" s="84" t="n"/>
+      <c r="O26" s="84" t="n"/>
+    </row>
+    <row r="27" ht="200" customHeight="1">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Temperatura de diseño verano / invierno / media</t>
         </is>
       </c>
-      <c r="B33" s="84" t="n"/>
-      <c r="C33" s="84" t="n"/>
-      <c r="D33" s="84" t="n"/>
-      <c r="E33" s="84" t="n"/>
-      <c r="F33" s="84" t="n"/>
-      <c r="G33" s="84" t="n"/>
-      <c r="H33" s="84" t="n"/>
-      <c r="I33" s="83" t="inlineStr">
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
+      <c r="H27" s="84" t="n"/>
+      <c r="I27" s="83" t="inlineStr">
         <is>
           <t>21 °C / 3 °C / 14 °C</t>
         </is>
       </c>
-      <c r="J33" s="84" t="n"/>
-      <c r="K33" s="84" t="n"/>
-      <c r="L33" s="84" t="n"/>
-      <c r="M33" s="84" t="n"/>
-      <c r="N33" s="84" t="n"/>
-      <c r="O33" s="84" t="n"/>
-    </row>
-    <row r="34" ht="76" customHeight="1">
-      <c r="A34" s="83" t="inlineStr">
+      <c r="J27" s="84" t="n"/>
+      <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+    </row>
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="83" t="inlineStr">
         <is>
           <t>Humedad relativa media anual</t>
         </is>
       </c>
-      <c r="B34" s="84" t="n"/>
-      <c r="C34" s="84" t="n"/>
-      <c r="D34" s="84" t="n"/>
-      <c r="E34" s="84" t="n"/>
-      <c r="F34" s="84" t="n"/>
-      <c r="G34" s="84" t="n"/>
-      <c r="H34" s="84" t="n"/>
-      <c r="I34" s="83" t="inlineStr">
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="83" t="inlineStr">
         <is>
           <t>84 %</t>
         </is>
       </c>
-      <c r="J34" s="84" t="n"/>
-      <c r="K34" s="84" t="n"/>
-      <c r="L34" s="84" t="n"/>
-      <c r="M34" s="84" t="n"/>
-      <c r="N34" s="84" t="n"/>
-      <c r="O34" s="84" t="n"/>
-    </row>
-    <row r="35" ht="152" customHeight="1">
+      <c r="J28" s="84" t="n"/>
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="84" t="n"/>
+      <c r="N28" s="84" t="n"/>
+      <c r="O28" s="84" t="n"/>
+    </row>
+    <row r="29" ht="200" customHeight="1">
+      <c r="A29" s="83" t="inlineStr">
+        <is>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="83" t="inlineStr">
+        <is>
+          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
+        </is>
+      </c>
+      <c r="J29" s="84" t="n"/>
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+    </row>
+    <row r="30" ht="200" customHeight="1">
+      <c r="A30" s="83" t="inlineStr">
+        <is>
+          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B30" s="84" t="n"/>
+      <c r="C30" s="84" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="84" t="n"/>
+      <c r="F30" s="84" t="n"/>
+      <c r="G30" s="84" t="n"/>
+      <c r="H30" s="84" t="n"/>
+      <c r="I30" s="83" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="J30" s="84" t="n"/>
+      <c r="K30" s="84" t="n"/>
+      <c r="L30" s="84" t="n"/>
+      <c r="M30" s="84" t="n"/>
+      <c r="N30" s="84" t="n"/>
+      <c r="O30" s="84" t="n"/>
+    </row>
+    <row r="31" ht="50" customHeight="1"/>
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="81" t="inlineStr">
+        <is>
+          <t>3. Punto de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="82" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="n"/>
+      <c r="C34" s="82" t="n"/>
+      <c r="D34" s="82" t="n"/>
+      <c r="E34" s="82" t="n"/>
+      <c r="F34" s="82" t="inlineStr">
+        <is>
+          <t>En el sitio (ρ = 0.88 kg/m³)</t>
+        </is>
+      </c>
+      <c r="G34" s="82" t="n"/>
+      <c r="H34" s="82" t="n"/>
+      <c r="I34" s="82" t="n"/>
+      <c r="J34" s="82" t="n"/>
+      <c r="K34" s="82" t="inlineStr">
+        <is>
+          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="L34" s="82" t="n"/>
+      <c r="M34" s="82" t="n"/>
+      <c r="N34" s="82" t="n"/>
+      <c r="O34" s="82" t="n"/>
+    </row>
+    <row r="35" ht="200" customHeight="1">
       <c r="A35" s="83" t="inlineStr">
         <is>
-          <t>Densidad del aire de diseño</t>
+          <t>Caudal</t>
         </is>
       </c>
       <c r="B35" s="84" t="n"/>
       <c r="C35" s="84" t="n"/>
       <c r="D35" s="84" t="n"/>
       <c r="E35" s="84" t="n"/>
-      <c r="F35" s="84" t="n"/>
+      <c r="F35" s="83" t="inlineStr">
+        <is>
+          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
+        </is>
+      </c>
       <c r="G35" s="84" t="n"/>
       <c r="H35" s="84" t="n"/>
-      <c r="I35" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ a 20 °C (0.87 kg/m³ en condición 0.4 %)</t>
-        </is>
-      </c>
+      <c r="I35" s="84" t="n"/>
       <c r="J35" s="84" t="n"/>
-      <c r="K35" s="84" t="n"/>
+      <c r="K35" s="83" t="inlineStr">
+        <is>
+          <t>Sin cambio (máquina de volumen constante)</t>
+        </is>
+      </c>
       <c r="L35" s="84" t="n"/>
       <c r="M35" s="84" t="n"/>
       <c r="N35" s="84" t="n"/>
       <c r="O35" s="84" t="n"/>
     </row>
-    <row r="36" ht="152" customHeight="1">
+    <row r="36" ht="200" customHeight="1">
       <c r="A36" s="83" t="inlineStr">
         <is>
-          <t>Factor de densidad k (vs. catálogo 1.2 kg/m³)</t>
+          <t>ΔP total, escenario de diseño (filtro cargado)</t>
         </is>
       </c>
       <c r="B36" s="84" t="n"/>
       <c r="C36" s="84" t="n"/>
       <c r="D36" s="84" t="n"/>
       <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
+      <c r="F36" s="83" t="inlineStr">
+        <is>
+          <t>165 Pa</t>
+        </is>
+      </c>
       <c r="G36" s="84" t="n"/>
       <c r="H36" s="84" t="n"/>
-      <c r="I36" s="83" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
+      <c r="I36" s="84" t="n"/>
       <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
+      <c r="K36" s="83" t="inlineStr">
+        <is>
+          <t>225 Pa</t>
+        </is>
+      </c>
       <c r="L36" s="84" t="n"/>
       <c r="M36" s="84" t="n"/>
       <c r="N36" s="84" t="n"/>
       <c r="O36" s="84" t="n"/>
     </row>
-    <row r="37" ht="38" customHeight="1"/>
-    <row r="38" ht="76" customHeight="1">
-      <c r="A38" s="81" t="inlineStr">
-        <is>
-          <t>3. Punto de trabajo</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="76" customHeight="1">
-      <c r="A39" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 2. Punto de trabajo en el sitio y punto equivalente de selección en catálogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="114" customHeight="1">
-      <c r="A40" s="82" t="inlineStr">
-        <is>
-          <t>Magnitud</t>
-        </is>
-      </c>
-      <c r="B40" s="82" t="n"/>
-      <c r="C40" s="82" t="n"/>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="inlineStr">
-        <is>
-          <t>En el sitio (ρ = 0.88 kg/m³)</t>
-        </is>
-      </c>
-      <c r="G40" s="82" t="n"/>
-      <c r="H40" s="82" t="n"/>
-      <c r="I40" s="82" t="n"/>
-      <c r="J40" s="82" t="n"/>
-      <c r="K40" s="82" t="inlineStr">
-        <is>
-          <t>Equivalente catálogo (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="L40" s="82" t="n"/>
-      <c r="M40" s="82" t="n"/>
-      <c r="N40" s="82" t="n"/>
-      <c r="O40" s="82" t="n"/>
-    </row>
-    <row r="41" ht="152" customHeight="1">
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="83" t="inlineStr">
+        <is>
+          <t>ΔP total, escenario filtro limpio</t>
+        </is>
+      </c>
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="84" t="n"/>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="84" t="n"/>
+      <c r="F37" s="83" t="inlineStr">
+        <is>
+          <t>70 Pa</t>
+        </is>
+      </c>
+      <c r="G37" s="84" t="n"/>
+      <c r="H37" s="84" t="n"/>
+      <c r="I37" s="84" t="n"/>
+      <c r="J37" s="84" t="n"/>
+      <c r="K37" s="83" t="inlineStr">
+        <is>
+          <t>95 Pa</t>
+        </is>
+      </c>
+      <c r="L37" s="84" t="n"/>
+      <c r="M37" s="84" t="n"/>
+      <c r="N37" s="84" t="n"/>
+      <c r="O37" s="84" t="n"/>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="83" t="inlineStr">
+        <is>
+          <t>Composición ΔP diseño</t>
+        </is>
+      </c>
+      <c r="B38" s="84" t="n"/>
+      <c r="C38" s="84" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="84" t="n"/>
+      <c r="F38" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 154 Pa + rejillas 11 Pa</t>
+        </is>
+      </c>
+      <c r="G38" s="84" t="n"/>
+      <c r="H38" s="84" t="n"/>
+      <c r="I38" s="84" t="n"/>
+      <c r="J38" s="84" t="n"/>
+      <c r="K38" s="83" t="inlineStr">
+        <is>
+          <t>Filtro 210 Pa + 15 Pa</t>
+        </is>
+      </c>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="83" t="inlineStr">
+        <is>
+          <t>Diámetro del impulsor (uniformidad planta)</t>
+        </is>
+      </c>
+      <c r="B39" s="84" t="n"/>
+      <c r="C39" s="84" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="83" t="inlineStr">
+        <is>
+          <t>560 mm (22 in)</t>
+        </is>
+      </c>
+      <c r="G39" s="84" t="n"/>
+      <c r="H39" s="84" t="n"/>
+      <c r="I39" s="84" t="n"/>
+      <c r="J39" s="84" t="n"/>
+      <c r="K39" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="84" t="n"/>
+      <c r="M39" s="84" t="n"/>
+      <c r="N39" s="84" t="n"/>
+      <c r="O39" s="84" t="n"/>
+    </row>
+    <row r="40" ht="100" customHeight="1">
+      <c r="A40" s="83" t="inlineStr">
+        <is>
+          <t>Velocidad en boca (Ø560 mm)</t>
+        </is>
+      </c>
+      <c r="B40" s="84" t="n"/>
+      <c r="C40" s="84" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="83" t="inlineStr">
+        <is>
+          <t>4.33 m/s</t>
+        </is>
+      </c>
+      <c r="G40" s="84" t="n"/>
+      <c r="H40" s="84" t="n"/>
+      <c r="I40" s="84" t="n"/>
+      <c r="J40" s="84" t="n"/>
+      <c r="K40" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+    </row>
+    <row r="41" ht="150" customHeight="1">
       <c r="A41" s="83" t="inlineStr">
         <is>
-          <t>Caudal</t>
+          <t>Potencia teórica de aire (η = 0.55)</t>
         </is>
       </c>
       <c r="B41" s="84" t="n"/>
@@ -4518,7 +4649,7 @@
       <c r="E41" s="84" t="n"/>
       <c r="F41" s="83" t="inlineStr">
         <is>
-          <t>3 840 m³/h = 64 m³/min = 1.0667 m³/s = 2 260 CFM</t>
+          <t>0.320 kW = 0.43 HP</t>
         </is>
       </c>
       <c r="G41" s="84" t="n"/>
@@ -4527,7 +4658,7 @@
       <c r="J41" s="84" t="n"/>
       <c r="K41" s="83" t="inlineStr">
         <is>
-          <t>Sin cambio (máquina de volumen constante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L41" s="84" t="n"/>
@@ -4535,392 +4666,296 @@
       <c r="N41" s="84" t="n"/>
       <c r="O41" s="84" t="n"/>
     </row>
-    <row r="42" ht="152" customHeight="1">
-      <c r="A42" s="83" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario de diseño (filtro cargado)</t>
-        </is>
-      </c>
-      <c r="B42" s="84" t="n"/>
-      <c r="C42" s="84" t="n"/>
-      <c r="D42" s="84" t="n"/>
-      <c r="E42" s="84" t="n"/>
-      <c r="F42" s="83" t="inlineStr">
-        <is>
-          <t>165 Pa</t>
-        </is>
-      </c>
-      <c r="G42" s="84" t="n"/>
-      <c r="H42" s="84" t="n"/>
-      <c r="I42" s="84" t="n"/>
-      <c r="J42" s="84" t="n"/>
-      <c r="K42" s="83" t="inlineStr">
-        <is>
-          <t>225 Pa</t>
-        </is>
-      </c>
-      <c r="L42" s="84" t="n"/>
-      <c r="M42" s="84" t="n"/>
-      <c r="N42" s="84" t="n"/>
-      <c r="O42" s="84" t="n"/>
-    </row>
-    <row r="43" ht="114" customHeight="1">
-      <c r="A43" s="83" t="inlineStr">
-        <is>
-          <t>ΔP total, escenario filtro limpio</t>
-        </is>
-      </c>
-      <c r="B43" s="84" t="n"/>
-      <c r="C43" s="84" t="n"/>
-      <c r="D43" s="84" t="n"/>
-      <c r="E43" s="84" t="n"/>
-      <c r="F43" s="83" t="inlineStr">
-        <is>
-          <t>70 Pa</t>
-        </is>
-      </c>
-      <c r="G43" s="84" t="n"/>
-      <c r="H43" s="84" t="n"/>
-      <c r="I43" s="84" t="n"/>
-      <c r="J43" s="84" t="n"/>
-      <c r="K43" s="83" t="inlineStr">
-        <is>
-          <t>95 Pa</t>
-        </is>
-      </c>
-      <c r="L43" s="84" t="n"/>
-      <c r="M43" s="84" t="n"/>
-      <c r="N43" s="84" t="n"/>
-      <c r="O43" s="84" t="n"/>
-    </row>
-    <row r="44" ht="114" customHeight="1">
-      <c r="A44" s="83" t="inlineStr">
-        <is>
-          <t>Composición ΔP diseño</t>
-        </is>
-      </c>
-      <c r="B44" s="84" t="n"/>
-      <c r="C44" s="84" t="n"/>
-      <c r="D44" s="84" t="n"/>
-      <c r="E44" s="84" t="n"/>
-      <c r="F44" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 154 Pa + rejillas 11 Pa</t>
-        </is>
-      </c>
-      <c r="G44" s="84" t="n"/>
-      <c r="H44" s="84" t="n"/>
-      <c r="I44" s="84" t="n"/>
-      <c r="J44" s="84" t="n"/>
-      <c r="K44" s="83" t="inlineStr">
-        <is>
-          <t>Filtro 210 Pa + 15 Pa</t>
-        </is>
-      </c>
-      <c r="L44" s="84" t="n"/>
-      <c r="M44" s="84" t="n"/>
-      <c r="N44" s="84" t="n"/>
-      <c r="O44" s="84" t="n"/>
-    </row>
-    <row r="45" ht="114" customHeight="1">
-      <c r="A45" s="83" t="inlineStr">
-        <is>
-          <t>Diámetro del impulsor (uniformidad planta)</t>
-        </is>
-      </c>
-      <c r="B45" s="84" t="n"/>
-      <c r="C45" s="84" t="n"/>
-      <c r="D45" s="84" t="n"/>
-      <c r="E45" s="84" t="n"/>
-      <c r="F45" s="83" t="inlineStr">
-        <is>
-          <t>560 mm (22 in)</t>
-        </is>
-      </c>
-      <c r="G45" s="84" t="n"/>
-      <c r="H45" s="84" t="n"/>
-      <c r="I45" s="84" t="n"/>
-      <c r="J45" s="84" t="n"/>
-      <c r="K45" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="84" t="n"/>
-      <c r="M45" s="84" t="n"/>
-      <c r="N45" s="84" t="n"/>
-      <c r="O45" s="84" t="n"/>
-    </row>
-    <row r="46" ht="76" customHeight="1">
-      <c r="A46" s="83" t="inlineStr">
-        <is>
-          <t>Velocidad en boca (Ø560 mm)</t>
-        </is>
-      </c>
-      <c r="B46" s="84" t="n"/>
-      <c r="C46" s="84" t="n"/>
-      <c r="D46" s="84" t="n"/>
-      <c r="E46" s="84" t="n"/>
-      <c r="F46" s="83" t="inlineStr">
-        <is>
-          <t>4.33 m/s</t>
-        </is>
-      </c>
-      <c r="G46" s="84" t="n"/>
-      <c r="H46" s="84" t="n"/>
-      <c r="I46" s="84" t="n"/>
-      <c r="J46" s="84" t="n"/>
-      <c r="K46" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="84" t="n"/>
-      <c r="M46" s="84" t="n"/>
-      <c r="N46" s="84" t="n"/>
-      <c r="O46" s="84" t="n"/>
-    </row>
-    <row r="47" ht="114" customHeight="1">
-      <c r="A47" s="83" t="inlineStr">
-        <is>
-          <t>Potencia teórica de aire (η = 0.55)</t>
-        </is>
-      </c>
-      <c r="B47" s="84" t="n"/>
-      <c r="C47" s="84" t="n"/>
-      <c r="D47" s="84" t="n"/>
-      <c r="E47" s="84" t="n"/>
-      <c r="F47" s="83" t="inlineStr">
-        <is>
-          <t>0.320 kW = 0.43 HP</t>
-        </is>
-      </c>
-      <c r="G47" s="84" t="n"/>
-      <c r="H47" s="84" t="n"/>
-      <c r="I47" s="84" t="n"/>
-      <c r="J47" s="84" t="n"/>
-      <c r="K47" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="84" t="n"/>
-      <c r="M47" s="84" t="n"/>
-      <c r="N47" s="84" t="n"/>
-      <c r="O47" s="84" t="n"/>
-    </row>
-    <row r="48" ht="38" customHeight="1"/>
-    <row r="49" ht="684" customHeight="1">
-      <c r="A49" s="86" t="inlineStr">
+    <row r="42" ht="50" customHeight="1"/>
+    <row r="43" ht="700" customHeight="1">
+      <c r="A43" s="85" t="inlineStr">
         <is>
           <t>3.1. La selección se efectúa sobre catálogo a densidad estándar en el punto 3 840 m³/h @ 225 Pa, aplicando las leyes de los ventiladores (P ∝ ρ, potencia ∝ ρ, Q constante) según Twin City Fan FE-1600 (http://eu.tcf.com/wp-content/uploads/sites/4/2018/06/Temperature-Altitude-Effects-on-Fans-FE-1600-1.pdf) (consulta 2026-07-23). El tamaño comercial queda fijado en Ø560 mm por uniformidad con el montaje típico instalado en la planta; las RPM exactas se confirman con el software de selección del fabricante.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="38" customHeight="1"/>
-    <row r="51" ht="494" customHeight="1">
-      <c r="A51" s="86" t="inlineStr">
+    <row r="44" ht="700" customHeight="1">
+      <c r="A44" s="85" t="inlineStr">
         <is>
           <t>3.2. El ventilador seleccionado entregará en el sitio el mismo caudal a las mismas RPM, con presión y potencia reducidas en el factor 0.733; la eficiencia mínima exigible es 0.55 (dato provisional, a verificar contra la curva de la selección final). El margen sobre la potencia de eje (motor provisional 0.75 HP vs. 0.43 HP teóricos, con margen de servicio 1.5) absorbe el derateo por altitud de NEMA MG-1 (≈9 % a 2 558 msnm) y el factor de servicio; la potencia final del motor se confirma con la curva de catálogo de la selección.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1"/>
-    <row r="53" ht="38" customHeight="1"/>
-    <row r="54" ht="38" customHeight="1"/>
-    <row r="55" ht="114" customHeight="1">
-      <c r="A55" s="81" t="inlineStr">
+    <row r="45" ht="50" customHeight="1"/>
+    <row r="46" ht="150" customHeight="1">
+      <c r="A46" s="81" t="inlineStr">
         <is>
           <t>4. Tipo y materiales de construcción</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="A56" s="87" t="inlineStr">
+    <row r="47" ht="50" customHeight="1">
+      <c r="A47" s="86" t="inlineStr">
         <is>
           <t>Tabla 3. Requisitos de construcción.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="A57" s="82" t="inlineStr">
+    <row r="48" ht="50" customHeight="1">
+      <c r="A48" s="82" t="inlineStr">
         <is>
           <t>Componente</t>
         </is>
       </c>
-      <c r="B57" s="82" t="n"/>
-      <c r="C57" s="82" t="n"/>
-      <c r="D57" s="82" t="n"/>
-      <c r="E57" s="82" t="n"/>
-      <c r="F57" s="82" t="n"/>
-      <c r="G57" s="82" t="n"/>
-      <c r="H57" s="82" t="n"/>
-      <c r="I57" s="82" t="inlineStr">
+      <c r="B48" s="82" t="n"/>
+      <c r="C48" s="82" t="n"/>
+      <c r="D48" s="82" t="n"/>
+      <c r="E48" s="82" t="n"/>
+      <c r="F48" s="82" t="n"/>
+      <c r="G48" s="82" t="n"/>
+      <c r="H48" s="82" t="n"/>
+      <c r="I48" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J57" s="82" t="n"/>
-      <c r="K57" s="82" t="n"/>
-      <c r="L57" s="82" t="n"/>
-      <c r="M57" s="82" t="n"/>
-      <c r="N57" s="82" t="n"/>
-      <c r="O57" s="82" t="n"/>
-    </row>
-    <row r="58" ht="380" customHeight="1">
-      <c r="A58" s="83" t="inlineStr">
+      <c r="J48" s="82" t="n"/>
+      <c r="K48" s="82" t="n"/>
+      <c r="L48" s="82" t="n"/>
+      <c r="M48" s="82" t="n"/>
+      <c r="N48" s="82" t="n"/>
+      <c r="O48" s="82" t="n"/>
+    </row>
+    <row r="49" ht="500" customHeight="1">
+      <c r="A49" s="83" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B58" s="84" t="n"/>
-      <c r="C58" s="84" t="n"/>
-      <c r="D58" s="84" t="n"/>
-      <c r="E58" s="84" t="n"/>
-      <c r="F58" s="84" t="n"/>
-      <c r="G58" s="84" t="n"/>
-      <c r="H58" s="84" t="n"/>
-      <c r="I58" s="83" t="inlineStr">
+      <c r="B49" s="84" t="n"/>
+      <c r="C49" s="84" t="n"/>
+      <c r="D49" s="84" t="n"/>
+      <c r="E49" s="84" t="n"/>
+      <c r="F49" s="84" t="n"/>
+      <c r="G49" s="84" t="n"/>
+      <c r="H49" s="84" t="n"/>
+      <c r="I49" s="83" t="inlineStr">
         <is>
           <t>Axial mural (placa mural / wall fan), Ø560 mm, transmisión directa (motor en el cubo del impulsor); montaje en muro mediante estructura de unión</t>
         </is>
       </c>
-      <c r="J58" s="84" t="n"/>
-      <c r="K58" s="84" t="n"/>
-      <c r="L58" s="84" t="n"/>
-      <c r="M58" s="84" t="n"/>
-      <c r="N58" s="84" t="n"/>
-      <c r="O58" s="84" t="n"/>
-    </row>
-    <row r="59" ht="456" customHeight="1">
-      <c r="A59" s="83" t="inlineStr">
+      <c r="J49" s="84" t="n"/>
+      <c r="K49" s="84" t="n"/>
+      <c r="L49" s="84" t="n"/>
+      <c r="M49" s="84" t="n"/>
+      <c r="N49" s="84" t="n"/>
+      <c r="O49" s="84" t="n"/>
+    </row>
+    <row r="50" ht="600" customHeight="1">
+      <c r="A50" s="83" t="inlineStr">
         <is>
           <t>Carcasa, placa mural y rodete</t>
         </is>
       </c>
-      <c r="B59" s="84" t="n"/>
-      <c r="C59" s="84" t="n"/>
-      <c r="D59" s="84" t="n"/>
-      <c r="E59" s="84" t="n"/>
-      <c r="F59" s="84" t="n"/>
-      <c r="G59" s="84" t="n"/>
-      <c r="H59" s="84" t="n"/>
-      <c r="I59" s="83" t="inlineStr">
+      <c r="B50" s="84" t="n"/>
+      <c r="C50" s="84" t="n"/>
+      <c r="D50" s="84" t="n"/>
+      <c r="E50" s="84" t="n"/>
+      <c r="F50" s="84" t="n"/>
+      <c r="G50" s="84" t="n"/>
+      <c r="H50" s="84" t="n"/>
+      <c r="I50" s="83" t="inlineStr">
         <is>
           <t>PRFV con resina viniléster, laminado según ASTM C582/D4167; alternativa: acero con recubrimiento epóxico anticorrosivo (segunda línea, con inspección programada)</t>
         </is>
       </c>
-      <c r="J59" s="84" t="n"/>
-      <c r="K59" s="84" t="n"/>
-      <c r="L59" s="84" t="n"/>
-      <c r="M59" s="84" t="n"/>
-      <c r="N59" s="84" t="n"/>
-      <c r="O59" s="84" t="n"/>
-    </row>
-    <row r="60" ht="190" customHeight="1">
-      <c r="A60" s="83" t="inlineStr">
+      <c r="J50" s="84" t="n"/>
+      <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
+      <c r="O50" s="84" t="n"/>
+    </row>
+    <row r="51" ht="250" customHeight="1">
+      <c r="A51" s="83" t="inlineStr">
         <is>
           <t>Elementos metálicos en la corriente</t>
         </is>
       </c>
-      <c r="B60" s="84" t="n"/>
-      <c r="C60" s="84" t="n"/>
-      <c r="D60" s="84" t="n"/>
-      <c r="E60" s="84" t="n"/>
-      <c r="F60" s="84" t="n"/>
-      <c r="G60" s="84" t="n"/>
-      <c r="H60" s="84" t="n"/>
-      <c r="I60" s="83" t="inlineStr">
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="84" t="n"/>
+      <c r="D51" s="84" t="n"/>
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="84" t="n"/>
+      <c r="G51" s="84" t="n"/>
+      <c r="H51" s="84" t="n"/>
+      <c r="I51" s="83" t="inlineStr">
         <is>
           <t>Mínimos; eje del motor en acero inoxidable con protección anticorrosiva</t>
         </is>
       </c>
-      <c r="J60" s="84" t="n"/>
-      <c r="K60" s="84" t="n"/>
-      <c r="L60" s="84" t="n"/>
-      <c r="M60" s="84" t="n"/>
-      <c r="N60" s="84" t="n"/>
-      <c r="O60" s="84" t="n"/>
-    </row>
-    <row r="61" ht="570" customHeight="1">
-      <c r="A61" s="83" t="inlineStr">
+      <c r="J51" s="84" t="n"/>
+      <c r="K51" s="84" t="n"/>
+      <c r="L51" s="84" t="n"/>
+      <c r="M51" s="84" t="n"/>
+      <c r="N51" s="84" t="n"/>
+      <c r="O51" s="84" t="n"/>
+    </row>
+    <row r="52" ht="750" customHeight="1">
+      <c r="A52" s="83" t="inlineStr">
         <is>
           <t>Motor en la corriente de aire</t>
         </is>
       </c>
-      <c r="B61" s="84" t="n"/>
-      <c r="C61" s="84" t="n"/>
-      <c r="D61" s="84" t="n"/>
-      <c r="E61" s="84" t="n"/>
-      <c r="F61" s="84" t="n"/>
-      <c r="G61" s="84" t="n"/>
-      <c r="H61" s="84" t="n"/>
-      <c r="I61" s="83" t="inlineStr">
+      <c r="B52" s="84" t="n"/>
+      <c r="C52" s="84" t="n"/>
+      <c r="D52" s="84" t="n"/>
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="84" t="n"/>
+      <c r="G52" s="84" t="n"/>
+      <c r="H52" s="84" t="n"/>
+      <c r="I52" s="83" t="inlineStr">
         <is>
           <t>Encapsulado severe duty (ver Tabla 4) — la transmisión directa ubica el motor dentro de la corriente; se exige ejecución anticorrosiva reforzada, criterio ya operado por la planta en sus montajes típicos</t>
         </is>
       </c>
-      <c r="J61" s="84" t="n"/>
-      <c r="K61" s="84" t="n"/>
-      <c r="L61" s="84" t="n"/>
-      <c r="M61" s="84" t="n"/>
-      <c r="N61" s="84" t="n"/>
-      <c r="O61" s="84" t="n"/>
-    </row>
-    <row r="62" ht="152" customHeight="1">
-      <c r="A62" s="83" t="inlineStr">
+      <c r="J52" s="84" t="n"/>
+      <c r="K52" s="84" t="n"/>
+      <c r="L52" s="84" t="n"/>
+      <c r="M52" s="84" t="n"/>
+      <c r="N52" s="84" t="n"/>
+      <c r="O52" s="84" t="n"/>
+    </row>
+    <row r="53" ht="200" customHeight="1">
+      <c r="A53" s="83" t="inlineStr">
         <is>
           <t>Construcción contra chispa</t>
         </is>
       </c>
-      <c r="B62" s="84" t="n"/>
-      <c r="C62" s="84" t="n"/>
-      <c r="D62" s="84" t="n"/>
-      <c r="E62" s="84" t="n"/>
-      <c r="F62" s="84" t="n"/>
-      <c r="G62" s="84" t="n"/>
-      <c r="H62" s="84" t="n"/>
-      <c r="I62" s="83" t="inlineStr">
+      <c r="B53" s="84" t="n"/>
+      <c r="C53" s="84" t="n"/>
+      <c r="D53" s="84" t="n"/>
+      <c r="E53" s="84" t="n"/>
+      <c r="F53" s="84" t="n"/>
+      <c r="G53" s="84" t="n"/>
+      <c r="H53" s="84" t="n"/>
+      <c r="I53" s="83" t="inlineStr">
         <is>
           <t>AMCA 99 Spark A (dato típico de especificación para PRFV)</t>
         </is>
       </c>
-      <c r="J62" s="84" t="n"/>
-      <c r="K62" s="84" t="n"/>
-      <c r="L62" s="84" t="n"/>
-      <c r="M62" s="84" t="n"/>
-      <c r="N62" s="84" t="n"/>
-      <c r="O62" s="84" t="n"/>
-    </row>
-    <row r="63" ht="114" customHeight="1">
-      <c r="A63" s="83" t="inlineStr">
+      <c r="J53" s="84" t="n"/>
+      <c r="K53" s="84" t="n"/>
+      <c r="L53" s="84" t="n"/>
+      <c r="M53" s="84" t="n"/>
+      <c r="N53" s="84" t="n"/>
+      <c r="O53" s="84" t="n"/>
+    </row>
+    <row r="54" ht="150" customHeight="1">
+      <c r="A54" s="83" t="inlineStr">
         <is>
           <t>Certificación de desempeño</t>
         </is>
       </c>
-      <c r="B63" s="84" t="n"/>
-      <c r="C63" s="84" t="n"/>
-      <c r="D63" s="84" t="n"/>
-      <c r="E63" s="84" t="n"/>
-      <c r="F63" s="84" t="n"/>
-      <c r="G63" s="84" t="n"/>
-      <c r="H63" s="84" t="n"/>
-      <c r="I63" s="83" t="inlineStr">
+      <c r="B54" s="84" t="n"/>
+      <c r="C54" s="84" t="n"/>
+      <c r="D54" s="84" t="n"/>
+      <c r="E54" s="84" t="n"/>
+      <c r="F54" s="84" t="n"/>
+      <c r="G54" s="84" t="n"/>
+      <c r="H54" s="84" t="n"/>
+      <c r="I54" s="83" t="inlineStr">
         <is>
           <t>AMCA 210/211 (sello AMCA exigible)</t>
         </is>
       </c>
-      <c r="J63" s="84" t="n"/>
-      <c r="K63" s="84" t="n"/>
-      <c r="L63" s="84" t="n"/>
-      <c r="M63" s="84" t="n"/>
-      <c r="N63" s="84" t="n"/>
-      <c r="O63" s="84" t="n"/>
-    </row>
-    <row r="64" ht="304" customHeight="1">
+      <c r="J54" s="84" t="n"/>
+      <c r="K54" s="84" t="n"/>
+      <c r="L54" s="84" t="n"/>
+      <c r="M54" s="84" t="n"/>
+      <c r="N54" s="84" t="n"/>
+      <c r="O54" s="84" t="n"/>
+    </row>
+    <row r="55" ht="400" customHeight="1">
+      <c r="A55" s="83" t="inlineStr">
+        <is>
+          <t>Descartado</t>
+        </is>
+      </c>
+      <c r="B55" s="84" t="n"/>
+      <c r="C55" s="84" t="n"/>
+      <c r="D55" s="84" t="n"/>
+      <c r="E55" s="84" t="n"/>
+      <c r="F55" s="84" t="n"/>
+      <c r="G55" s="84" t="n"/>
+      <c r="H55" s="84" t="n"/>
+      <c r="I55" s="83" t="inlineStr">
+        <is>
+          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado desnudo en la corriente de aire</t>
+        </is>
+      </c>
+      <c r="J55" s="84" t="n"/>
+      <c r="K55" s="84" t="n"/>
+      <c r="L55" s="84" t="n"/>
+      <c r="M55" s="84" t="n"/>
+      <c r="N55" s="84" t="n"/>
+      <c r="O55" s="84" t="n"/>
+    </row>
+    <row r="56" ht="50" customHeight="1"/>
+    <row r="57" ht="1200" customHeight="1">
+      <c r="A57" s="87" t="inlineStr">
+        <is>
+          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23). El montaje típico de la planta usa acero galvanizado y pintura electrostática; para este servicio se eleva la especificación a PRFV o epóxico anticorrosivo por la atmósfera clorada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1"/>
+    <row r="59" ht="750" customHeight="1">
+      <c r="A59" s="87" t="inlineStr">
+        <is>
+          <t>Nota de ingeniería. La adopción del montaje mural de transmisión directa deja el motor dentro de la corriente de aire corrosivo, a diferencia de una configuración de transmisión por bandas con el motor fuera de la corriente. El riesgo se mitiga con la ejecución encapsulada severe duty de la Tabla 4 y con el programa de inspección semestral de la Tabla de mantenimiento de la descripción técnica de planta; la alternativa de transmisión por bandas queda documentada como opción si la vida del motor en servicio resultara inferior a la esperada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="50" customHeight="1"/>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="81" t="inlineStr">
+        <is>
+          <t>5. Motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 4. Especificación del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="82" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="n"/>
+      <c r="C63" s="82" t="n"/>
+      <c r="D63" s="82" t="n"/>
+      <c r="E63" s="82" t="n"/>
+      <c r="F63" s="82" t="n"/>
+      <c r="G63" s="82" t="n"/>
+      <c r="H63" s="82" t="n"/>
+      <c r="I63" s="82" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J63" s="82" t="n"/>
+      <c r="K63" s="82" t="n"/>
+      <c r="L63" s="82" t="n"/>
+      <c r="M63" s="82" t="n"/>
+      <c r="N63" s="82" t="n"/>
+      <c r="O63" s="82" t="n"/>
+    </row>
+    <row r="64" ht="250" customHeight="1">
       <c r="A64" s="83" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Potencia instalada</t>
         </is>
       </c>
       <c r="B64" s="84" t="n"/>
@@ -4932,7 +4967,7 @@
       <c r="H64" s="84" t="n"/>
       <c r="I64" s="83" t="inlineStr">
         <is>
-          <t>Acero inoxidable en la corriente (picadura por cloruros); acero galvanizado desnudo en la corriente de aire</t>
+          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
         </is>
       </c>
       <c r="J64" s="84" t="n"/>
@@ -4942,888 +4977,788 @@
       <c r="N64" s="84" t="n"/>
       <c r="O64" s="84" t="n"/>
     </row>
-    <row r="65" ht="38" customHeight="1"/>
-    <row r="66" ht="608" customHeight="1">
-      <c r="A66" s="85" t="inlineStr">
-        <is>
-          <t>Justificación de materiales: las resinas viniléster tipo Derakane se especifican expresamente para cloro e hipoclorito (INEOS — Derakane Resin Selection Guide (http://www.ineos.com/globalassets/ineos-group/businesses/ineos-composites/markets/corrosion/derakane-resin-selection-guide.pdf), consulta 2026-07-23); el polipropileno ofrece alta resistencia a cloruros e hipoclorito a temperatura ambiente (Plastec (https://www.plastecventilation.com/collections/plastec-series), consulta 2026-07-23). El montaje típico de la planta usa acero galvanizado y pintura electrostática; para este servicio se eleva la especificación a PRFV o epóxico anticorrosivo por la atmósfera clorada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="38" customHeight="1"/>
-    <row r="68" ht="38" customHeight="1"/>
-    <row r="69" ht="494" customHeight="1">
-      <c r="A69" s="85" t="inlineStr">
-        <is>
-          <t>Nota de ingeniería (REV2). La adopción del montaje mural de transmisión directa deja el motor dentro de la corriente de aire corrosivo, a diferencia de la configuración de transmisión por bandas evaluada en REV1. El riesgo se mitiga con la ejecución encapsulada severe duty de la Tabla 4 y con el programa de inspección semestral de la Tabla de mantenimiento de la descripción técnica de planta; la alternativa de transmisión por bandas queda documentada como opción si la vida del motor en servicio resultara inferior a la esperada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="38" customHeight="1"/>
-    <row r="71" ht="38" customHeight="1"/>
-    <row r="72" ht="38" customHeight="1"/>
-    <row r="73" ht="38" customHeight="1">
-      <c r="A73" s="81" t="inlineStr">
-        <is>
-          <t>5. Motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="38" customHeight="1">
-      <c r="A74" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 4. Especificación del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="38" customHeight="1">
-      <c r="A75" s="82" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B75" s="82" t="n"/>
-      <c r="C75" s="82" t="n"/>
-      <c r="D75" s="82" t="n"/>
-      <c r="E75" s="82" t="n"/>
-      <c r="F75" s="82" t="n"/>
-      <c r="G75" s="82" t="n"/>
-      <c r="H75" s="82" t="n"/>
-      <c r="I75" s="82" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="J75" s="82" t="n"/>
-      <c r="K75" s="82" t="n"/>
-      <c r="L75" s="82" t="n"/>
-      <c r="M75" s="82" t="n"/>
-      <c r="N75" s="82" t="n"/>
-      <c r="O75" s="82" t="n"/>
-    </row>
-    <row r="76" ht="190" customHeight="1">
-      <c r="A76" s="83" t="inlineStr">
-        <is>
-          <t>Potencia instalada</t>
-        </is>
-      </c>
-      <c r="B76" s="84" t="n"/>
-      <c r="C76" s="84" t="n"/>
-      <c r="D76" s="84" t="n"/>
-      <c r="E76" s="84" t="n"/>
-      <c r="F76" s="84" t="n"/>
-      <c r="G76" s="84" t="n"/>
-      <c r="H76" s="84" t="n"/>
-      <c r="I76" s="83" t="inlineStr">
-        <is>
-          <t>0.75 HP (provisional; confirmar con la curva de la selección final)</t>
-        </is>
-      </c>
-      <c r="J76" s="84" t="n"/>
-      <c r="K76" s="84" t="n"/>
-      <c r="L76" s="84" t="n"/>
-      <c r="M76" s="84" t="n"/>
-      <c r="N76" s="84" t="n"/>
-      <c r="O76" s="84" t="n"/>
-    </row>
-    <row r="77" ht="456" customHeight="1">
+    <row r="65" ht="600" customHeight="1">
+      <c r="A65" s="83" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="B65" s="84" t="n"/>
+      <c r="C65" s="84" t="n"/>
+      <c r="D65" s="84" t="n"/>
+      <c r="E65" s="84" t="n"/>
+      <c r="F65" s="84" t="n"/>
+      <c r="G65" s="84" t="n"/>
+      <c r="H65" s="84" t="n"/>
+      <c r="I65" s="83" t="inlineStr">
+        <is>
+          <t>TEFC encapsulado, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos, eje inox (referencia IEEE 841 o equivalente)</t>
+        </is>
+      </c>
+      <c r="J65" s="84" t="n"/>
+      <c r="K65" s="84" t="n"/>
+      <c r="L65" s="84" t="n"/>
+      <c r="M65" s="84" t="n"/>
+      <c r="N65" s="84" t="n"/>
+      <c r="O65" s="84" t="n"/>
+    </row>
+    <row r="66" ht="300" customHeight="1">
+      <c r="A66" s="83" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B66" s="84" t="n"/>
+      <c r="C66" s="84" t="n"/>
+      <c r="D66" s="84" t="n"/>
+      <c r="E66" s="84" t="n"/>
+      <c r="F66" s="84" t="n"/>
+      <c r="G66" s="84" t="n"/>
+      <c r="H66" s="84" t="n"/>
+      <c r="I66" s="83" t="inlineStr">
+        <is>
+          <t>En el cubo del impulsor, dentro de la corriente de aire (transmisión directa)</t>
+        </is>
+      </c>
+      <c r="J66" s="84" t="n"/>
+      <c r="K66" s="84" t="n"/>
+      <c r="L66" s="84" t="n"/>
+      <c r="M66" s="84" t="n"/>
+      <c r="N66" s="84" t="n"/>
+      <c r="O66" s="84" t="n"/>
+    </row>
+    <row r="67" ht="200" customHeight="1">
+      <c r="A67" s="83" t="inlineStr">
+        <is>
+          <t>Aislamiento / protección</t>
+        </is>
+      </c>
+      <c r="B67" s="84" t="n"/>
+      <c r="C67" s="84" t="n"/>
+      <c r="D67" s="84" t="n"/>
+      <c r="E67" s="84" t="n"/>
+      <c r="F67" s="84" t="n"/>
+      <c r="G67" s="84" t="n"/>
+      <c r="H67" s="84" t="n"/>
+      <c r="I67" s="83" t="inlineStr">
+        <is>
+          <t>Clase F (H preferible) / IP56 mínimo (IP66 preferible)</t>
+        </is>
+      </c>
+      <c r="J67" s="84" t="n"/>
+      <c r="K67" s="84" t="n"/>
+      <c r="L67" s="84" t="n"/>
+      <c r="M67" s="84" t="n"/>
+      <c r="N67" s="84" t="n"/>
+      <c r="O67" s="84" t="n"/>
+    </row>
+    <row r="68" ht="200" customHeight="1">
+      <c r="A68" s="83" t="inlineStr">
+        <is>
+          <t>Tensión / fases / frecuencia</t>
+        </is>
+      </c>
+      <c r="B68" s="84" t="n"/>
+      <c r="C68" s="84" t="n"/>
+      <c r="D68" s="84" t="n"/>
+      <c r="E68" s="84" t="n"/>
+      <c r="F68" s="84" t="n"/>
+      <c r="G68" s="84" t="n"/>
+      <c r="H68" s="84" t="n"/>
+      <c r="I68" s="83" t="inlineStr">
+        <is>
+          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J68" s="84" t="n"/>
+      <c r="K68" s="84" t="n"/>
+      <c r="L68" s="84" t="n"/>
+      <c r="M68" s="84" t="n"/>
+      <c r="N68" s="84" t="n"/>
+      <c r="O68" s="84" t="n"/>
+    </row>
+    <row r="69" ht="250" customHeight="1">
+      <c r="A69" s="83" t="inlineStr">
+        <is>
+          <t>Derateo por altitud</t>
+        </is>
+      </c>
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="84" t="n"/>
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="84" t="n"/>
+      <c r="H69" s="84" t="n"/>
+      <c r="I69" s="83" t="inlineStr">
+        <is>
+          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
+        </is>
+      </c>
+      <c r="J69" s="84" t="n"/>
+      <c r="K69" s="84" t="n"/>
+      <c r="L69" s="84" t="n"/>
+      <c r="M69" s="84" t="n"/>
+      <c r="N69" s="84" t="n"/>
+      <c r="O69" s="84" t="n"/>
+    </row>
+    <row r="70" ht="350" customHeight="1">
+      <c r="A70" s="83" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B70" s="84" t="n"/>
+      <c r="C70" s="84" t="n"/>
+      <c r="D70" s="84" t="n"/>
+      <c r="E70" s="84" t="n"/>
+      <c r="F70" s="84" t="n"/>
+      <c r="G70" s="84" t="n"/>
+      <c r="H70" s="84" t="n"/>
+      <c r="I70" s="83" t="inlineStr">
+        <is>
+          <t>Calentador anticondensación (paradas largas); caja de conexiones sellada, prensaestopas niquelados</t>
+        </is>
+      </c>
+      <c r="J70" s="84" t="n"/>
+      <c r="K70" s="84" t="n"/>
+      <c r="L70" s="84" t="n"/>
+      <c r="M70" s="84" t="n"/>
+      <c r="N70" s="84" t="n"/>
+      <c r="O70" s="84" t="n"/>
+    </row>
+    <row r="71" ht="50" customHeight="1"/>
+    <row r="72" ht="400" customHeight="1">
+      <c r="A72" s="87" t="inlineStr">
+        <is>
+          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="50" customHeight="1"/>
+    <row r="74" ht="50" customHeight="1">
+      <c r="A74" s="81" t="inlineStr">
+        <is>
+          <t>6. Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="100" customHeight="1">
+      <c r="A75" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 5. Accesorios del conjunto de montaje (uniformidad con la planta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="100" customHeight="1">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="n"/>
+      <c r="C76" s="82" t="n"/>
+      <c r="D76" s="82" t="n"/>
+      <c r="E76" s="82" t="n"/>
+      <c r="F76" s="82" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="G76" s="82" t="n"/>
+      <c r="H76" s="82" t="n"/>
+      <c r="I76" s="82" t="n"/>
+      <c r="J76" s="82" t="n"/>
+      <c r="K76" s="82" t="inlineStr">
+        <is>
+          <t>Material / especificación</t>
+        </is>
+      </c>
+      <c r="L76" s="82" t="n"/>
+      <c r="M76" s="82" t="n"/>
+      <c r="N76" s="82" t="n"/>
+      <c r="O76" s="82" t="n"/>
+    </row>
+    <row r="77" ht="400" customHeight="1">
       <c r="A77" s="83" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Cubierta intemperie</t>
         </is>
       </c>
       <c r="B77" s="84" t="n"/>
       <c r="C77" s="84" t="n"/>
       <c r="D77" s="84" t="n"/>
       <c r="E77" s="84" t="n"/>
-      <c r="F77" s="84" t="n"/>
+      <c r="F77" s="83" t="inlineStr">
+        <is>
+          <t>Protección contra lluvia, radiación solar e ingreso directo de agua; aloja el banco de filtración (ver HD-FILT-001)</t>
+        </is>
+      </c>
       <c r="G77" s="84" t="n"/>
       <c r="H77" s="84" t="n"/>
-      <c r="I77" s="83" t="inlineStr">
-        <is>
-          <t>TEFC encapsulado, severe duty, pintura epóxica, protección interna anticorrosiva, sellos de eje en ambos extremos, eje inox (referencia IEEE 841 o equivalente)</t>
-        </is>
-      </c>
+      <c r="I77" s="84" t="n"/>
       <c r="J77" s="84" t="n"/>
-      <c r="K77" s="84" t="n"/>
+      <c r="K77" s="83" t="inlineStr">
+        <is>
+          <t>PRFV o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L</t>
+        </is>
+      </c>
       <c r="L77" s="84" t="n"/>
       <c r="M77" s="84" t="n"/>
       <c r="N77" s="84" t="n"/>
       <c r="O77" s="84" t="n"/>
     </row>
-    <row r="78" ht="228" customHeight="1">
+    <row r="78" ht="450" customHeight="1">
       <c r="A78" s="83" t="inlineStr">
         <is>
-          <t>Ubicación</t>
+          <t>Estructura de unión</t>
         </is>
       </c>
       <c r="B78" s="84" t="n"/>
       <c r="C78" s="84" t="n"/>
       <c r="D78" s="84" t="n"/>
       <c r="E78" s="84" t="n"/>
-      <c r="F78" s="84" t="n"/>
+      <c r="F78" s="83" t="inlineStr">
+        <is>
+          <t>Marco de soporte pernado al muro para fijación segura del ventilador; transmite cargas estáticas, dinámicas y vibraciones</t>
+        </is>
+      </c>
       <c r="G78" s="84" t="n"/>
       <c r="H78" s="84" t="n"/>
-      <c r="I78" s="83" t="inlineStr">
-        <is>
-          <t>En el cubo del impulsor, dentro de la corriente de aire (transmisión directa)</t>
-        </is>
-      </c>
+      <c r="I78" s="84" t="n"/>
       <c r="J78" s="84" t="n"/>
-      <c r="K78" s="84" t="n"/>
+      <c r="K78" s="83" t="inlineStr">
+        <is>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (A4) con aislamiento dieléctrico</t>
+        </is>
+      </c>
       <c r="L78" s="84" t="n"/>
       <c r="M78" s="84" t="n"/>
       <c r="N78" s="84" t="n"/>
       <c r="O78" s="84" t="n"/>
     </row>
-    <row r="79" ht="152" customHeight="1">
+    <row r="79" ht="300" customHeight="1">
       <c r="A79" s="83" t="inlineStr">
         <is>
-          <t>Aislamiento / protección</t>
+          <t>Malla de protección interior</t>
         </is>
       </c>
       <c r="B79" s="84" t="n"/>
       <c r="C79" s="84" t="n"/>
       <c r="D79" s="84" t="n"/>
       <c r="E79" s="84" t="n"/>
-      <c r="F79" s="84" t="n"/>
+      <c r="F79" s="83" t="inlineStr">
+        <is>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor</t>
+        </is>
+      </c>
       <c r="G79" s="84" t="n"/>
       <c r="H79" s="84" t="n"/>
-      <c r="I79" s="83" t="inlineStr">
-        <is>
-          <t>Clase F (H preferible) / IP56 mínimo (IP66 preferible)</t>
-        </is>
-      </c>
+      <c r="I79" s="84" t="n"/>
       <c r="J79" s="84" t="n"/>
-      <c r="K79" s="84" t="n"/>
+      <c r="K79" s="83" t="inlineStr">
+        <is>
+          <t>Malla inox 316 o galvanizada con pintura epóxica, marco desmontable</t>
+        </is>
+      </c>
       <c r="L79" s="84" t="n"/>
       <c r="M79" s="84" t="n"/>
       <c r="N79" s="84" t="n"/>
       <c r="O79" s="84" t="n"/>
     </row>
-    <row r="80" ht="152" customHeight="1">
+    <row r="80" ht="250" customHeight="1">
       <c r="A80" s="83" t="inlineStr">
         <is>
-          <t>Tensión / fases / frecuencia</t>
+          <t>Sellado del pasamuros</t>
         </is>
       </c>
       <c r="B80" s="84" t="n"/>
       <c r="C80" s="84" t="n"/>
       <c r="D80" s="84" t="n"/>
       <c r="E80" s="84" t="n"/>
-      <c r="F80" s="84" t="n"/>
+      <c r="F80" s="83" t="inlineStr">
+        <is>
+          <t>Evita recirculaciones y filtraciones no controladas en el vano</t>
+        </is>
+      </c>
       <c r="G80" s="84" t="n"/>
       <c r="H80" s="84" t="n"/>
-      <c r="I80" s="83" t="inlineStr">
-        <is>
-          <t>440 V, 3φ, 60 Hz (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
+      <c r="I80" s="84" t="n"/>
       <c r="J80" s="84" t="n"/>
-      <c r="K80" s="84" t="n"/>
+      <c r="K80" s="83" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi)</t>
+        </is>
+      </c>
       <c r="L80" s="84" t="n"/>
       <c r="M80" s="84" t="n"/>
       <c r="N80" s="84" t="n"/>
       <c r="O80" s="84" t="n"/>
     </row>
-    <row r="81" ht="190" customHeight="1">
+    <row r="81" ht="300" customHeight="1">
       <c r="A81" s="83" t="inlineStr">
         <is>
-          <t>Derateo por altitud</t>
+          <t>Guardamotor y tablero</t>
         </is>
       </c>
       <c r="B81" s="84" t="n"/>
       <c r="C81" s="84" t="n"/>
       <c r="D81" s="84" t="n"/>
       <c r="E81" s="84" t="n"/>
-      <c r="F81" s="84" t="n"/>
+      <c r="F81" s="83" t="inlineStr">
+        <is>
+          <t>Protección eléctrica conforme a RETIE (ver listado_equipos.md, ítems 11-12)</t>
+        </is>
+      </c>
       <c r="G81" s="84" t="n"/>
       <c r="H81" s="84" t="n"/>
-      <c r="I81" s="83" t="inlineStr">
-        <is>
-          <t>≈9 % (NEMA MG-1); absorbido por el margen de selección (§3.2)</t>
-        </is>
-      </c>
+      <c r="I81" s="84" t="n"/>
       <c r="J81" s="84" t="n"/>
-      <c r="K81" s="84" t="n"/>
+      <c r="K81" s="83" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo, prensaestopas niquelados</t>
+        </is>
+      </c>
       <c r="L81" s="84" t="n"/>
       <c r="M81" s="84" t="n"/>
       <c r="N81" s="84" t="n"/>
       <c r="O81" s="84" t="n"/>
     </row>
-    <row r="82" ht="266" customHeight="1">
-      <c r="A82" s="83" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B82" s="84" t="n"/>
-      <c r="C82" s="84" t="n"/>
-      <c r="D82" s="84" t="n"/>
-      <c r="E82" s="84" t="n"/>
-      <c r="F82" s="84" t="n"/>
-      <c r="G82" s="84" t="n"/>
-      <c r="H82" s="84" t="n"/>
-      <c r="I82" s="83" t="inlineStr">
-        <is>
-          <t>Calentador anticondensación (paradas largas); caja de conexiones sellada, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="J82" s="84" t="n"/>
-      <c r="K82" s="84" t="n"/>
-      <c r="L82" s="84" t="n"/>
-      <c r="M82" s="84" t="n"/>
-      <c r="N82" s="84" t="n"/>
-      <c r="O82" s="84" t="n"/>
-    </row>
-    <row r="83" ht="38" customHeight="1"/>
-    <row r="84" ht="380" customHeight="1">
-      <c r="A84" s="85" t="inlineStr">
-        <is>
-          <t>Referencias de especificación: Leeson/Regal Severe Duty (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor-Reliance IEEE 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319) (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="38" customHeight="1"/>
-    <row r="86" ht="38" customHeight="1"/>
-    <row r="87" ht="38" customHeight="1">
-      <c r="A87" s="81" t="inlineStr">
-        <is>
-          <t>6. Accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="76" customHeight="1">
-      <c r="A88" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 5. Accesorios del conjunto de montaje (uniformidad con la planta).</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="76" customHeight="1">
-      <c r="A89" s="82" t="inlineStr">
-        <is>
-          <t>Ítem</t>
-        </is>
-      </c>
-      <c r="B89" s="82" t="n"/>
-      <c r="C89" s="82" t="n"/>
-      <c r="D89" s="82" t="n"/>
-      <c r="E89" s="82" t="n"/>
-      <c r="F89" s="82" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="G89" s="82" t="n"/>
-      <c r="H89" s="82" t="n"/>
-      <c r="I89" s="82" t="n"/>
-      <c r="J89" s="82" t="n"/>
-      <c r="K89" s="82" t="inlineStr">
-        <is>
-          <t>Material / especificación</t>
-        </is>
-      </c>
-      <c r="L89" s="82" t="n"/>
-      <c r="M89" s="82" t="n"/>
-      <c r="N89" s="82" t="n"/>
-      <c r="O89" s="82" t="n"/>
-    </row>
-    <row r="90" ht="304" customHeight="1">
+    <row r="82" ht="50" customHeight="1"/>
+    <row r="83" ht="250" customHeight="1">
+      <c r="A83" s="85" t="inlineStr">
+        <is>
+          <t>6.1. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="50" customHeight="1"/>
+    <row r="85" ht="100" customHeight="1">
+      <c r="A85" s="81" t="inlineStr">
+        <is>
+          <t>7. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="200" customHeight="1">
+      <c r="A86" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 6. Candidatos (consulta 2026-07-23, ajustada 2026-07-27 a tipo mural); RPM final por confirmar con proveedor en el punto 3 840 m³/h @ 225 Pa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="100" customHeight="1">
+      <c r="A87" s="82" t="inlineStr">
+        <is>
+          <t>Fabricante / línea</t>
+        </is>
+      </c>
+      <c r="B87" s="82" t="n"/>
+      <c r="C87" s="82" t="n"/>
+      <c r="D87" s="82" t="n"/>
+      <c r="E87" s="82" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F87" s="82" t="n"/>
+      <c r="G87" s="82" t="n"/>
+      <c r="H87" s="82" t="n"/>
+      <c r="I87" s="82" t="inlineStr">
+        <is>
+          <t>Canal en Colombia</t>
+        </is>
+      </c>
+      <c r="J87" s="82" t="n"/>
+      <c r="K87" s="82" t="n"/>
+      <c r="L87" s="82" t="n"/>
+      <c r="M87" s="82" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N87" s="82" t="n"/>
+      <c r="O87" s="82" t="n"/>
+    </row>
+    <row r="88" ht="500" customHeight="1">
+      <c r="A88" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca HQD/HGT mural anticorrosivo — primera opción por uniformidad y canal local</t>
+        </is>
+      </c>
+      <c r="B88" s="84" t="n"/>
+      <c r="C88" s="84" t="n"/>
+      <c r="D88" s="84" t="n"/>
+      <c r="E88" s="83" t="inlineStr">
+        <is>
+          <t>PRFV / epóxico, mural transmisión directa</t>
+        </is>
+      </c>
+      <c r="F88" s="84" t="n"/>
+      <c r="G88" s="84" t="n"/>
+      <c r="H88" s="84" t="n"/>
+      <c r="I88" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
+        </is>
+      </c>
+      <c r="J88" s="84" t="n"/>
+      <c r="K88" s="84" t="n"/>
+      <c r="L88" s="84" t="n"/>
+      <c r="M88" s="83" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
+        </is>
+      </c>
+      <c r="N88" s="84" t="n"/>
+      <c r="O88" s="84" t="n"/>
+    </row>
+    <row r="89" ht="400" customHeight="1">
+      <c r="A89" s="83" t="inlineStr">
+        <is>
+          <t>Greenheck mural (línea industrial)</t>
+        </is>
+      </c>
+      <c r="B89" s="84" t="n"/>
+      <c r="C89" s="84" t="n"/>
+      <c r="D89" s="84" t="n"/>
+      <c r="E89" s="83" t="inlineStr">
+        <is>
+          <t>Acero con recubrimiento epóxico</t>
+        </is>
+      </c>
+      <c r="F89" s="84" t="n"/>
+      <c r="G89" s="84" t="n"/>
+      <c r="H89" s="84" t="n"/>
+      <c r="I89" s="83" t="inlineStr">
+        <is>
+          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
+        </is>
+      </c>
+      <c r="J89" s="84" t="n"/>
+      <c r="K89" s="84" t="n"/>
+      <c r="L89" s="84" t="n"/>
+      <c r="M89" s="83" t="inlineStr">
+        <is>
+          <t>Greenheck (https://www.greenheck.com); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
+        </is>
+      </c>
+      <c r="N89" s="84" t="n"/>
+      <c r="O89" s="84" t="n"/>
+    </row>
+    <row r="90" ht="150" customHeight="1">
       <c r="A90" s="83" t="inlineStr">
         <is>
-          <t>Cubierta intemperie</t>
+          <t>Aerovent / Twin City Fan (línea mural FRP)</t>
         </is>
       </c>
       <c r="B90" s="84" t="n"/>
       <c r="C90" s="84" t="n"/>
       <c r="D90" s="84" t="n"/>
-      <c r="E90" s="84" t="n"/>
-      <c r="F90" s="83" t="inlineStr">
-        <is>
-          <t>Protección contra lluvia, radiación solar e ingreso directo de agua; aloja el banco de filtración (ver HD-FILT-001)</t>
-        </is>
-      </c>
+      <c r="E90" s="83" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F90" s="84" t="n"/>
       <c r="G90" s="84" t="n"/>
       <c r="H90" s="84" t="n"/>
-      <c r="I90" s="84" t="n"/>
+      <c r="I90" s="83" t="inlineStr">
+        <is>
+          <t>Por confirmar representante/canal local</t>
+        </is>
+      </c>
       <c r="J90" s="84" t="n"/>
-      <c r="K90" s="83" t="inlineStr">
-        <is>
-          <t>PRFV o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L</t>
-        </is>
-      </c>
+      <c r="K90" s="84" t="n"/>
       <c r="L90" s="84" t="n"/>
-      <c r="M90" s="84" t="n"/>
+      <c r="M90" s="83" t="inlineStr">
+        <is>
+          <t>Aerovent (https://www.aerovent.com)</t>
+        </is>
+      </c>
       <c r="N90" s="84" t="n"/>
       <c r="O90" s="84" t="n"/>
     </row>
-    <row r="91" ht="342" customHeight="1">
+    <row r="91" ht="250" customHeight="1">
       <c r="A91" s="83" t="inlineStr">
         <is>
-          <t>Estructura de unión</t>
+          <t>New York Blower FRP mural</t>
         </is>
       </c>
       <c r="B91" s="84" t="n"/>
       <c r="C91" s="84" t="n"/>
       <c r="D91" s="84" t="n"/>
-      <c r="E91" s="84" t="n"/>
-      <c r="F91" s="83" t="inlineStr">
-        <is>
-          <t>Marco de soporte pernado al muro para fijación segura del ventilador; transmite cargas estáticas, dinámicas y vibraciones</t>
-        </is>
-      </c>
+      <c r="E91" s="83" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="F91" s="84" t="n"/>
       <c r="G91" s="84" t="n"/>
       <c r="H91" s="84" t="n"/>
-      <c r="I91" s="84" t="n"/>
+      <c r="I91" s="83" t="inlineStr">
+        <is>
+          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
+        </is>
+      </c>
       <c r="J91" s="84" t="n"/>
-      <c r="K91" s="83" t="inlineStr">
-        <is>
-          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (A4) con aislamiento dieléctrico</t>
-        </is>
-      </c>
+      <c r="K91" s="84" t="n"/>
       <c r="L91" s="84" t="n"/>
-      <c r="M91" s="84" t="n"/>
+      <c r="M91" s="83" t="inlineStr">
+        <is>
+          <t>NYB (https://www.nyb.com/)</t>
+        </is>
+      </c>
       <c r="N91" s="84" t="n"/>
       <c r="O91" s="84" t="n"/>
     </row>
-    <row r="92" ht="228" customHeight="1">
+    <row r="92" ht="250" customHeight="1">
       <c r="A92" s="83" t="inlineStr">
         <is>
-          <t>Malla de protección interior</t>
+          <t>Plastec</t>
         </is>
       </c>
       <c r="B92" s="84" t="n"/>
       <c r="C92" s="84" t="n"/>
       <c r="D92" s="84" t="n"/>
-      <c r="E92" s="84" t="n"/>
-      <c r="F92" s="83" t="inlineStr">
-        <is>
-          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor</t>
-        </is>
-      </c>
+      <c r="E92" s="83" t="inlineStr">
+        <is>
+          <t>Polipropileno</t>
+        </is>
+      </c>
+      <c r="F92" s="84" t="n"/>
       <c r="G92" s="84" t="n"/>
       <c r="H92" s="84" t="n"/>
-      <c r="I92" s="84" t="n"/>
+      <c r="I92" s="83" t="inlineStr">
+        <is>
+          <t>Importación directa (despacho 48 h declarado)</t>
+        </is>
+      </c>
       <c r="J92" s="84" t="n"/>
-      <c r="K92" s="83" t="inlineStr">
-        <is>
-          <t>Malla inox 316 o galvanizada con pintura epóxica, marco desmontable</t>
-        </is>
-      </c>
+      <c r="K92" s="84" t="n"/>
       <c r="L92" s="84" t="n"/>
-      <c r="M92" s="84" t="n"/>
+      <c r="M92" s="83" t="inlineStr">
+        <is>
+          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
+        </is>
+      </c>
       <c r="N92" s="84" t="n"/>
       <c r="O92" s="84" t="n"/>
     </row>
-    <row r="93" ht="190" customHeight="1">
-      <c r="A93" s="83" t="inlineStr">
-        <is>
-          <t>Sellado del pasamuros</t>
-        </is>
-      </c>
-      <c r="B93" s="84" t="n"/>
-      <c r="C93" s="84" t="n"/>
-      <c r="D93" s="84" t="n"/>
-      <c r="E93" s="84" t="n"/>
-      <c r="F93" s="83" t="inlineStr">
-        <is>
-          <t>Evita recirculaciones y filtraciones no controladas en el vano</t>
-        </is>
-      </c>
-      <c r="G93" s="84" t="n"/>
-      <c r="H93" s="84" t="n"/>
-      <c r="I93" s="84" t="n"/>
-      <c r="J93" s="84" t="n"/>
-      <c r="K93" s="83" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi)</t>
-        </is>
-      </c>
-      <c r="L93" s="84" t="n"/>
-      <c r="M93" s="84" t="n"/>
-      <c r="N93" s="84" t="n"/>
-      <c r="O93" s="84" t="n"/>
-    </row>
-    <row r="94" ht="228" customHeight="1">
-      <c r="A94" s="83" t="inlineStr">
-        <is>
-          <t>Guardamotor y tablero</t>
-        </is>
-      </c>
-      <c r="B94" s="84" t="n"/>
-      <c r="C94" s="84" t="n"/>
-      <c r="D94" s="84" t="n"/>
-      <c r="E94" s="84" t="n"/>
-      <c r="F94" s="83" t="inlineStr">
-        <is>
-          <t>Protección eléctrica conforme a RETIE (ver listado_equipos.md, ítems 11-12)</t>
-        </is>
-      </c>
-      <c r="G94" s="84" t="n"/>
-      <c r="H94" s="84" t="n"/>
-      <c r="I94" s="84" t="n"/>
-      <c r="J94" s="84" t="n"/>
-      <c r="K94" s="83" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo, prensaestopas niquelados</t>
-        </is>
-      </c>
-      <c r="L94" s="84" t="n"/>
-      <c r="M94" s="84" t="n"/>
-      <c r="N94" s="84" t="n"/>
-      <c r="O94" s="84" t="n"/>
-    </row>
-    <row r="95" ht="38" customHeight="1"/>
-    <row r="96" ht="152" customHeight="1">
-      <c r="A96" s="86" t="inlineStr">
-        <is>
-          <t>6.1. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="38" customHeight="1"/>
-    <row r="98" ht="76" customHeight="1">
-      <c r="A98" s="81" t="inlineStr">
-        <is>
-          <t>7. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="114" customHeight="1">
-      <c r="A99" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 6. Candidatos (consulta 2026-07-23, ajustada 2026-07-27 a tipo mural); RPM final por confirmar con proveedor en el punto 3 840 m³/h @ 225 Pa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="76" customHeight="1">
-      <c r="A100" s="82" t="inlineStr">
-        <is>
-          <t>Fabricante / línea</t>
-        </is>
-      </c>
-      <c r="B100" s="82" t="n"/>
-      <c r="C100" s="82" t="n"/>
-      <c r="D100" s="82" t="n"/>
-      <c r="E100" s="82" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="F100" s="82" t="n"/>
-      <c r="G100" s="82" t="n"/>
-      <c r="H100" s="82" t="n"/>
-      <c r="I100" s="82" t="inlineStr">
-        <is>
-          <t>Canal en Colombia</t>
-        </is>
-      </c>
-      <c r="J100" s="82" t="n"/>
-      <c r="K100" s="82" t="n"/>
-      <c r="L100" s="82" t="n"/>
-      <c r="M100" s="82" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N100" s="82" t="n"/>
-      <c r="O100" s="82" t="n"/>
-    </row>
-    <row r="101" ht="380" customHeight="1">
-      <c r="A101" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca HQD/HGT mural anticorrosivo — primera opción por uniformidad y canal local</t>
-        </is>
-      </c>
-      <c r="B101" s="84" t="n"/>
-      <c r="C101" s="84" t="n"/>
-      <c r="D101" s="84" t="n"/>
-      <c r="E101" s="83" t="inlineStr">
-        <is>
-          <t>PRFV / epóxico, mural transmisión directa</t>
-        </is>
-      </c>
-      <c r="F101" s="84" t="n"/>
-      <c r="G101" s="84" t="n"/>
-      <c r="H101" s="84" t="n"/>
-      <c r="I101" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca Colombia (filial, catálogo 60 Hz)</t>
-        </is>
-      </c>
-      <c r="J101" s="84" t="n"/>
-      <c r="K101" s="84" t="n"/>
-      <c r="L101" s="84" t="n"/>
-      <c r="M101" s="83" t="inlineStr">
-        <is>
-          <t>Sodeca (https://www.sodeca.com); catálogo Colombia (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf)</t>
-        </is>
-      </c>
-      <c r="N101" s="84" t="n"/>
-      <c r="O101" s="84" t="n"/>
-    </row>
-    <row r="102" ht="304" customHeight="1">
-      <c r="A102" s="83" t="inlineStr">
-        <is>
-          <t>Greenheck mural (línea industrial)</t>
-        </is>
-      </c>
-      <c r="B102" s="84" t="n"/>
-      <c r="C102" s="84" t="n"/>
-      <c r="D102" s="84" t="n"/>
-      <c r="E102" s="83" t="inlineStr">
-        <is>
-          <t>Acero con recubrimiento epóxico</t>
-        </is>
-      </c>
-      <c r="F102" s="84" t="n"/>
-      <c r="G102" s="84" t="n"/>
-      <c r="H102" s="84" t="n"/>
-      <c r="I102" s="83" t="inlineStr">
-        <is>
-          <t>Prime Lines HVAC, Bogotá (representante oficial)</t>
-        </is>
-      </c>
-      <c r="J102" s="84" t="n"/>
-      <c r="K102" s="84" t="n"/>
-      <c r="L102" s="84" t="n"/>
-      <c r="M102" s="83" t="inlineStr">
-        <is>
-          <t>Greenheck (https://www.greenheck.com); rep. (https://www.greenheck.com/find-my-rep/2973_southamerica_colombia)</t>
-        </is>
-      </c>
-      <c r="N102" s="84" t="n"/>
-      <c r="O102" s="84" t="n"/>
-    </row>
-    <row r="103" ht="114" customHeight="1">
-      <c r="A103" s="83" t="inlineStr">
-        <is>
-          <t>Aerovent / Twin City Fan (línea mural FRP)</t>
-        </is>
-      </c>
-      <c r="B103" s="84" t="n"/>
-      <c r="C103" s="84" t="n"/>
-      <c r="D103" s="84" t="n"/>
-      <c r="E103" s="83" t="inlineStr">
-        <is>
-          <t>PRFV</t>
-        </is>
-      </c>
-      <c r="F103" s="84" t="n"/>
-      <c r="G103" s="84" t="n"/>
-      <c r="H103" s="84" t="n"/>
-      <c r="I103" s="83" t="inlineStr">
-        <is>
-          <t>Por confirmar representante/canal local</t>
-        </is>
-      </c>
-      <c r="J103" s="84" t="n"/>
-      <c r="K103" s="84" t="n"/>
-      <c r="L103" s="84" t="n"/>
-      <c r="M103" s="83" t="inlineStr">
-        <is>
-          <t>Aerovent (https://www.aerovent.com)</t>
-        </is>
-      </c>
-      <c r="N103" s="84" t="n"/>
-      <c r="O103" s="84" t="n"/>
-    </row>
-    <row r="104" ht="190" customHeight="1">
-      <c r="A104" s="83" t="inlineStr">
-        <is>
-          <t>New York Blower FRP mural</t>
-        </is>
-      </c>
-      <c r="B104" s="84" t="n"/>
-      <c r="C104" s="84" t="n"/>
-      <c r="D104" s="84" t="n"/>
-      <c r="E104" s="83" t="inlineStr">
-        <is>
-          <t>PRFV</t>
-        </is>
-      </c>
-      <c r="F104" s="84" t="n"/>
-      <c r="G104" s="84" t="n"/>
-      <c r="H104" s="84" t="n"/>
-      <c r="I104" s="83" t="inlineStr">
-        <is>
-          <t>Importación (plazo máx. ~3 meses, dato cliente 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="J104" s="84" t="n"/>
-      <c r="K104" s="84" t="n"/>
-      <c r="L104" s="84" t="n"/>
-      <c r="M104" s="83" t="inlineStr">
-        <is>
-          <t>NYB (https://www.nyb.com/)</t>
-        </is>
-      </c>
-      <c r="N104" s="84" t="n"/>
-      <c r="O104" s="84" t="n"/>
-    </row>
-    <row r="105" ht="190" customHeight="1">
-      <c r="A105" s="83" t="inlineStr">
-        <is>
-          <t>Plastec</t>
-        </is>
-      </c>
-      <c r="B105" s="84" t="n"/>
-      <c r="C105" s="84" t="n"/>
-      <c r="D105" s="84" t="n"/>
-      <c r="E105" s="83" t="inlineStr">
-        <is>
-          <t>Polipropileno</t>
-        </is>
-      </c>
-      <c r="F105" s="84" t="n"/>
-      <c r="G105" s="84" t="n"/>
-      <c r="H105" s="84" t="n"/>
-      <c r="I105" s="83" t="inlineStr">
-        <is>
-          <t>Importación directa (despacho 48 h declarado)</t>
-        </is>
-      </c>
-      <c r="J105" s="84" t="n"/>
-      <c r="K105" s="84" t="n"/>
-      <c r="L105" s="84" t="n"/>
-      <c r="M105" s="83" t="inlineStr">
-        <is>
-          <t>Plastec (https://www.plastecventilation.com/collections/plastec-series)</t>
-        </is>
-      </c>
-      <c r="N105" s="84" t="n"/>
-      <c r="O105" s="84" t="n"/>
-    </row>
-    <row r="106" ht="38" customHeight="1"/>
-    <row r="107" ht="38" customHeight="1">
-      <c r="A107" s="81" t="inlineStr">
+    <row r="93" ht="50" customHeight="1"/>
+    <row r="94" ht="50" customHeight="1">
+      <c r="A94" s="81" t="inlineStr">
         <is>
           <t>8. Montaje</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="418" customHeight="1">
-      <c r="A108" s="86" t="inlineStr">
+    <row r="95" ht="400" customHeight="1">
+      <c r="A95" s="85" t="inlineStr">
         <is>
           <t>8.1. El ventilador se instalará en muro/pasamuros, con el eje horizontal y a una cota aproximada de 3,0 m sobre el piso terminado del laboratorio. El sentido de flujo es: aspiración del aire exterior a través de la cubierta intemperie y su banco de filtración, descarga directa al interior del recinto.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="38" customHeight="1"/>
-    <row r="110" ht="380" customHeight="1">
-      <c r="A110" s="86" t="inlineStr">
+    <row r="96" ht="400" customHeight="1">
+      <c r="A96" s="85" t="inlineStr">
         <is>
           <t>8.2. El conjunto se soporta mediante una estructura de unión (marco de perfiles ASTM A36 galvanizados) pernada al muro con anclajes inox 316 (A4) y aislamiento dieléctrico frente a estructuras galvanizadas. El vano del muro se sella con silicona RTV neutra para evitar recirculaciones.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="38" customHeight="1"/>
-    <row r="112" ht="456" customHeight="1">
-      <c r="A112" s="86" t="inlineStr">
+    <row r="97" ht="450" customHeight="1">
+      <c r="A97" s="85" t="inlineStr">
         <is>
           <t>8.3. La cubierta intemperie se embrida directamente a la placa mural del ventilador por el lado exterior; aloja el banco de filtración (HD-FILT-001) y protege el conjunto contra lluvia y radiación solar. La altura de 3,0 m exige garantizar el acceso para cambio de filtros e inspección del ventilador (plataforma fija o escalera industrial).</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="38" customHeight="1"/>
-    <row r="114" ht="114" customHeight="1">
-      <c r="A114" s="86" t="inlineStr">
+    <row r="98" ht="200" customHeight="1">
+      <c r="A98" s="85" t="inlineStr">
         <is>
           <t>8.4. La malla de protección interior (jaula) se instala en la descarga del lado interior del muro, desmontable para inspección del impulsor.</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="152" customHeight="1">
-      <c r="A115" s="86" t="inlineStr">
+    <row r="99" ht="250" customHeight="1">
+      <c r="A99" s="85" t="inlineStr">
         <is>
           <t>8.5. La toma de aire exterior debe ubicarse a sotavento y alejada de las fuentes de cloro de la planta, conforme a la recomendación de la investigación del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="38" customHeight="1"/>
-    <row r="117" ht="76" customHeight="1">
-      <c r="A117" s="81" t="inlineStr">
+    <row r="100" ht="50" customHeight="1"/>
+    <row r="101" ht="100" customHeight="1">
+      <c r="A101" s="81" t="inlineStr">
         <is>
           <t>9. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="608" customHeight="1">
-      <c r="A118" s="86" t="inlineStr">
+    <row r="102" ht="600" customHeight="1">
+      <c r="A102" s="85" t="inlineStr">
         <is>
           <t>9.1. AMCA 210/211 (desempeño y certificación), AMCA 99 (Spark A), AMCA 300 (nivel sonoro), ASTM C582 y ASTM D4167 (laminados PRFV), NEMA MG-1 / IEC 60034-1 (motores y derateo por altitud), IEEE 841 (ejecución severe duty de referencia), RETIE y NTC 2050 (instalación eléctrica), ISO 12944 / prácticas NACE-AMPP (protección anticorrosiva del entorno de instalación), SMACNA HVAC Duct Construction Standards (referencia de construcción del montaje).</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="38" customHeight="1"/>
-    <row r="120" ht="76" customHeight="1">
-      <c r="A120" s="81" t="inlineStr">
+    <row r="103" ht="100" customHeight="1">
+      <c r="A103" s="81" t="inlineStr">
         <is>
           <t>Referencia gráfica</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="158">
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="K92:O92"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A120:O120"/>
-    <mergeCell ref="A55:O55"/>
-    <mergeCell ref="M104:O104"/>
+  <mergeCells count="147">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="K78:O78"/>
+    <mergeCell ref="I52:O52"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="K80:O80"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="I69:O69"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="I30:O30"/>
-    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="K41:O41"/>
-    <mergeCell ref="F45:J45"/>
-    <mergeCell ref="I77:O77"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="I104:L104"/>
-    <mergeCell ref="A110:O111"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="F76:J76"/>
+    <mergeCell ref="I90:L90"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="I80:O80"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="I61:O61"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="F47:J47"/>
-    <mergeCell ref="I57:O57"/>
-    <mergeCell ref="F46:J46"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="F92:J92"/>
-    <mergeCell ref="A73:O73"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A107:O107"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="E105:H105"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="I70:O70"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I54:O54"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A17:O18"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="K93:O93"/>
+    <mergeCell ref="A57:O58"/>
+    <mergeCell ref="I24:O24"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="A69:O71"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="K34:O34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="F78:J78"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="I82:O82"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="K36:O36"/>
     <mergeCell ref="I10:O10"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="F89:J89"/>
-    <mergeCell ref="I59:O59"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I60:O60"/>
-    <mergeCell ref="K94:O94"/>
+    <mergeCell ref="A101:O101"/>
+    <mergeCell ref="I50:O50"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="M89:O89"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K44:O44"/>
     <mergeCell ref="F41:J41"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="A84:O85"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="F35:J35"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="K40:O40"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="F91:J91"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="F93:J93"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="E104:H104"/>
-    <mergeCell ref="I62:O62"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="A61:O61"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A51:O53"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A112:O113"/>
+    <mergeCell ref="I88:L88"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="I64:O64"/>
-    <mergeCell ref="I79:O79"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="I51:O51"/>
+    <mergeCell ref="A74:O74"/>
     <mergeCell ref="F40:J40"/>
+    <mergeCell ref="K35:O35"/>
     <mergeCell ref="I63:O63"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="K91:O91"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="A49:O50"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="M103:O103"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F90:J90"/>
-    <mergeCell ref="A117:O117"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="I76:O76"/>
-    <mergeCell ref="A118:O119"/>
-    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="K76:O76"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="A85:O85"/>
+    <mergeCell ref="F79:J79"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="I49:O49"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="F81:J81"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="M87:O87"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A25:O26"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="A108:O109"/>
-    <mergeCell ref="I75:O75"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="I53:O53"/>
+    <mergeCell ref="A89:D89"/>
     <mergeCell ref="A63:H63"/>
+    <mergeCell ref="K38:O38"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="A94:O94"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A87:O87"/>
-    <mergeCell ref="F44:J44"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="I68:O68"/>
+    <mergeCell ref="A103:O103"/>
+    <mergeCell ref="M88:O88"/>
+    <mergeCell ref="I55:O55"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I67:O67"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="I48:O48"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="M90:O90"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A46:O46"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A66:O68"/>
-    <mergeCell ref="K89:O89"/>
-    <mergeCell ref="I78:O78"/>
-    <mergeCell ref="M105:O105"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="K79:O79"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="M101:O101"/>
-    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="K81:O81"/>
+    <mergeCell ref="F80:J80"/>
     <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I105:L105"/>
-    <mergeCell ref="K90:O90"/>
-    <mergeCell ref="I81:O81"/>
-    <mergeCell ref="F94:J94"/>
-    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="M91:O91"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="M100:O100"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="M102:O102"/>
-    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="I91:L91"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I100:L100"/>
-    <mergeCell ref="F43:J43"/>
-    <mergeCell ref="I102:L102"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="I58:O58"/>
-    <mergeCell ref="A22:O23"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="I92:L92"/>
+    <mergeCell ref="K37:O37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
